--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB7FF86-5637-46FC-A33B-7D69DD37C8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3510256-F516-4192-B971-D30FCC520E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendance" sheetId="2" r:id="rId1"/>
     <sheet name="Outsider students" sheetId="5" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="6" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1850" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1868" uniqueCount="77">
   <si>
     <t>Name</t>
   </si>
@@ -216,23 +217,56 @@
     <t>Out Of</t>
   </si>
   <si>
-    <t>Out Of 30</t>
-  </si>
-  <si>
-    <t>Test Marks</t>
-  </si>
-  <si>
     <t>Total/160</t>
   </si>
   <si>
-    <t>Out of 30</t>
+    <t>Out Of 5</t>
+  </si>
+  <si>
+    <t>Out of 5</t>
+  </si>
+  <si>
+    <t>HELI BHAVSAR</t>
+  </si>
+  <si>
+    <t>jagrav Bhatt</t>
+  </si>
+  <si>
+    <t>JESAL PRAJAPATI</t>
+  </si>
+  <si>
+    <t>prachi sathavara</t>
+  </si>
+  <si>
+    <t>Prajapati Sudhir Bhanubhai</t>
+  </si>
+  <si>
+    <t>Raiyani Dhruv Pravinbhai</t>
+  </si>
+  <si>
+    <t>SAEED MAHMADZUBER GHASURA</t>
+  </si>
+  <si>
+    <t>Shrinil Ankulkumar Mahesuria</t>
+  </si>
+  <si>
+    <t>trivedinisarg99@gmail.com</t>
+  </si>
+  <si>
+    <t>yash dodiya</t>
+  </si>
+  <si>
+    <t>Marks/20</t>
+  </si>
+  <si>
+    <t>Marks/5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,16 +274,39 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -257,13 +314,86 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF442F65"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFF8F9FA"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5523,6 +5653,7 @@
     <sortCondition ref="A2:A46"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6221,12 +6352,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0889FDC0-8C42-453F-9E90-7D3894357DF6}">
-  <dimension ref="A1:AL46"/>
+  <dimension ref="A1:AM40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -6234,7 +6366,7 @@
     <col min="38" max="38" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6344,13 +6476,16 @@
         <v>61</v>
       </c>
       <c r="AK1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AL1" t="s">
-        <v>63</v>
+        <v>75</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -6494,11 +6629,18 @@
         <v>160</v>
       </c>
       <c r="AK2">
-        <f>ROUND(AI2*30/160, 0)</f>
-        <v>20</v>
+        <f>ROUND(AI2*5/160, 2)</f>
+        <v>3.25</v>
+      </c>
+      <c r="AL2">
+        <v>10</v>
+      </c>
+      <c r="AM2">
+        <f>ROUND(AL2/4, 2)</f>
+        <v>2.5</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -6634,19 +6776,26 @@
         <v>5</v>
       </c>
       <c r="AI3">
-        <f t="shared" ref="AI3:AI46" si="0">SUM(C3:AH3)</f>
+        <f t="shared" ref="AI3:AI40" si="0">SUM(C3:AH3)</f>
         <v>100</v>
       </c>
       <c r="AJ3">
-        <f t="shared" ref="AJ3:AJ46" si="1">32*5</f>
+        <f t="shared" ref="AJ3:AJ40" si="1">32*5</f>
         <v>160</v>
       </c>
       <c r="AK3">
-        <f t="shared" ref="AK3:AK46" si="2">ROUND(AI3*30/160, 0)</f>
-        <v>19</v>
+        <f t="shared" ref="AK3:AK40" si="2">ROUND(AI3*5/160, 2)</f>
+        <v>3.13</v>
+      </c>
+      <c r="AL3">
+        <v>10</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" ref="AM3:AM6" si="3">ROUND(AL3/4, 2)</f>
+        <v>2.5</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -6791,10 +6940,17 @@
       </c>
       <c r="AK4">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>1.97</v>
+      </c>
+      <c r="AL4">
+        <v>16</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -6939,10 +7095,17 @@
       </c>
       <c r="AK5">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>2.34</v>
+      </c>
+      <c r="AL5">
+        <v>16</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -7087,10 +7250,17 @@
       </c>
       <c r="AK6">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>2.75</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>20</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -7235,10 +7405,13 @@
       </c>
       <c r="AK7">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>0.81</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -7383,10 +7556,17 @@
       </c>
       <c r="AK8">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>2.97</v>
+      </c>
+      <c r="AL8">
+        <v>16</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" ref="AM8:AM9" si="4">ROUND(AL8/4, 2)</f>
+        <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -7531,10 +7711,17 @@
       </c>
       <c r="AK9">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>2.72</v>
+      </c>
+      <c r="AL9">
+        <v>20</v>
+      </c>
+      <c r="AM9">
+        <f t="shared" si="4"/>
+        <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -7679,10 +7866,13 @@
       </c>
       <c r="AK10">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>1.66</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -7827,10 +8017,13 @@
       </c>
       <c r="AK11">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>2.16</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -7975,10 +8168,13 @@
       </c>
       <c r="AK12">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>2.84</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -8123,10 +8319,13 @@
       </c>
       <c r="AK13">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>2.81</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -8271,147 +8470,150 @@
       </c>
       <c r="AK14">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>0.84</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="C15">
-        <f>IF(Attendance!C15="P", 5, IF(Attendance!C15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!C16="P", 5, IF(Attendance!C16="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="D15">
-        <f>IF(Attendance!D15="P", 5, IF(Attendance!D15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!D16="P", 5, IF(Attendance!D16="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="E15">
-        <f>IF(Attendance!E15="P", 5, IF(Attendance!E15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!E16="P", 5, IF(Attendance!E16="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="F15">
-        <f>IF(Attendance!F15="P", 5, IF(Attendance!F15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!F16="P", 5, IF(Attendance!F16="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="G15">
-        <f>IF(Attendance!G15="P", 5, IF(Attendance!G15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!G16="P", 5, IF(Attendance!G16="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="H15">
-        <f>IF(Attendance!H15="P", 5, IF(Attendance!H15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!H16="P", 5, IF(Attendance!H16="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="I15">
-        <f>IF(Attendance!I15="P", 5, IF(Attendance!I15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!I16="P", 5, IF(Attendance!I16="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="J15">
-        <f>IF(Attendance!J15="P", 5, IF(Attendance!J15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!J16="P", 5, IF(Attendance!J16="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="K15">
-        <f>IF(Attendance!K15="P", 5, IF(Attendance!K15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!K16="P", 5, IF(Attendance!K16="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="L15">
-        <f>IF(Attendance!L15="P", 5, IF(Attendance!L15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!L16="P", 5, IF(Attendance!L16="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="M15">
-        <f>IF(Attendance!M15="P", 5, IF(Attendance!M15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!M16="P", 5, IF(Attendance!M16="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="N15">
-        <f>IF(Attendance!N15="P", 5, IF(Attendance!N15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!N16="P", 5, IF(Attendance!N16="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="O15">
-        <f>IF(Attendance!O15="P", 5, IF(Attendance!O15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!O16="P", 5, IF(Attendance!O16="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="P15">
-        <f>IF(Attendance!P15="P", 5, IF(Attendance!P15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!P16="P", 5, IF(Attendance!P16="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="Q15">
-        <f>IF(Attendance!Q15="P", 5, IF(Attendance!Q15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!Q16="P", 5, IF(Attendance!Q16="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="R15">
-        <f>IF(Attendance!R15="P", 5, IF(Attendance!R15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!R16="P", 5, IF(Attendance!R16="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="S15">
-        <f>IF(Attendance!S15="P", 5, IF(Attendance!S15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!S16="P", 5, IF(Attendance!S16="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="T15">
-        <f>IF(Attendance!T15="P", 5, IF(Attendance!T15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!T16="P", 5, IF(Attendance!T16="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="U15">
-        <f>IF(Attendance!U15="P", 5, IF(Attendance!U15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!U16="P", 5, IF(Attendance!U16="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="V15">
-        <f>IF(Attendance!V15="P", 5, IF(Attendance!V15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!V16="P", 5, IF(Attendance!V16="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="W15">
-        <f>IF(Attendance!W15="P", 5, IF(Attendance!W15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!W16="P", 5, IF(Attendance!W16="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="X15">
-        <f>IF(Attendance!X15="P", 5, IF(Attendance!X15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!X16="P", 5, IF(Attendance!X16="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="Y15">
-        <f>IF(Attendance!Y15="P", 5, IF(Attendance!Y15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!Y16="P", 5, IF(Attendance!Y16="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="Z15">
-        <f>IF(Attendance!Z15="P", 5, IF(Attendance!Z15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!Z16="P", 5, IF(Attendance!Z16="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AA15">
-        <f>IF(Attendance!AA15="P", 5, IF(Attendance!AA15="O", 3, 0))</f>
+        <f>IF(Attendance!AA16="P", 5, IF(Attendance!AA16="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="AB15">
-        <f>IF(Attendance!AB15="P", 5, IF(Attendance!AB15="O", 3, 0))</f>
+        <f>IF(Attendance!AB16="P", 5, IF(Attendance!AB16="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="AC15">
-        <f>IF(Attendance!AC15="P", 5, IF(Attendance!AC15="O", 3, 0))</f>
+        <f>IF(Attendance!AC16="P", 5, IF(Attendance!AC16="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AD15">
-        <f>IF(Attendance!AD15="P", 5, IF(Attendance!AD15="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AD16="P", 5, IF(Attendance!AD16="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <f>IF(Attendance!AE15="P", 5, IF(Attendance!AE15="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AE16="P", 5, IF(Attendance!AE16="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <f>IF(Attendance!AF15="P", 5, IF(Attendance!AF15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AF16="P", 5, IF(Attendance!AF16="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AG15">
-        <f>IF(Attendance!AG15="P", 5, IF(Attendance!AG15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AG16="P", 5, IF(Attendance!AG16="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AH15">
-        <f>IF(Attendance!AH15="P", 5, IF(Attendance!AH15="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AH16="P", 5, IF(Attendance!AH16="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AI15">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="AJ15">
         <f t="shared" si="1"/>
@@ -8419,147 +8621,154 @@
       </c>
       <c r="AK15">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3.13</v>
+      </c>
+      <c r="AL15">
+        <v>16</v>
+      </c>
+      <c r="AM15">
+        <f>ROUND(AL15/4, 2)</f>
+        <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16">
-        <f>IF(Attendance!C16="P", 5, IF(Attendance!C16="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!C18="P", 5, IF(Attendance!C18="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="D16">
-        <f>IF(Attendance!D16="P", 5, IF(Attendance!D16="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!D18="P", 5, IF(Attendance!D18="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="E16">
-        <f>IF(Attendance!E16="P", 5, IF(Attendance!E16="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!E18="P", 5, IF(Attendance!E18="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="F16">
-        <f>IF(Attendance!F16="P", 5, IF(Attendance!F16="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!F18="P", 5, IF(Attendance!F18="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="G16">
-        <f>IF(Attendance!G16="P", 5, IF(Attendance!G16="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!G18="P", 5, IF(Attendance!G18="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="H16">
-        <f>IF(Attendance!H16="P", 5, IF(Attendance!H16="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!H18="P", 5, IF(Attendance!H18="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="I16">
-        <f>IF(Attendance!I16="P", 5, IF(Attendance!I16="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!I18="P", 5, IF(Attendance!I18="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="J16">
-        <f>IF(Attendance!J16="P", 5, IF(Attendance!J16="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!J18="P", 5, IF(Attendance!J18="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="K16">
-        <f>IF(Attendance!K16="P", 5, IF(Attendance!K16="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!K18="P", 5, IF(Attendance!K18="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="L16">
-        <f>IF(Attendance!L16="P", 5, IF(Attendance!L16="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!L18="P", 5, IF(Attendance!L18="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="M16">
-        <f>IF(Attendance!M16="P", 5, IF(Attendance!M16="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!M18="P", 5, IF(Attendance!M18="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="N16">
-        <f>IF(Attendance!N16="P", 5, IF(Attendance!N16="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!N18="P", 5, IF(Attendance!N18="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="O16">
-        <f>IF(Attendance!O16="P", 5, IF(Attendance!O16="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!O18="P", 5, IF(Attendance!O18="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="P16">
-        <f>IF(Attendance!P16="P", 5, IF(Attendance!P16="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!P18="P", 5, IF(Attendance!P18="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <f>IF(Attendance!Q16="P", 5, IF(Attendance!Q16="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!Q18="P", 5, IF(Attendance!Q18="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="R16">
-        <f>IF(Attendance!R16="P", 5, IF(Attendance!R16="O", 3, 0))</f>
+        <f>IF(Attendance!R18="P", 5, IF(Attendance!R18="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="S16">
-        <f>IF(Attendance!S16="P", 5, IF(Attendance!S16="O", 3, 0))</f>
+        <f>IF(Attendance!S18="P", 5, IF(Attendance!S18="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="T16">
-        <f>IF(Attendance!T16="P", 5, IF(Attendance!T16="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!T18="P", 5, IF(Attendance!T18="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="U16">
-        <f>IF(Attendance!U16="P", 5, IF(Attendance!U16="O", 3, 0))</f>
+        <f>IF(Attendance!U18="P", 5, IF(Attendance!U18="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="V16">
-        <f>IF(Attendance!V16="P", 5, IF(Attendance!V16="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!V18="P", 5, IF(Attendance!V18="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="W16">
-        <f>IF(Attendance!W16="P", 5, IF(Attendance!W16="O", 3, 0))</f>
+        <f>IF(Attendance!W18="P", 5, IF(Attendance!W18="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="X16">
-        <f>IF(Attendance!X16="P", 5, IF(Attendance!X16="O", 3, 0))</f>
+        <f>IF(Attendance!X18="P", 5, IF(Attendance!X18="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="Y16">
-        <f>IF(Attendance!Y16="P", 5, IF(Attendance!Y16="O", 3, 0))</f>
+        <f>IF(Attendance!Y18="P", 5, IF(Attendance!Y18="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="Z16">
-        <f>IF(Attendance!Z16="P", 5, IF(Attendance!Z16="O", 3, 0))</f>
+        <f>IF(Attendance!Z18="P", 5, IF(Attendance!Z18="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AA16">
-        <f>IF(Attendance!AA16="P", 5, IF(Attendance!AA16="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AA18="P", 5, IF(Attendance!AA18="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AB16">
-        <f>IF(Attendance!AB16="P", 5, IF(Attendance!AB16="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AB18="P", 5, IF(Attendance!AB18="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AC16">
-        <f>IF(Attendance!AC16="P", 5, IF(Attendance!AC16="O", 3, 0))</f>
+        <f>IF(Attendance!AC18="P", 5, IF(Attendance!AC18="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AD16">
-        <f>IF(Attendance!AD16="P", 5, IF(Attendance!AD16="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AD18="P", 5, IF(Attendance!AD18="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AE16">
-        <f>IF(Attendance!AE16="P", 5, IF(Attendance!AE16="O", 3, 0))</f>
+        <f>IF(Attendance!AE18="P", 5, IF(Attendance!AE18="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="AF16">
-        <f>IF(Attendance!AF16="P", 5, IF(Attendance!AF16="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AF18="P", 5, IF(Attendance!AF18="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <f>IF(Attendance!AG16="P", 5, IF(Attendance!AG16="O", 3, 0))</f>
+        <f>IF(Attendance!AG18="P", 5, IF(Attendance!AG18="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AH16">
-        <f>IF(Attendance!AH16="P", 5, IF(Attendance!AH16="O", 3, 0))</f>
+        <f>IF(Attendance!AH18="P", 5, IF(Attendance!AH18="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AI16">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="AJ16">
         <f t="shared" si="1"/>
@@ -8567,147 +8776,154 @@
       </c>
       <c r="AK16">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>1.41</v>
+      </c>
+      <c r="AL16">
+        <v>6</v>
+      </c>
+      <c r="AM16">
+        <f t="shared" ref="AM16" si="5">ROUND(AL16/4, 2)</f>
+        <v>1.5</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17">
-        <f>IF(Attendance!C17="P", 5, IF(Attendance!C17="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!C19="P", 5, IF(Attendance!C19="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="D17">
-        <f>IF(Attendance!D17="P", 5, IF(Attendance!D17="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!D19="P", 5, IF(Attendance!D19="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="E17">
-        <f>IF(Attendance!E17="P", 5, IF(Attendance!E17="O", 3, 0))</f>
+        <f>IF(Attendance!E19="P", 5, IF(Attendance!E19="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="F17">
-        <f>IF(Attendance!F17="P", 5, IF(Attendance!F17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!F19="P", 5, IF(Attendance!F19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="G17">
-        <f>IF(Attendance!G17="P", 5, IF(Attendance!G17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!G19="P", 5, IF(Attendance!G19="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="H17">
-        <f>IF(Attendance!H17="P", 5, IF(Attendance!H17="O", 3, 0))</f>
+        <f>IF(Attendance!H19="P", 5, IF(Attendance!H19="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="I17">
-        <f>IF(Attendance!I17="P", 5, IF(Attendance!I17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!I19="P", 5, IF(Attendance!I19="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="J17">
-        <f>IF(Attendance!J17="P", 5, IF(Attendance!J17="O", 3, 0))</f>
+        <f>IF(Attendance!J19="P", 5, IF(Attendance!J19="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="K17">
-        <f>IF(Attendance!K17="P", 5, IF(Attendance!K17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!K19="P", 5, IF(Attendance!K19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="L17">
-        <f>IF(Attendance!L17="P", 5, IF(Attendance!L17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!L19="P", 5, IF(Attendance!L19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="M17">
-        <f>IF(Attendance!M17="P", 5, IF(Attendance!M17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!M19="P", 5, IF(Attendance!M19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="N17">
-        <f>IF(Attendance!N17="P", 5, IF(Attendance!N17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!N19="P", 5, IF(Attendance!N19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="O17">
-        <f>IF(Attendance!O17="P", 5, IF(Attendance!O17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!O19="P", 5, IF(Attendance!O19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="P17">
-        <f>IF(Attendance!P17="P", 5, IF(Attendance!P17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!P19="P", 5, IF(Attendance!P19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <f>IF(Attendance!Q17="P", 5, IF(Attendance!Q17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!Q19="P", 5, IF(Attendance!Q19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="R17">
-        <f>IF(Attendance!R17="P", 5, IF(Attendance!R17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!R19="P", 5, IF(Attendance!R19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="S17">
-        <f>IF(Attendance!S17="P", 5, IF(Attendance!S17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!S19="P", 5, IF(Attendance!S19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="T17">
-        <f>IF(Attendance!T17="P", 5, IF(Attendance!T17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!T19="P", 5, IF(Attendance!T19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="U17">
-        <f>IF(Attendance!U17="P", 5, IF(Attendance!U17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!U19="P", 5, IF(Attendance!U19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="V17">
-        <f>IF(Attendance!V17="P", 5, IF(Attendance!V17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!V19="P", 5, IF(Attendance!V19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="W17">
-        <f>IF(Attendance!W17="P", 5, IF(Attendance!W17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!W19="P", 5, IF(Attendance!W19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="X17">
-        <f>IF(Attendance!X17="P", 5, IF(Attendance!X17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!X19="P", 5, IF(Attendance!X19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <f>IF(Attendance!Y17="P", 5, IF(Attendance!Y17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!Y19="P", 5, IF(Attendance!Y19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <f>IF(Attendance!Z17="P", 5, IF(Attendance!Z17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!Z19="P", 5, IF(Attendance!Z19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <f>IF(Attendance!AA17="P", 5, IF(Attendance!AA17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AA19="P", 5, IF(Attendance!AA19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <f>IF(Attendance!AB17="P", 5, IF(Attendance!AB17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AB19="P", 5, IF(Attendance!AB19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <f>IF(Attendance!AC17="P", 5, IF(Attendance!AC17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AC19="P", 5, IF(Attendance!AC19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <f>IF(Attendance!AD17="P", 5, IF(Attendance!AD17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AD19="P", 5, IF(Attendance!AD19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <f>IF(Attendance!AE17="P", 5, IF(Attendance!AE17="O", 3, 0))</f>
+        <f>IF(Attendance!AE19="P", 5, IF(Attendance!AE19="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="AF17">
-        <f>IF(Attendance!AF17="P", 5, IF(Attendance!AF17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AF19="P", 5, IF(Attendance!AF19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <f>IF(Attendance!AG17="P", 5, IF(Attendance!AG17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AG19="P", 5, IF(Attendance!AG19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AH17">
-        <f>IF(Attendance!AH17="P", 5, IF(Attendance!AH17="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AH19="P", 5, IF(Attendance!AH19="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AI17">
         <f t="shared" si="0"/>
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="AJ17">
         <f t="shared" si="1"/>
@@ -8715,147 +8931,150 @@
       </c>
       <c r="AK17">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>0.84</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
       </c>
       <c r="C18">
-        <f>IF(Attendance!C18="P", 5, IF(Attendance!C18="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!C20="P", 5, IF(Attendance!C20="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="D18">
-        <f>IF(Attendance!D18="P", 5, IF(Attendance!D18="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!D20="P", 5, IF(Attendance!D20="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="E18">
-        <f>IF(Attendance!E18="P", 5, IF(Attendance!E18="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!E20="P", 5, IF(Attendance!E20="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="F18">
-        <f>IF(Attendance!F18="P", 5, IF(Attendance!F18="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!F20="P", 5, IF(Attendance!F20="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="G18">
-        <f>IF(Attendance!G18="P", 5, IF(Attendance!G18="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!G20="P", 5, IF(Attendance!G20="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="H18">
-        <f>IF(Attendance!H18="P", 5, IF(Attendance!H18="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!H20="P", 5, IF(Attendance!H20="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="I18">
-        <f>IF(Attendance!I18="P", 5, IF(Attendance!I18="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!I20="P", 5, IF(Attendance!I20="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="J18">
-        <f>IF(Attendance!J18="P", 5, IF(Attendance!J18="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!J20="P", 5, IF(Attendance!J20="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="K18">
-        <f>IF(Attendance!K18="P", 5, IF(Attendance!K18="O", 3, 0))</f>
+        <f>IF(Attendance!K20="P", 5, IF(Attendance!K20="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="L18">
-        <f>IF(Attendance!L18="P", 5, IF(Attendance!L18="O", 3, 0))</f>
+        <f>IF(Attendance!L20="P", 5, IF(Attendance!L20="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="M18">
-        <f>IF(Attendance!M18="P", 5, IF(Attendance!M18="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!M20="P", 5, IF(Attendance!M20="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="N18">
-        <f>IF(Attendance!N18="P", 5, IF(Attendance!N18="O", 3, 0))</f>
+        <f>IF(Attendance!N20="P", 5, IF(Attendance!N20="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="O18">
-        <f>IF(Attendance!O18="P", 5, IF(Attendance!O18="O", 3, 0))</f>
+        <f>IF(Attendance!O20="P", 5, IF(Attendance!O20="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="P18">
-        <f>IF(Attendance!P18="P", 5, IF(Attendance!P18="O", 3, 0))</f>
+        <f>IF(Attendance!P20="P", 5, IF(Attendance!P20="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="Q18">
-        <f>IF(Attendance!Q18="P", 5, IF(Attendance!Q18="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!Q20="P", 5, IF(Attendance!Q20="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="R18">
-        <f>IF(Attendance!R18="P", 5, IF(Attendance!R18="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!R20="P", 5, IF(Attendance!R20="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="S18">
-        <f>IF(Attendance!S18="P", 5, IF(Attendance!S18="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!S20="P", 5, IF(Attendance!S20="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="T18">
-        <f>IF(Attendance!T18="P", 5, IF(Attendance!T18="O", 3, 0))</f>
+        <f>IF(Attendance!T20="P", 5, IF(Attendance!T20="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="U18">
-        <f>IF(Attendance!U18="P", 5, IF(Attendance!U18="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!U20="P", 5, IF(Attendance!U20="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="V18">
-        <f>IF(Attendance!V18="P", 5, IF(Attendance!V18="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!V20="P", 5, IF(Attendance!V20="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="W18">
-        <f>IF(Attendance!W18="P", 5, IF(Attendance!W18="O", 3, 0))</f>
+        <f>IF(Attendance!W20="P", 5, IF(Attendance!W20="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="X18">
-        <f>IF(Attendance!X18="P", 5, IF(Attendance!X18="O", 3, 0))</f>
+        <f>IF(Attendance!X20="P", 5, IF(Attendance!X20="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="Y18">
-        <f>IF(Attendance!Y18="P", 5, IF(Attendance!Y18="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!Y20="P", 5, IF(Attendance!Y20="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="Z18">
-        <f>IF(Attendance!Z18="P", 5, IF(Attendance!Z18="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!Z20="P", 5, IF(Attendance!Z20="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AA18">
-        <f>IF(Attendance!AA18="P", 5, IF(Attendance!AA18="O", 3, 0))</f>
+        <f>IF(Attendance!AA20="P", 5, IF(Attendance!AA20="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AB18">
-        <f>IF(Attendance!AB18="P", 5, IF(Attendance!AB18="O", 3, 0))</f>
+        <f>IF(Attendance!AB20="P", 5, IF(Attendance!AB20="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AC18">
-        <f>IF(Attendance!AC18="P", 5, IF(Attendance!AC18="O", 3, 0))</f>
+        <f>IF(Attendance!AC20="P", 5, IF(Attendance!AC20="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AD18">
-        <f>IF(Attendance!AD18="P", 5, IF(Attendance!AD18="O", 3, 0))</f>
+        <f>IF(Attendance!AD20="P", 5, IF(Attendance!AD20="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AE18">
-        <f>IF(Attendance!AE18="P", 5, IF(Attendance!AE18="O", 3, 0))</f>
+        <f>IF(Attendance!AE20="P", 5, IF(Attendance!AE20="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="AF18">
-        <f>IF(Attendance!AF18="P", 5, IF(Attendance!AF18="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AF20="P", 5, IF(Attendance!AF20="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AG18">
-        <f>IF(Attendance!AG18="P", 5, IF(Attendance!AG18="O", 3, 0))</f>
+        <f>IF(Attendance!AG20="P", 5, IF(Attendance!AG20="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AH18">
-        <f>IF(Attendance!AH18="P", 5, IF(Attendance!AH18="O", 3, 0))</f>
+        <f>IF(Attendance!AH20="P", 5, IF(Attendance!AH20="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AI18">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="AJ18">
         <f t="shared" si="1"/>
@@ -8863,147 +9082,154 @@
       </c>
       <c r="AK18">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>3.28</v>
+      </c>
+      <c r="AL18">
+        <v>6</v>
+      </c>
+      <c r="AM18">
+        <f t="shared" ref="AM18:AM19" si="6">ROUND(AL18/4, 2)</f>
+        <v>1.5</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
       </c>
       <c r="C19">
-        <f>IF(Attendance!C19="P", 5, IF(Attendance!C19="O", 3, 0))</f>
+        <f>IF(Attendance!C21="P", 5, IF(Attendance!C21="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="D19">
-        <f>IF(Attendance!D19="P", 5, IF(Attendance!D19="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!D21="P", 5, IF(Attendance!D21="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="E19">
-        <f>IF(Attendance!E19="P", 5, IF(Attendance!E19="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!E21="P", 5, IF(Attendance!E21="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="F19">
-        <f>IF(Attendance!F19="P", 5, IF(Attendance!F19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!F21="P", 5, IF(Attendance!F21="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="G19">
-        <f>IF(Attendance!G19="P", 5, IF(Attendance!G19="O", 3, 0))</f>
+        <f>IF(Attendance!G21="P", 5, IF(Attendance!G21="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="H19">
-        <f>IF(Attendance!H19="P", 5, IF(Attendance!H19="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!H21="P", 5, IF(Attendance!H21="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="I19">
-        <f>IF(Attendance!I19="P", 5, IF(Attendance!I19="O", 3, 0))</f>
+        <f>IF(Attendance!I21="P", 5, IF(Attendance!I21="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="J19">
-        <f>IF(Attendance!J19="P", 5, IF(Attendance!J19="O", 3, 0))</f>
+        <f>IF(Attendance!J21="P", 5, IF(Attendance!J21="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="K19">
-        <f>IF(Attendance!K19="P", 5, IF(Attendance!K19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!K21="P", 5, IF(Attendance!K21="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="L19">
-        <f>IF(Attendance!L19="P", 5, IF(Attendance!L19="O", 3, 0))</f>
+        <f>IF(Attendance!L21="P", 5, IF(Attendance!L21="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="M19">
-        <f>IF(Attendance!M19="P", 5, IF(Attendance!M19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!M21="P", 5, IF(Attendance!M21="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="N19">
-        <f>IF(Attendance!N19="P", 5, IF(Attendance!N19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!N21="P", 5, IF(Attendance!N21="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="O19">
-        <f>IF(Attendance!O19="P", 5, IF(Attendance!O19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!O21="P", 5, IF(Attendance!O21="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="P19">
-        <f>IF(Attendance!P19="P", 5, IF(Attendance!P19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!P21="P", 5, IF(Attendance!P21="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <f>IF(Attendance!Q19="P", 5, IF(Attendance!Q19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!Q21="P", 5, IF(Attendance!Q21="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="R19">
-        <f>IF(Attendance!R19="P", 5, IF(Attendance!R19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!R21="P", 5, IF(Attendance!R21="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="S19">
-        <f>IF(Attendance!S19="P", 5, IF(Attendance!S19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!S21="P", 5, IF(Attendance!S21="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="T19">
-        <f>IF(Attendance!T19="P", 5, IF(Attendance!T19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!T21="P", 5, IF(Attendance!T21="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="U19">
-        <f>IF(Attendance!U19="P", 5, IF(Attendance!U19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!U21="P", 5, IF(Attendance!U21="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="V19">
-        <f>IF(Attendance!V19="P", 5, IF(Attendance!V19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!V21="P", 5, IF(Attendance!V21="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="W19">
-        <f>IF(Attendance!W19="P", 5, IF(Attendance!W19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!W21="P", 5, IF(Attendance!W21="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="X19">
-        <f>IF(Attendance!X19="P", 5, IF(Attendance!X19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!X21="P", 5, IF(Attendance!X21="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="Y19">
-        <f>IF(Attendance!Y19="P", 5, IF(Attendance!Y19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!Y21="P", 5, IF(Attendance!Y21="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="Z19">
-        <f>IF(Attendance!Z19="P", 5, IF(Attendance!Z19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!Z21="P", 5, IF(Attendance!Z21="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AA19">
-        <f>IF(Attendance!AA19="P", 5, IF(Attendance!AA19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AA21="P", 5, IF(Attendance!AA21="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AB19">
-        <f>IF(Attendance!AB19="P", 5, IF(Attendance!AB19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AB21="P", 5, IF(Attendance!AB21="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AC19">
-        <f>IF(Attendance!AC19="P", 5, IF(Attendance!AC19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AC21="P", 5, IF(Attendance!AC21="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AD19">
-        <f>IF(Attendance!AD19="P", 5, IF(Attendance!AD19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AD21="P", 5, IF(Attendance!AD21="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AE19">
-        <f>IF(Attendance!AE19="P", 5, IF(Attendance!AE19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AE21="P", 5, IF(Attendance!AE21="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AF19">
-        <f>IF(Attendance!AF19="P", 5, IF(Attendance!AF19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AF21="P", 5, IF(Attendance!AF21="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AG19">
-        <f>IF(Attendance!AG19="P", 5, IF(Attendance!AG19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AG21="P", 5, IF(Attendance!AG21="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AH19">
-        <f>IF(Attendance!AH19="P", 5, IF(Attendance!AH19="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AH21="P", 5, IF(Attendance!AH21="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AI19">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>141</v>
       </c>
       <c r="AJ19">
         <f t="shared" si="1"/>
@@ -9011,147 +9237,154 @@
       </c>
       <c r="AK19">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4.41</v>
+      </c>
+      <c r="AL19">
+        <v>10</v>
+      </c>
+      <c r="AM19">
+        <f t="shared" si="6"/>
+        <v>2.5</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
       </c>
       <c r="C20">
-        <f>IF(Attendance!C20="P", 5, IF(Attendance!C20="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!C23="P", 5, IF(Attendance!C23="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="D20">
-        <f>IF(Attendance!D20="P", 5, IF(Attendance!D20="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!D23="P", 5, IF(Attendance!D23="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="E20">
-        <f>IF(Attendance!E20="P", 5, IF(Attendance!E20="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!E23="P", 5, IF(Attendance!E23="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="F20">
-        <f>IF(Attendance!F20="P", 5, IF(Attendance!F20="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!F23="P", 5, IF(Attendance!F23="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="G20">
-        <f>IF(Attendance!G20="P", 5, IF(Attendance!G20="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!G23="P", 5, IF(Attendance!G23="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="H20">
-        <f>IF(Attendance!H20="P", 5, IF(Attendance!H20="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!H23="P", 5, IF(Attendance!H23="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="I20">
-        <f>IF(Attendance!I20="P", 5, IF(Attendance!I20="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!I23="P", 5, IF(Attendance!I23="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="J20">
-        <f>IF(Attendance!J20="P", 5, IF(Attendance!J20="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!J23="P", 5, IF(Attendance!J23="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="K20">
-        <f>IF(Attendance!K20="P", 5, IF(Attendance!K20="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!K23="P", 5, IF(Attendance!K23="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="L20">
-        <f>IF(Attendance!L20="P", 5, IF(Attendance!L20="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!L23="P", 5, IF(Attendance!L23="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="M20">
-        <f>IF(Attendance!M20="P", 5, IF(Attendance!M20="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!M23="P", 5, IF(Attendance!M23="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="N20">
-        <f>IF(Attendance!N20="P", 5, IF(Attendance!N20="O", 3, 0))</f>
+        <f>IF(Attendance!N23="P", 5, IF(Attendance!N23="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="O20">
-        <f>IF(Attendance!O20="P", 5, IF(Attendance!O20="O", 3, 0))</f>
+        <f>IF(Attendance!O23="P", 5, IF(Attendance!O23="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="P20">
-        <f>IF(Attendance!P20="P", 5, IF(Attendance!P20="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!P23="P", 5, IF(Attendance!P23="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="Q20">
-        <f>IF(Attendance!Q20="P", 5, IF(Attendance!Q20="O", 3, 0))</f>
+        <f>IF(Attendance!Q23="P", 5, IF(Attendance!Q23="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="R20">
-        <f>IF(Attendance!R20="P", 5, IF(Attendance!R20="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!R23="P", 5, IF(Attendance!R23="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="S20">
-        <f>IF(Attendance!S20="P", 5, IF(Attendance!S20="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!S23="P", 5, IF(Attendance!S23="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="T20">
-        <f>IF(Attendance!T20="P", 5, IF(Attendance!T20="O", 3, 0))</f>
+        <f>IF(Attendance!T23="P", 5, IF(Attendance!T23="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="U20">
-        <f>IF(Attendance!U20="P", 5, IF(Attendance!U20="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!U23="P", 5, IF(Attendance!U23="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="V20">
-        <f>IF(Attendance!V20="P", 5, IF(Attendance!V20="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!V23="P", 5, IF(Attendance!V23="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="W20">
-        <f>IF(Attendance!W20="P", 5, IF(Attendance!W20="O", 3, 0))</f>
+        <f>IF(Attendance!W23="P", 5, IF(Attendance!W23="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="X20">
-        <f>IF(Attendance!X20="P", 5, IF(Attendance!X20="O", 3, 0))</f>
+        <f>IF(Attendance!X23="P", 5, IF(Attendance!X23="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="Y20">
-        <f>IF(Attendance!Y20="P", 5, IF(Attendance!Y20="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!Y23="P", 5, IF(Attendance!Y23="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="Z20">
-        <f>IF(Attendance!Z20="P", 5, IF(Attendance!Z20="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!Z23="P", 5, IF(Attendance!Z23="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AA20">
-        <f>IF(Attendance!AA20="P", 5, IF(Attendance!AA20="O", 3, 0))</f>
+        <f>IF(Attendance!AA23="P", 5, IF(Attendance!AA23="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AB20">
-        <f>IF(Attendance!AB20="P", 5, IF(Attendance!AB20="O", 3, 0))</f>
+        <f>IF(Attendance!AB23="P", 5, IF(Attendance!AB23="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AC20">
-        <f>IF(Attendance!AC20="P", 5, IF(Attendance!AC20="O", 3, 0))</f>
+        <f>IF(Attendance!AC23="P", 5, IF(Attendance!AC23="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AD20">
-        <f>IF(Attendance!AD20="P", 5, IF(Attendance!AD20="O", 3, 0))</f>
+        <f>IF(Attendance!AD23="P", 5, IF(Attendance!AD23="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AE20">
-        <f>IF(Attendance!AE20="P", 5, IF(Attendance!AE20="O", 3, 0))</f>
+        <f>IF(Attendance!AE23="P", 5, IF(Attendance!AE23="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="AF20">
-        <f>IF(Attendance!AF20="P", 5, IF(Attendance!AF20="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AF23="P", 5, IF(Attendance!AF23="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AG20">
-        <f>IF(Attendance!AG20="P", 5, IF(Attendance!AG20="O", 3, 0))</f>
+        <f>IF(Attendance!AG23="P", 5, IF(Attendance!AG23="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AH20">
-        <f>IF(Attendance!AH20="P", 5, IF(Attendance!AH20="O", 3, 0))</f>
+        <f>IF(Attendance!AH23="P", 5, IF(Attendance!AH23="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AI20">
         <f t="shared" si="0"/>
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="AJ20">
         <f t="shared" si="1"/>
@@ -9159,147 +9392,150 @@
       </c>
       <c r="AK20">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>2.06</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
       </c>
       <c r="C21">
-        <f>IF(Attendance!C21="P", 5, IF(Attendance!C21="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!C24="P", 5, IF(Attendance!C24="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="D21">
-        <f>IF(Attendance!D21="P", 5, IF(Attendance!D21="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!D24="P", 5, IF(Attendance!D24="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="E21">
-        <f>IF(Attendance!E21="P", 5, IF(Attendance!E21="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!E24="P", 5, IF(Attendance!E24="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="F21">
-        <f>IF(Attendance!F21="P", 5, IF(Attendance!F21="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!F24="P", 5, IF(Attendance!F24="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="G21">
-        <f>IF(Attendance!G21="P", 5, IF(Attendance!G21="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!G24="P", 5, IF(Attendance!G24="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="H21">
-        <f>IF(Attendance!H21="P", 5, IF(Attendance!H21="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!H24="P", 5, IF(Attendance!H24="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="I21">
-        <f>IF(Attendance!I21="P", 5, IF(Attendance!I21="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!I24="P", 5, IF(Attendance!I24="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="J21">
-        <f>IF(Attendance!J21="P", 5, IF(Attendance!J21="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!J24="P", 5, IF(Attendance!J24="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="K21">
-        <f>IF(Attendance!K21="P", 5, IF(Attendance!K21="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!K24="P", 5, IF(Attendance!K24="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="L21">
-        <f>IF(Attendance!L21="P", 5, IF(Attendance!L21="O", 3, 0))</f>
+        <f>IF(Attendance!L24="P", 5, IF(Attendance!L24="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="M21">
-        <f>IF(Attendance!M21="P", 5, IF(Attendance!M21="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!M24="P", 5, IF(Attendance!M24="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="N21">
-        <f>IF(Attendance!N21="P", 5, IF(Attendance!N21="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!N24="P", 5, IF(Attendance!N24="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="O21">
-        <f>IF(Attendance!O21="P", 5, IF(Attendance!O21="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!O24="P", 5, IF(Attendance!O24="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="P21">
-        <f>IF(Attendance!P21="P", 5, IF(Attendance!P21="O", 3, 0))</f>
+        <f>IF(Attendance!P24="P", 5, IF(Attendance!P24="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="Q21">
-        <f>IF(Attendance!Q21="P", 5, IF(Attendance!Q21="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!Q24="P", 5, IF(Attendance!Q24="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="R21">
-        <f>IF(Attendance!R21="P", 5, IF(Attendance!R21="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!R24="P", 5, IF(Attendance!R24="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="S21">
-        <f>IF(Attendance!S21="P", 5, IF(Attendance!S21="O", 3, 0))</f>
+        <f>IF(Attendance!S24="P", 5, IF(Attendance!S24="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="T21">
-        <f>IF(Attendance!T21="P", 5, IF(Attendance!T21="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!T24="P", 5, IF(Attendance!T24="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="U21">
-        <f>IF(Attendance!U21="P", 5, IF(Attendance!U21="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!U24="P", 5, IF(Attendance!U24="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="V21">
-        <f>IF(Attendance!V21="P", 5, IF(Attendance!V21="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!V24="P", 5, IF(Attendance!V24="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="W21">
-        <f>IF(Attendance!W21="P", 5, IF(Attendance!W21="O", 3, 0))</f>
+        <f>IF(Attendance!W24="P", 5, IF(Attendance!W24="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="X21">
-        <f>IF(Attendance!X21="P", 5, IF(Attendance!X21="O", 3, 0))</f>
+        <f>IF(Attendance!X24="P", 5, IF(Attendance!X24="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="Y21">
-        <f>IF(Attendance!Y21="P", 5, IF(Attendance!Y21="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!Y24="P", 5, IF(Attendance!Y24="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <f>IF(Attendance!Z21="P", 5, IF(Attendance!Z21="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!Z24="P", 5, IF(Attendance!Z24="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AA21">
-        <f>IF(Attendance!AA21="P", 5, IF(Attendance!AA21="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AA24="P", 5, IF(Attendance!AA24="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AB21">
-        <f>IF(Attendance!AB21="P", 5, IF(Attendance!AB21="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AB24="P", 5, IF(Attendance!AB24="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AC21">
-        <f>IF(Attendance!AC21="P", 5, IF(Attendance!AC21="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AC24="P", 5, IF(Attendance!AC24="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <f>IF(Attendance!AD21="P", 5, IF(Attendance!AD21="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AD24="P", 5, IF(Attendance!AD24="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <f>IF(Attendance!AE21="P", 5, IF(Attendance!AE21="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AE24="P", 5, IF(Attendance!AE24="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <f>IF(Attendance!AF21="P", 5, IF(Attendance!AF21="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AF24="P", 5, IF(Attendance!AF24="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <f>IF(Attendance!AG21="P", 5, IF(Attendance!AG21="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AG24="P", 5, IF(Attendance!AG24="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AH21">
-        <f>IF(Attendance!AH21="P", 5, IF(Attendance!AH21="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AH24="P", 5, IF(Attendance!AH24="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AI21">
         <f t="shared" si="0"/>
-        <v>141</v>
+        <v>34</v>
       </c>
       <c r="AJ21">
         <f t="shared" si="1"/>
@@ -9307,147 +9543,150 @@
       </c>
       <c r="AK21">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>1.06</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C22">
-        <f>IF(Attendance!C22="P", 5, IF(Attendance!C22="O", 3, 0))</f>
+        <f>IF(Attendance!C25="P", 5, IF(Attendance!C25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="D22">
-        <f>IF(Attendance!D22="P", 5, IF(Attendance!D22="O", 3, 0))</f>
+        <f>IF(Attendance!D25="P", 5, IF(Attendance!D25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="E22">
-        <f>IF(Attendance!E22="P", 5, IF(Attendance!E22="O", 3, 0))</f>
+        <f>IF(Attendance!E25="P", 5, IF(Attendance!E25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="F22">
-        <f>IF(Attendance!F22="P", 5, IF(Attendance!F22="O", 3, 0))</f>
+        <f>IF(Attendance!F25="P", 5, IF(Attendance!F25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="G22">
-        <f>IF(Attendance!G22="P", 5, IF(Attendance!G22="O", 3, 0))</f>
+        <f>IF(Attendance!G25="P", 5, IF(Attendance!G25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="H22">
-        <f>IF(Attendance!H22="P", 5, IF(Attendance!H22="O", 3, 0))</f>
+        <f>IF(Attendance!H25="P", 5, IF(Attendance!H25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="I22">
-        <f>IF(Attendance!I22="P", 5, IF(Attendance!I22="O", 3, 0))</f>
+        <f>IF(Attendance!I25="P", 5, IF(Attendance!I25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="J22">
-        <f>IF(Attendance!J22="P", 5, IF(Attendance!J22="O", 3, 0))</f>
+        <f>IF(Attendance!J25="P", 5, IF(Attendance!J25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="K22">
-        <f>IF(Attendance!K22="P", 5, IF(Attendance!K22="O", 3, 0))</f>
+        <f>IF(Attendance!K25="P", 5, IF(Attendance!K25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="L22">
-        <f>IF(Attendance!L22="P", 5, IF(Attendance!L22="O", 3, 0))</f>
+        <f>IF(Attendance!L25="P", 5, IF(Attendance!L25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="M22">
-        <f>IF(Attendance!M22="P", 5, IF(Attendance!M22="O", 3, 0))</f>
+        <f>IF(Attendance!M25="P", 5, IF(Attendance!M25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="N22">
-        <f>IF(Attendance!N22="P", 5, IF(Attendance!N22="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!N25="P", 5, IF(Attendance!N25="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="O22">
-        <f>IF(Attendance!O22="P", 5, IF(Attendance!O22="O", 3, 0))</f>
+        <f>IF(Attendance!O25="P", 5, IF(Attendance!O25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="P22">
-        <f>IF(Attendance!P22="P", 5, IF(Attendance!P22="O", 3, 0))</f>
+        <f>IF(Attendance!P25="P", 5, IF(Attendance!P25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="Q22">
-        <f>IF(Attendance!Q22="P", 5, IF(Attendance!Q22="O", 3, 0))</f>
+        <f>IF(Attendance!Q25="P", 5, IF(Attendance!Q25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="R22">
-        <f>IF(Attendance!R22="P", 5, IF(Attendance!R22="O", 3, 0))</f>
+        <f>IF(Attendance!R25="P", 5, IF(Attendance!R25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="S22">
-        <f>IF(Attendance!S22="P", 5, IF(Attendance!S22="O", 3, 0))</f>
+        <f>IF(Attendance!S25="P", 5, IF(Attendance!S25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="T22">
-        <f>IF(Attendance!T22="P", 5, IF(Attendance!T22="O", 3, 0))</f>
+        <f>IF(Attendance!T25="P", 5, IF(Attendance!T25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="U22">
-        <f>IF(Attendance!U22="P", 5, IF(Attendance!U22="O", 3, 0))</f>
+        <f>IF(Attendance!U25="P", 5, IF(Attendance!U25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="V22">
-        <f>IF(Attendance!V22="P", 5, IF(Attendance!V22="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!V25="P", 5, IF(Attendance!V25="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="W22">
-        <f>IF(Attendance!W22="P", 5, IF(Attendance!W22="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!W25="P", 5, IF(Attendance!W25="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="X22">
-        <f>IF(Attendance!X22="P", 5, IF(Attendance!X22="O", 3, 0))</f>
+        <f>IF(Attendance!X25="P", 5, IF(Attendance!X25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="Y22">
-        <f>IF(Attendance!Y22="P", 5, IF(Attendance!Y22="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!Y25="P", 5, IF(Attendance!Y25="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="Z22">
-        <f>IF(Attendance!Z22="P", 5, IF(Attendance!Z22="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!Z25="P", 5, IF(Attendance!Z25="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AA22">
-        <f>IF(Attendance!AA22="P", 5, IF(Attendance!AA22="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AA25="P", 5, IF(Attendance!AA25="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AB22">
-        <f>IF(Attendance!AB22="P", 5, IF(Attendance!AB22="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AB25="P", 5, IF(Attendance!AB25="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AC22">
-        <f>IF(Attendance!AC22="P", 5, IF(Attendance!AC22="O", 3, 0))</f>
+        <f>IF(Attendance!AC25="P", 5, IF(Attendance!AC25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="AD22">
-        <f>IF(Attendance!AD22="P", 5, IF(Attendance!AD22="O", 3, 0))</f>
+        <f>IF(Attendance!AD25="P", 5, IF(Attendance!AD25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="AE22">
-        <f>IF(Attendance!AE22="P", 5, IF(Attendance!AE22="O", 3, 0))</f>
+        <f>IF(Attendance!AE25="P", 5, IF(Attendance!AE25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="AF22">
-        <f>IF(Attendance!AF22="P", 5, IF(Attendance!AF22="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AF25="P", 5, IF(Attendance!AF25="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AG22">
-        <f>IF(Attendance!AG22="P", 5, IF(Attendance!AG22="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AG25="P", 5, IF(Attendance!AG25="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AH22">
-        <f>IF(Attendance!AH22="P", 5, IF(Attendance!AH22="O", 3, 0))</f>
+        <f>IF(Attendance!AH25="P", 5, IF(Attendance!AH25="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="AI22">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="AJ22">
         <f t="shared" si="1"/>
@@ -9455,147 +9694,150 @@
       </c>
       <c r="AK22">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.88</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
         <v>34</v>
       </c>
       <c r="C23">
-        <f>IF(Attendance!C23="P", 5, IF(Attendance!C23="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!C26="P", 5, IF(Attendance!C26="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="D23">
-        <f>IF(Attendance!D23="P", 5, IF(Attendance!D23="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!D26="P", 5, IF(Attendance!D26="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="E23">
-        <f>IF(Attendance!E23="P", 5, IF(Attendance!E23="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!E26="P", 5, IF(Attendance!E26="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="F23">
-        <f>IF(Attendance!F23="P", 5, IF(Attendance!F23="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!F26="P", 5, IF(Attendance!F26="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="G23">
-        <f>IF(Attendance!G23="P", 5, IF(Attendance!G23="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!G26="P", 5, IF(Attendance!G26="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="H23">
-        <f>IF(Attendance!H23="P", 5, IF(Attendance!H23="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!H26="P", 5, IF(Attendance!H26="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="I23">
-        <f>IF(Attendance!I23="P", 5, IF(Attendance!I23="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!I26="P", 5, IF(Attendance!I26="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="J23">
-        <f>IF(Attendance!J23="P", 5, IF(Attendance!J23="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!J26="P", 5, IF(Attendance!J26="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="K23">
-        <f>IF(Attendance!K23="P", 5, IF(Attendance!K23="O", 3, 0))</f>
+        <f>IF(Attendance!K26="P", 5, IF(Attendance!K26="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="L23">
-        <f>IF(Attendance!L23="P", 5, IF(Attendance!L23="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!L26="P", 5, IF(Attendance!L26="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="M23">
-        <f>IF(Attendance!M23="P", 5, IF(Attendance!M23="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!M26="P", 5, IF(Attendance!M26="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="N23">
-        <f>IF(Attendance!N23="P", 5, IF(Attendance!N23="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!N26="P", 5, IF(Attendance!N26="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="O23">
-        <f>IF(Attendance!O23="P", 5, IF(Attendance!O23="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!O26="P", 5, IF(Attendance!O26="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="P23">
-        <f>IF(Attendance!P23="P", 5, IF(Attendance!P23="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!P26="P", 5, IF(Attendance!P26="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <f>IF(Attendance!Q23="P", 5, IF(Attendance!Q23="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!Q26="P", 5, IF(Attendance!Q26="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="R23">
-        <f>IF(Attendance!R23="P", 5, IF(Attendance!R23="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!R26="P", 5, IF(Attendance!R26="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="S23">
-        <f>IF(Attendance!S23="P", 5, IF(Attendance!S23="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!S26="P", 5, IF(Attendance!S26="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="T23">
-        <f>IF(Attendance!T23="P", 5, IF(Attendance!T23="O", 3, 0))</f>
+        <f>IF(Attendance!T26="P", 5, IF(Attendance!T26="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="U23">
-        <f>IF(Attendance!U23="P", 5, IF(Attendance!U23="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!U26="P", 5, IF(Attendance!U26="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="V23">
-        <f>IF(Attendance!V23="P", 5, IF(Attendance!V23="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!V26="P", 5, IF(Attendance!V26="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="W23">
-        <f>IF(Attendance!W23="P", 5, IF(Attendance!W23="O", 3, 0))</f>
+        <f>IF(Attendance!W26="P", 5, IF(Attendance!W26="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="X23">
-        <f>IF(Attendance!X23="P", 5, IF(Attendance!X23="O", 3, 0))</f>
+        <f>IF(Attendance!X26="P", 5, IF(Attendance!X26="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="Y23">
-        <f>IF(Attendance!Y23="P", 5, IF(Attendance!Y23="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!Y26="P", 5, IF(Attendance!Y26="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="Z23">
-        <f>IF(Attendance!Z23="P", 5, IF(Attendance!Z23="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!Z26="P", 5, IF(Attendance!Z26="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AA23">
-        <f>IF(Attendance!AA23="P", 5, IF(Attendance!AA23="O", 3, 0))</f>
+        <f>IF(Attendance!AA26="P", 5, IF(Attendance!AA26="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AB23">
-        <f>IF(Attendance!AB23="P", 5, IF(Attendance!AB23="O", 3, 0))</f>
+        <f>IF(Attendance!AB26="P", 5, IF(Attendance!AB26="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AC23">
-        <f>IF(Attendance!AC23="P", 5, IF(Attendance!AC23="O", 3, 0))</f>
+        <f>IF(Attendance!AC26="P", 5, IF(Attendance!AC26="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AD23">
-        <f>IF(Attendance!AD23="P", 5, IF(Attendance!AD23="O", 3, 0))</f>
+        <f>IF(Attendance!AD26="P", 5, IF(Attendance!AD26="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AE23">
-        <f>IF(Attendance!AE23="P", 5, IF(Attendance!AE23="O", 3, 0))</f>
+        <f>IF(Attendance!AE26="P", 5, IF(Attendance!AE26="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="AF23">
-        <f>IF(Attendance!AF23="P", 5, IF(Attendance!AF23="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AF26="P", 5, IF(Attendance!AF26="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AG23">
-        <f>IF(Attendance!AG23="P", 5, IF(Attendance!AG23="O", 3, 0))</f>
+        <f>IF(Attendance!AG26="P", 5, IF(Attendance!AG26="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AH23">
-        <f>IF(Attendance!AH23="P", 5, IF(Attendance!AH23="O", 3, 0))</f>
+        <f>IF(Attendance!AH26="P", 5, IF(Attendance!AH26="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AI23">
         <f t="shared" si="0"/>
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="AJ23">
         <f t="shared" si="1"/>
@@ -9603,147 +9845,154 @@
       </c>
       <c r="AK23">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>4.22</v>
+      </c>
+      <c r="AL23">
+        <v>10</v>
+      </c>
+      <c r="AM23">
+        <f t="shared" ref="AM23" si="7">ROUND(AL23/4, 2)</f>
+        <v>2.5</v>
       </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
         <v>34</v>
       </c>
       <c r="C24">
-        <f>IF(Attendance!C24="P", 5, IF(Attendance!C24="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!C27="P", 5, IF(Attendance!C27="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="D24">
-        <f>IF(Attendance!D24="P", 5, IF(Attendance!D24="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!D27="P", 5, IF(Attendance!D27="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="E24">
-        <f>IF(Attendance!E24="P", 5, IF(Attendance!E24="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!E27="P", 5, IF(Attendance!E27="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="F24">
-        <f>IF(Attendance!F24="P", 5, IF(Attendance!F24="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!F27="P", 5, IF(Attendance!F27="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="G24">
-        <f>IF(Attendance!G24="P", 5, IF(Attendance!G24="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!G27="P", 5, IF(Attendance!G27="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="H24">
-        <f>IF(Attendance!H24="P", 5, IF(Attendance!H24="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!H27="P", 5, IF(Attendance!H27="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="I24">
-        <f>IF(Attendance!I24="P", 5, IF(Attendance!I24="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!I27="P", 5, IF(Attendance!I27="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="J24">
-        <f>IF(Attendance!J24="P", 5, IF(Attendance!J24="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!J27="P", 5, IF(Attendance!J27="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="K24">
-        <f>IF(Attendance!K24="P", 5, IF(Attendance!K24="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!K27="P", 5, IF(Attendance!K27="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="L24">
-        <f>IF(Attendance!L24="P", 5, IF(Attendance!L24="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!L27="P", 5, IF(Attendance!L27="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="M24">
-        <f>IF(Attendance!M24="P", 5, IF(Attendance!M24="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!M27="P", 5, IF(Attendance!M27="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="N24">
-        <f>IF(Attendance!N24="P", 5, IF(Attendance!N24="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!N27="P", 5, IF(Attendance!N27="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="O24">
-        <f>IF(Attendance!O24="P", 5, IF(Attendance!O24="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!O27="P", 5, IF(Attendance!O27="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="P24">
-        <f>IF(Attendance!P24="P", 5, IF(Attendance!P24="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!P27="P", 5, IF(Attendance!P27="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="Q24">
-        <f>IF(Attendance!Q24="P", 5, IF(Attendance!Q24="O", 3, 0))</f>
+        <f>IF(Attendance!Q27="P", 5, IF(Attendance!Q27="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="R24">
-        <f>IF(Attendance!R24="P", 5, IF(Attendance!R24="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!R27="P", 5, IF(Attendance!R27="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="S24">
-        <f>IF(Attendance!S24="P", 5, IF(Attendance!S24="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!S27="P", 5, IF(Attendance!S27="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="T24">
-        <f>IF(Attendance!T24="P", 5, IF(Attendance!T24="O", 3, 0))</f>
+        <f>IF(Attendance!T27="P", 5, IF(Attendance!T27="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="U24">
-        <f>IF(Attendance!U24="P", 5, IF(Attendance!U24="O", 3, 0))</f>
+        <f>IF(Attendance!U27="P", 5, IF(Attendance!U27="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="V24">
-        <f>IF(Attendance!V24="P", 5, IF(Attendance!V24="O", 3, 0))</f>
+        <f>IF(Attendance!V27="P", 5, IF(Attendance!V27="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="W24">
-        <f>IF(Attendance!W24="P", 5, IF(Attendance!W24="O", 3, 0))</f>
+        <f>IF(Attendance!W27="P", 5, IF(Attendance!W27="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="X24">
-        <f>IF(Attendance!X24="P", 5, IF(Attendance!X24="O", 3, 0))</f>
+        <f>IF(Attendance!X27="P", 5, IF(Attendance!X27="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="Y24">
-        <f>IF(Attendance!Y24="P", 5, IF(Attendance!Y24="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!Y27="P", 5, IF(Attendance!Y27="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="Z24">
-        <f>IF(Attendance!Z24="P", 5, IF(Attendance!Z24="O", 3, 0))</f>
+        <f>IF(Attendance!Z27="P", 5, IF(Attendance!Z27="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AA24">
-        <f>IF(Attendance!AA24="P", 5, IF(Attendance!AA24="O", 3, 0))</f>
+        <f>IF(Attendance!AA27="P", 5, IF(Attendance!AA27="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AB24">
-        <f>IF(Attendance!AB24="P", 5, IF(Attendance!AB24="O", 3, 0))</f>
+        <f>IF(Attendance!AB27="P", 5, IF(Attendance!AB27="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="AC24">
-        <f>IF(Attendance!AC24="P", 5, IF(Attendance!AC24="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AC27="P", 5, IF(Attendance!AC27="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AD24">
-        <f>IF(Attendance!AD24="P", 5, IF(Attendance!AD24="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AD27="P", 5, IF(Attendance!AD27="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AE24">
-        <f>IF(Attendance!AE24="P", 5, IF(Attendance!AE24="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AE27="P", 5, IF(Attendance!AE27="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AF24">
-        <f>IF(Attendance!AF24="P", 5, IF(Attendance!AF24="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AF27="P", 5, IF(Attendance!AF27="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AG24">
-        <f>IF(Attendance!AG24="P", 5, IF(Attendance!AG24="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AG27="P", 5, IF(Attendance!AG27="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AH24">
-        <f>IF(Attendance!AH24="P", 5, IF(Attendance!AH24="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AH27="P", 5, IF(Attendance!AH27="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AI24">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="AJ24">
         <f t="shared" si="1"/>
@@ -9751,147 +10000,154 @@
       </c>
       <c r="AK24">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>2.97</v>
+      </c>
+      <c r="AL24">
+        <v>20</v>
+      </c>
+      <c r="AM24">
+        <f>ROUND(AL24/4, 2)</f>
+        <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
       </c>
       <c r="C25">
-        <f>IF(Attendance!C25="P", 5, IF(Attendance!C25="O", 3, 0))</f>
+        <f>IF(Attendance!C29="P", 5, IF(Attendance!C29="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="D25">
-        <f>IF(Attendance!D25="P", 5, IF(Attendance!D25="O", 3, 0))</f>
+        <f>IF(Attendance!D29="P", 5, IF(Attendance!D29="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="E25">
-        <f>IF(Attendance!E25="P", 5, IF(Attendance!E25="O", 3, 0))</f>
+        <f>IF(Attendance!E29="P", 5, IF(Attendance!E29="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="F25">
-        <f>IF(Attendance!F25="P", 5, IF(Attendance!F25="O", 3, 0))</f>
+        <f>IF(Attendance!F29="P", 5, IF(Attendance!F29="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="G25">
-        <f>IF(Attendance!G25="P", 5, IF(Attendance!G25="O", 3, 0))</f>
+        <f>IF(Attendance!G29="P", 5, IF(Attendance!G29="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="H25">
-        <f>IF(Attendance!H25="P", 5, IF(Attendance!H25="O", 3, 0))</f>
+        <f>IF(Attendance!H29="P", 5, IF(Attendance!H29="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="I25">
-        <f>IF(Attendance!I25="P", 5, IF(Attendance!I25="O", 3, 0))</f>
+        <f>IF(Attendance!I29="P", 5, IF(Attendance!I29="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="J25">
-        <f>IF(Attendance!J25="P", 5, IF(Attendance!J25="O", 3, 0))</f>
+        <f>IF(Attendance!J29="P", 5, IF(Attendance!J29="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="K25">
-        <f>IF(Attendance!K25="P", 5, IF(Attendance!K25="O", 3, 0))</f>
+        <f>IF(Attendance!K29="P", 5, IF(Attendance!K29="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="L25">
-        <f>IF(Attendance!L25="P", 5, IF(Attendance!L25="O", 3, 0))</f>
+        <f>IF(Attendance!L29="P", 5, IF(Attendance!L29="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="M25">
-        <f>IF(Attendance!M25="P", 5, IF(Attendance!M25="O", 3, 0))</f>
+        <f>IF(Attendance!M29="P", 5, IF(Attendance!M29="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="N25">
-        <f>IF(Attendance!N25="P", 5, IF(Attendance!N25="O", 3, 0))</f>
+        <f>IF(Attendance!N29="P", 5, IF(Attendance!N29="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="O25">
-        <f>IF(Attendance!O25="P", 5, IF(Attendance!O25="O", 3, 0))</f>
+        <f>IF(Attendance!O29="P", 5, IF(Attendance!O29="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="P25">
-        <f>IF(Attendance!P25="P", 5, IF(Attendance!P25="O", 3, 0))</f>
+        <f>IF(Attendance!P29="P", 5, IF(Attendance!P29="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="Q25">
-        <f>IF(Attendance!Q25="P", 5, IF(Attendance!Q25="O", 3, 0))</f>
+        <f>IF(Attendance!Q29="P", 5, IF(Attendance!Q29="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="R25">
-        <f>IF(Attendance!R25="P", 5, IF(Attendance!R25="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!R29="P", 5, IF(Attendance!R29="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="S25">
-        <f>IF(Attendance!S25="P", 5, IF(Attendance!S25="O", 3, 0))</f>
+        <f>IF(Attendance!S29="P", 5, IF(Attendance!S29="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="T25">
-        <f>IF(Attendance!T25="P", 5, IF(Attendance!T25="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!T29="P", 5, IF(Attendance!T29="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="U25">
-        <f>IF(Attendance!U25="P", 5, IF(Attendance!U25="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!U29="P", 5, IF(Attendance!U29="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="V25">
-        <f>IF(Attendance!V25="P", 5, IF(Attendance!V25="O", 3, 0))</f>
+        <f>IF(Attendance!V29="P", 5, IF(Attendance!V29="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="W25">
-        <f>IF(Attendance!W25="P", 5, IF(Attendance!W25="O", 3, 0))</f>
+        <f>IF(Attendance!W29="P", 5, IF(Attendance!W29="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="X25">
-        <f>IF(Attendance!X25="P", 5, IF(Attendance!X25="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!X29="P", 5, IF(Attendance!X29="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="Y25">
-        <f>IF(Attendance!Y25="P", 5, IF(Attendance!Y25="O", 3, 0))</f>
+        <f>IF(Attendance!Y29="P", 5, IF(Attendance!Y29="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="Z25">
-        <f>IF(Attendance!Z25="P", 5, IF(Attendance!Z25="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!Z29="P", 5, IF(Attendance!Z29="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AA25">
-        <f>IF(Attendance!AA25="P", 5, IF(Attendance!AA25="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AA29="P", 5, IF(Attendance!AA29="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AB25">
-        <f>IF(Attendance!AB25="P", 5, IF(Attendance!AB25="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AB29="P", 5, IF(Attendance!AB29="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AC25">
-        <f>IF(Attendance!AC25="P", 5, IF(Attendance!AC25="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AC29="P", 5, IF(Attendance!AC29="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AD25">
-        <f>IF(Attendance!AD25="P", 5, IF(Attendance!AD25="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AD29="P", 5, IF(Attendance!AD29="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AE25">
-        <f>IF(Attendance!AE25="P", 5, IF(Attendance!AE25="O", 3, 0))</f>
+        <f>IF(Attendance!AE29="P", 5, IF(Attendance!AE29="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="AF25">
-        <f>IF(Attendance!AF25="P", 5, IF(Attendance!AF25="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AF29="P", 5, IF(Attendance!AF29="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AG25">
-        <f>IF(Attendance!AG25="P", 5, IF(Attendance!AG25="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AG29="P", 5, IF(Attendance!AG29="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AH25">
-        <f>IF(Attendance!AH25="P", 5, IF(Attendance!AH25="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AH29="P", 5, IF(Attendance!AH29="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AI25">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="AJ25">
         <f t="shared" si="1"/>
@@ -9899,147 +10155,154 @@
       </c>
       <c r="AK25">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AL25">
+        <v>10</v>
+      </c>
+      <c r="AM25">
+        <f>ROUND(AL25/4, 2)</f>
+        <v>2.5</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
       </c>
       <c r="C26">
-        <f>IF(Attendance!C26="P", 5, IF(Attendance!C26="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!C30="P", 5, IF(Attendance!C30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="D26">
-        <f>IF(Attendance!D26="P", 5, IF(Attendance!D26="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!D30="P", 5, IF(Attendance!D30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="E26">
-        <f>IF(Attendance!E26="P", 5, IF(Attendance!E26="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!E30="P", 5, IF(Attendance!E30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="F26">
-        <f>IF(Attendance!F26="P", 5, IF(Attendance!F26="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!F30="P", 5, IF(Attendance!F30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="G26">
-        <f>IF(Attendance!G26="P", 5, IF(Attendance!G26="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!G30="P", 5, IF(Attendance!G30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="H26">
-        <f>IF(Attendance!H26="P", 5, IF(Attendance!H26="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!H30="P", 5, IF(Attendance!H30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="I26">
-        <f>IF(Attendance!I26="P", 5, IF(Attendance!I26="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!I30="P", 5, IF(Attendance!I30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="J26">
-        <f>IF(Attendance!J26="P", 5, IF(Attendance!J26="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!J30="P", 5, IF(Attendance!J30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="K26">
-        <f>IF(Attendance!K26="P", 5, IF(Attendance!K26="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!K30="P", 5, IF(Attendance!K30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="L26">
-        <f>IF(Attendance!L26="P", 5, IF(Attendance!L26="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!L30="P", 5, IF(Attendance!L30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="M26">
-        <f>IF(Attendance!M26="P", 5, IF(Attendance!M26="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!M30="P", 5, IF(Attendance!M30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="N26">
-        <f>IF(Attendance!N26="P", 5, IF(Attendance!N26="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!N30="P", 5, IF(Attendance!N30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="O26">
-        <f>IF(Attendance!O26="P", 5, IF(Attendance!O26="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!O30="P", 5, IF(Attendance!O30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="P26">
-        <f>IF(Attendance!P26="P", 5, IF(Attendance!P26="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!P30="P", 5, IF(Attendance!P30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <f>IF(Attendance!Q26="P", 5, IF(Attendance!Q26="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!Q30="P", 5, IF(Attendance!Q30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="R26">
-        <f>IF(Attendance!R26="P", 5, IF(Attendance!R26="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!R30="P", 5, IF(Attendance!R30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="S26">
-        <f>IF(Attendance!S26="P", 5, IF(Attendance!S26="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!S30="P", 5, IF(Attendance!S30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="T26">
-        <f>IF(Attendance!T26="P", 5, IF(Attendance!T26="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!T30="P", 5, IF(Attendance!T30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="U26">
-        <f>IF(Attendance!U26="P", 5, IF(Attendance!U26="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!U30="P", 5, IF(Attendance!U30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="V26">
-        <f>IF(Attendance!V26="P", 5, IF(Attendance!V26="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!V30="P", 5, IF(Attendance!V30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="W26">
-        <f>IF(Attendance!W26="P", 5, IF(Attendance!W26="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!W30="P", 5, IF(Attendance!W30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="X26">
-        <f>IF(Attendance!X26="P", 5, IF(Attendance!X26="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!X30="P", 5, IF(Attendance!X30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="Y26">
-        <f>IF(Attendance!Y26="P", 5, IF(Attendance!Y26="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!Y30="P", 5, IF(Attendance!Y30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <f>IF(Attendance!Z26="P", 5, IF(Attendance!Z26="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!Z30="P", 5, IF(Attendance!Z30="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <f>IF(Attendance!AA26="P", 5, IF(Attendance!AA26="O", 3, 0))</f>
+        <f>IF(Attendance!AA30="P", 5, IF(Attendance!AA30="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AB26">
-        <f>IF(Attendance!AB26="P", 5, IF(Attendance!AB26="O", 3, 0))</f>
+        <f>IF(Attendance!AB30="P", 5, IF(Attendance!AB30="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AC26">
-        <f>IF(Attendance!AC26="P", 5, IF(Attendance!AC26="O", 3, 0))</f>
+        <f>IF(Attendance!AC30="P", 5, IF(Attendance!AC30="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AD26">
-        <f>IF(Attendance!AD26="P", 5, IF(Attendance!AD26="O", 3, 0))</f>
+        <f>IF(Attendance!AD30="P", 5, IF(Attendance!AD30="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AE26">
-        <f>IF(Attendance!AE26="P", 5, IF(Attendance!AE26="O", 3, 0))</f>
+        <f>IF(Attendance!AE30="P", 5, IF(Attendance!AE30="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="AF26">
-        <f>IF(Attendance!AF26="P", 5, IF(Attendance!AF26="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AF30="P", 5, IF(Attendance!AF30="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AG26">
-        <f>IF(Attendance!AG26="P", 5, IF(Attendance!AG26="O", 3, 0))</f>
+        <f>IF(Attendance!AG30="P", 5, IF(Attendance!AG30="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AH26">
-        <f>IF(Attendance!AH26="P", 5, IF(Attendance!AH26="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AH30="P", 5, IF(Attendance!AH30="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AI26">
         <f t="shared" si="0"/>
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="AJ26">
         <f t="shared" si="1"/>
@@ -10047,147 +10310,154 @@
       </c>
       <c r="AK26">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>0.72</v>
+      </c>
+      <c r="AL26">
+        <v>6</v>
+      </c>
+      <c r="AM26">
+        <f t="shared" ref="AM26:AM27" si="8">ROUND(AL26/4, 2)</f>
+        <v>1.5</v>
       </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="B27" t="s">
         <v>34</v>
       </c>
       <c r="C27">
-        <f>IF(Attendance!C27="P", 5, IF(Attendance!C27="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!C31="P", 5, IF(Attendance!C31="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="D27">
-        <f>IF(Attendance!D27="P", 5, IF(Attendance!D27="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!D31="P", 5, IF(Attendance!D31="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="E27">
-        <f>IF(Attendance!E27="P", 5, IF(Attendance!E27="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!E31="P", 5, IF(Attendance!E31="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="F27">
-        <f>IF(Attendance!F27="P", 5, IF(Attendance!F27="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!F31="P", 5, IF(Attendance!F31="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="G27">
-        <f>IF(Attendance!G27="P", 5, IF(Attendance!G27="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!G31="P", 5, IF(Attendance!G31="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="H27">
-        <f>IF(Attendance!H27="P", 5, IF(Attendance!H27="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!H31="P", 5, IF(Attendance!H31="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="I27">
-        <f>IF(Attendance!I27="P", 5, IF(Attendance!I27="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!I31="P", 5, IF(Attendance!I31="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="J27">
-        <f>IF(Attendance!J27="P", 5, IF(Attendance!J27="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!J31="P", 5, IF(Attendance!J31="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="K27">
-        <f>IF(Attendance!K27="P", 5, IF(Attendance!K27="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!K31="P", 5, IF(Attendance!K31="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="L27">
-        <f>IF(Attendance!L27="P", 5, IF(Attendance!L27="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!L31="P", 5, IF(Attendance!L31="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="M27">
-        <f>IF(Attendance!M27="P", 5, IF(Attendance!M27="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!M31="P", 5, IF(Attendance!M31="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="N27">
-        <f>IF(Attendance!N27="P", 5, IF(Attendance!N27="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!N31="P", 5, IF(Attendance!N31="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="O27">
-        <f>IF(Attendance!O27="P", 5, IF(Attendance!O27="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!O31="P", 5, IF(Attendance!O31="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="P27">
-        <f>IF(Attendance!P27="P", 5, IF(Attendance!P27="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!P31="P", 5, IF(Attendance!P31="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <f>IF(Attendance!Q27="P", 5, IF(Attendance!Q27="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!Q31="P", 5, IF(Attendance!Q31="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="R27">
-        <f>IF(Attendance!R27="P", 5, IF(Attendance!R27="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!R31="P", 5, IF(Attendance!R31="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="S27">
-        <f>IF(Attendance!S27="P", 5, IF(Attendance!S27="O", 3, 0))</f>
+        <f>IF(Attendance!S31="P", 5, IF(Attendance!S31="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="T27">
-        <f>IF(Attendance!T27="P", 5, IF(Attendance!T27="O", 3, 0))</f>
+        <f>IF(Attendance!T31="P", 5, IF(Attendance!T31="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="U27">
-        <f>IF(Attendance!U27="P", 5, IF(Attendance!U27="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!U31="P", 5, IF(Attendance!U31="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="V27">
-        <f>IF(Attendance!V27="P", 5, IF(Attendance!V27="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!V31="P", 5, IF(Attendance!V31="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="W27">
-        <f>IF(Attendance!W27="P", 5, IF(Attendance!W27="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!W31="P", 5, IF(Attendance!W31="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="X27">
-        <f>IF(Attendance!X27="P", 5, IF(Attendance!X27="O", 3, 0))</f>
+        <f>IF(Attendance!X31="P", 5, IF(Attendance!X31="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="Y27">
-        <f>IF(Attendance!Y27="P", 5, IF(Attendance!Y27="O", 3, 0))</f>
+        <f>IF(Attendance!Y31="P", 5, IF(Attendance!Y31="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="Z27">
-        <f>IF(Attendance!Z27="P", 5, IF(Attendance!Z27="O", 3, 0))</f>
+        <f>IF(Attendance!Z31="P", 5, IF(Attendance!Z31="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AA27">
-        <f>IF(Attendance!AA27="P", 5, IF(Attendance!AA27="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AA31="P", 5, IF(Attendance!AA31="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AB27">
-        <f>IF(Attendance!AB27="P", 5, IF(Attendance!AB27="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AB31="P", 5, IF(Attendance!AB31="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AC27">
-        <f>IF(Attendance!AC27="P", 5, IF(Attendance!AC27="O", 3, 0))</f>
+        <f>IF(Attendance!AC31="P", 5, IF(Attendance!AC31="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AD27">
-        <f>IF(Attendance!AD27="P", 5, IF(Attendance!AD27="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AD31="P", 5, IF(Attendance!AD31="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <f>IF(Attendance!AE27="P", 5, IF(Attendance!AE27="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AE31="P", 5, IF(Attendance!AE31="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <f>IF(Attendance!AF27="P", 5, IF(Attendance!AF27="O", 3, 0))</f>
+        <f>IF(Attendance!AF31="P", 5, IF(Attendance!AF31="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AG27">
-        <f>IF(Attendance!AG27="P", 5, IF(Attendance!AG27="O", 3, 0))</f>
+        <f>IF(Attendance!AG31="P", 5, IF(Attendance!AG31="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AH27">
-        <f>IF(Attendance!AH27="P", 5, IF(Attendance!AH27="O", 3, 0))</f>
+        <f>IF(Attendance!AH31="P", 5, IF(Attendance!AH31="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AI27">
         <f t="shared" si="0"/>
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AJ27">
         <f t="shared" si="1"/>
@@ -10195,147 +10465,154 @@
       </c>
       <c r="AK27">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>1.88</v>
+      </c>
+      <c r="AL27">
+        <v>16</v>
+      </c>
+      <c r="AM27">
+        <f t="shared" si="8"/>
+        <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C28">
-        <f>IF(Attendance!C28="P", 5, IF(Attendance!C28="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!C32="P", 5, IF(Attendance!C32="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="D28">
-        <f>IF(Attendance!D28="P", 5, IF(Attendance!D28="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!D32="P", 5, IF(Attendance!D32="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="E28">
-        <f>IF(Attendance!E28="P", 5, IF(Attendance!E28="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!E32="P", 5, IF(Attendance!E32="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="F28">
-        <f>IF(Attendance!F28="P", 5, IF(Attendance!F28="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!F32="P", 5, IF(Attendance!F32="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="G28">
-        <f>IF(Attendance!G28="P", 5, IF(Attendance!G28="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!G32="P", 5, IF(Attendance!G32="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="H28">
-        <f>IF(Attendance!H28="P", 5, IF(Attendance!H28="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!H32="P", 5, IF(Attendance!H32="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="I28">
-        <f>IF(Attendance!I28="P", 5, IF(Attendance!I28="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!I32="P", 5, IF(Attendance!I32="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="J28">
-        <f>IF(Attendance!J28="P", 5, IF(Attendance!J28="O", 3, 0))</f>
+        <f>IF(Attendance!J32="P", 5, IF(Attendance!J32="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="K28">
-        <f>IF(Attendance!K28="P", 5, IF(Attendance!K28="O", 3, 0))</f>
+        <f>IF(Attendance!K32="P", 5, IF(Attendance!K32="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="L28">
-        <f>IF(Attendance!L28="P", 5, IF(Attendance!L28="O", 3, 0))</f>
+        <f>IF(Attendance!L32="P", 5, IF(Attendance!L32="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="M28">
-        <f>IF(Attendance!M28="P", 5, IF(Attendance!M28="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!M32="P", 5, IF(Attendance!M32="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="N28">
-        <f>IF(Attendance!N28="P", 5, IF(Attendance!N28="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!N32="P", 5, IF(Attendance!N32="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="O28">
-        <f>IF(Attendance!O28="P", 5, IF(Attendance!O28="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!O32="P", 5, IF(Attendance!O32="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="P28">
-        <f>IF(Attendance!P28="P", 5, IF(Attendance!P28="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!P32="P", 5, IF(Attendance!P32="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="Q28">
-        <f>IF(Attendance!Q28="P", 5, IF(Attendance!Q28="O", 3, 0))</f>
+        <f>IF(Attendance!Q32="P", 5, IF(Attendance!Q32="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="R28">
-        <f>IF(Attendance!R28="P", 5, IF(Attendance!R28="O", 3, 0))</f>
+        <f>IF(Attendance!R32="P", 5, IF(Attendance!R32="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="S28">
-        <f>IF(Attendance!S28="P", 5, IF(Attendance!S28="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!S32="P", 5, IF(Attendance!S32="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="T28">
-        <f>IF(Attendance!T28="P", 5, IF(Attendance!T28="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!T32="P", 5, IF(Attendance!T32="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="U28">
-        <f>IF(Attendance!U28="P", 5, IF(Attendance!U28="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!U32="P", 5, IF(Attendance!U32="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="V28">
-        <f>IF(Attendance!V28="P", 5, IF(Attendance!V28="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!V32="P", 5, IF(Attendance!V32="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="W28">
-        <f>IF(Attendance!W28="P", 5, IF(Attendance!W28="O", 3, 0))</f>
+        <f>IF(Attendance!W32="P", 5, IF(Attendance!W32="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="X28">
-        <f>IF(Attendance!X28="P", 5, IF(Attendance!X28="O", 3, 0))</f>
+        <f>IF(Attendance!X32="P", 5, IF(Attendance!X32="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="Y28">
-        <f>IF(Attendance!Y28="P", 5, IF(Attendance!Y28="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!Y32="P", 5, IF(Attendance!Y32="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="Z28">
-        <f>IF(Attendance!Z28="P", 5, IF(Attendance!Z28="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!Z32="P", 5, IF(Attendance!Z32="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AA28">
-        <f>IF(Attendance!AA28="P", 5, IF(Attendance!AA28="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AA32="P", 5, IF(Attendance!AA32="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AB28">
-        <f>IF(Attendance!AB28="P", 5, IF(Attendance!AB28="O", 3, 0))</f>
+        <f>IF(Attendance!AB32="P", 5, IF(Attendance!AB32="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="AC28">
-        <f>IF(Attendance!AC28="P", 5, IF(Attendance!AC28="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AC32="P", 5, IF(Attendance!AC32="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <f>IF(Attendance!AD28="P", 5, IF(Attendance!AD28="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AD32="P", 5, IF(Attendance!AD32="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <f>IF(Attendance!AE28="P", 5, IF(Attendance!AE28="O", 3, 0))</f>
+        <f>IF(Attendance!AE32="P", 5, IF(Attendance!AE32="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AF28">
-        <f>IF(Attendance!AF28="P", 5, IF(Attendance!AF28="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AF32="P", 5, IF(Attendance!AF32="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <f>IF(Attendance!AG28="P", 5, IF(Attendance!AG28="O", 3, 0))</f>
+        <f>IF(Attendance!AG32="P", 5, IF(Attendance!AG32="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AH28">
-        <f>IF(Attendance!AH28="P", 5, IF(Attendance!AH28="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AH32="P", 5, IF(Attendance!AH32="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AI28">
         <f t="shared" si="0"/>
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AJ28">
         <f t="shared" si="1"/>
@@ -10343,147 +10620,150 @@
       </c>
       <c r="AK28">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>2.38</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="B29" t="s">
         <v>34</v>
       </c>
       <c r="C29">
-        <f>IF(Attendance!C29="P", 5, IF(Attendance!C29="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!C33="P", 5, IF(Attendance!C33="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="D29">
-        <f>IF(Attendance!D29="P", 5, IF(Attendance!D29="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!D33="P", 5, IF(Attendance!D33="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="E29">
-        <f>IF(Attendance!E29="P", 5, IF(Attendance!E29="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!E33="P", 5, IF(Attendance!E33="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="F29">
-        <f>IF(Attendance!F29="P", 5, IF(Attendance!F29="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!F33="P", 5, IF(Attendance!F33="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="G29">
-        <f>IF(Attendance!G29="P", 5, IF(Attendance!G29="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!G33="P", 5, IF(Attendance!G33="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="H29">
-        <f>IF(Attendance!H29="P", 5, IF(Attendance!H29="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!H33="P", 5, IF(Attendance!H33="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="I29">
-        <f>IF(Attendance!I29="P", 5, IF(Attendance!I29="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!I33="P", 5, IF(Attendance!I33="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="J29">
-        <f>IF(Attendance!J29="P", 5, IF(Attendance!J29="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!J33="P", 5, IF(Attendance!J33="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="K29">
-        <f>IF(Attendance!K29="P", 5, IF(Attendance!K29="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!K33="P", 5, IF(Attendance!K33="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="L29">
-        <f>IF(Attendance!L29="P", 5, IF(Attendance!L29="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!L33="P", 5, IF(Attendance!L33="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="M29">
-        <f>IF(Attendance!M29="P", 5, IF(Attendance!M29="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!M33="P", 5, IF(Attendance!M33="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="N29">
-        <f>IF(Attendance!N29="P", 5, IF(Attendance!N29="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!N33="P", 5, IF(Attendance!N33="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="O29">
-        <f>IF(Attendance!O29="P", 5, IF(Attendance!O29="O", 3, 0))</f>
+        <f>IF(Attendance!O33="P", 5, IF(Attendance!O33="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="P29">
-        <f>IF(Attendance!P29="P", 5, IF(Attendance!P29="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!P33="P", 5, IF(Attendance!P33="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="Q29">
-        <f>IF(Attendance!Q29="P", 5, IF(Attendance!Q29="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!Q33="P", 5, IF(Attendance!Q33="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="R29">
-        <f>IF(Attendance!R29="P", 5, IF(Attendance!R29="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!R33="P", 5, IF(Attendance!R33="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="S29">
-        <f>IF(Attendance!S29="P", 5, IF(Attendance!S29="O", 3, 0))</f>
+        <f>IF(Attendance!S33="P", 5, IF(Attendance!S33="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="T29">
-        <f>IF(Attendance!T29="P", 5, IF(Attendance!T29="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!T33="P", 5, IF(Attendance!T33="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="U29">
-        <f>IF(Attendance!U29="P", 5, IF(Attendance!U29="O", 3, 0))</f>
+        <f>IF(Attendance!U33="P", 5, IF(Attendance!U33="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="V29">
-        <f>IF(Attendance!V29="P", 5, IF(Attendance!V29="O", 3, 0))</f>
+        <f>IF(Attendance!V33="P", 5, IF(Attendance!V33="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="W29">
-        <f>IF(Attendance!W29="P", 5, IF(Attendance!W29="O", 3, 0))</f>
+        <f>IF(Attendance!W33="P", 5, IF(Attendance!W33="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="X29">
-        <f>IF(Attendance!X29="P", 5, IF(Attendance!X29="O", 3, 0))</f>
+        <f>IF(Attendance!X33="P", 5, IF(Attendance!X33="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="Y29">
-        <f>IF(Attendance!Y29="P", 5, IF(Attendance!Y29="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!Y33="P", 5, IF(Attendance!Y33="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="Z29">
-        <f>IF(Attendance!Z29="P", 5, IF(Attendance!Z29="O", 3, 0))</f>
+        <f>IF(Attendance!Z33="P", 5, IF(Attendance!Z33="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AA29">
-        <f>IF(Attendance!AA29="P", 5, IF(Attendance!AA29="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AA33="P", 5, IF(Attendance!AA33="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AB29">
-        <f>IF(Attendance!AB29="P", 5, IF(Attendance!AB29="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AB33="P", 5, IF(Attendance!AB33="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AC29">
-        <f>IF(Attendance!AC29="P", 5, IF(Attendance!AC29="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AC33="P", 5, IF(Attendance!AC33="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <f>IF(Attendance!AD29="P", 5, IF(Attendance!AD29="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AD33="P", 5, IF(Attendance!AD33="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AE29">
-        <f>IF(Attendance!AE29="P", 5, IF(Attendance!AE29="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AE33="P", 5, IF(Attendance!AE33="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AF29">
-        <f>IF(Attendance!AF29="P", 5, IF(Attendance!AF29="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AF33="P", 5, IF(Attendance!AF33="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AG29">
-        <f>IF(Attendance!AG29="P", 5, IF(Attendance!AG29="O", 3, 0))</f>
+        <f>IF(Attendance!AG33="P", 5, IF(Attendance!AG33="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="AH29">
-        <f>IF(Attendance!AH29="P", 5, IF(Attendance!AH29="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AH33="P", 5, IF(Attendance!AH33="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AI29">
         <f t="shared" si="0"/>
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AJ29">
         <f t="shared" si="1"/>
@@ -10491,147 +10771,150 @@
       </c>
       <c r="AK29">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>3.13</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="B30" t="s">
         <v>34</v>
       </c>
       <c r="C30">
-        <f>IF(Attendance!C30="P", 5, IF(Attendance!C30="O", 3, 0))</f>
+        <f>IF(Attendance!C34="P", 5, IF(Attendance!C34="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="D30">
-        <f>IF(Attendance!D30="P", 5, IF(Attendance!D30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!D34="P", 5, IF(Attendance!D34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="E30">
-        <f>IF(Attendance!E30="P", 5, IF(Attendance!E30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!E34="P", 5, IF(Attendance!E34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="F30">
-        <f>IF(Attendance!F30="P", 5, IF(Attendance!F30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!F34="P", 5, IF(Attendance!F34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="G30">
-        <f>IF(Attendance!G30="P", 5, IF(Attendance!G30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!G34="P", 5, IF(Attendance!G34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="H30">
-        <f>IF(Attendance!H30="P", 5, IF(Attendance!H30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!H34="P", 5, IF(Attendance!H34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="I30">
-        <f>IF(Attendance!I30="P", 5, IF(Attendance!I30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!I34="P", 5, IF(Attendance!I34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="J30">
-        <f>IF(Attendance!J30="P", 5, IF(Attendance!J30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!J34="P", 5, IF(Attendance!J34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="K30">
-        <f>IF(Attendance!K30="P", 5, IF(Attendance!K30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!K34="P", 5, IF(Attendance!K34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="L30">
-        <f>IF(Attendance!L30="P", 5, IF(Attendance!L30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!L34="P", 5, IF(Attendance!L34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="M30">
-        <f>IF(Attendance!M30="P", 5, IF(Attendance!M30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!M34="P", 5, IF(Attendance!M34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="N30">
-        <f>IF(Attendance!N30="P", 5, IF(Attendance!N30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!N34="P", 5, IF(Attendance!N34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="O30">
-        <f>IF(Attendance!O30="P", 5, IF(Attendance!O30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!O34="P", 5, IF(Attendance!O34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="P30">
-        <f>IF(Attendance!P30="P", 5, IF(Attendance!P30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!P34="P", 5, IF(Attendance!P34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="Q30">
-        <f>IF(Attendance!Q30="P", 5, IF(Attendance!Q30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!Q34="P", 5, IF(Attendance!Q34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="R30">
-        <f>IF(Attendance!R30="P", 5, IF(Attendance!R30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!R34="P", 5, IF(Attendance!R34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="S30">
-        <f>IF(Attendance!S30="P", 5, IF(Attendance!S30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!S34="P", 5, IF(Attendance!S34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="T30">
-        <f>IF(Attendance!T30="P", 5, IF(Attendance!T30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!T34="P", 5, IF(Attendance!T34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="U30">
-        <f>IF(Attendance!U30="P", 5, IF(Attendance!U30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!U34="P", 5, IF(Attendance!U34="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="V30">
-        <f>IF(Attendance!V30="P", 5, IF(Attendance!V30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!V34="P", 5, IF(Attendance!V34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="W30">
-        <f>IF(Attendance!W30="P", 5, IF(Attendance!W30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!W34="P", 5, IF(Attendance!W34="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="X30">
-        <f>IF(Attendance!X30="P", 5, IF(Attendance!X30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!X34="P", 5, IF(Attendance!X34="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="Y30">
-        <f>IF(Attendance!Y30="P", 5, IF(Attendance!Y30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!Y34="P", 5, IF(Attendance!Y34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="Z30">
-        <f>IF(Attendance!Z30="P", 5, IF(Attendance!Z30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!Z34="P", 5, IF(Attendance!Z34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AA30">
-        <f>IF(Attendance!AA30="P", 5, IF(Attendance!AA30="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AA34="P", 5, IF(Attendance!AA34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AB30">
-        <f>IF(Attendance!AB30="P", 5, IF(Attendance!AB30="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AB34="P", 5, IF(Attendance!AB34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AC30">
-        <f>IF(Attendance!AC30="P", 5, IF(Attendance!AC30="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AC34="P", 5, IF(Attendance!AC34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AD30">
-        <f>IF(Attendance!AD30="P", 5, IF(Attendance!AD30="O", 3, 0))</f>
+        <f>IF(Attendance!AD34="P", 5, IF(Attendance!AD34="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AE30">
-        <f>IF(Attendance!AE30="P", 5, IF(Attendance!AE30="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AE34="P", 5, IF(Attendance!AE34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AF30">
-        <f>IF(Attendance!AF30="P", 5, IF(Attendance!AF30="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AF34="P", 5, IF(Attendance!AF34="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AG30">
-        <f>IF(Attendance!AG30="P", 5, IF(Attendance!AG30="O", 3, 0))</f>
+        <f>IF(Attendance!AG34="P", 5, IF(Attendance!AG34="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AH30">
-        <f>IF(Attendance!AH30="P", 5, IF(Attendance!AH30="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AH34="P", 5, IF(Attendance!AH34="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AI30">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="AJ30">
         <f t="shared" si="1"/>
@@ -10639,147 +10922,150 @@
       </c>
       <c r="AK30">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>4.47</v>
+      </c>
+      <c r="AM30">
+        <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
       </c>
       <c r="C31">
-        <f>IF(Attendance!C31="P", 5, IF(Attendance!C31="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!C35="P", 5, IF(Attendance!C35="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="D31">
-        <f>IF(Attendance!D31="P", 5, IF(Attendance!D31="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!D35="P", 5, IF(Attendance!D35="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="E31">
-        <f>IF(Attendance!E31="P", 5, IF(Attendance!E31="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!E35="P", 5, IF(Attendance!E35="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="F31">
-        <f>IF(Attendance!F31="P", 5, IF(Attendance!F31="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!F35="P", 5, IF(Attendance!F35="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="G31">
-        <f>IF(Attendance!G31="P", 5, IF(Attendance!G31="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!G35="P", 5, IF(Attendance!G35="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="H31">
-        <f>IF(Attendance!H31="P", 5, IF(Attendance!H31="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!H35="P", 5, IF(Attendance!H35="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="I31">
-        <f>IF(Attendance!I31="P", 5, IF(Attendance!I31="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!I35="P", 5, IF(Attendance!I35="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="J31">
-        <f>IF(Attendance!J31="P", 5, IF(Attendance!J31="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!J35="P", 5, IF(Attendance!J35="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="K31">
-        <f>IF(Attendance!K31="P", 5, IF(Attendance!K31="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!K35="P", 5, IF(Attendance!K35="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="L31">
-        <f>IF(Attendance!L31="P", 5, IF(Attendance!L31="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!L35="P", 5, IF(Attendance!L35="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="M31">
-        <f>IF(Attendance!M31="P", 5, IF(Attendance!M31="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!M35="P", 5, IF(Attendance!M35="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="N31">
-        <f>IF(Attendance!N31="P", 5, IF(Attendance!N31="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!N35="P", 5, IF(Attendance!N35="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="O31">
-        <f>IF(Attendance!O31="P", 5, IF(Attendance!O31="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!O35="P", 5, IF(Attendance!O35="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="P31">
-        <f>IF(Attendance!P31="P", 5, IF(Attendance!P31="O", 3, 0))</f>
+        <f>IF(Attendance!P35="P", 5, IF(Attendance!P35="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="Q31">
-        <f>IF(Attendance!Q31="P", 5, IF(Attendance!Q31="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!Q35="P", 5, IF(Attendance!Q35="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="R31">
-        <f>IF(Attendance!R31="P", 5, IF(Attendance!R31="O", 3, 0))</f>
+        <f>IF(Attendance!R35="P", 5, IF(Attendance!R35="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="S31">
-        <f>IF(Attendance!S31="P", 5, IF(Attendance!S31="O", 3, 0))</f>
+        <f>IF(Attendance!S35="P", 5, IF(Attendance!S35="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="T31">
-        <f>IF(Attendance!T31="P", 5, IF(Attendance!T31="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!T35="P", 5, IF(Attendance!T35="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="U31">
-        <f>IF(Attendance!U31="P", 5, IF(Attendance!U31="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!U35="P", 5, IF(Attendance!U35="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="V31">
-        <f>IF(Attendance!V31="P", 5, IF(Attendance!V31="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!V35="P", 5, IF(Attendance!V35="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="W31">
-        <f>IF(Attendance!W31="P", 5, IF(Attendance!W31="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!W35="P", 5, IF(Attendance!W35="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="X31">
-        <f>IF(Attendance!X31="P", 5, IF(Attendance!X31="O", 3, 0))</f>
+        <f>IF(Attendance!X35="P", 5, IF(Attendance!X35="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="Y31">
-        <f>IF(Attendance!Y31="P", 5, IF(Attendance!Y31="O", 3, 0))</f>
+        <f>IF(Attendance!Y35="P", 5, IF(Attendance!Y35="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="Z31">
-        <f>IF(Attendance!Z31="P", 5, IF(Attendance!Z31="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!Z35="P", 5, IF(Attendance!Z35="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AA31">
-        <f>IF(Attendance!AA31="P", 5, IF(Attendance!AA31="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AA35="P", 5, IF(Attendance!AA35="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AB31">
-        <f>IF(Attendance!AB31="P", 5, IF(Attendance!AB31="O", 3, 0))</f>
+        <f>IF(Attendance!AB35="P", 5, IF(Attendance!AB35="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AC31">
-        <f>IF(Attendance!AC31="P", 5, IF(Attendance!AC31="O", 3, 0))</f>
+        <f>IF(Attendance!AC35="P", 5, IF(Attendance!AC35="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AD31">
-        <f>IF(Attendance!AD31="P", 5, IF(Attendance!AD31="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AD35="P", 5, IF(Attendance!AD35="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AE31">
-        <f>IF(Attendance!AE31="P", 5, IF(Attendance!AE31="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AE35="P", 5, IF(Attendance!AE35="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AF31">
-        <f>IF(Attendance!AF31="P", 5, IF(Attendance!AF31="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AF35="P", 5, IF(Attendance!AF35="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AG31">
-        <f>IF(Attendance!AG31="P", 5, IF(Attendance!AG31="O", 3, 0))</f>
+        <f>IF(Attendance!AG35="P", 5, IF(Attendance!AG35="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AH31">
-        <f>IF(Attendance!AH31="P", 5, IF(Attendance!AH31="O", 3, 0))</f>
+        <f>IF(Attendance!AH35="P", 5, IF(Attendance!AH35="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AI31">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="AJ31">
         <f t="shared" si="1"/>
@@ -10787,147 +11073,154 @@
       </c>
       <c r="AK31">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>3.69</v>
+      </c>
+      <c r="AL31">
+        <v>16</v>
+      </c>
+      <c r="AM31">
+        <f t="shared" ref="AM31:AM32" si="9">ROUND(AL31/4, 2)</f>
+        <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B32" t="s">
         <v>34</v>
       </c>
       <c r="C32">
-        <f>IF(Attendance!C32="P", 5, IF(Attendance!C32="O", 3, 0))</f>
+        <f>IF(Attendance!C37="P", 5, IF(Attendance!C37="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="D32">
-        <f>IF(Attendance!D32="P", 5, IF(Attendance!D32="O", 3, 0))</f>
+        <f>IF(Attendance!D37="P", 5, IF(Attendance!D37="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="E32">
-        <f>IF(Attendance!E32="P", 5, IF(Attendance!E32="O", 3, 0))</f>
+        <f>IF(Attendance!E37="P", 5, IF(Attendance!E37="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="F32">
-        <f>IF(Attendance!F32="P", 5, IF(Attendance!F32="O", 3, 0))</f>
+        <f>IF(Attendance!F37="P", 5, IF(Attendance!F37="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="G32">
-        <f>IF(Attendance!G32="P", 5, IF(Attendance!G32="O", 3, 0))</f>
+        <f>IF(Attendance!G37="P", 5, IF(Attendance!G37="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="H32">
-        <f>IF(Attendance!H32="P", 5, IF(Attendance!H32="O", 3, 0))</f>
+        <f>IF(Attendance!H37="P", 5, IF(Attendance!H37="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="I32">
-        <f>IF(Attendance!I32="P", 5, IF(Attendance!I32="O", 3, 0))</f>
+        <f>IF(Attendance!I37="P", 5, IF(Attendance!I37="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="J32">
-        <f>IF(Attendance!J32="P", 5, IF(Attendance!J32="O", 3, 0))</f>
+        <f>IF(Attendance!J37="P", 5, IF(Attendance!J37="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="K32">
-        <f>IF(Attendance!K32="P", 5, IF(Attendance!K32="O", 3, 0))</f>
+        <f>IF(Attendance!K37="P", 5, IF(Attendance!K37="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="L32">
-        <f>IF(Attendance!L32="P", 5, IF(Attendance!L32="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!L37="P", 5, IF(Attendance!L37="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="M32">
-        <f>IF(Attendance!M32="P", 5, IF(Attendance!M32="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!M37="P", 5, IF(Attendance!M37="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="N32">
-        <f>IF(Attendance!N32="P", 5, IF(Attendance!N32="O", 3, 0))</f>
+        <f>IF(Attendance!N37="P", 5, IF(Attendance!N37="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="O32">
-        <f>IF(Attendance!O32="P", 5, IF(Attendance!O32="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!O37="P", 5, IF(Attendance!O37="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="P32">
-        <f>IF(Attendance!P32="P", 5, IF(Attendance!P32="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!P37="P", 5, IF(Attendance!P37="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="Q32">
-        <f>IF(Attendance!Q32="P", 5, IF(Attendance!Q32="O", 3, 0))</f>
+        <f>IF(Attendance!Q37="P", 5, IF(Attendance!Q37="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="R32">
-        <f>IF(Attendance!R32="P", 5, IF(Attendance!R32="O", 3, 0))</f>
+        <f>IF(Attendance!R37="P", 5, IF(Attendance!R37="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="S32">
-        <f>IF(Attendance!S32="P", 5, IF(Attendance!S32="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!S37="P", 5, IF(Attendance!S37="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="T32">
-        <f>IF(Attendance!T32="P", 5, IF(Attendance!T32="O", 3, 0))</f>
+        <f>IF(Attendance!T37="P", 5, IF(Attendance!T37="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="U32">
-        <f>IF(Attendance!U32="P", 5, IF(Attendance!U32="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!U37="P", 5, IF(Attendance!U37="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="V32">
-        <f>IF(Attendance!V32="P", 5, IF(Attendance!V32="O", 3, 0))</f>
+        <f>IF(Attendance!V37="P", 5, IF(Attendance!V37="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="W32">
-        <f>IF(Attendance!W32="P", 5, IF(Attendance!W32="O", 3, 0))</f>
+        <f>IF(Attendance!W37="P", 5, IF(Attendance!W37="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="X32">
-        <f>IF(Attendance!X32="P", 5, IF(Attendance!X32="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!X37="P", 5, IF(Attendance!X37="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <f>IF(Attendance!Y32="P", 5, IF(Attendance!Y32="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!Y37="P", 5, IF(Attendance!Y37="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="Z32">
-        <f>IF(Attendance!Z32="P", 5, IF(Attendance!Z32="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!Z37="P", 5, IF(Attendance!Z37="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AA32">
-        <f>IF(Attendance!AA32="P", 5, IF(Attendance!AA32="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AA37="P", 5, IF(Attendance!AA37="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AB32">
-        <f>IF(Attendance!AB32="P", 5, IF(Attendance!AB32="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AB37="P", 5, IF(Attendance!AB37="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AC32">
-        <f>IF(Attendance!AC32="P", 5, IF(Attendance!AC32="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AC37="P", 5, IF(Attendance!AC37="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AD32">
-        <f>IF(Attendance!AD32="P", 5, IF(Attendance!AD32="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AD37="P", 5, IF(Attendance!AD37="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AE32">
-        <f>IF(Attendance!AE32="P", 5, IF(Attendance!AE32="O", 3, 0))</f>
+        <f>IF(Attendance!AE37="P", 5, IF(Attendance!AE37="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AF32">
-        <f>IF(Attendance!AF32="P", 5, IF(Attendance!AF32="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AF37="P", 5, IF(Attendance!AF37="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AG32">
-        <f>IF(Attendance!AG32="P", 5, IF(Attendance!AG32="O", 3, 0))</f>
+        <f>IF(Attendance!AG37="P", 5, IF(Attendance!AG37="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AH32">
-        <f>IF(Attendance!AH32="P", 5, IF(Attendance!AH32="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AH37="P", 5, IF(Attendance!AH37="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AI32">
         <f t="shared" si="0"/>
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AJ32">
         <f t="shared" si="1"/>
@@ -10935,147 +11228,154 @@
       </c>
       <c r="AK32">
         <f t="shared" si="2"/>
+        <v>2.44</v>
+      </c>
+      <c r="AL32">
+        <v>10</v>
+      </c>
+      <c r="AM32">
+        <f t="shared" si="9"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>10</v>
       </c>
       <c r="B33" t="s">
         <v>34</v>
       </c>
       <c r="C33">
-        <f>IF(Attendance!C33="P", 5, IF(Attendance!C33="O", 3, 0))</f>
+        <f>IF(Attendance!C38="P", 5, IF(Attendance!C38="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="D33">
-        <f>IF(Attendance!D33="P", 5, IF(Attendance!D33="O", 3, 0))</f>
+        <f>IF(Attendance!D38="P", 5, IF(Attendance!D38="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="E33">
-        <f>IF(Attendance!E33="P", 5, IF(Attendance!E33="O", 3, 0))</f>
+        <f>IF(Attendance!E38="P", 5, IF(Attendance!E38="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="F33">
-        <f>IF(Attendance!F33="P", 5, IF(Attendance!F33="O", 3, 0))</f>
+        <f>IF(Attendance!F38="P", 5, IF(Attendance!F38="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="G33">
-        <f>IF(Attendance!G33="P", 5, IF(Attendance!G33="O", 3, 0))</f>
+        <f>IF(Attendance!G38="P", 5, IF(Attendance!G38="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="H33">
-        <f>IF(Attendance!H33="P", 5, IF(Attendance!H33="O", 3, 0))</f>
+        <f>IF(Attendance!H38="P", 5, IF(Attendance!H38="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="I33">
-        <f>IF(Attendance!I33="P", 5, IF(Attendance!I33="O", 3, 0))</f>
+        <f>IF(Attendance!I38="P", 5, IF(Attendance!I38="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="J33">
-        <f>IF(Attendance!J33="P", 5, IF(Attendance!J33="O", 3, 0))</f>
+        <f>IF(Attendance!J38="P", 5, IF(Attendance!J38="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="K33">
-        <f>IF(Attendance!K33="P", 5, IF(Attendance!K33="O", 3, 0))</f>
+        <f>IF(Attendance!K38="P", 5, IF(Attendance!K38="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="L33">
-        <f>IF(Attendance!L33="P", 5, IF(Attendance!L33="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!L38="P", 5, IF(Attendance!L38="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="M33">
-        <f>IF(Attendance!M33="P", 5, IF(Attendance!M33="O", 3, 0))</f>
+        <f>IF(Attendance!M38="P", 5, IF(Attendance!M38="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="N33">
-        <f>IF(Attendance!N33="P", 5, IF(Attendance!N33="O", 3, 0))</f>
+        <f>IF(Attendance!N38="P", 5, IF(Attendance!N38="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="O33">
-        <f>IF(Attendance!O33="P", 5, IF(Attendance!O33="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!O38="P", 5, IF(Attendance!O38="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="P33">
-        <f>IF(Attendance!P33="P", 5, IF(Attendance!P33="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!P38="P", 5, IF(Attendance!P38="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="Q33">
-        <f>IF(Attendance!Q33="P", 5, IF(Attendance!Q33="O", 3, 0))</f>
+        <f>IF(Attendance!Q38="P", 5, IF(Attendance!Q38="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="R33">
-        <f>IF(Attendance!R33="P", 5, IF(Attendance!R33="O", 3, 0))</f>
+        <f>IF(Attendance!R38="P", 5, IF(Attendance!R38="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="S33">
-        <f>IF(Attendance!S33="P", 5, IF(Attendance!S33="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!S38="P", 5, IF(Attendance!S38="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="T33">
-        <f>IF(Attendance!T33="P", 5, IF(Attendance!T33="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!T38="P", 5, IF(Attendance!T38="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="U33">
-        <f>IF(Attendance!U33="P", 5, IF(Attendance!U33="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!U38="P", 5, IF(Attendance!U38="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="V33">
-        <f>IF(Attendance!V33="P", 5, IF(Attendance!V33="O", 3, 0))</f>
+        <f>IF(Attendance!V38="P", 5, IF(Attendance!V38="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="W33">
-        <f>IF(Attendance!W33="P", 5, IF(Attendance!W33="O", 3, 0))</f>
+        <f>IF(Attendance!W38="P", 5, IF(Attendance!W38="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="X33">
-        <f>IF(Attendance!X33="P", 5, IF(Attendance!X33="O", 3, 0))</f>
+        <f>IF(Attendance!X38="P", 5, IF(Attendance!X38="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="Y33">
-        <f>IF(Attendance!Y33="P", 5, IF(Attendance!Y33="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!Y38="P", 5, IF(Attendance!Y38="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="Z33">
-        <f>IF(Attendance!Z33="P", 5, IF(Attendance!Z33="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!Z38="P", 5, IF(Attendance!Z38="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AA33">
-        <f>IF(Attendance!AA33="P", 5, IF(Attendance!AA33="O", 3, 0))</f>
+        <f>IF(Attendance!AA38="P", 5, IF(Attendance!AA38="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AB33">
-        <f>IF(Attendance!AB33="P", 5, IF(Attendance!AB33="O", 3, 0))</f>
+        <f>IF(Attendance!AB38="P", 5, IF(Attendance!AB38="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AC33">
-        <f>IF(Attendance!AC33="P", 5, IF(Attendance!AC33="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AC38="P", 5, IF(Attendance!AC38="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AD33">
-        <f>IF(Attendance!AD33="P", 5, IF(Attendance!AD33="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AD38="P", 5, IF(Attendance!AD38="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AE33">
-        <f>IF(Attendance!AE33="P", 5, IF(Attendance!AE33="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AE38="P", 5, IF(Attendance!AE38="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AF33">
-        <f>IF(Attendance!AF33="P", 5, IF(Attendance!AF33="O", 3, 0))</f>
+        <f>IF(Attendance!AF38="P", 5, IF(Attendance!AF38="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AG33">
-        <f>IF(Attendance!AG33="P", 5, IF(Attendance!AG33="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AG38="P", 5, IF(Attendance!AG38="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AH33">
-        <f>IF(Attendance!AH33="P", 5, IF(Attendance!AH33="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AH38="P", 5, IF(Attendance!AH38="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AI33">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AJ33">
         <f t="shared" si="1"/>
@@ -11083,147 +11383,154 @@
       </c>
       <c r="AK33">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>3.63</v>
+      </c>
+      <c r="AL33">
+        <v>10</v>
+      </c>
+      <c r="AM33">
+        <f t="shared" ref="AM33" si="10">ROUND(AL33/4, 2)</f>
+        <v>2.5</v>
       </c>
     </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B34" t="s">
         <v>34</v>
       </c>
       <c r="C34">
-        <f>IF(Attendance!C34="P", 5, IF(Attendance!C34="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!C39="P", 5, IF(Attendance!C39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="D34">
-        <f>IF(Attendance!D34="P", 5, IF(Attendance!D34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!D39="P", 5, IF(Attendance!D39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="E34">
-        <f>IF(Attendance!E34="P", 5, IF(Attendance!E34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!E39="P", 5, IF(Attendance!E39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="F34">
-        <f>IF(Attendance!F34="P", 5, IF(Attendance!F34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!F39="P", 5, IF(Attendance!F39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="G34">
-        <f>IF(Attendance!G34="P", 5, IF(Attendance!G34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!G39="P", 5, IF(Attendance!G39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="H34">
-        <f>IF(Attendance!H34="P", 5, IF(Attendance!H34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!H39="P", 5, IF(Attendance!H39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="I34">
-        <f>IF(Attendance!I34="P", 5, IF(Attendance!I34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!I39="P", 5, IF(Attendance!I39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="J34">
-        <f>IF(Attendance!J34="P", 5, IF(Attendance!J34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!J39="P", 5, IF(Attendance!J39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="K34">
-        <f>IF(Attendance!K34="P", 5, IF(Attendance!K34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!K39="P", 5, IF(Attendance!K39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="L34">
-        <f>IF(Attendance!L34="P", 5, IF(Attendance!L34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!L39="P", 5, IF(Attendance!L39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="M34">
-        <f>IF(Attendance!M34="P", 5, IF(Attendance!M34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!M39="P", 5, IF(Attendance!M39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="N34">
-        <f>IF(Attendance!N34="P", 5, IF(Attendance!N34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!N39="P", 5, IF(Attendance!N39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="O34">
-        <f>IF(Attendance!O34="P", 5, IF(Attendance!O34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!O39="P", 5, IF(Attendance!O39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="P34">
-        <f>IF(Attendance!P34="P", 5, IF(Attendance!P34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!P39="P", 5, IF(Attendance!P39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="Q34">
-        <f>IF(Attendance!Q34="P", 5, IF(Attendance!Q34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!Q39="P", 5, IF(Attendance!Q39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="R34">
-        <f>IF(Attendance!R34="P", 5, IF(Attendance!R34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!R39="P", 5, IF(Attendance!R39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="S34">
-        <f>IF(Attendance!S34="P", 5, IF(Attendance!S34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!S39="P", 5, IF(Attendance!S39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="T34">
-        <f>IF(Attendance!T34="P", 5, IF(Attendance!T34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!T39="P", 5, IF(Attendance!T39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="U34">
-        <f>IF(Attendance!U34="P", 5, IF(Attendance!U34="O", 3, 0))</f>
+        <f>IF(Attendance!U39="P", 5, IF(Attendance!U39="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="V34">
-        <f>IF(Attendance!V34="P", 5, IF(Attendance!V34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!V39="P", 5, IF(Attendance!V39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="W34">
-        <f>IF(Attendance!W34="P", 5, IF(Attendance!W34="O", 3, 0))</f>
+        <f>IF(Attendance!W39="P", 5, IF(Attendance!W39="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="X34">
-        <f>IF(Attendance!X34="P", 5, IF(Attendance!X34="O", 3, 0))</f>
+        <f>IF(Attendance!X39="P", 5, IF(Attendance!X39="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="Y34">
-        <f>IF(Attendance!Y34="P", 5, IF(Attendance!Y34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!Y39="P", 5, IF(Attendance!Y39="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="Z34">
-        <f>IF(Attendance!Z34="P", 5, IF(Attendance!Z34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!Z39="P", 5, IF(Attendance!Z39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AA34">
-        <f>IF(Attendance!AA34="P", 5, IF(Attendance!AA34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AA39="P", 5, IF(Attendance!AA39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AB34">
-        <f>IF(Attendance!AB34="P", 5, IF(Attendance!AB34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AB39="P", 5, IF(Attendance!AB39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AC34">
-        <f>IF(Attendance!AC34="P", 5, IF(Attendance!AC34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AC39="P", 5, IF(Attendance!AC39="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <f>IF(Attendance!AD34="P", 5, IF(Attendance!AD34="O", 3, 0))</f>
+        <f>IF(Attendance!AD39="P", 5, IF(Attendance!AD39="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AE34">
-        <f>IF(Attendance!AE34="P", 5, IF(Attendance!AE34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AE39="P", 5, IF(Attendance!AE39="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <f>IF(Attendance!AF34="P", 5, IF(Attendance!AF34="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AF39="P", 5, IF(Attendance!AF39="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AG34">
-        <f>IF(Attendance!AG34="P", 5, IF(Attendance!AG34="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AG39="P", 5, IF(Attendance!AG39="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AH34">
-        <f>IF(Attendance!AH34="P", 5, IF(Attendance!AH34="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AH39="P", 5, IF(Attendance!AH39="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AI34">
         <f t="shared" si="0"/>
-        <v>143</v>
+        <v>81</v>
       </c>
       <c r="AJ34">
         <f t="shared" si="1"/>
@@ -11231,147 +11538,150 @@
       </c>
       <c r="AK34">
         <f t="shared" si="2"/>
-        <v>27</v>
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B35" t="s">
         <v>34</v>
       </c>
       <c r="C35">
-        <f>IF(Attendance!C35="P", 5, IF(Attendance!C35="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!C40="P", 5, IF(Attendance!C40="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="D35">
-        <f>IF(Attendance!D35="P", 5, IF(Attendance!D35="O", 3, 0))</f>
+        <f>IF(Attendance!D40="P", 5, IF(Attendance!D40="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="E35">
-        <f>IF(Attendance!E35="P", 5, IF(Attendance!E35="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!E40="P", 5, IF(Attendance!E40="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="F35">
-        <f>IF(Attendance!F35="P", 5, IF(Attendance!F35="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!F40="P", 5, IF(Attendance!F40="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="G35">
-        <f>IF(Attendance!G35="P", 5, IF(Attendance!G35="O", 3, 0))</f>
+        <f>IF(Attendance!G40="P", 5, IF(Attendance!G40="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="H35">
-        <f>IF(Attendance!H35="P", 5, IF(Attendance!H35="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!H40="P", 5, IF(Attendance!H40="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="I35">
-        <f>IF(Attendance!I35="P", 5, IF(Attendance!I35="O", 3, 0))</f>
+        <f>IF(Attendance!I40="P", 5, IF(Attendance!I40="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="J35">
-        <f>IF(Attendance!J35="P", 5, IF(Attendance!J35="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!J40="P", 5, IF(Attendance!J40="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="K35">
-        <f>IF(Attendance!K35="P", 5, IF(Attendance!K35="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!K40="P", 5, IF(Attendance!K40="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="L35">
-        <f>IF(Attendance!L35="P", 5, IF(Attendance!L35="O", 3, 0))</f>
+        <f>IF(Attendance!L40="P", 5, IF(Attendance!L40="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="M35">
-        <f>IF(Attendance!M35="P", 5, IF(Attendance!M35="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!M40="P", 5, IF(Attendance!M40="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="N35">
-        <f>IF(Attendance!N35="P", 5, IF(Attendance!N35="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!N40="P", 5, IF(Attendance!N40="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="O35">
-        <f>IF(Attendance!O35="P", 5, IF(Attendance!O35="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!O40="P", 5, IF(Attendance!O40="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="P35">
-        <f>IF(Attendance!P35="P", 5, IF(Attendance!P35="O", 3, 0))</f>
+        <f>IF(Attendance!P40="P", 5, IF(Attendance!P40="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="Q35">
-        <f>IF(Attendance!Q35="P", 5, IF(Attendance!Q35="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!Q40="P", 5, IF(Attendance!Q40="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="R35">
-        <f>IF(Attendance!R35="P", 5, IF(Attendance!R35="O", 3, 0))</f>
+        <f>IF(Attendance!R40="P", 5, IF(Attendance!R40="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="S35">
-        <f>IF(Attendance!S35="P", 5, IF(Attendance!S35="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!S40="P", 5, IF(Attendance!S40="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="T35">
-        <f>IF(Attendance!T35="P", 5, IF(Attendance!T35="O", 3, 0))</f>
+        <f>IF(Attendance!T40="P", 5, IF(Attendance!T40="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="U35">
-        <f>IF(Attendance!U35="P", 5, IF(Attendance!U35="O", 3, 0))</f>
+        <f>IF(Attendance!U40="P", 5, IF(Attendance!U40="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="V35">
-        <f>IF(Attendance!V35="P", 5, IF(Attendance!V35="O", 3, 0))</f>
+        <f>IF(Attendance!V40="P", 5, IF(Attendance!V40="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="W35">
-        <f>IF(Attendance!W35="P", 5, IF(Attendance!W35="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!W40="P", 5, IF(Attendance!W40="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="X35">
-        <f>IF(Attendance!X35="P", 5, IF(Attendance!X35="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!X40="P", 5, IF(Attendance!X40="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="Y35">
-        <f>IF(Attendance!Y35="P", 5, IF(Attendance!Y35="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!Y40="P", 5, IF(Attendance!Y40="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="Z35">
-        <f>IF(Attendance!Z35="P", 5, IF(Attendance!Z35="O", 3, 0))</f>
+        <f>IF(Attendance!Z40="P", 5, IF(Attendance!Z40="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="AA35">
-        <f>IF(Attendance!AA35="P", 5, IF(Attendance!AA35="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AA40="P", 5, IF(Attendance!AA40="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AB35">
-        <f>IF(Attendance!AB35="P", 5, IF(Attendance!AB35="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AB40="P", 5, IF(Attendance!AB40="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AC35">
-        <f>IF(Attendance!AC35="P", 5, IF(Attendance!AC35="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AC40="P", 5, IF(Attendance!AC40="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AD35">
-        <f>IF(Attendance!AD35="P", 5, IF(Attendance!AD35="O", 3, 0))</f>
+        <f>IF(Attendance!AD40="P", 5, IF(Attendance!AD40="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="AE35">
-        <f>IF(Attendance!AE35="P", 5, IF(Attendance!AE35="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AE40="P", 5, IF(Attendance!AE40="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AF35">
-        <f>IF(Attendance!AF35="P", 5, IF(Attendance!AF35="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AF40="P", 5, IF(Attendance!AF40="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AG35">
-        <f>IF(Attendance!AG35="P", 5, IF(Attendance!AG35="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AG40="P", 5, IF(Attendance!AG40="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AH35">
-        <f>IF(Attendance!AH35="P", 5, IF(Attendance!AH35="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AH40="P", 5, IF(Attendance!AH40="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AI35">
         <f t="shared" si="0"/>
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="AJ35">
         <f t="shared" si="1"/>
@@ -11379,147 +11689,150 @@
       </c>
       <c r="AK35">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>4.16</v>
+      </c>
+      <c r="AM35">
+        <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C36">
-        <f>IF(Attendance!C36="P", 5, IF(Attendance!C36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!C41="P", 5, IF(Attendance!C41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="D36">
-        <f>IF(Attendance!D36="P", 5, IF(Attendance!D36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!D41="P", 5, IF(Attendance!D41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="E36">
-        <f>IF(Attendance!E36="P", 5, IF(Attendance!E36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!E41="P", 5, IF(Attendance!E41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="F36">
-        <f>IF(Attendance!F36="P", 5, IF(Attendance!F36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!F41="P", 5, IF(Attendance!F41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="G36">
-        <f>IF(Attendance!G36="P", 5, IF(Attendance!G36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!G41="P", 5, IF(Attendance!G41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="H36">
-        <f>IF(Attendance!H36="P", 5, IF(Attendance!H36="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!H41="P", 5, IF(Attendance!H41="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="I36">
-        <f>IF(Attendance!I36="P", 5, IF(Attendance!I36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!I41="P", 5, IF(Attendance!I41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="J36">
-        <f>IF(Attendance!J36="P", 5, IF(Attendance!J36="O", 3, 0))</f>
+        <f>IF(Attendance!J41="P", 5, IF(Attendance!J41="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="K36">
-        <f>IF(Attendance!K36="P", 5, IF(Attendance!K36="O", 3, 0))</f>
+        <f>IF(Attendance!K41="P", 5, IF(Attendance!K41="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="L36">
-        <f>IF(Attendance!L36="P", 5, IF(Attendance!L36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!L41="P", 5, IF(Attendance!L41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="M36">
-        <f>IF(Attendance!M36="P", 5, IF(Attendance!M36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!M41="P", 5, IF(Attendance!M41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="N36">
-        <f>IF(Attendance!N36="P", 5, IF(Attendance!N36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!N41="P", 5, IF(Attendance!N41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="O36">
-        <f>IF(Attendance!O36="P", 5, IF(Attendance!O36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!O41="P", 5, IF(Attendance!O41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="P36">
-        <f>IF(Attendance!P36="P", 5, IF(Attendance!P36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!P41="P", 5, IF(Attendance!P41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <f>IF(Attendance!Q36="P", 5, IF(Attendance!Q36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!Q41="P", 5, IF(Attendance!Q41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="R36">
-        <f>IF(Attendance!R36="P", 5, IF(Attendance!R36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!R41="P", 5, IF(Attendance!R41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="S36">
-        <f>IF(Attendance!S36="P", 5, IF(Attendance!S36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!S41="P", 5, IF(Attendance!S41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="T36">
-        <f>IF(Attendance!T36="P", 5, IF(Attendance!T36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!T41="P", 5, IF(Attendance!T41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="U36">
-        <f>IF(Attendance!U36="P", 5, IF(Attendance!U36="O", 3, 0))</f>
+        <f>IF(Attendance!U41="P", 5, IF(Attendance!U41="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="V36">
-        <f>IF(Attendance!V36="P", 5, IF(Attendance!V36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!V41="P", 5, IF(Attendance!V41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="W36">
-        <f>IF(Attendance!W36="P", 5, IF(Attendance!W36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!W41="P", 5, IF(Attendance!W41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="X36">
-        <f>IF(Attendance!X36="P", 5, IF(Attendance!X36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!X41="P", 5, IF(Attendance!X41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="Y36">
-        <f>IF(Attendance!Y36="P", 5, IF(Attendance!Y36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!Y41="P", 5, IF(Attendance!Y41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="Z36">
-        <f>IF(Attendance!Z36="P", 5, IF(Attendance!Z36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!Z41="P", 5, IF(Attendance!Z41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AA36">
-        <f>IF(Attendance!AA36="P", 5, IF(Attendance!AA36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AA41="P", 5, IF(Attendance!AA41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AB36">
-        <f>IF(Attendance!AB36="P", 5, IF(Attendance!AB36="O", 3, 0))</f>
+        <f>IF(Attendance!AB41="P", 5, IF(Attendance!AB41="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="AC36">
-        <f>IF(Attendance!AC36="P", 5, IF(Attendance!AC36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AC41="P", 5, IF(Attendance!AC41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AD36">
-        <f>IF(Attendance!AD36="P", 5, IF(Attendance!AD36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AD41="P", 5, IF(Attendance!AD41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AE36">
-        <f>IF(Attendance!AE36="P", 5, IF(Attendance!AE36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AE41="P", 5, IF(Attendance!AE41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AF36">
-        <f>IF(Attendance!AF36="P", 5, IF(Attendance!AF36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AF41="P", 5, IF(Attendance!AF41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AG36">
-        <f>IF(Attendance!AG36="P", 5, IF(Attendance!AG36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AG41="P", 5, IF(Attendance!AG41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AH36">
-        <f>IF(Attendance!AH36="P", 5, IF(Attendance!AH36="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AH41="P", 5, IF(Attendance!AH41="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AI36">
         <f t="shared" si="0"/>
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="AJ36">
         <f t="shared" si="1"/>
@@ -11527,147 +11840,150 @@
       </c>
       <c r="AK36">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AM36">
+        <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B37" t="s">
         <v>34</v>
       </c>
       <c r="C37">
-        <f>IF(Attendance!C37="P", 5, IF(Attendance!C37="O", 3, 0))</f>
+        <f>IF(Attendance!C42="P", 5, IF(Attendance!C42="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="D37">
-        <f>IF(Attendance!D37="P", 5, IF(Attendance!D37="O", 3, 0))</f>
+        <f>IF(Attendance!D42="P", 5, IF(Attendance!D42="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="E37">
-        <f>IF(Attendance!E37="P", 5, IF(Attendance!E37="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!E42="P", 5, IF(Attendance!E42="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="F37">
-        <f>IF(Attendance!F37="P", 5, IF(Attendance!F37="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!F42="P", 5, IF(Attendance!F42="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="G37">
-        <f>IF(Attendance!G37="P", 5, IF(Attendance!G37="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!G42="P", 5, IF(Attendance!G42="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="H37">
-        <f>IF(Attendance!H37="P", 5, IF(Attendance!H37="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!H42="P", 5, IF(Attendance!H42="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="I37">
-        <f>IF(Attendance!I37="P", 5, IF(Attendance!I37="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!I42="P", 5, IF(Attendance!I42="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="J37">
-        <f>IF(Attendance!J37="P", 5, IF(Attendance!J37="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!J42="P", 5, IF(Attendance!J42="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="K37">
-        <f>IF(Attendance!K37="P", 5, IF(Attendance!K37="O", 3, 0))</f>
+        <f>IF(Attendance!K42="P", 5, IF(Attendance!K42="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="L37">
-        <f>IF(Attendance!L37="P", 5, IF(Attendance!L37="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!L42="P", 5, IF(Attendance!L42="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="M37">
-        <f>IF(Attendance!M37="P", 5, IF(Attendance!M37="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!M42="P", 5, IF(Attendance!M42="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="N37">
-        <f>IF(Attendance!N37="P", 5, IF(Attendance!N37="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!N42="P", 5, IF(Attendance!N42="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="O37">
-        <f>IF(Attendance!O37="P", 5, IF(Attendance!O37="O", 3, 0))</f>
+        <f>IF(Attendance!O42="P", 5, IF(Attendance!O42="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="P37">
-        <f>IF(Attendance!P37="P", 5, IF(Attendance!P37="O", 3, 0))</f>
+        <f>IF(Attendance!P42="P", 5, IF(Attendance!P42="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="Q37">
-        <f>IF(Attendance!Q37="P", 5, IF(Attendance!Q37="O", 3, 0))</f>
+        <f>IF(Attendance!Q42="P", 5, IF(Attendance!Q42="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="R37">
-        <f>IF(Attendance!R37="P", 5, IF(Attendance!R37="O", 3, 0))</f>
+        <f>IF(Attendance!R42="P", 5, IF(Attendance!R42="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="S37">
-        <f>IF(Attendance!S37="P", 5, IF(Attendance!S37="O", 3, 0))</f>
+        <f>IF(Attendance!S42="P", 5, IF(Attendance!S42="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="T37">
-        <f>IF(Attendance!T37="P", 5, IF(Attendance!T37="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!T42="P", 5, IF(Attendance!T42="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="U37">
-        <f>IF(Attendance!U37="P", 5, IF(Attendance!U37="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!U42="P", 5, IF(Attendance!U42="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="V37">
-        <f>IF(Attendance!V37="P", 5, IF(Attendance!V37="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!V42="P", 5, IF(Attendance!V42="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="W37">
-        <f>IF(Attendance!W37="P", 5, IF(Attendance!W37="O", 3, 0))</f>
+        <f>IF(Attendance!W42="P", 5, IF(Attendance!W42="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="X37">
-        <f>IF(Attendance!X37="P", 5, IF(Attendance!X37="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!X42="P", 5, IF(Attendance!X42="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="Y37">
-        <f>IF(Attendance!Y37="P", 5, IF(Attendance!Y37="O", 3, 0))</f>
+        <f>IF(Attendance!Y42="P", 5, IF(Attendance!Y42="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="Z37">
-        <f>IF(Attendance!Z37="P", 5, IF(Attendance!Z37="O", 3, 0))</f>
+        <f>IF(Attendance!Z42="P", 5, IF(Attendance!Z42="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AA37">
-        <f>IF(Attendance!AA37="P", 5, IF(Attendance!AA37="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AA42="P", 5, IF(Attendance!AA42="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AB37">
-        <f>IF(Attendance!AB37="P", 5, IF(Attendance!AB37="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!AB42="P", 5, IF(Attendance!AB42="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AC37">
-        <f>IF(Attendance!AC37="P", 5, IF(Attendance!AC37="O", 3, 0))</f>
+        <f>IF(Attendance!AC42="P", 5, IF(Attendance!AC42="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AD37">
-        <f>IF(Attendance!AD37="P", 5, IF(Attendance!AD37="O", 3, 0))</f>
+        <f>IF(Attendance!AD42="P", 5, IF(Attendance!AD42="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AE37">
-        <f>IF(Attendance!AE37="P", 5, IF(Attendance!AE37="O", 3, 0))</f>
+        <f>IF(Attendance!AE42="P", 5, IF(Attendance!AE42="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AF37">
-        <f>IF(Attendance!AF37="P", 5, IF(Attendance!AF37="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AF42="P", 5, IF(Attendance!AF42="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AG37">
-        <f>IF(Attendance!AG37="P", 5, IF(Attendance!AG37="O", 3, 0))</f>
+        <f>IF(Attendance!AG42="P", 5, IF(Attendance!AG42="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AH37">
-        <f>IF(Attendance!AH37="P", 5, IF(Attendance!AH37="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AH42="P", 5, IF(Attendance!AH42="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AI37">
         <f t="shared" si="0"/>
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AJ37">
         <f t="shared" si="1"/>
@@ -11675,147 +11991,154 @@
       </c>
       <c r="AK37">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>2.72</v>
+      </c>
+      <c r="AL37">
+        <v>14</v>
+      </c>
+      <c r="AM37">
+        <f t="shared" ref="AM37" si="11">ROUND(AL37/4, 2)</f>
+        <v>3.5</v>
       </c>
     </row>
-    <row r="38" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B38" t="s">
         <v>34</v>
       </c>
       <c r="C38">
-        <f>IF(Attendance!C38="P", 5, IF(Attendance!C38="O", 3, 0))</f>
+        <f>IF(Attendance!C44="P", 5, IF(Attendance!C44="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="D38">
-        <f>IF(Attendance!D38="P", 5, IF(Attendance!D38="O", 3, 0))</f>
+        <f>IF(Attendance!D44="P", 5, IF(Attendance!D44="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="E38">
-        <f>IF(Attendance!E38="P", 5, IF(Attendance!E38="O", 3, 0))</f>
+        <f>IF(Attendance!E44="P", 5, IF(Attendance!E44="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="F38">
-        <f>IF(Attendance!F38="P", 5, IF(Attendance!F38="O", 3, 0))</f>
+        <f>IF(Attendance!F44="P", 5, IF(Attendance!F44="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="G38">
-        <f>IF(Attendance!G38="P", 5, IF(Attendance!G38="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!G44="P", 5, IF(Attendance!G44="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="H38">
-        <f>IF(Attendance!H38="P", 5, IF(Attendance!H38="O", 3, 0))</f>
+        <f>IF(Attendance!H44="P", 5, IF(Attendance!H44="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="I38">
-        <f>IF(Attendance!I38="P", 5, IF(Attendance!I38="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!I44="P", 5, IF(Attendance!I44="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="J38">
-        <f>IF(Attendance!J38="P", 5, IF(Attendance!J38="O", 3, 0))</f>
+        <f>IF(Attendance!J44="P", 5, IF(Attendance!J44="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="K38">
-        <f>IF(Attendance!K38="P", 5, IF(Attendance!K38="O", 3, 0))</f>
+        <f>IF(Attendance!K44="P", 5, IF(Attendance!K44="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="L38">
-        <f>IF(Attendance!L38="P", 5, IF(Attendance!L38="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!L44="P", 5, IF(Attendance!L44="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="M38">
-        <f>IF(Attendance!M38="P", 5, IF(Attendance!M38="O", 3, 0))</f>
+        <f>IF(Attendance!M44="P", 5, IF(Attendance!M44="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="N38">
-        <f>IF(Attendance!N38="P", 5, IF(Attendance!N38="O", 3, 0))</f>
+        <f>IF(Attendance!N44="P", 5, IF(Attendance!N44="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="O38">
-        <f>IF(Attendance!O38="P", 5, IF(Attendance!O38="O", 3, 0))</f>
+        <f>IF(Attendance!O44="P", 5, IF(Attendance!O44="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="P38">
-        <f>IF(Attendance!P38="P", 5, IF(Attendance!P38="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!P44="P", 5, IF(Attendance!P44="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="Q38">
-        <f>IF(Attendance!Q38="P", 5, IF(Attendance!Q38="O", 3, 0))</f>
+        <f>IF(Attendance!Q44="P", 5, IF(Attendance!Q44="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="R38">
-        <f>IF(Attendance!R38="P", 5, IF(Attendance!R38="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!R44="P", 5, IF(Attendance!R44="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="S38">
-        <f>IF(Attendance!S38="P", 5, IF(Attendance!S38="O", 3, 0))</f>
+        <f>IF(Attendance!S44="P", 5, IF(Attendance!S44="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="T38">
-        <f>IF(Attendance!T38="P", 5, IF(Attendance!T38="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!T44="P", 5, IF(Attendance!T44="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="U38">
-        <f>IF(Attendance!U38="P", 5, IF(Attendance!U38="O", 3, 0))</f>
+        <f>IF(Attendance!U44="P", 5, IF(Attendance!U44="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="V38">
-        <f>IF(Attendance!V38="P", 5, IF(Attendance!V38="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!V44="P", 5, IF(Attendance!V44="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="W38">
-        <f>IF(Attendance!W38="P", 5, IF(Attendance!W38="O", 3, 0))</f>
+        <f>IF(Attendance!W44="P", 5, IF(Attendance!W44="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="X38">
-        <f>IF(Attendance!X38="P", 5, IF(Attendance!X38="O", 3, 0))</f>
+        <f>IF(Attendance!X44="P", 5, IF(Attendance!X44="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="Y38">
-        <f>IF(Attendance!Y38="P", 5, IF(Attendance!Y38="O", 3, 0))</f>
+        <f>IF(Attendance!Y44="P", 5, IF(Attendance!Y44="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="Z38">
-        <f>IF(Attendance!Z38="P", 5, IF(Attendance!Z38="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!Z44="P", 5, IF(Attendance!Z44="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AA38">
-        <f>IF(Attendance!AA38="P", 5, IF(Attendance!AA38="O", 3, 0))</f>
+        <f>IF(Attendance!AA44="P", 5, IF(Attendance!AA44="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AB38">
-        <f>IF(Attendance!AB38="P", 5, IF(Attendance!AB38="O", 3, 0))</f>
+        <f>IF(Attendance!AB44="P", 5, IF(Attendance!AB44="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AC38">
-        <f>IF(Attendance!AC38="P", 5, IF(Attendance!AC38="O", 3, 0))</f>
+        <f>IF(Attendance!AC44="P", 5, IF(Attendance!AC44="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AD38">
-        <f>IF(Attendance!AD38="P", 5, IF(Attendance!AD38="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AD44="P", 5, IF(Attendance!AD44="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AE38">
-        <f>IF(Attendance!AE38="P", 5, IF(Attendance!AE38="O", 3, 0))</f>
+        <f>IF(Attendance!AE44="P", 5, IF(Attendance!AE44="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AF38">
-        <f>IF(Attendance!AF38="P", 5, IF(Attendance!AF38="O", 3, 0))</f>
+        <f>IF(Attendance!AF44="P", 5, IF(Attendance!AF44="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AG38">
-        <f>IF(Attendance!AG38="P", 5, IF(Attendance!AG38="O", 3, 0))</f>
+        <f>IF(Attendance!AG44="P", 5, IF(Attendance!AG44="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AH38">
-        <f>IF(Attendance!AH38="P", 5, IF(Attendance!AH38="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AH44="P", 5, IF(Attendance!AH44="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AI38">
         <f t="shared" si="0"/>
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="AJ38">
         <f t="shared" si="1"/>
@@ -11823,147 +12146,154 @@
       </c>
       <c r="AK38">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>3</v>
+      </c>
+      <c r="AL38">
+        <v>20</v>
+      </c>
+      <c r="AM38">
+        <f t="shared" ref="AM38:AM40" si="12">ROUND(AL38/4, 2)</f>
+        <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
         <v>34</v>
       </c>
       <c r="C39">
-        <f>IF(Attendance!C39="P", 5, IF(Attendance!C39="O", 3, 0))</f>
+        <f>IF(Attendance!C45="P", 5, IF(Attendance!C45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="D39">
-        <f>IF(Attendance!D39="P", 5, IF(Attendance!D39="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!D45="P", 5, IF(Attendance!D45="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="E39">
-        <f>IF(Attendance!E39="P", 5, IF(Attendance!E39="O", 3, 0))</f>
+        <f>IF(Attendance!E45="P", 5, IF(Attendance!E45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="F39">
-        <f>IF(Attendance!F39="P", 5, IF(Attendance!F39="O", 3, 0))</f>
+        <f>IF(Attendance!F45="P", 5, IF(Attendance!F45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="G39">
-        <f>IF(Attendance!G39="P", 5, IF(Attendance!G39="O", 3, 0))</f>
+        <f>IF(Attendance!G45="P", 5, IF(Attendance!G45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="H39">
-        <f>IF(Attendance!H39="P", 5, IF(Attendance!H39="O", 3, 0))</f>
+        <f>IF(Attendance!H45="P", 5, IF(Attendance!H45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="I39">
-        <f>IF(Attendance!I39="P", 5, IF(Attendance!I39="O", 3, 0))</f>
+        <f>IF(Attendance!I45="P", 5, IF(Attendance!I45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="J39">
-        <f>IF(Attendance!J39="P", 5, IF(Attendance!J39="O", 3, 0))</f>
+        <f>IF(Attendance!J45="P", 5, IF(Attendance!J45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="K39">
-        <f>IF(Attendance!K39="P", 5, IF(Attendance!K39="O", 3, 0))</f>
+        <f>IF(Attendance!K45="P", 5, IF(Attendance!K45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="L39">
-        <f>IF(Attendance!L39="P", 5, IF(Attendance!L39="O", 3, 0))</f>
+        <f>IF(Attendance!L45="P", 5, IF(Attendance!L45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="M39">
-        <f>IF(Attendance!M39="P", 5, IF(Attendance!M39="O", 3, 0))</f>
+        <f>IF(Attendance!M45="P", 5, IF(Attendance!M45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="N39">
-        <f>IF(Attendance!N39="P", 5, IF(Attendance!N39="O", 3, 0))</f>
+        <f>IF(Attendance!N45="P", 5, IF(Attendance!N45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="O39">
-        <f>IF(Attendance!O39="P", 5, IF(Attendance!O39="O", 3, 0))</f>
+        <f>IF(Attendance!O45="P", 5, IF(Attendance!O45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="P39">
-        <f>IF(Attendance!P39="P", 5, IF(Attendance!P39="O", 3, 0))</f>
+        <f>IF(Attendance!P45="P", 5, IF(Attendance!P45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="Q39">
-        <f>IF(Attendance!Q39="P", 5, IF(Attendance!Q39="O", 3, 0))</f>
+        <f>IF(Attendance!Q45="P", 5, IF(Attendance!Q45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="R39">
-        <f>IF(Attendance!R39="P", 5, IF(Attendance!R39="O", 3, 0))</f>
+        <f>IF(Attendance!R45="P", 5, IF(Attendance!R45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="S39">
-        <f>IF(Attendance!S39="P", 5, IF(Attendance!S39="O", 3, 0))</f>
+        <f>IF(Attendance!S45="P", 5, IF(Attendance!S45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="T39">
-        <f>IF(Attendance!T39="P", 5, IF(Attendance!T39="O", 3, 0))</f>
+        <f>IF(Attendance!T45="P", 5, IF(Attendance!T45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="U39">
-        <f>IF(Attendance!U39="P", 5, IF(Attendance!U39="O", 3, 0))</f>
+        <f>IF(Attendance!U45="P", 5, IF(Attendance!U45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="V39">
-        <f>IF(Attendance!V39="P", 5, IF(Attendance!V39="O", 3, 0))</f>
+        <f>IF(Attendance!V45="P", 5, IF(Attendance!V45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="W39">
-        <f>IF(Attendance!W39="P", 5, IF(Attendance!W39="O", 3, 0))</f>
+        <f>IF(Attendance!W45="P", 5, IF(Attendance!W45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="X39">
-        <f>IF(Attendance!X39="P", 5, IF(Attendance!X39="O", 3, 0))</f>
+        <f>IF(Attendance!X45="P", 5, IF(Attendance!X45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="Y39">
-        <f>IF(Attendance!Y39="P", 5, IF(Attendance!Y39="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!Y45="P", 5, IF(Attendance!Y45="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="Z39">
-        <f>IF(Attendance!Z39="P", 5, IF(Attendance!Z39="O", 3, 0))</f>
+        <f>IF(Attendance!Z45="P", 5, IF(Attendance!Z45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AA39">
-        <f>IF(Attendance!AA39="P", 5, IF(Attendance!AA39="O", 3, 0))</f>
+        <f>IF(Attendance!AA45="P", 5, IF(Attendance!AA45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AB39">
-        <f>IF(Attendance!AB39="P", 5, IF(Attendance!AB39="O", 3, 0))</f>
+        <f>IF(Attendance!AB45="P", 5, IF(Attendance!AB45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AC39">
-        <f>IF(Attendance!AC39="P", 5, IF(Attendance!AC39="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AC45="P", 5, IF(Attendance!AC45="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AD39">
-        <f>IF(Attendance!AD39="P", 5, IF(Attendance!AD39="O", 3, 0))</f>
+        <f>IF(Attendance!AD45="P", 5, IF(Attendance!AD45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AE39">
-        <f>IF(Attendance!AE39="P", 5, IF(Attendance!AE39="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AE45="P", 5, IF(Attendance!AE45="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AF39">
-        <f>IF(Attendance!AF39="P", 5, IF(Attendance!AF39="O", 3, 0))</f>
+        <f>IF(Attendance!AF45="P", 5, IF(Attendance!AF45="O", 3, 0))</f>
         <v>3</v>
       </c>
       <c r="AG39">
-        <f>IF(Attendance!AG39="P", 5, IF(Attendance!AG39="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AG45="P", 5, IF(Attendance!AG45="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AH39">
-        <f>IF(Attendance!AH39="P", 5, IF(Attendance!AH39="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AH45="P", 5, IF(Attendance!AH45="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AI39">
         <f t="shared" si="0"/>
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="AJ39">
         <f t="shared" si="1"/>
@@ -11971,147 +12301,154 @@
       </c>
       <c r="AK39">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>3.06</v>
+      </c>
+      <c r="AL39">
+        <v>20</v>
+      </c>
+      <c r="AM39">
+        <f t="shared" si="12"/>
+        <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="B40" t="s">
         <v>34</v>
       </c>
       <c r="C40">
-        <f>IF(Attendance!C40="P", 5, IF(Attendance!C40="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!C46="P", 5, IF(Attendance!C46="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="D40">
-        <f>IF(Attendance!D40="P", 5, IF(Attendance!D40="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!D46="P", 5, IF(Attendance!D46="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="E40">
-        <f>IF(Attendance!E40="P", 5, IF(Attendance!E40="O", 3, 0))</f>
+        <f>IF(Attendance!E46="P", 5, IF(Attendance!E46="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="F40">
-        <f>IF(Attendance!F40="P", 5, IF(Attendance!F40="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!F46="P", 5, IF(Attendance!F46="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="G40">
-        <f>IF(Attendance!G40="P", 5, IF(Attendance!G40="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!G46="P", 5, IF(Attendance!G46="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="H40">
-        <f>IF(Attendance!H40="P", 5, IF(Attendance!H40="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!H46="P", 5, IF(Attendance!H46="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="I40">
-        <f>IF(Attendance!I40="P", 5, IF(Attendance!I40="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!I46="P", 5, IF(Attendance!I46="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="J40">
-        <f>IF(Attendance!J40="P", 5, IF(Attendance!J40="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!J46="P", 5, IF(Attendance!J46="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="K40">
-        <f>IF(Attendance!K40="P", 5, IF(Attendance!K40="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!K46="P", 5, IF(Attendance!K46="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="L40">
-        <f>IF(Attendance!L40="P", 5, IF(Attendance!L40="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!L46="P", 5, IF(Attendance!L46="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="M40">
-        <f>IF(Attendance!M40="P", 5, IF(Attendance!M40="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!M46="P", 5, IF(Attendance!M46="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="N40">
-        <f>IF(Attendance!N40="P", 5, IF(Attendance!N40="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!N46="P", 5, IF(Attendance!N46="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="O40">
-        <f>IF(Attendance!O40="P", 5, IF(Attendance!O40="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!O46="P", 5, IF(Attendance!O46="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="P40">
-        <f>IF(Attendance!P40="P", 5, IF(Attendance!P40="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!P46="P", 5, IF(Attendance!P46="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <f>IF(Attendance!Q40="P", 5, IF(Attendance!Q40="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!Q46="P", 5, IF(Attendance!Q46="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="R40">
-        <f>IF(Attendance!R40="P", 5, IF(Attendance!R40="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!R46="P", 5, IF(Attendance!R46="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="S40">
-        <f>IF(Attendance!S40="P", 5, IF(Attendance!S40="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!S46="P", 5, IF(Attendance!S46="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="T40">
-        <f>IF(Attendance!T40="P", 5, IF(Attendance!T40="O", 3, 0))</f>
+        <f>IF(Attendance!T46="P", 5, IF(Attendance!T46="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="U40">
-        <f>IF(Attendance!U40="P", 5, IF(Attendance!U40="O", 3, 0))</f>
-        <v>3</v>
+        <f>IF(Attendance!U46="P", 5, IF(Attendance!U46="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="V40">
-        <f>IF(Attendance!V40="P", 5, IF(Attendance!V40="O", 3, 0))</f>
+        <f>IF(Attendance!V46="P", 5, IF(Attendance!V46="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="W40">
-        <f>IF(Attendance!W40="P", 5, IF(Attendance!W40="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!W46="P", 5, IF(Attendance!W46="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="X40">
-        <f>IF(Attendance!X40="P", 5, IF(Attendance!X40="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!X46="P", 5, IF(Attendance!X46="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="Y40">
-        <f>IF(Attendance!Y40="P", 5, IF(Attendance!Y40="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!Y46="P", 5, IF(Attendance!Y46="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="Z40">
-        <f>IF(Attendance!Z40="P", 5, IF(Attendance!Z40="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!Z46="P", 5, IF(Attendance!Z46="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <f>IF(Attendance!AA40="P", 5, IF(Attendance!AA40="O", 3, 0))</f>
+        <f>IF(Attendance!AA46="P", 5, IF(Attendance!AA46="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="AB40">
-        <f>IF(Attendance!AB40="P", 5, IF(Attendance!AB40="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AB46="P", 5, IF(Attendance!AB46="O", 3, 0))</f>
+        <v>3</v>
       </c>
       <c r="AC40">
-        <f>IF(Attendance!AC40="P", 5, IF(Attendance!AC40="O", 3, 0))</f>
-        <v>5</v>
+        <f>IF(Attendance!AC46="P", 5, IF(Attendance!AC46="O", 3, 0))</f>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <f>IF(Attendance!AD40="P", 5, IF(Attendance!AD40="O", 3, 0))</f>
+        <f>IF(Attendance!AD46="P", 5, IF(Attendance!AD46="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="AE40">
-        <f>IF(Attendance!AE40="P", 5, IF(Attendance!AE40="O", 3, 0))</f>
+        <f>IF(Attendance!AE46="P", 5, IF(Attendance!AE46="O", 3, 0))</f>
         <v>0</v>
       </c>
       <c r="AF40">
-        <f>IF(Attendance!AF40="P", 5, IF(Attendance!AF40="O", 3, 0))</f>
-        <v>0</v>
+        <f>IF(Attendance!AF46="P", 5, IF(Attendance!AF46="O", 3, 0))</f>
+        <v>5</v>
       </c>
       <c r="AG40">
-        <f>IF(Attendance!AG40="P", 5, IF(Attendance!AG40="O", 3, 0))</f>
+        <f>IF(Attendance!AG46="P", 5, IF(Attendance!AG46="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="AH40">
-        <f>IF(Attendance!AH40="P", 5, IF(Attendance!AH40="O", 3, 0))</f>
+        <f>IF(Attendance!AH46="P", 5, IF(Attendance!AH46="O", 3, 0))</f>
         <v>5</v>
       </c>
       <c r="AI40">
         <f t="shared" si="0"/>
-        <v>133</v>
+        <v>58</v>
       </c>
       <c r="AJ40">
         <f t="shared" si="1"/>
@@ -12119,912 +12456,32 @@
       </c>
       <c r="AK40">
         <f t="shared" si="2"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" t="s">
-        <v>34</v>
-      </c>
-      <c r="C41">
-        <f>IF(Attendance!C41="P", 5, IF(Attendance!C41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="D41">
-        <f>IF(Attendance!D41="P", 5, IF(Attendance!D41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="E41">
-        <f>IF(Attendance!E41="P", 5, IF(Attendance!E41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="F41">
-        <f>IF(Attendance!F41="P", 5, IF(Attendance!F41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="G41">
-        <f>IF(Attendance!G41="P", 5, IF(Attendance!G41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <f>IF(Attendance!H41="P", 5, IF(Attendance!H41="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="I41">
-        <f>IF(Attendance!I41="P", 5, IF(Attendance!I41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <f>IF(Attendance!J41="P", 5, IF(Attendance!J41="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="K41">
-        <f>IF(Attendance!K41="P", 5, IF(Attendance!K41="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="L41">
-        <f>IF(Attendance!L41="P", 5, IF(Attendance!L41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <f>IF(Attendance!M41="P", 5, IF(Attendance!M41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="N41">
-        <f>IF(Attendance!N41="P", 5, IF(Attendance!N41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="O41">
-        <f>IF(Attendance!O41="P", 5, IF(Attendance!O41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="P41">
-        <f>IF(Attendance!P41="P", 5, IF(Attendance!P41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="Q41">
-        <f>IF(Attendance!Q41="P", 5, IF(Attendance!Q41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="R41">
-        <f>IF(Attendance!R41="P", 5, IF(Attendance!R41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="S41">
-        <f>IF(Attendance!S41="P", 5, IF(Attendance!S41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="T41">
-        <f>IF(Attendance!T41="P", 5, IF(Attendance!T41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="U41">
-        <f>IF(Attendance!U41="P", 5, IF(Attendance!U41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="V41">
-        <f>IF(Attendance!V41="P", 5, IF(Attendance!V41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="W41">
-        <f>IF(Attendance!W41="P", 5, IF(Attendance!W41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="X41">
-        <f>IF(Attendance!X41="P", 5, IF(Attendance!X41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="Y41">
-        <f>IF(Attendance!Y41="P", 5, IF(Attendance!Y41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="Z41">
-        <f>IF(Attendance!Z41="P", 5, IF(Attendance!Z41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="AA41">
-        <f>IF(Attendance!AA41="P", 5, IF(Attendance!AA41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="AB41">
-        <f>IF(Attendance!AB41="P", 5, IF(Attendance!AB41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="AC41">
-        <f>IF(Attendance!AC41="P", 5, IF(Attendance!AC41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="AD41">
-        <f>IF(Attendance!AD41="P", 5, IF(Attendance!AD41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="AE41">
-        <f>IF(Attendance!AE41="P", 5, IF(Attendance!AE41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="AF41">
-        <f>IF(Attendance!AF41="P", 5, IF(Attendance!AF41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="AG41">
-        <f>IF(Attendance!AG41="P", 5, IF(Attendance!AG41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="AH41">
-        <f>IF(Attendance!AH41="P", 5, IF(Attendance!AH41="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="AI41">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AJ41">
-        <f t="shared" si="1"/>
-        <v>160</v>
-      </c>
-      <c r="AK41">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>29</v>
-      </c>
-      <c r="B42" t="s">
-        <v>34</v>
-      </c>
-      <c r="C42">
-        <f>IF(Attendance!C42="P", 5, IF(Attendance!C42="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="D42">
-        <f>IF(Attendance!D42="P", 5, IF(Attendance!D42="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="E42">
-        <f>IF(Attendance!E42="P", 5, IF(Attendance!E42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="F42">
-        <f>IF(Attendance!F42="P", 5, IF(Attendance!F42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="G42">
-        <f>IF(Attendance!G42="P", 5, IF(Attendance!G42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="H42">
-        <f>IF(Attendance!H42="P", 5, IF(Attendance!H42="O", 3, 0))</f>
-        <v>5</v>
-      </c>
-      <c r="I42">
-        <f>IF(Attendance!I42="P", 5, IF(Attendance!I42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="J42">
-        <f>IF(Attendance!J42="P", 5, IF(Attendance!J42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="K42">
-        <f>IF(Attendance!K42="P", 5, IF(Attendance!K42="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="L42">
-        <f>IF(Attendance!L42="P", 5, IF(Attendance!L42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="M42">
-        <f>IF(Attendance!M42="P", 5, IF(Attendance!M42="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="N42">
-        <f>IF(Attendance!N42="P", 5, IF(Attendance!N42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="O42">
-        <f>IF(Attendance!O42="P", 5, IF(Attendance!O42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="P42">
-        <f>IF(Attendance!P42="P", 5, IF(Attendance!P42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="Q42">
-        <f>IF(Attendance!Q42="P", 5, IF(Attendance!Q42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="R42">
-        <f>IF(Attendance!R42="P", 5, IF(Attendance!R42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="S42">
-        <f>IF(Attendance!S42="P", 5, IF(Attendance!S42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="T42">
-        <f>IF(Attendance!T42="P", 5, IF(Attendance!T42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="U42">
-        <f>IF(Attendance!U42="P", 5, IF(Attendance!U42="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="V42">
-        <f>IF(Attendance!V42="P", 5, IF(Attendance!V42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="W42">
-        <f>IF(Attendance!W42="P", 5, IF(Attendance!W42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="X42">
-        <f>IF(Attendance!X42="P", 5, IF(Attendance!X42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="Y42">
-        <f>IF(Attendance!Y42="P", 5, IF(Attendance!Y42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="Z42">
-        <f>IF(Attendance!Z42="P", 5, IF(Attendance!Z42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AA42">
-        <f>IF(Attendance!AA42="P", 5, IF(Attendance!AA42="O", 3, 0))</f>
-        <v>5</v>
-      </c>
-      <c r="AB42">
-        <f>IF(Attendance!AB42="P", 5, IF(Attendance!AB42="O", 3, 0))</f>
-        <v>5</v>
-      </c>
-      <c r="AC42">
-        <f>IF(Attendance!AC42="P", 5, IF(Attendance!AC42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AD42">
-        <f>IF(Attendance!AD42="P", 5, IF(Attendance!AD42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AE42">
-        <f>IF(Attendance!AE42="P", 5, IF(Attendance!AE42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AF42">
-        <f>IF(Attendance!AF42="P", 5, IF(Attendance!AF42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AG42">
-        <f>IF(Attendance!AG42="P", 5, IF(Attendance!AG42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AH42">
-        <f>IF(Attendance!AH42="P", 5, IF(Attendance!AH42="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AI42">
-        <f t="shared" si="0"/>
-        <v>87</v>
-      </c>
-      <c r="AJ42">
-        <f t="shared" si="1"/>
-        <v>160</v>
-      </c>
-      <c r="AK42">
-        <f t="shared" si="2"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" t="s">
-        <v>50</v>
-      </c>
-      <c r="C43">
-        <f>IF(Attendance!C43="P", 5, IF(Attendance!C43="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="D43">
-        <f>IF(Attendance!D43="P", 5, IF(Attendance!D43="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="E43">
-        <f>IF(Attendance!E43="P", 5, IF(Attendance!E43="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="F43">
-        <f>IF(Attendance!F43="P", 5, IF(Attendance!F43="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <f>IF(Attendance!G43="P", 5, IF(Attendance!G43="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <f>IF(Attendance!H43="P", 5, IF(Attendance!H43="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <f>IF(Attendance!I43="P", 5, IF(Attendance!I43="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="J43">
-        <f>IF(Attendance!J43="P", 5, IF(Attendance!J43="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <f>IF(Attendance!K43="P", 5, IF(Attendance!K43="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="L43">
-        <f>IF(Attendance!L43="P", 5, IF(Attendance!L43="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <f>IF(Attendance!M43="P", 5, IF(Attendance!M43="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="N43">
-        <f>IF(Attendance!N43="P", 5, IF(Attendance!N43="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="O43">
-        <f>IF(Attendance!O43="P", 5, IF(Attendance!O43="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="P43">
-        <f>IF(Attendance!P43="P", 5, IF(Attendance!P43="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="Q43">
-        <f>IF(Attendance!Q43="P", 5, IF(Attendance!Q43="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="R43">
-        <f>IF(Attendance!R43="P", 5, IF(Attendance!R43="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="S43">
-        <f>IF(Attendance!S43="P", 5, IF(Attendance!S43="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="T43">
-        <f>IF(Attendance!T43="P", 5, IF(Attendance!T43="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="U43">
-        <f>IF(Attendance!U43="P", 5, IF(Attendance!U43="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="V43">
-        <f>IF(Attendance!V43="P", 5, IF(Attendance!V43="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="W43">
-        <f>IF(Attendance!W43="P", 5, IF(Attendance!W43="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="X43">
-        <f>IF(Attendance!X43="P", 5, IF(Attendance!X43="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="Y43">
-        <f>IF(Attendance!Y43="P", 5, IF(Attendance!Y43="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="Z43">
-        <f>IF(Attendance!Z43="P", 5, IF(Attendance!Z43="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AA43">
-        <f>IF(Attendance!AA43="P", 5, IF(Attendance!AA43="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AB43">
-        <f>IF(Attendance!AB43="P", 5, IF(Attendance!AB43="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="AC43">
-        <f>IF(Attendance!AC43="P", 5, IF(Attendance!AC43="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="AD43">
-        <f>IF(Attendance!AD43="P", 5, IF(Attendance!AD43="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AE43">
-        <f>IF(Attendance!AE43="P", 5, IF(Attendance!AE43="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AF43">
-        <f>IF(Attendance!AF43="P", 5, IF(Attendance!AF43="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AG43">
-        <f>IF(Attendance!AG43="P", 5, IF(Attendance!AG43="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AH43">
-        <f>IF(Attendance!AH43="P", 5, IF(Attendance!AH43="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AI43">
-        <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-      <c r="AJ43">
-        <f t="shared" si="1"/>
-        <v>160</v>
-      </c>
-      <c r="AK43">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>16</v>
-      </c>
-      <c r="B44" t="s">
-        <v>34</v>
-      </c>
-      <c r="C44">
-        <f>IF(Attendance!C44="P", 5, IF(Attendance!C44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="D44">
-        <f>IF(Attendance!D44="P", 5, IF(Attendance!D44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="E44">
-        <f>IF(Attendance!E44="P", 5, IF(Attendance!E44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="F44">
-        <f>IF(Attendance!F44="P", 5, IF(Attendance!F44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="G44">
-        <f>IF(Attendance!G44="P", 5, IF(Attendance!G44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="H44">
-        <f>IF(Attendance!H44="P", 5, IF(Attendance!H44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="I44">
-        <f>IF(Attendance!I44="P", 5, IF(Attendance!I44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="J44">
-        <f>IF(Attendance!J44="P", 5, IF(Attendance!J44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="K44">
-        <f>IF(Attendance!K44="P", 5, IF(Attendance!K44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="L44">
-        <f>IF(Attendance!L44="P", 5, IF(Attendance!L44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="M44">
-        <f>IF(Attendance!M44="P", 5, IF(Attendance!M44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="N44">
-        <f>IF(Attendance!N44="P", 5, IF(Attendance!N44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="O44">
-        <f>IF(Attendance!O44="P", 5, IF(Attendance!O44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="P44">
-        <f>IF(Attendance!P44="P", 5, IF(Attendance!P44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="Q44">
-        <f>IF(Attendance!Q44="P", 5, IF(Attendance!Q44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="R44">
-        <f>IF(Attendance!R44="P", 5, IF(Attendance!R44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="S44">
-        <f>IF(Attendance!S44="P", 5, IF(Attendance!S44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="T44">
-        <f>IF(Attendance!T44="P", 5, IF(Attendance!T44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="U44">
-        <f>IF(Attendance!U44="P", 5, IF(Attendance!U44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="V44">
-        <f>IF(Attendance!V44="P", 5, IF(Attendance!V44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="W44">
-        <f>IF(Attendance!W44="P", 5, IF(Attendance!W44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="X44">
-        <f>IF(Attendance!X44="P", 5, IF(Attendance!X44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="Y44">
-        <f>IF(Attendance!Y44="P", 5, IF(Attendance!Y44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="Z44">
-        <f>IF(Attendance!Z44="P", 5, IF(Attendance!Z44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AA44">
-        <f>IF(Attendance!AA44="P", 5, IF(Attendance!AA44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AB44">
-        <f>IF(Attendance!AB44="P", 5, IF(Attendance!AB44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AC44">
-        <f>IF(Attendance!AC44="P", 5, IF(Attendance!AC44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AD44">
-        <f>IF(Attendance!AD44="P", 5, IF(Attendance!AD44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AE44">
-        <f>IF(Attendance!AE44="P", 5, IF(Attendance!AE44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AF44">
-        <f>IF(Attendance!AF44="P", 5, IF(Attendance!AF44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AG44">
-        <f>IF(Attendance!AG44="P", 5, IF(Attendance!AG44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AH44">
-        <f>IF(Attendance!AH44="P", 5, IF(Attendance!AH44="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AI44">
-        <f t="shared" si="0"/>
-        <v>96</v>
-      </c>
-      <c r="AJ44">
-        <f t="shared" si="1"/>
-        <v>160</v>
-      </c>
-      <c r="AK44">
-        <f t="shared" si="2"/>
+        <v>1.81</v>
+      </c>
+      <c r="AL40">
         <v>18</v>
       </c>
-    </row>
-    <row r="45" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>17</v>
-      </c>
-      <c r="B45" t="s">
-        <v>34</v>
-      </c>
-      <c r="C45">
-        <f>IF(Attendance!C45="P", 5, IF(Attendance!C45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="D45">
-        <f>IF(Attendance!D45="P", 5, IF(Attendance!D45="O", 3, 0))</f>
-        <v>5</v>
-      </c>
-      <c r="E45">
-        <f>IF(Attendance!E45="P", 5, IF(Attendance!E45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="F45">
-        <f>IF(Attendance!F45="P", 5, IF(Attendance!F45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="G45">
-        <f>IF(Attendance!G45="P", 5, IF(Attendance!G45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="H45">
-        <f>IF(Attendance!H45="P", 5, IF(Attendance!H45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="I45">
-        <f>IF(Attendance!I45="P", 5, IF(Attendance!I45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="J45">
-        <f>IF(Attendance!J45="P", 5, IF(Attendance!J45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="K45">
-        <f>IF(Attendance!K45="P", 5, IF(Attendance!K45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="L45">
-        <f>IF(Attendance!L45="P", 5, IF(Attendance!L45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="M45">
-        <f>IF(Attendance!M45="P", 5, IF(Attendance!M45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="N45">
-        <f>IF(Attendance!N45="P", 5, IF(Attendance!N45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="O45">
-        <f>IF(Attendance!O45="P", 5, IF(Attendance!O45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="P45">
-        <f>IF(Attendance!P45="P", 5, IF(Attendance!P45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="Q45">
-        <f>IF(Attendance!Q45="P", 5, IF(Attendance!Q45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="R45">
-        <f>IF(Attendance!R45="P", 5, IF(Attendance!R45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="S45">
-        <f>IF(Attendance!S45="P", 5, IF(Attendance!S45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="T45">
-        <f>IF(Attendance!T45="P", 5, IF(Attendance!T45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="U45">
-        <f>IF(Attendance!U45="P", 5, IF(Attendance!U45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="V45">
-        <f>IF(Attendance!V45="P", 5, IF(Attendance!V45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="W45">
-        <f>IF(Attendance!W45="P", 5, IF(Attendance!W45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="X45">
-        <f>IF(Attendance!X45="P", 5, IF(Attendance!X45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="Y45">
-        <f>IF(Attendance!Y45="P", 5, IF(Attendance!Y45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="Z45">
-        <f>IF(Attendance!Z45="P", 5, IF(Attendance!Z45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AA45">
-        <f>IF(Attendance!AA45="P", 5, IF(Attendance!AA45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AB45">
-        <f>IF(Attendance!AB45="P", 5, IF(Attendance!AB45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AC45">
-        <f>IF(Attendance!AC45="P", 5, IF(Attendance!AC45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AD45">
-        <f>IF(Attendance!AD45="P", 5, IF(Attendance!AD45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AE45">
-        <f>IF(Attendance!AE45="P", 5, IF(Attendance!AE45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AF45">
-        <f>IF(Attendance!AF45="P", 5, IF(Attendance!AF45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AG45">
-        <f>IF(Attendance!AG45="P", 5, IF(Attendance!AG45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AH45">
-        <f>IF(Attendance!AH45="P", 5, IF(Attendance!AH45="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AI45">
-        <f t="shared" si="0"/>
-        <v>98</v>
-      </c>
-      <c r="AJ45">
-        <f t="shared" si="1"/>
-        <v>160</v>
-      </c>
-      <c r="AK45">
-        <f t="shared" si="2"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="46" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>55</v>
-      </c>
-      <c r="B46" t="s">
-        <v>34</v>
-      </c>
-      <c r="C46">
-        <f>IF(Attendance!C46="P", 5, IF(Attendance!C46="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="D46">
-        <f>IF(Attendance!D46="P", 5, IF(Attendance!D46="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="E46">
-        <f>IF(Attendance!E46="P", 5, IF(Attendance!E46="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="F46">
-        <f>IF(Attendance!F46="P", 5, IF(Attendance!F46="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="G46">
-        <f>IF(Attendance!G46="P", 5, IF(Attendance!G46="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <f>IF(Attendance!H46="P", 5, IF(Attendance!H46="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <f>IF(Attendance!I46="P", 5, IF(Attendance!I46="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <f>IF(Attendance!J46="P", 5, IF(Attendance!J46="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <f>IF(Attendance!K46="P", 5, IF(Attendance!K46="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="L46">
-        <f>IF(Attendance!L46="P", 5, IF(Attendance!L46="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="M46">
-        <f>IF(Attendance!M46="P", 5, IF(Attendance!M46="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="N46">
-        <f>IF(Attendance!N46="P", 5, IF(Attendance!N46="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="O46">
-        <f>IF(Attendance!O46="P", 5, IF(Attendance!O46="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="P46">
-        <f>IF(Attendance!P46="P", 5, IF(Attendance!P46="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="Q46">
-        <f>IF(Attendance!Q46="P", 5, IF(Attendance!Q46="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="R46">
-        <f>IF(Attendance!R46="P", 5, IF(Attendance!R46="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="S46">
-        <f>IF(Attendance!S46="P", 5, IF(Attendance!S46="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="T46">
-        <f>IF(Attendance!T46="P", 5, IF(Attendance!T46="O", 3, 0))</f>
-        <v>5</v>
-      </c>
-      <c r="U46">
-        <f>IF(Attendance!U46="P", 5, IF(Attendance!U46="O", 3, 0))</f>
-        <v>5</v>
-      </c>
-      <c r="V46">
-        <f>IF(Attendance!V46="P", 5, IF(Attendance!V46="O", 3, 0))</f>
-        <v>5</v>
-      </c>
-      <c r="W46">
-        <f>IF(Attendance!W46="P", 5, IF(Attendance!W46="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="X46">
-        <f>IF(Attendance!X46="P", 5, IF(Attendance!X46="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="Y46">
-        <f>IF(Attendance!Y46="P", 5, IF(Attendance!Y46="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="Z46">
-        <f>IF(Attendance!Z46="P", 5, IF(Attendance!Z46="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="AA46">
-        <f>IF(Attendance!AA46="P", 5, IF(Attendance!AA46="O", 3, 0))</f>
-        <v>5</v>
-      </c>
-      <c r="AB46">
-        <f>IF(Attendance!AB46="P", 5, IF(Attendance!AB46="O", 3, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="AC46">
-        <f>IF(Attendance!AC46="P", 5, IF(Attendance!AC46="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="AD46">
-        <f>IF(Attendance!AD46="P", 5, IF(Attendance!AD46="O", 3, 0))</f>
-        <v>5</v>
-      </c>
-      <c r="AE46">
-        <f>IF(Attendance!AE46="P", 5, IF(Attendance!AE46="O", 3, 0))</f>
-        <v>0</v>
-      </c>
-      <c r="AF46">
-        <f>IF(Attendance!AF46="P", 5, IF(Attendance!AF46="O", 3, 0))</f>
-        <v>5</v>
-      </c>
-      <c r="AG46">
-        <f>IF(Attendance!AG46="P", 5, IF(Attendance!AG46="O", 3, 0))</f>
-        <v>5</v>
-      </c>
-      <c r="AH46">
-        <f>IF(Attendance!AH46="P", 5, IF(Attendance!AH46="O", 3, 0))</f>
-        <v>5</v>
-      </c>
-      <c r="AI46">
-        <f t="shared" si="0"/>
-        <v>58</v>
-      </c>
-      <c r="AJ46">
-        <f t="shared" si="1"/>
-        <v>160</v>
-      </c>
-      <c r="AK46">
-        <f t="shared" si="2"/>
-        <v>11</v>
+      <c r="AM40">
+        <f t="shared" si="12"/>
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72391264-C949-474E-92EC-AAF525C1839B}">
-  <dimension ref="A1:AJ7"/>
+  <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -13128,13 +12585,19 @@
         <v>45587</v>
       </c>
       <c r="AI1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AJ1" t="s">
         <v>64</v>
       </c>
-      <c r="AJ1" t="s">
-        <v>65</v>
+      <c r="AK1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -13274,11 +12737,14 @@
         <v>15</v>
       </c>
       <c r="AJ2">
-        <f>ROUND(AI2*30/160, 0)</f>
-        <v>3</v>
+        <f>ROUND(AI2*5/160, 2)</f>
+        <v>0.47</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -13418,11 +12884,14 @@
         <v>145</v>
       </c>
       <c r="AJ3">
-        <f t="shared" ref="AJ3:AJ7" si="1">ROUND(AI3*30/160, 0)</f>
-        <v>27</v>
+        <f t="shared" ref="AJ3:AJ7" si="1">ROUND(AI3*5/160, 2)</f>
+        <v>4.53</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>47</v>
       </c>
@@ -13563,10 +13032,13 @@
       </c>
       <c r="AJ4">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.16</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -13707,10 +13179,17 @@
       </c>
       <c r="AJ5">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>4.22</v>
+      </c>
+      <c r="AK5">
+        <v>18</v>
+      </c>
+      <c r="AL5">
+        <f>ROUND(AK5/4, 2)</f>
+        <v>4.5</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -13851,10 +13330,17 @@
       </c>
       <c r="AJ6">
         <f t="shared" si="1"/>
-        <v>27</v>
+        <v>4.53</v>
+      </c>
+      <c r="AK6">
+        <v>20</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" ref="AL6" si="2">ROUND(AK6/4, 2)</f>
+        <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>49</v>
       </c>
@@ -13995,10 +13481,336 @@
       </c>
       <c r="AJ7">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>2.81</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139CA830-C4C3-4AA5-93F2-A9AE770B0D69}">
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="33.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <f>ROUND(B2/4, 2)</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:C26" si="0">ROUND(B3/4, 2)</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4">
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5">
+        <v>16</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="6">
+        <v>20</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12">
+        <v>20</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13">
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16">
+        <v>10</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17">
+        <v>16</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18">
+        <v>20</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19">
+        <v>16</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20">
+        <v>20</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21">
+        <v>10</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="0"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22">
+        <v>10</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="0"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23">
+        <v>14</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="0"/>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24">
+        <v>20</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25">
+        <v>20</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26">
+        <v>18</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3510256-F516-4192-B971-D30FCC520E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E62544-1471-45CD-930C-D1328490C0CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendance" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1868" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="77">
   <si>
     <t>Name</t>
   </si>
@@ -393,7 +393,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -708,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:AI48"/>
+  <dimension ref="A1:AJ48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -725,7 +725,7 @@
     <col min="30" max="30" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -831,8 +831,11 @@
       <c r="AI1" s="1">
         <v>45590</v>
       </c>
+      <c r="AJ1" s="1">
+        <v>45594</v>
+      </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -938,8 +941,11 @@
       <c r="AI2" t="s">
         <v>2</v>
       </c>
+      <c r="AJ2" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1045,8 +1051,11 @@
       <c r="AI3" t="s">
         <v>2</v>
       </c>
+      <c r="AJ3" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1152,8 +1161,11 @@
       <c r="AI4" t="s">
         <v>2</v>
       </c>
+      <c r="AJ4" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -1260,7 +1272,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1366,8 +1378,11 @@
       <c r="AI6" t="s">
         <v>2</v>
       </c>
+      <c r="AJ6" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1474,7 +1489,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1580,8 +1595,11 @@
       <c r="AI8" t="s">
         <v>25</v>
       </c>
+      <c r="AJ8" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1688,7 +1706,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -1792,7 +1810,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1899,7 +1917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2006,7 +2024,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2112,8 +2130,11 @@
       <c r="AI13" t="s">
         <v>2</v>
       </c>
+      <c r="AJ13" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -2220,7 +2241,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -2327,7 +2348,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -2434,7 +2455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -2540,8 +2561,11 @@
       <c r="AI17" t="s">
         <v>2</v>
       </c>
+      <c r="AJ17" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -2647,8 +2671,11 @@
       <c r="AI18" t="s">
         <v>2</v>
       </c>
+      <c r="AJ18" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -2755,7 +2782,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2862,7 +2889,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +2995,11 @@
       <c r="AI21" t="s">
         <v>1</v>
       </c>
+      <c r="AJ21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -3049,7 +3079,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -3156,7 +3186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -3263,7 +3293,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -3370,7 +3400,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -3476,8 +3506,11 @@
       <c r="AI26" t="s">
         <v>2</v>
       </c>
+      <c r="AJ26" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -3583,8 +3616,11 @@
       <c r="AI27" t="s">
         <v>2</v>
       </c>
+      <c r="AJ27" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -3690,8 +3726,11 @@
       <c r="AI28" t="s">
         <v>2</v>
       </c>
+      <c r="AJ28" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -3797,8 +3836,11 @@
       <c r="AI29" t="s">
         <v>1</v>
       </c>
+      <c r="AJ29" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -3905,7 +3947,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -3984,8 +4026,11 @@
       <c r="AI31" t="s">
         <v>2</v>
       </c>
+      <c r="AJ31" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>45</v>
       </c>
@@ -4091,8 +4136,11 @@
       <c r="AI32" t="s">
         <v>25</v>
       </c>
+      <c r="AJ32" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -4199,7 +4247,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>24</v>
       </c>
@@ -4305,8 +4353,11 @@
       <c r="AI34" t="s">
         <v>2</v>
       </c>
+      <c r="AJ34" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -4412,8 +4463,11 @@
       <c r="AI35" t="s">
         <v>2</v>
       </c>
+      <c r="AJ35" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -4520,7 +4574,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -4626,8 +4680,11 @@
       <c r="AI37" t="s">
         <v>2</v>
       </c>
+      <c r="AJ37" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -4733,8 +4790,11 @@
       <c r="AI38" t="s">
         <v>2</v>
       </c>
+      <c r="AJ38" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -4841,7 +4901,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>23</v>
       </c>
@@ -4948,7 +5008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -5055,7 +5115,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -5161,8 +5221,11 @@
       <c r="AI42" t="s">
         <v>1</v>
       </c>
+      <c r="AJ42" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>49</v>
       </c>
@@ -5242,7 +5305,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>16</v>
       </c>
@@ -5348,8 +5411,11 @@
       <c r="AI44" t="s">
         <v>2</v>
       </c>
+      <c r="AJ44" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -5456,7 +5522,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>55</v>
       </c>
@@ -5562,8 +5628,11 @@
       <c r="AI46" t="s">
         <v>1</v>
       </c>
+      <c r="AJ46" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>38</v>
       </c>

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E62544-1471-45CD-930C-D1328490C0CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3FE127-4613-4542-8C87-AEDA5DB971C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="77">
   <si>
     <t>Name</t>
   </si>
@@ -708,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:AJ48"/>
+  <dimension ref="A1:AK48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -725,7 +725,7 @@
     <col min="30" max="30" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -834,8 +834,11 @@
       <c r="AJ1" s="1">
         <v>45594</v>
       </c>
+      <c r="AK1" s="1">
+        <v>45601</v>
+      </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -944,8 +947,11 @@
       <c r="AJ2" t="s">
         <v>2</v>
       </c>
+      <c r="AK2" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1054,8 +1060,11 @@
       <c r="AJ3" t="s">
         <v>2</v>
       </c>
+      <c r="AK3" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1165,7 +1174,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -1272,7 +1281,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1381,8 +1390,11 @@
       <c r="AJ6" t="s">
         <v>1</v>
       </c>
+      <c r="AK6" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1489,7 +1501,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1598,8 +1610,11 @@
       <c r="AJ8" t="s">
         <v>2</v>
       </c>
+      <c r="AK8" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1706,7 +1721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -1810,7 +1825,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1917,7 +1932,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2024,7 +2039,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2134,7 +2149,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -2241,7 +2256,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -2347,8 +2362,11 @@
       <c r="AI15" t="s">
         <v>25</v>
       </c>
+      <c r="AK15" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -2455,7 +2473,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -2564,8 +2582,11 @@
       <c r="AJ17" t="s">
         <v>2</v>
       </c>
+      <c r="AK17" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -2675,7 +2696,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -2782,7 +2803,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2889,7 +2910,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2998,8 +3019,11 @@
       <c r="AJ21" t="s">
         <v>1</v>
       </c>
+      <c r="AK21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -3079,7 +3103,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -3186,7 +3210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -3293,7 +3317,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -3399,8 +3423,11 @@
       <c r="AI25" t="s">
         <v>2</v>
       </c>
+      <c r="AK25" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -3510,7 +3537,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -3619,8 +3646,11 @@
       <c r="AJ27" t="s">
         <v>2</v>
       </c>
+      <c r="AK27" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -3729,8 +3759,11 @@
       <c r="AJ28" t="s">
         <v>2</v>
       </c>
+      <c r="AK28" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -3840,7 +3873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -3947,7 +3980,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -4029,8 +4062,11 @@
       <c r="AJ31" t="s">
         <v>2</v>
       </c>
+      <c r="AK31" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>45</v>
       </c>
@@ -4140,7 +4176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -4247,7 +4283,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>24</v>
       </c>
@@ -4356,8 +4392,11 @@
       <c r="AJ34" t="s">
         <v>2</v>
       </c>
+      <c r="AK34" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -4466,8 +4505,11 @@
       <c r="AJ35" t="s">
         <v>2</v>
       </c>
+      <c r="AK35" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -4573,8 +4615,11 @@
       <c r="AI36" t="s">
         <v>2</v>
       </c>
+      <c r="AK36" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -4684,7 +4729,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -4794,7 +4839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -4901,7 +4946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>23</v>
       </c>
@@ -5008,7 +5053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -5115,7 +5160,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -5224,8 +5269,11 @@
       <c r="AJ42" t="s">
         <v>2</v>
       </c>
+      <c r="AK42" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>49</v>
       </c>
@@ -5304,8 +5352,11 @@
       <c r="AI43" t="s">
         <v>2</v>
       </c>
+      <c r="AK43" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="44" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>16</v>
       </c>
@@ -5414,8 +5465,11 @@
       <c r="AJ44" t="s">
         <v>2</v>
       </c>
+      <c r="AK44" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -5522,7 +5576,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>55</v>
       </c>
@@ -5631,8 +5685,11 @@
       <c r="AJ46" t="s">
         <v>1</v>
       </c>
+      <c r="AK46" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>38</v>
       </c>

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3FE127-4613-4542-8C87-AEDA5DB971C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342C2C6F-3334-4415-9E26-560B094E384D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2052" uniqueCount="79">
   <si>
     <t>Name</t>
   </si>
@@ -260,6 +260,12 @@
   </si>
   <si>
     <t>Marks/5</t>
+  </si>
+  <si>
+    <t>Vedanshi Shah</t>
+  </si>
+  <si>
+    <t>Prit Patel</t>
   </si>
 </sst>
 </file>
@@ -708,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:AK48"/>
+  <dimension ref="A1:AM50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -725,7 +731,7 @@
     <col min="30" max="30" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -837,8 +843,14 @@
       <c r="AK1" s="1">
         <v>45601</v>
       </c>
+      <c r="AL1" s="1">
+        <v>45604</v>
+      </c>
+      <c r="AM1" s="1">
+        <v>45608</v>
+      </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -950,8 +962,14 @@
       <c r="AK2" t="s">
         <v>2</v>
       </c>
+      <c r="AL2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1063,8 +1081,14 @@
       <c r="AK3" t="s">
         <v>2</v>
       </c>
+      <c r="AL3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1173,8 +1197,14 @@
       <c r="AJ4" t="s">
         <v>2</v>
       </c>
+      <c r="AL4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -1280,8 +1310,20 @@
       <c r="AI5" t="s">
         <v>25</v>
       </c>
+      <c r="AJ5" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1393,8 +1435,14 @@
       <c r="AK6" t="s">
         <v>1</v>
       </c>
+      <c r="AL6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1501,7 +1549,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1613,8 +1661,11 @@
       <c r="AK8" t="s">
         <v>2</v>
       </c>
+      <c r="AL8" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1720,8 +1771,14 @@
       <c r="AI9" t="s">
         <v>2</v>
       </c>
+      <c r="AL9" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -1825,7 +1882,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1932,7 +1989,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2038,8 +2095,14 @@
       <c r="AI12" t="s">
         <v>25</v>
       </c>
+      <c r="AL12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2148,8 +2211,14 @@
       <c r="AJ13" t="s">
         <v>2</v>
       </c>
+      <c r="AL13" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -2256,7 +2325,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -2365,8 +2434,11 @@
       <c r="AK15" t="s">
         <v>2</v>
       </c>
+      <c r="AM15" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -2472,8 +2544,14 @@
       <c r="AI16" t="s">
         <v>2</v>
       </c>
+      <c r="AL16" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM16" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -2585,8 +2663,11 @@
       <c r="AK17" t="s">
         <v>2</v>
       </c>
+      <c r="AL17" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -2695,8 +2776,14 @@
       <c r="AJ18" t="s">
         <v>2</v>
       </c>
+      <c r="AL18" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM18" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -2803,7 +2890,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2909,8 +2996,14 @@
       <c r="AI20" t="s">
         <v>2</v>
       </c>
+      <c r="AL20" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM20" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3022,8 +3115,14 @@
       <c r="AK21" t="s">
         <v>1</v>
       </c>
+      <c r="AL21" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -3103,7 +3202,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -3209,8 +3308,14 @@
       <c r="AI23" t="s">
         <v>2</v>
       </c>
+      <c r="AL23" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM23" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -3317,7 +3422,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -3427,7 +3532,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -3536,8 +3641,17 @@
       <c r="AJ26" t="s">
         <v>2</v>
       </c>
+      <c r="AK26" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM26" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -3649,8 +3763,14 @@
       <c r="AK27" t="s">
         <v>2</v>
       </c>
+      <c r="AL27" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM27" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -3762,8 +3882,14 @@
       <c r="AK28" t="s">
         <v>2</v>
       </c>
+      <c r="AL28" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM28" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -3872,8 +3998,14 @@
       <c r="AJ29" t="s">
         <v>2</v>
       </c>
+      <c r="AL29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM29" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -3980,7 +4112,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -4066,7 +4198,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>45</v>
       </c>
@@ -4175,8 +4307,14 @@
       <c r="AJ32" t="s">
         <v>1</v>
       </c>
+      <c r="AL32" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM32" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -4282,8 +4420,11 @@
       <c r="AI33" t="s">
         <v>2</v>
       </c>
+      <c r="AM33" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>24</v>
       </c>
@@ -4395,8 +4536,14 @@
       <c r="AK34" t="s">
         <v>2</v>
       </c>
+      <c r="AL34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM34" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -4508,8 +4655,14 @@
       <c r="AK35" t="s">
         <v>1</v>
       </c>
+      <c r="AL35" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM35" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="36" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -4618,8 +4771,14 @@
       <c r="AK36" t="s">
         <v>2</v>
       </c>
+      <c r="AL36" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM36" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="37" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -4728,8 +4887,14 @@
       <c r="AJ37" t="s">
         <v>2</v>
       </c>
+      <c r="AL37" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM37" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="38" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -4838,8 +5003,14 @@
       <c r="AJ38" t="s">
         <v>1</v>
       </c>
+      <c r="AL38" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM38" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -4945,8 +5116,11 @@
       <c r="AI39" t="s">
         <v>2</v>
       </c>
+      <c r="AM39" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="40" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>23</v>
       </c>
@@ -5052,8 +5226,11 @@
       <c r="AI40" t="s">
         <v>1</v>
       </c>
+      <c r="AM40" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="41" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -5160,7 +5337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -5272,8 +5449,14 @@
       <c r="AK42" t="s">
         <v>2</v>
       </c>
+      <c r="AL42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM42" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="43" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>49</v>
       </c>
@@ -5355,8 +5538,11 @@
       <c r="AK43" t="s">
         <v>2</v>
       </c>
+      <c r="AL43" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="44" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>16</v>
       </c>
@@ -5468,8 +5654,14 @@
       <c r="AK44" t="s">
         <v>2</v>
       </c>
+      <c r="AL44" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM44" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="45" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -5575,8 +5767,20 @@
       <c r="AI45" t="s">
         <v>25</v>
       </c>
+      <c r="AJ45" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK45" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL45" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM45" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="46" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>55</v>
       </c>
@@ -5688,88 +5892,332 @@
       <c r="AK46" t="s">
         <v>1</v>
       </c>
+      <c r="AL46" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM46" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="48" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>77</v>
+      </c>
+      <c r="B47" t="s">
+        <v>34</v>
+      </c>
+      <c r="C47" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" t="s">
+        <v>32</v>
+      </c>
+      <c r="E47" t="s">
+        <v>32</v>
+      </c>
+      <c r="F47" t="s">
+        <v>32</v>
+      </c>
+      <c r="G47" t="s">
+        <v>32</v>
+      </c>
+      <c r="H47" t="s">
+        <v>32</v>
+      </c>
+      <c r="I47" t="s">
+        <v>32</v>
+      </c>
+      <c r="J47" t="s">
+        <v>32</v>
+      </c>
+      <c r="K47" t="s">
+        <v>32</v>
+      </c>
+      <c r="L47" t="s">
+        <v>32</v>
+      </c>
+      <c r="M47" t="s">
+        <v>32</v>
+      </c>
+      <c r="N47" t="s">
+        <v>32</v>
+      </c>
+      <c r="O47" t="s">
+        <v>32</v>
+      </c>
+      <c r="P47" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>32</v>
+      </c>
+      <c r="R47" t="s">
+        <v>32</v>
+      </c>
+      <c r="S47" t="s">
+        <v>32</v>
+      </c>
+      <c r="T47" t="s">
+        <v>32</v>
+      </c>
+      <c r="U47" t="s">
+        <v>32</v>
+      </c>
+      <c r="V47" t="s">
+        <v>32</v>
+      </c>
+      <c r="W47" t="s">
+        <v>32</v>
+      </c>
+      <c r="X47" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD47" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE47" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF47" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG47" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH47" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI47" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ47" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK47" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL47" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM47" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>78</v>
+      </c>
+      <c r="B48" t="s">
+        <v>34</v>
+      </c>
+      <c r="C48" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" t="s">
+        <v>32</v>
+      </c>
+      <c r="E48" t="s">
+        <v>32</v>
+      </c>
+      <c r="F48" t="s">
+        <v>32</v>
+      </c>
+      <c r="G48" t="s">
+        <v>32</v>
+      </c>
+      <c r="H48" t="s">
+        <v>32</v>
+      </c>
+      <c r="I48" t="s">
+        <v>32</v>
+      </c>
+      <c r="J48" t="s">
+        <v>32</v>
+      </c>
+      <c r="K48" t="s">
+        <v>32</v>
+      </c>
+      <c r="L48" t="s">
+        <v>32</v>
+      </c>
+      <c r="M48" t="s">
+        <v>32</v>
+      </c>
+      <c r="N48" t="s">
+        <v>32</v>
+      </c>
+      <c r="O48" t="s">
+        <v>32</v>
+      </c>
+      <c r="P48" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>32</v>
+      </c>
+      <c r="R48" t="s">
+        <v>32</v>
+      </c>
+      <c r="S48" t="s">
+        <v>32</v>
+      </c>
+      <c r="T48" t="s">
+        <v>32</v>
+      </c>
+      <c r="U48" t="s">
+        <v>32</v>
+      </c>
+      <c r="V48" t="s">
+        <v>32</v>
+      </c>
+      <c r="W48" t="s">
+        <v>32</v>
+      </c>
+      <c r="X48" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD48" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE48" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF48" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG48" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH48" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI48" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ48" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK48" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL48" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM48" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>38</v>
       </c>
-      <c r="C48">
+      <c r="C50">
         <f>COUNTIF(C1:C41, "P") +COUNTIF(C1:C41, "O")</f>
         <v>19</v>
       </c>
-      <c r="D48">
+      <c r="D50">
         <f>COUNTIF(D1:D41, "P") +COUNTIF(D1:D41, "O")</f>
         <v>21</v>
       </c>
-      <c r="E48">
+      <c r="E50">
         <f>COUNTIF(E1:E41, "P") +COUNTIF(E1:E41, "O")</f>
         <v>22</v>
       </c>
-      <c r="F48">
+      <c r="F50">
         <f>COUNTIF(F1:F41, "P") +COUNTIF(F1:F41, "O")</f>
         <v>24</v>
       </c>
-      <c r="G48">
-        <f t="shared" ref="G48:V48" si="0">COUNTIF(G1:G41, "P") +COUNTIF(G1:G41, "O")</f>
+      <c r="G50">
+        <f t="shared" ref="G50:V50" si="0">COUNTIF(G1:G41, "P") +COUNTIF(G1:G41, "O")</f>
         <v>24</v>
       </c>
-      <c r="H48">
+      <c r="H50">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="I48">
+      <c r="I50">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="J48">
+      <c r="J50">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="K48">
+      <c r="K50">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="L48">
+      <c r="L50">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="M48">
+      <c r="M50">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="N48">
+      <c r="N50">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="O48">
+      <c r="O50">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="P48">
+      <c r="P50">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="Q48">
+      <c r="Q50">
         <f>COUNTIF(Q1:Q41, "P") +COUNTIF(Q1:Q41, "O")</f>
         <v>28</v>
       </c>
-      <c r="R48">
+      <c r="R50">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="S48">
+      <c r="S50">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="T48">
+      <c r="T50">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="U48">
+      <c r="U50">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="V48">
+      <c r="V50">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342C2C6F-3334-4415-9E26-560B094E384D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9AB597F-3040-4ABB-A055-5711108E99D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2052" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2083" uniqueCount="79">
   <si>
     <t>Name</t>
   </si>
@@ -714,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:AM50"/>
+  <dimension ref="A1:AN50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -731,7 +731,7 @@
     <col min="30" max="30" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -849,8 +849,11 @@
       <c r="AM1" s="1">
         <v>45608</v>
       </c>
+      <c r="AN1" s="1">
+        <v>45611</v>
+      </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -968,8 +971,11 @@
       <c r="AM2" t="s">
         <v>2</v>
       </c>
+      <c r="AN2" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1087,8 +1093,11 @@
       <c r="AM3" t="s">
         <v>1</v>
       </c>
+      <c r="AN3" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1204,7 +1213,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -1322,8 +1331,11 @@
       <c r="AM5" t="s">
         <v>2</v>
       </c>
+      <c r="AN5" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1441,8 +1453,11 @@
       <c r="AM6" t="s">
         <v>1</v>
       </c>
+      <c r="AN6" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1549,7 +1564,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1665,7 +1680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1777,8 +1792,11 @@
       <c r="AM9" t="s">
         <v>2</v>
       </c>
+      <c r="AN9" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -1882,7 +1900,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1989,7 +2007,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2101,8 +2119,11 @@
       <c r="AM12" t="s">
         <v>1</v>
       </c>
+      <c r="AN12" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2217,8 +2238,11 @@
       <c r="AM13" t="s">
         <v>2</v>
       </c>
+      <c r="AN13" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -2325,7 +2349,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -2437,8 +2461,11 @@
       <c r="AM15" t="s">
         <v>2</v>
       </c>
+      <c r="AN15" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -2550,8 +2577,11 @@
       <c r="AM16" t="s">
         <v>1</v>
       </c>
+      <c r="AN16" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -2667,7 +2697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -2782,8 +2812,11 @@
       <c r="AM18" t="s">
         <v>2</v>
       </c>
+      <c r="AN18" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -2890,7 +2923,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -3003,7 +3036,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3121,8 +3154,11 @@
       <c r="AM21" t="s">
         <v>1</v>
       </c>
+      <c r="AN21" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -3202,7 +3238,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -3315,7 +3351,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -3422,7 +3458,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3567,11 @@
       <c r="AK25" t="s">
         <v>2</v>
       </c>
+      <c r="AN25" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -3650,8 +3689,11 @@
       <c r="AM26" t="s">
         <v>1</v>
       </c>
+      <c r="AN26" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -3769,8 +3811,11 @@
       <c r="AM27" t="s">
         <v>2</v>
       </c>
+      <c r="AN27" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -3889,7 +3934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -4004,8 +4049,11 @@
       <c r="AM29" t="s">
         <v>1</v>
       </c>
+      <c r="AN29" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="30" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -4112,7 +4160,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -4197,8 +4245,11 @@
       <c r="AK31" t="s">
         <v>2</v>
       </c>
+      <c r="AN31" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="32" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>45</v>
       </c>
@@ -4313,8 +4364,11 @@
       <c r="AM32" t="s">
         <v>2</v>
       </c>
+      <c r="AN32" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -4424,7 +4478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>24</v>
       </c>
@@ -4542,8 +4596,11 @@
       <c r="AM34" t="s">
         <v>1</v>
       </c>
+      <c r="AN34" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -4661,8 +4718,11 @@
       <c r="AM35" t="s">
         <v>2</v>
       </c>
+      <c r="AN35" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -4777,8 +4837,11 @@
       <c r="AM36" t="s">
         <v>2</v>
       </c>
+      <c r="AN36" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="37" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -4893,8 +4956,11 @@
       <c r="AM37" t="s">
         <v>1</v>
       </c>
+      <c r="AN37" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -5009,8 +5075,11 @@
       <c r="AM38" t="s">
         <v>2</v>
       </c>
+      <c r="AN38" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -5119,8 +5188,11 @@
       <c r="AM39" t="s">
         <v>2</v>
       </c>
+      <c r="AN39" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="40" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>23</v>
       </c>
@@ -5229,8 +5301,11 @@
       <c r="AM40" t="s">
         <v>1</v>
       </c>
+      <c r="AN40" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="41" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -5337,7 +5412,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -5455,8 +5530,11 @@
       <c r="AM42" t="s">
         <v>2</v>
       </c>
+      <c r="AN42" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="43" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>49</v>
       </c>
@@ -5541,8 +5619,11 @@
       <c r="AL43" t="s">
         <v>2</v>
       </c>
+      <c r="AN43" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="44" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>16</v>
       </c>
@@ -5660,8 +5741,11 @@
       <c r="AM44" t="s">
         <v>2</v>
       </c>
+      <c r="AN44" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="45" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -5779,8 +5863,11 @@
       <c r="AM45" t="s">
         <v>2</v>
       </c>
+      <c r="AN45" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="46" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>55</v>
       </c>
@@ -5898,8 +5985,11 @@
       <c r="AM46" t="s">
         <v>1</v>
       </c>
+      <c r="AN46" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="47" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>77</v>
       </c>
@@ -6017,8 +6107,11 @@
       <c r="AM47" t="s">
         <v>1</v>
       </c>
+      <c r="AN47" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="48" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>78</v>
       </c>
@@ -6134,6 +6227,9 @@
         <v>32</v>
       </c>
       <c r="AM48" t="s">
+        <v>2</v>
+      </c>
+      <c r="AN48" t="s">
         <v>2</v>
       </c>
     </row>

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9AB597F-3040-4ABB-A055-5711108E99D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5C7FCB-1206-416A-9239-94D47B7A4CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2083" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2197" uniqueCount="79">
   <si>
     <t>Name</t>
   </si>
@@ -714,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:AN50"/>
+  <dimension ref="A1:AP50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -731,7 +731,7 @@
     <col min="30" max="30" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -852,8 +852,14 @@
       <c r="AN1" s="1">
         <v>45611</v>
       </c>
+      <c r="AO1" s="1">
+        <v>45615</v>
+      </c>
+      <c r="AP1" s="1">
+        <v>45622</v>
+      </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -974,8 +980,14 @@
       <c r="AN2" t="s">
         <v>2</v>
       </c>
+      <c r="AO2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1096,8 +1108,14 @@
       <c r="AN3" t="s">
         <v>2</v>
       </c>
+      <c r="AO3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1212,8 +1230,17 @@
       <c r="AM4" t="s">
         <v>2</v>
       </c>
+      <c r="AN4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -1334,8 +1361,14 @@
       <c r="AN5" t="s">
         <v>2</v>
       </c>
+      <c r="AO5" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1456,8 +1489,14 @@
       <c r="AN6" t="s">
         <v>1</v>
       </c>
+      <c r="AO6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1563,8 +1602,14 @@
       <c r="AI7" t="s">
         <v>25</v>
       </c>
+      <c r="AO7" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1679,8 +1724,20 @@
       <c r="AL8" t="s">
         <v>2</v>
       </c>
+      <c r="AM8" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1795,8 +1852,14 @@
       <c r="AN9" t="s">
         <v>2</v>
       </c>
+      <c r="AO9" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -1899,8 +1962,14 @@
       <c r="AH10" t="s">
         <v>51</v>
       </c>
+      <c r="AO10" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -2006,8 +2075,14 @@
       <c r="AI11" t="s">
         <v>2</v>
       </c>
+      <c r="AO11" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2122,8 +2197,14 @@
       <c r="AN12" t="s">
         <v>1</v>
       </c>
+      <c r="AO12" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2241,8 +2322,14 @@
       <c r="AN13" t="s">
         <v>2</v>
       </c>
+      <c r="AO13" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -2348,8 +2435,14 @@
       <c r="AI14" t="s">
         <v>25</v>
       </c>
+      <c r="AO14" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP14" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -2458,14 +2551,23 @@
       <c r="AK15" t="s">
         <v>2</v>
       </c>
+      <c r="AL15" t="s">
+        <v>25</v>
+      </c>
       <c r="AM15" t="s">
         <v>2</v>
       </c>
       <c r="AN15" t="s">
         <v>2</v>
       </c>
+      <c r="AO15" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP15" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -2571,6 +2673,12 @@
       <c r="AI16" t="s">
         <v>2</v>
       </c>
+      <c r="AJ16" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>25</v>
+      </c>
       <c r="AL16" t="s">
         <v>2</v>
       </c>
@@ -2580,8 +2688,14 @@
       <c r="AN16" t="s">
         <v>2</v>
       </c>
+      <c r="AO16" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP16" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="17" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -2696,8 +2810,20 @@
       <c r="AL17" t="s">
         <v>2</v>
       </c>
+      <c r="AM17" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO17" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP17" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="18" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -2806,6 +2932,9 @@
       <c r="AJ18" t="s">
         <v>2</v>
       </c>
+      <c r="AK18" t="s">
+        <v>25</v>
+      </c>
       <c r="AL18" t="s">
         <v>2</v>
       </c>
@@ -2815,8 +2944,14 @@
       <c r="AN18" t="s">
         <v>2</v>
       </c>
+      <c r="AO18" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP18" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="19" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -2922,8 +3057,14 @@
       <c r="AI19" t="s">
         <v>25</v>
       </c>
+      <c r="AO19" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP19" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="20" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -3029,14 +3170,29 @@
       <c r="AI20" t="s">
         <v>2</v>
       </c>
+      <c r="AJ20" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>25</v>
+      </c>
       <c r="AL20" t="s">
         <v>2</v>
       </c>
       <c r="AM20" t="s">
         <v>2</v>
       </c>
+      <c r="AN20" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO20" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP20" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="21" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3157,8 +3313,14 @@
       <c r="AN21" t="s">
         <v>2</v>
       </c>
+      <c r="AO21" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -3237,8 +3399,14 @@
       <c r="AI22" t="s">
         <v>25</v>
       </c>
+      <c r="AO22" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP22" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="23" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -3350,8 +3518,14 @@
       <c r="AM23" t="s">
         <v>2</v>
       </c>
+      <c r="AO23" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP23" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="24" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -3457,8 +3631,14 @@
       <c r="AI24" t="s">
         <v>25</v>
       </c>
+      <c r="AO24" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP24" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="25" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -3570,8 +3750,14 @@
       <c r="AN25" t="s">
         <v>2</v>
       </c>
+      <c r="AO25" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP25" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="26" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -3692,8 +3878,14 @@
       <c r="AN26" t="s">
         <v>2</v>
       </c>
+      <c r="AO26" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP26" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="27" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -3814,8 +4006,14 @@
       <c r="AN27" t="s">
         <v>2</v>
       </c>
+      <c r="AO27" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP27" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="28" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -3933,8 +4131,14 @@
       <c r="AM28" t="s">
         <v>2</v>
       </c>
+      <c r="AO28" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP28" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="29" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -4052,8 +4256,14 @@
       <c r="AN29" t="s">
         <v>1</v>
       </c>
+      <c r="AO29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP29" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="30" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -4159,8 +4369,29 @@
       <c r="AI30" t="s">
         <v>25</v>
       </c>
+      <c r="AJ30" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM30" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO30" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP30" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="31" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -4248,8 +4479,14 @@
       <c r="AN31" t="s">
         <v>2</v>
       </c>
+      <c r="AO31" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP31" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="32" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>45</v>
       </c>
@@ -4367,8 +4604,14 @@
       <c r="AN32" t="s">
         <v>1</v>
       </c>
+      <c r="AO32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP32" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -4477,8 +4720,17 @@
       <c r="AM33" t="s">
         <v>1</v>
       </c>
+      <c r="AN33" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP33" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="34" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>24</v>
       </c>
@@ -4599,8 +4851,14 @@
       <c r="AN34" t="s">
         <v>1</v>
       </c>
+      <c r="AO34" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP34" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="35" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -4721,8 +4979,14 @@
       <c r="AN35" t="s">
         <v>2</v>
       </c>
+      <c r="AO35" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP35" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="36" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -4840,8 +5104,14 @@
       <c r="AN36" t="s">
         <v>2</v>
       </c>
+      <c r="AO36" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP36" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="37" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -4959,8 +5229,14 @@
       <c r="AN37" t="s">
         <v>2</v>
       </c>
+      <c r="AO37" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP37" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="38" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -5078,8 +5354,14 @@
       <c r="AN38" t="s">
         <v>2</v>
       </c>
+      <c r="AO38" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP38" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -5191,8 +5473,14 @@
       <c r="AN39" t="s">
         <v>2</v>
       </c>
+      <c r="AO39" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP39" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="40" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>23</v>
       </c>
@@ -5304,8 +5592,14 @@
       <c r="AN40" t="s">
         <v>1</v>
       </c>
+      <c r="AO40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP40" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="41" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -5411,8 +5705,14 @@
       <c r="AI41" t="s">
         <v>25</v>
       </c>
+      <c r="AO41" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP41" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="42" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -5533,8 +5833,14 @@
       <c r="AN42" t="s">
         <v>2</v>
       </c>
+      <c r="AO42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP42" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="43" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>49</v>
       </c>
@@ -5613,17 +5919,29 @@
       <c r="AI43" t="s">
         <v>2</v>
       </c>
+      <c r="AJ43" t="s">
+        <v>25</v>
+      </c>
       <c r="AK43" t="s">
         <v>2</v>
       </c>
       <c r="AL43" t="s">
         <v>2</v>
       </c>
+      <c r="AM43" t="s">
+        <v>25</v>
+      </c>
       <c r="AN43" t="s">
         <v>2</v>
       </c>
+      <c r="AO43" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP43" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="44" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>16</v>
       </c>
@@ -5744,8 +6062,14 @@
       <c r="AN44" t="s">
         <v>2</v>
       </c>
+      <c r="AO44" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP44" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="45" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -5866,8 +6190,14 @@
       <c r="AN45" t="s">
         <v>2</v>
       </c>
+      <c r="AO45" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP45" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="46" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>55</v>
       </c>
@@ -5988,8 +6318,14 @@
       <c r="AN46" t="s">
         <v>1</v>
       </c>
+      <c r="AO46" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP46" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="47" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>77</v>
       </c>
@@ -6110,8 +6446,14 @@
       <c r="AN47" t="s">
         <v>1</v>
       </c>
+      <c r="AO47" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP47" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="48" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>78</v>
       </c>
@@ -6230,6 +6572,12 @@
         <v>2</v>
       </c>
       <c r="AN48" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO48" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP48" t="s">
         <v>2</v>
       </c>
     </row>

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5C7FCB-1206-416A-9239-94D47B7A4CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{789F7372-D329-4065-B915-CFBE631E1874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2197" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="79">
   <si>
     <t>Name</t>
   </si>
@@ -714,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:AP50"/>
+  <dimension ref="A1:AQ50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -729,9 +729,12 @@
     <col min="26" max="27" width="5.5546875" bestFit="1" customWidth="1"/>
     <col min="28" max="29" width="6.5546875" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="36" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="6" bestFit="1" customWidth="1"/>
+    <col min="39" max="43" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -858,8 +861,11 @@
       <c r="AP1" s="1">
         <v>45622</v>
       </c>
+      <c r="AQ1" s="1">
+        <v>45625</v>
+      </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -986,8 +992,11 @@
       <c r="AP2" t="s">
         <v>2</v>
       </c>
+      <c r="AQ2" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1114,8 +1123,11 @@
       <c r="AP3" t="s">
         <v>1</v>
       </c>
+      <c r="AQ3" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1239,8 +1251,11 @@
       <c r="AP4" t="s">
         <v>25</v>
       </c>
+      <c r="AQ4" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -1367,8 +1382,11 @@
       <c r="AP5" t="s">
         <v>25</v>
       </c>
+      <c r="AQ5" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1495,8 +1513,11 @@
       <c r="AP6" t="s">
         <v>1</v>
       </c>
+      <c r="AQ6" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1602,14 +1623,20 @@
       <c r="AI7" t="s">
         <v>25</v>
       </c>
+      <c r="AN7" t="s">
+        <v>25</v>
+      </c>
       <c r="AO7" t="s">
         <v>25</v>
       </c>
       <c r="AP7" t="s">
         <v>25</v>
       </c>
+      <c r="AQ7" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1736,8 +1763,11 @@
       <c r="AP8" t="s">
         <v>25</v>
       </c>
+      <c r="AQ8" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1858,8 +1888,11 @@
       <c r="AP9" t="s">
         <v>2</v>
       </c>
+      <c r="AQ9" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -1962,14 +1995,20 @@
       <c r="AH10" t="s">
         <v>51</v>
       </c>
+      <c r="AN10" t="s">
+        <v>25</v>
+      </c>
       <c r="AO10" t="s">
         <v>25</v>
       </c>
       <c r="AP10" t="s">
         <v>25</v>
       </c>
+      <c r="AQ10" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -2075,14 +2114,20 @@
       <c r="AI11" t="s">
         <v>2</v>
       </c>
+      <c r="AN11" t="s">
+        <v>25</v>
+      </c>
       <c r="AO11" t="s">
         <v>25</v>
       </c>
       <c r="AP11" t="s">
         <v>25</v>
       </c>
+      <c r="AQ11" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2203,8 +2248,11 @@
       <c r="AP12" t="s">
         <v>2</v>
       </c>
+      <c r="AQ12" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2328,8 +2376,11 @@
       <c r="AP13" t="s">
         <v>2</v>
       </c>
+      <c r="AQ13" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -2435,14 +2486,20 @@
       <c r="AI14" t="s">
         <v>25</v>
       </c>
+      <c r="AN14" t="s">
+        <v>25</v>
+      </c>
       <c r="AO14" t="s">
         <v>25</v>
       </c>
       <c r="AP14" t="s">
         <v>25</v>
       </c>
+      <c r="AQ14" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -2566,8 +2623,11 @@
       <c r="AP15" t="s">
         <v>2</v>
       </c>
+      <c r="AQ15" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -2694,8 +2754,11 @@
       <c r="AP16" t="s">
         <v>2</v>
       </c>
+      <c r="AQ16" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -2822,8 +2885,11 @@
       <c r="AP17" t="s">
         <v>25</v>
       </c>
+      <c r="AQ17" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -2950,8 +3016,11 @@
       <c r="AP18" t="s">
         <v>25</v>
       </c>
+      <c r="AQ18" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -3057,14 +3126,20 @@
       <c r="AI19" t="s">
         <v>25</v>
       </c>
+      <c r="AN19" t="s">
+        <v>25</v>
+      </c>
       <c r="AO19" t="s">
         <v>25</v>
       </c>
       <c r="AP19" t="s">
         <v>25</v>
       </c>
+      <c r="AQ19" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -3191,8 +3266,11 @@
       <c r="AP20" t="s">
         <v>25</v>
       </c>
+      <c r="AQ20" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3319,8 +3397,11 @@
       <c r="AP21" t="s">
         <v>1</v>
       </c>
+      <c r="AQ21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -3399,14 +3480,20 @@
       <c r="AI22" t="s">
         <v>25</v>
       </c>
+      <c r="AN22" t="s">
+        <v>25</v>
+      </c>
       <c r="AO22" t="s">
         <v>25</v>
       </c>
       <c r="AP22" t="s">
         <v>25</v>
       </c>
+      <c r="AQ22" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -3518,14 +3605,20 @@
       <c r="AM23" t="s">
         <v>2</v>
       </c>
+      <c r="AN23" t="s">
+        <v>25</v>
+      </c>
       <c r="AO23" t="s">
         <v>2</v>
       </c>
       <c r="AP23" t="s">
         <v>25</v>
       </c>
+      <c r="AQ23" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -3631,14 +3724,20 @@
       <c r="AI24" t="s">
         <v>25</v>
       </c>
+      <c r="AN24" t="s">
+        <v>25</v>
+      </c>
       <c r="AO24" t="s">
         <v>25</v>
       </c>
       <c r="AP24" t="s">
         <v>25</v>
       </c>
+      <c r="AQ24" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -3756,8 +3855,11 @@
       <c r="AP25" t="s">
         <v>25</v>
       </c>
+      <c r="AQ25" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -3884,8 +3986,11 @@
       <c r="AP26" t="s">
         <v>1</v>
       </c>
+      <c r="AQ26" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -4012,8 +4117,11 @@
       <c r="AP27" t="s">
         <v>2</v>
       </c>
+      <c r="AQ27" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -4131,14 +4239,20 @@
       <c r="AM28" t="s">
         <v>2</v>
       </c>
+      <c r="AN28" t="s">
+        <v>25</v>
+      </c>
       <c r="AO28" t="s">
         <v>2</v>
       </c>
       <c r="AP28" t="s">
         <v>25</v>
       </c>
+      <c r="AQ28" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -4262,8 +4376,11 @@
       <c r="AP29" t="s">
         <v>1</v>
       </c>
+      <c r="AQ29" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -4390,8 +4507,11 @@
       <c r="AP30" t="s">
         <v>2</v>
       </c>
+      <c r="AQ30" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -4485,8 +4605,11 @@
       <c r="AP31" t="s">
         <v>1</v>
       </c>
+      <c r="AQ31" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>45</v>
       </c>
@@ -4610,8 +4733,11 @@
       <c r="AP32" t="s">
         <v>1</v>
       </c>
+      <c r="AQ32" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -4729,8 +4855,11 @@
       <c r="AP33" t="s">
         <v>25</v>
       </c>
+      <c r="AQ33" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>24</v>
       </c>
@@ -4857,8 +4986,11 @@
       <c r="AP34" t="s">
         <v>1</v>
       </c>
+      <c r="AQ34" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -4985,8 +5117,11 @@
       <c r="AP35" t="s">
         <v>2</v>
       </c>
+      <c r="AQ35" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -5110,8 +5245,11 @@
       <c r="AP36" t="s">
         <v>2</v>
       </c>
+      <c r="AQ36" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="37" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -5235,8 +5373,11 @@
       <c r="AP37" t="s">
         <v>1</v>
       </c>
+      <c r="AQ37" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="38" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -5360,8 +5501,11 @@
       <c r="AP38" t="s">
         <v>2</v>
       </c>
+      <c r="AQ38" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -5479,8 +5623,11 @@
       <c r="AP39" t="s">
         <v>2</v>
       </c>
+      <c r="AQ39" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="40" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>23</v>
       </c>
@@ -5598,8 +5745,11 @@
       <c r="AP40" t="s">
         <v>25</v>
       </c>
+      <c r="AQ40" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="41" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -5705,14 +5855,20 @@
       <c r="AI41" t="s">
         <v>25</v>
       </c>
+      <c r="AN41" t="s">
+        <v>25</v>
+      </c>
       <c r="AO41" t="s">
         <v>25</v>
       </c>
       <c r="AP41" t="s">
         <v>25</v>
       </c>
+      <c r="AQ41" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="42" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -5839,8 +5995,11 @@
       <c r="AP42" t="s">
         <v>25</v>
       </c>
+      <c r="AQ42" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="43" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>49</v>
       </c>
@@ -5940,8 +6099,11 @@
       <c r="AP43" t="s">
         <v>2</v>
       </c>
+      <c r="AQ43" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="44" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>16</v>
       </c>
@@ -6068,8 +6230,11 @@
       <c r="AP44" t="s">
         <v>2</v>
       </c>
+      <c r="AQ44" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="45" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -6196,8 +6361,11 @@
       <c r="AP45" t="s">
         <v>2</v>
       </c>
+      <c r="AQ45" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="46" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>55</v>
       </c>
@@ -6324,8 +6492,11 @@
       <c r="AP46" t="s">
         <v>1</v>
       </c>
+      <c r="AQ46" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="47" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>77</v>
       </c>
@@ -6452,8 +6623,11 @@
       <c r="AP47" t="s">
         <v>1</v>
       </c>
+      <c r="AQ47" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>78</v>
       </c>
@@ -6579,6 +6753,9 @@
       </c>
       <c r="AP48" t="s">
         <v>2</v>
+      </c>
+      <c r="AQ48" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.3">

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{789F7372-D329-4065-B915-CFBE631E1874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0504FC8-5495-4D1E-93B1-01D7798DC66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -19,6 +19,9 @@
     <sheet name="Sheet4" sheetId="6" r:id="rId4"/>
     <sheet name="Sheet2" sheetId="7" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Attendance!$A$1:$AR$48</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -29,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2350" uniqueCount="79">
   <si>
     <t>Name</t>
   </si>
@@ -714,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:AQ50"/>
+  <dimension ref="A1:AT50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -734,7 +737,7 @@
     <col min="39" max="43" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -864,8 +867,17 @@
       <c r="AQ1" s="1">
         <v>45625</v>
       </c>
+      <c r="AR1" s="1">
+        <v>45629</v>
+      </c>
+      <c r="AS1" s="1">
+        <v>45632</v>
+      </c>
+      <c r="AT1" s="1">
+        <v>45636</v>
+      </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -995,8 +1007,17 @@
       <c r="AQ2" t="s">
         <v>2</v>
       </c>
+      <c r="AR2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1126,8 +1147,17 @@
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
+      <c r="AR3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1254,8 +1284,11 @@
       <c r="AQ4" t="s">
         <v>25</v>
       </c>
+      <c r="AR4" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -1385,8 +1418,14 @@
       <c r="AQ5" t="s">
         <v>25</v>
       </c>
+      <c r="AR5" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1516,8 +1555,17 @@
       <c r="AQ6" t="s">
         <v>2</v>
       </c>
+      <c r="AR6" t="s">
+        <v>25</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1635,8 +1683,11 @@
       <c r="AQ7" t="s">
         <v>25</v>
       </c>
+      <c r="AR7" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1766,8 +1817,11 @@
       <c r="AQ8" t="s">
         <v>25</v>
       </c>
+      <c r="AR8" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1891,8 +1945,14 @@
       <c r="AQ9" t="s">
         <v>25</v>
       </c>
+      <c r="AR9" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -2007,8 +2067,11 @@
       <c r="AQ10" t="s">
         <v>25</v>
       </c>
+      <c r="AR10" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -2126,8 +2189,11 @@
       <c r="AQ11" t="s">
         <v>25</v>
       </c>
+      <c r="AR11" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2251,8 +2317,17 @@
       <c r="AQ12" t="s">
         <v>2</v>
       </c>
+      <c r="AR12" t="s">
+        <v>25</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2379,8 +2454,14 @@
       <c r="AQ13" t="s">
         <v>2</v>
       </c>
+      <c r="AR13" t="s">
+        <v>25</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -2498,8 +2579,11 @@
       <c r="AQ14" t="s">
         <v>25</v>
       </c>
+      <c r="AR14" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -2626,8 +2710,17 @@
       <c r="AQ15" t="s">
         <v>2</v>
       </c>
+      <c r="AR15" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS15" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT15" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -2757,8 +2850,17 @@
       <c r="AQ16" t="s">
         <v>2</v>
       </c>
+      <c r="AR16" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS16" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT16" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -2888,8 +2990,17 @@
       <c r="AQ17" t="s">
         <v>2</v>
       </c>
+      <c r="AR17" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS17" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT17" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -3019,8 +3130,17 @@
       <c r="AQ18" t="s">
         <v>2</v>
       </c>
+      <c r="AR18" t="s">
+        <v>25</v>
+      </c>
+      <c r="AS18" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT18" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -3138,8 +3258,11 @@
       <c r="AQ19" t="s">
         <v>25</v>
       </c>
+      <c r="AR19" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -3269,8 +3392,14 @@
       <c r="AQ20" t="s">
         <v>2</v>
       </c>
+      <c r="AR20" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT20" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3400,8 +3529,17 @@
       <c r="AQ21" t="s">
         <v>1</v>
       </c>
+      <c r="AR21" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS21" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -3492,8 +3630,11 @@
       <c r="AQ22" t="s">
         <v>25</v>
       </c>
+      <c r="AR22" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -3617,8 +3758,17 @@
       <c r="AQ23" t="s">
         <v>25</v>
       </c>
+      <c r="AR23" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS23" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT23" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -3736,8 +3886,11 @@
       <c r="AQ24" t="s">
         <v>25</v>
       </c>
+      <c r="AR24" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -3858,8 +4011,11 @@
       <c r="AQ25" t="s">
         <v>25</v>
       </c>
+      <c r="AR25" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -3989,8 +4145,14 @@
       <c r="AQ26" t="s">
         <v>1</v>
       </c>
+      <c r="AR26" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT26" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -4120,8 +4282,14 @@
       <c r="AQ27" t="s">
         <v>25</v>
       </c>
+      <c r="AR27" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT27" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -4251,8 +4419,17 @@
       <c r="AQ28" t="s">
         <v>2</v>
       </c>
+      <c r="AR28" t="s">
+        <v>25</v>
+      </c>
+      <c r="AS28" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT28" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -4379,8 +4556,11 @@
       <c r="AQ29" t="s">
         <v>2</v>
       </c>
+      <c r="AR29" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -4510,8 +4690,14 @@
       <c r="AQ30" t="s">
         <v>2</v>
       </c>
+      <c r="AR30" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS30" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -4608,10 +4794,16 @@
       <c r="AQ31" t="s">
         <v>2</v>
       </c>
+      <c r="AR31" t="s">
+        <v>25</v>
+      </c>
+      <c r="AS31" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="B32" t="s">
         <v>34</v>
@@ -4644,159 +4836,165 @@
         <v>32</v>
       </c>
       <c r="L32" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="M32" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="N32" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="O32" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="P32" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="Q32" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="R32" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="S32" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="T32" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="U32" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="V32" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="W32" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="X32" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="Y32" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="Z32" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AA32" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB32" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AC32" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AD32" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AE32" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AF32" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AG32" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AH32" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AI32" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AJ32" t="s">
-        <v>1</v>
+        <v>32</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>32</v>
       </c>
       <c r="AL32" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AM32" t="s">
         <v>2</v>
       </c>
       <c r="AN32" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO32" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP32" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ32" t="s">
         <v>25</v>
       </c>
+      <c r="AR32" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
         <v>34</v>
       </c>
       <c r="C33" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D33" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="E33" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="F33" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="G33" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="H33" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="I33" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="J33" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="K33" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="L33" t="s">
         <v>2</v>
       </c>
       <c r="M33" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N33" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q33" t="s">
         <v>2</v>
       </c>
       <c r="R33" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S33" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T33" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="U33" t="s">
         <v>1</v>
@@ -4814,114 +5012,123 @@
         <v>1</v>
       </c>
       <c r="Z33" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA33" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB33" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AC33" t="s">
         <v>25</v>
       </c>
       <c r="AD33" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AE33" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF33" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AG33" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AI33" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL33" t="s">
         <v>2</v>
       </c>
       <c r="AM33" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN33" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AO33" t="s">
         <v>1</v>
       </c>
       <c r="AP33" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AQ33" t="s">
         <v>25</v>
       </c>
+      <c r="AR33" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B34" t="s">
         <v>34</v>
       </c>
       <c r="C34" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" t="s">
         <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" t="s">
         <v>1</v>
       </c>
       <c r="J34" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K34" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M34" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N34" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O34" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="P34" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R34" t="s">
         <v>1</v>
       </c>
       <c r="S34" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T34" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="U34" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V34" t="s">
         <v>1</v>
@@ -4936,16 +5143,16 @@
         <v>1</v>
       </c>
       <c r="Z34" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA34" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB34" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC34" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AD34" t="s">
         <v>2</v>
@@ -4954,10 +5161,10 @@
         <v>1</v>
       </c>
       <c r="AF34" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG34" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH34" t="s">
         <v>2</v>
@@ -4965,88 +5172,82 @@
       <c r="AI34" t="s">
         <v>2</v>
       </c>
-      <c r="AJ34" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK34" t="s">
-        <v>2</v>
-      </c>
-      <c r="AL34" t="s">
-        <v>1</v>
-      </c>
       <c r="AM34" t="s">
         <v>1</v>
       </c>
       <c r="AN34" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AO34" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP34" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AQ34" t="s">
-        <v>2</v>
+        <v>25</v>
+      </c>
+      <c r="AR34" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B35" t="s">
         <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D35" t="s">
         <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35" t="s">
         <v>1</v>
       </c>
       <c r="H35" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I35" t="s">
         <v>1</v>
       </c>
       <c r="J35" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L35" t="s">
         <v>1</v>
       </c>
       <c r="M35" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N35" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O35" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P35" t="s">
         <v>1</v>
       </c>
       <c r="Q35" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R35" t="s">
         <v>1</v>
       </c>
       <c r="S35" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T35" t="s">
         <v>1</v>
@@ -5064,25 +5265,25 @@
         <v>2</v>
       </c>
       <c r="Y35" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="s">
         <v>1</v>
       </c>
       <c r="AA35" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB35" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC35" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD35" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE35" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF35" t="s">
         <v>1</v>
@@ -5100,316 +5301,340 @@
         <v>2</v>
       </c>
       <c r="AK35" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL35" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM35" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN35" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO35" t="s">
         <v>2</v>
       </c>
       <c r="AP35" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ35" t="s">
         <v>2</v>
       </c>
+      <c r="AR35" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS35" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="36" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1</v>
+      </c>
+      <c r="E36" t="s">
+        <v>2</v>
+      </c>
+      <c r="F36" t="s">
+        <v>2</v>
+      </c>
+      <c r="G36" t="s">
+        <v>1</v>
+      </c>
+      <c r="H36" t="s">
+        <v>2</v>
+      </c>
+      <c r="I36" t="s">
+        <v>1</v>
+      </c>
+      <c r="J36" t="s">
+        <v>2</v>
+      </c>
+      <c r="K36" t="s">
+        <v>2</v>
+      </c>
+      <c r="L36" t="s">
+        <v>1</v>
+      </c>
+      <c r="M36" t="s">
+        <v>2</v>
+      </c>
+      <c r="N36" t="s">
+        <v>2</v>
+      </c>
+      <c r="O36" t="s">
+        <v>2</v>
+      </c>
+      <c r="P36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>2</v>
+      </c>
+      <c r="R36" t="s">
+        <v>1</v>
+      </c>
+      <c r="S36" t="s">
+        <v>2</v>
+      </c>
+      <c r="T36" t="s">
+        <v>1</v>
+      </c>
+      <c r="U36" t="s">
+        <v>2</v>
+      </c>
+      <c r="V36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W36" t="s">
+        <v>2</v>
+      </c>
+      <c r="X36" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE36" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF36" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG36" t="s">
+        <v>2</v>
+      </c>
+      <c r="AH36" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI36" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK36" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL36" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM36" t="s">
+        <v>2</v>
+      </c>
+      <c r="AN36" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO36" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP36" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ36" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR36" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT36" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>12</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>37</v>
       </c>
-      <c r="C36" t="s">
-        <v>2</v>
-      </c>
-      <c r="D36" t="s">
-        <v>2</v>
-      </c>
-      <c r="E36" t="s">
-        <v>2</v>
-      </c>
-      <c r="F36" t="s">
-        <v>2</v>
-      </c>
-      <c r="G36" t="s">
-        <v>2</v>
-      </c>
-      <c r="H36" t="s">
-        <v>25</v>
-      </c>
-      <c r="I36" t="s">
-        <v>2</v>
-      </c>
-      <c r="J36" t="s">
-        <v>2</v>
-      </c>
-      <c r="K36" t="s">
-        <v>2</v>
-      </c>
-      <c r="L36" t="s">
-        <v>2</v>
-      </c>
-      <c r="M36" t="s">
-        <v>2</v>
-      </c>
-      <c r="N36" t="s">
-        <v>2</v>
-      </c>
-      <c r="O36" t="s">
-        <v>2</v>
-      </c>
-      <c r="P36" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>2</v>
-      </c>
-      <c r="R36" t="s">
-        <v>2</v>
-      </c>
-      <c r="S36" t="s">
-        <v>2</v>
-      </c>
-      <c r="T36" t="s">
-        <v>2</v>
-      </c>
-      <c r="U36" t="s">
-        <v>25</v>
-      </c>
-      <c r="V36" t="s">
-        <v>2</v>
-      </c>
-      <c r="W36" t="s">
-        <v>2</v>
-      </c>
-      <c r="X36" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y36" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z36" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA36" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB36" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC36" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD36" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE36" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF36" t="s">
-        <v>2</v>
-      </c>
-      <c r="AG36" t="s">
-        <v>2</v>
-      </c>
-      <c r="AH36" t="s">
-        <v>2</v>
-      </c>
-      <c r="AI36" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK36" t="s">
-        <v>2</v>
-      </c>
-      <c r="AL36" t="s">
-        <v>2</v>
-      </c>
-      <c r="AM36" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN36" t="s">
-        <v>2</v>
-      </c>
-      <c r="AO36" t="s">
-        <v>2</v>
-      </c>
-      <c r="AP36" t="s">
-        <v>2</v>
-      </c>
-      <c r="AQ36" t="s">
+      <c r="C37" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" t="s">
+        <v>2</v>
+      </c>
+      <c r="E37" t="s">
+        <v>2</v>
+      </c>
+      <c r="F37" t="s">
+        <v>2</v>
+      </c>
+      <c r="G37" t="s">
+        <v>2</v>
+      </c>
+      <c r="H37" t="s">
+        <v>25</v>
+      </c>
+      <c r="I37" t="s">
+        <v>2</v>
+      </c>
+      <c r="J37" t="s">
+        <v>2</v>
+      </c>
+      <c r="K37" t="s">
+        <v>2</v>
+      </c>
+      <c r="L37" t="s">
+        <v>2</v>
+      </c>
+      <c r="M37" t="s">
+        <v>2</v>
+      </c>
+      <c r="N37" t="s">
+        <v>2</v>
+      </c>
+      <c r="O37" t="s">
+        <v>2</v>
+      </c>
+      <c r="P37" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>2</v>
+      </c>
+      <c r="R37" t="s">
+        <v>2</v>
+      </c>
+      <c r="S37" t="s">
+        <v>2</v>
+      </c>
+      <c r="T37" t="s">
+        <v>2</v>
+      </c>
+      <c r="U37" t="s">
+        <v>25</v>
+      </c>
+      <c r="V37" t="s">
+        <v>2</v>
+      </c>
+      <c r="W37" t="s">
+        <v>2</v>
+      </c>
+      <c r="X37" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>2</v>
+      </c>
+      <c r="AE37" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF37" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG37" t="s">
+        <v>2</v>
+      </c>
+      <c r="AH37" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK37" t="s">
+        <v>2</v>
+      </c>
+      <c r="AL37" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM37" t="s">
+        <v>2</v>
+      </c>
+      <c r="AN37" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO37" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP37" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ37" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR37" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS37" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT37" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="38" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>42</v>
-      </c>
-      <c r="B37" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" t="s">
-        <v>32</v>
-      </c>
-      <c r="D37" t="s">
-        <v>32</v>
-      </c>
-      <c r="E37" t="s">
-        <v>32</v>
-      </c>
-      <c r="F37" t="s">
-        <v>32</v>
-      </c>
-      <c r="G37" t="s">
-        <v>32</v>
-      </c>
-      <c r="H37" t="s">
-        <v>32</v>
-      </c>
-      <c r="I37" t="s">
-        <v>32</v>
-      </c>
-      <c r="J37" t="s">
-        <v>32</v>
-      </c>
-      <c r="K37" t="s">
-        <v>32</v>
-      </c>
-      <c r="L37" t="s">
-        <v>1</v>
-      </c>
-      <c r="M37" t="s">
-        <v>2</v>
-      </c>
-      <c r="N37" t="s">
-        <v>1</v>
-      </c>
-      <c r="O37" t="s">
-        <v>2</v>
-      </c>
-      <c r="P37" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>2</v>
-      </c>
-      <c r="R37" t="s">
-        <v>2</v>
-      </c>
-      <c r="S37" t="s">
-        <v>2</v>
-      </c>
-      <c r="T37" t="s">
-        <v>1</v>
-      </c>
-      <c r="U37" t="s">
-        <v>2</v>
-      </c>
-      <c r="V37" t="s">
-        <v>1</v>
-      </c>
-      <c r="W37" t="s">
-        <v>2</v>
-      </c>
-      <c r="X37" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y37" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z37" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA37" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB37" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC37" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD37" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE37" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG37" t="s">
-        <v>2</v>
-      </c>
-      <c r="AH37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI37" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ37" t="s">
-        <v>2</v>
-      </c>
-      <c r="AL37" t="s">
-        <v>2</v>
-      </c>
-      <c r="AM37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN37" t="s">
-        <v>2</v>
-      </c>
-      <c r="AO37" t="s">
-        <v>2</v>
-      </c>
-      <c r="AP37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQ37" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>14</v>
       </c>
       <c r="B38" t="s">
         <v>34</v>
       </c>
       <c r="C38" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D38" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="E38" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="F38" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="G38" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="H38" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="I38" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="J38" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="K38" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="L38" t="s">
         <v>1</v>
@@ -5418,19 +5643,19 @@
         <v>2</v>
       </c>
       <c r="N38" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O38" t="s">
         <v>2</v>
       </c>
       <c r="P38" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="s">
         <v>2</v>
       </c>
       <c r="R38" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S38" t="s">
         <v>2</v>
@@ -5448,13 +5673,13 @@
         <v>2</v>
       </c>
       <c r="X38" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="Y38" t="s">
         <v>2</v>
       </c>
       <c r="Z38" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA38" t="s">
         <v>2</v>
@@ -5466,13 +5691,13 @@
         <v>2</v>
       </c>
       <c r="AD38" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE38" t="s">
         <v>2</v>
       </c>
       <c r="AF38" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG38" t="s">
         <v>2</v>
@@ -5484,13 +5709,13 @@
         <v>2</v>
       </c>
       <c r="AJ38" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL38" t="s">
         <v>2</v>
       </c>
       <c r="AM38" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN38" t="s">
         <v>2</v>
@@ -5499,15 +5724,24 @@
         <v>2</v>
       </c>
       <c r="AP38" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ38" t="s">
+        <v>25</v>
+      </c>
+      <c r="AR38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS38" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT38" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B39" t="s">
         <v>34</v>
@@ -5525,13 +5759,13 @@
         <v>2</v>
       </c>
       <c r="G39" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" t="s">
         <v>2</v>
       </c>
       <c r="I39" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="s">
         <v>2</v>
@@ -5540,7 +5774,7 @@
         <v>2</v>
       </c>
       <c r="L39" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M39" t="s">
         <v>2</v>
@@ -5552,25 +5786,25 @@
         <v>2</v>
       </c>
       <c r="P39" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q39" t="s">
         <v>2</v>
       </c>
       <c r="R39" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S39" t="s">
         <v>2</v>
       </c>
       <c r="T39" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U39" t="s">
         <v>2</v>
       </c>
       <c r="V39" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W39" t="s">
         <v>2</v>
@@ -5579,10 +5813,10 @@
         <v>2</v>
       </c>
       <c r="Y39" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="Z39" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA39" t="s">
         <v>2</v>
@@ -5591,26 +5825,32 @@
         <v>2</v>
       </c>
       <c r="AC39" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AD39" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE39" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AF39" t="s">
         <v>2</v>
       </c>
       <c r="AG39" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AH39" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AI39" t="s">
         <v>2</v>
       </c>
+      <c r="AJ39" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL39" t="s">
+        <v>2</v>
+      </c>
       <c r="AM39" t="s">
         <v>2</v>
       </c>
@@ -5624,221 +5864,233 @@
         <v>2</v>
       </c>
       <c r="AQ39" t="s">
-        <v>25</v>
+        <v>2</v>
+      </c>
+      <c r="AR39" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS39" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT39" t="s">
+        <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B40" t="s">
         <v>34</v>
       </c>
       <c r="C40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U40" t="s">
         <v>2</v>
       </c>
       <c r="V40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X40" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="Y40" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="Z40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB40" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AC40" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AD40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE40" t="s">
         <v>25</v>
       </c>
       <c r="AF40" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AG40" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AH40" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AI40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP40" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AQ40" t="s">
-        <v>2</v>
+        <v>25</v>
+      </c>
+      <c r="AR40" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="B41" t="s">
         <v>34</v>
       </c>
       <c r="C41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E41" t="s">
         <v>25</v>
       </c>
       <c r="F41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H41" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="J41" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="M41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="N41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="O41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="Q41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="R41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="S41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="U41" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="V41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="W41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="X41" t="s">
         <v>25</v>
       </c>
       <c r="Y41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AA41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AB41" t="s">
         <v>25</v>
       </c>
       <c r="AC41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AD41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AE41" t="s">
         <v>25</v>
@@ -5847,30 +6099,36 @@
         <v>25</v>
       </c>
       <c r="AG41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AH41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AI41" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="AM41" t="s">
+        <v>1</v>
       </c>
       <c r="AN41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AO41" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AP41" t="s">
         <v>25</v>
       </c>
       <c r="AQ41" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR41" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B42" t="s">
         <v>34</v>
@@ -5882,115 +6140,103 @@
         <v>25</v>
       </c>
       <c r="E42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="F42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="G42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H42" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="J42" t="s">
         <v>2</v>
       </c>
       <c r="K42" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="L42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="M42" t="s">
         <v>25</v>
       </c>
       <c r="N42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="O42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="P42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="Q42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="R42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="S42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="U42" t="s">
         <v>25</v>
       </c>
       <c r="V42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="W42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="X42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="Y42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="Z42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AA42" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AB42" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AC42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AD42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AE42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AF42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AG42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AH42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AI42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ42" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK42" t="s">
-        <v>2</v>
-      </c>
-      <c r="AL42" t="s">
-        <v>2</v>
-      </c>
-      <c r="AM42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AN42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AO42" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AP42" t="s">
         <v>25</v>
@@ -5998,16 +6244,46 @@
       <c r="AQ42" t="s">
         <v>25</v>
       </c>
+      <c r="AR42" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>34</v>
+      </c>
+      <c r="C43" t="s">
+        <v>25</v>
+      </c>
+      <c r="D43" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" t="s">
+        <v>2</v>
+      </c>
+      <c r="F43" t="s">
+        <v>2</v>
+      </c>
+      <c r="G43" t="s">
+        <v>2</v>
+      </c>
+      <c r="H43" t="s">
+        <v>1</v>
+      </c>
+      <c r="I43" t="s">
+        <v>2</v>
+      </c>
+      <c r="J43" t="s">
+        <v>2</v>
+      </c>
+      <c r="K43" t="s">
+        <v>25</v>
       </c>
       <c r="L43" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="M43" t="s">
         <v>25</v>
@@ -6034,7 +6310,7 @@
         <v>2</v>
       </c>
       <c r="U43" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="V43" t="s">
         <v>2</v>
@@ -6046,19 +6322,19 @@
         <v>2</v>
       </c>
       <c r="Y43" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="Z43" t="s">
         <v>2</v>
       </c>
       <c r="AA43" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB43" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AC43" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AD43" t="s">
         <v>2</v>
@@ -6076,10 +6352,10 @@
         <v>2</v>
       </c>
       <c r="AI43" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ43" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AK43" t="s">
         <v>2</v>
@@ -6088,191 +6364,182 @@
         <v>2</v>
       </c>
       <c r="AM43" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AN43" t="s">
         <v>2</v>
       </c>
       <c r="AO43" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AP43" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AQ43" t="s">
+        <v>25</v>
+      </c>
+      <c r="AR43" t="s">
+        <v>25</v>
+      </c>
+      <c r="AS43" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT43" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="B44" t="s">
         <v>34</v>
       </c>
       <c r="C44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="E44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="F44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="G44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="H44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="I44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="J44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="K44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="L44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="M44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="N44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="O44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="P44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="Q44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="R44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="S44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="T44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="U44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="V44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="W44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="X44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="Y44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="Z44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AA44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AB44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AC44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AD44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AE44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AF44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AG44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AH44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AI44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AJ44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AK44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AL44" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AM44" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN44" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO44" t="s">
         <v>2</v>
       </c>
       <c r="AP44" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ44" t="s">
         <v>2</v>
       </c>
+      <c r="AR44" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS44" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT44" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>34</v>
-      </c>
-      <c r="C45" t="s">
-        <v>2</v>
-      </c>
-      <c r="D45" t="s">
-        <v>1</v>
-      </c>
-      <c r="E45" t="s">
-        <v>2</v>
-      </c>
-      <c r="F45" t="s">
-        <v>2</v>
-      </c>
-      <c r="G45" t="s">
-        <v>2</v>
-      </c>
-      <c r="H45" t="s">
-        <v>2</v>
-      </c>
-      <c r="I45" t="s">
-        <v>2</v>
-      </c>
-      <c r="J45" t="s">
-        <v>2</v>
-      </c>
-      <c r="K45" t="s">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="L45" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="M45" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="N45" t="s">
         <v>2</v>
@@ -6308,7 +6575,7 @@
         <v>2</v>
       </c>
       <c r="Y45" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="Z45" t="s">
         <v>2</v>
@@ -6317,10 +6584,10 @@
         <v>2</v>
       </c>
       <c r="AB45" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AC45" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AD45" t="s">
         <v>2</v>
@@ -6338,25 +6605,25 @@
         <v>2</v>
       </c>
       <c r="AI45" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AJ45" t="s">
         <v>25</v>
       </c>
       <c r="AK45" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AL45" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AM45" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AN45" t="s">
         <v>2</v>
       </c>
       <c r="AO45" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AP45" t="s">
         <v>2</v>
@@ -6364,58 +6631,64 @@
       <c r="AQ45" t="s">
         <v>2</v>
       </c>
+      <c r="AR45" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT45" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="B46" t="s">
         <v>34</v>
       </c>
       <c r="C46" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="D46" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E46" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F46" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G46" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="H46" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="I46" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="J46" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K46" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="L46" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="M46" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="N46" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="O46" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="P46" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="Q46" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="R46" t="s">
         <v>2</v>
@@ -6424,13 +6697,13 @@
         <v>2</v>
       </c>
       <c r="T46" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U46" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V46" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W46" t="s">
         <v>2</v>
@@ -6442,194 +6715,212 @@
         <v>2</v>
       </c>
       <c r="Z46" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AA46" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="s">
         <v>2</v>
       </c>
       <c r="AC46" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AD46" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE46" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AF46" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG46" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH46" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI46" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ46" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK46" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL46" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="AM46" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN46" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO46" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP46" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ46" t="s">
         <v>2</v>
       </c>
+      <c r="AR46" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS46" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT46" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="B47" t="s">
         <v>34</v>
       </c>
       <c r="C47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="D47" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="E47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="H47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="I47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="J47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="L47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="M47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="N47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="O47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="P47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="R47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="S47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="T47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="U47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="V47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="W47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="X47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="Y47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="Z47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="AA47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="AB47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="AC47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="AD47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="AE47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="AF47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="AG47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="AH47" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="AI47" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AJ47" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AK47" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AL47" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AM47" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN47" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO47" t="s">
         <v>2</v>
       </c>
       <c r="AP47" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ47" t="s">
         <v>2</v>
       </c>
+      <c r="AR47" t="s">
+        <v>25</v>
+      </c>
+      <c r="AS47" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT47" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="B48" t="s">
         <v>34</v>
@@ -6680,85 +6971,94 @@
         <v>32</v>
       </c>
       <c r="R48" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="S48" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="T48" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="U48" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="V48" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="W48" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="X48" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="Y48" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="Z48" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AA48" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="AB48" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="AC48" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AD48" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="AE48" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AF48" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="AG48" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="AH48" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="AI48" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="AJ48" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="AK48" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="AL48" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AM48" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN48" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO48" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP48" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ48" t="s">
-        <v>25</v>
+        <v>2</v>
+      </c>
+      <c r="AR48" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS48" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT48" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>38</v>
       </c>
@@ -6779,12 +7079,12 @@
         <v>24</v>
       </c>
       <c r="G50">
-        <f t="shared" ref="G50:V50" si="0">COUNTIF(G1:G41, "P") +COUNTIF(G1:G41, "O")</f>
+        <f t="shared" ref="G50:AT50" si="0">COUNTIF(G1:G41, "P") +COUNTIF(G1:G41, "O")</f>
         <v>24</v>
       </c>
       <c r="H50">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I50">
         <f t="shared" si="0"/>
@@ -6792,11 +7092,11 @@
       </c>
       <c r="J50">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K50">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L50">
         <f t="shared" si="0"/>
@@ -6842,8 +7142,109 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
+      <c r="W50">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="X50">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="Y50">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="Z50">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="AA50">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="AB50">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AC50">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="AD50">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="AE50">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AF50">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="AG50">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="AH50">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="AI50">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="AJ50">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AK50">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AL50">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AM50">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="AN50">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AO50">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="AP50">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AQ50">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AR50">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AS50">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="AT50">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AR48" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AR48">
+      <sortCondition ref="A1:A48"/>
+    </sortState>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC46">
     <sortCondition ref="A2:A46"/>
   </sortState>
@@ -11715,67 +12116,67 @@
       </c>
       <c r="L28">
         <f>IF(Attendance!L32="P", 5, IF(Attendance!L32="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M28">
         <f>IF(Attendance!M32="P", 5, IF(Attendance!M32="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N28">
         <f>IF(Attendance!N32="P", 5, IF(Attendance!N32="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O28">
         <f>IF(Attendance!O32="P", 5, IF(Attendance!O32="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P28">
         <f>IF(Attendance!P32="P", 5, IF(Attendance!P32="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q28">
         <f>IF(Attendance!Q32="P", 5, IF(Attendance!Q32="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R28">
         <f>IF(Attendance!R32="P", 5, IF(Attendance!R32="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S28">
         <f>IF(Attendance!S32="P", 5, IF(Attendance!S32="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T28">
         <f>IF(Attendance!T32="P", 5, IF(Attendance!T32="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U28">
         <f>IF(Attendance!U32="P", 5, IF(Attendance!U32="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V28">
         <f>IF(Attendance!V32="P", 5, IF(Attendance!V32="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W28">
         <f>IF(Attendance!W32="P", 5, IF(Attendance!W32="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X28">
         <f>IF(Attendance!X32="P", 5, IF(Attendance!X32="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y28">
         <f>IF(Attendance!Y32="P", 5, IF(Attendance!Y32="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z28">
         <f>IF(Attendance!Z32="P", 5, IF(Attendance!Z32="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA28">
         <f>IF(Attendance!AA32="P", 5, IF(Attendance!AA32="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB28">
         <f>IF(Attendance!AB32="P", 5, IF(Attendance!AB32="O", 3, 0))</f>
@@ -11791,7 +12192,7 @@
       </c>
       <c r="AE28">
         <f>IF(Attendance!AE32="P", 5, IF(Attendance!AE32="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF28">
         <f>IF(Attendance!AF32="P", 5, IF(Attendance!AF32="O", 3, 0))</f>
@@ -11799,7 +12200,7 @@
       </c>
       <c r="AG28">
         <f>IF(Attendance!AG32="P", 5, IF(Attendance!AG32="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH28">
         <f>IF(Attendance!AH32="P", 5, IF(Attendance!AH32="O", 3, 0))</f>
@@ -11807,7 +12208,7 @@
       </c>
       <c r="AI28">
         <f t="shared" si="0"/>
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="AJ28">
         <f t="shared" si="1"/>
@@ -11815,7 +12216,7 @@
       </c>
       <c r="AK28">
         <f t="shared" si="2"/>
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AM28">
         <v>0</v>
@@ -11830,39 +12231,39 @@
       </c>
       <c r="C29">
         <f>IF(Attendance!C33="P", 5, IF(Attendance!C33="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <f>IF(Attendance!D33="P", 5, IF(Attendance!D33="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E29">
         <f>IF(Attendance!E33="P", 5, IF(Attendance!E33="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F29">
         <f>IF(Attendance!F33="P", 5, IF(Attendance!F33="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G29">
         <f>IF(Attendance!G33="P", 5, IF(Attendance!G33="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H29">
         <f>IF(Attendance!H33="P", 5, IF(Attendance!H33="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I29">
         <f>IF(Attendance!I33="P", 5, IF(Attendance!I33="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J29">
         <f>IF(Attendance!J33="P", 5, IF(Attendance!J33="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K29">
         <f>IF(Attendance!K33="P", 5, IF(Attendance!K33="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L29">
         <f>IF(Attendance!L33="P", 5, IF(Attendance!L33="O", 3, 0))</f>
@@ -11870,19 +12271,19 @@
       </c>
       <c r="M29">
         <f>IF(Attendance!M33="P", 5, IF(Attendance!M33="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <f>IF(Attendance!N33="P", 5, IF(Attendance!N33="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O29">
         <f>IF(Attendance!O33="P", 5, IF(Attendance!O33="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P29">
         <f>IF(Attendance!P33="P", 5, IF(Attendance!P33="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q29">
         <f>IF(Attendance!Q33="P", 5, IF(Attendance!Q33="O", 3, 0))</f>
@@ -11890,15 +12291,15 @@
       </c>
       <c r="R29">
         <f>IF(Attendance!R33="P", 5, IF(Attendance!R33="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S29">
         <f>IF(Attendance!S33="P", 5, IF(Attendance!S33="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T29">
         <f>IF(Attendance!T33="P", 5, IF(Attendance!T33="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29">
         <f>IF(Attendance!U33="P", 5, IF(Attendance!U33="O", 3, 0))</f>
@@ -11922,15 +12323,15 @@
       </c>
       <c r="Z29">
         <f>IF(Attendance!Z33="P", 5, IF(Attendance!Z33="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA29">
         <f>IF(Attendance!AA33="P", 5, IF(Attendance!AA33="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB29">
         <f>IF(Attendance!AB33="P", 5, IF(Attendance!AB33="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC29">
         <f>IF(Attendance!AC33="P", 5, IF(Attendance!AC33="O", 3, 0))</f>
@@ -11938,27 +12339,27 @@
       </c>
       <c r="AD29">
         <f>IF(Attendance!AD33="P", 5, IF(Attendance!AD33="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE29">
         <f>IF(Attendance!AE33="P", 5, IF(Attendance!AE33="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AF29">
         <f>IF(Attendance!AF33="P", 5, IF(Attendance!AF33="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG29">
         <f>IF(Attendance!AG33="P", 5, IF(Attendance!AG33="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AH29">
         <f>IF(Attendance!AH33="P", 5, IF(Attendance!AH33="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI29">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="AJ29">
         <f t="shared" si="1"/>
@@ -11966,7 +12367,7 @@
       </c>
       <c r="AK29">
         <f t="shared" si="2"/>
-        <v>3.13</v>
+        <v>2.38</v>
       </c>
       <c r="AM29">
         <v>0</v>
@@ -11981,19 +12382,19 @@
       </c>
       <c r="C30">
         <f>IF(Attendance!C34="P", 5, IF(Attendance!C34="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D30">
         <f>IF(Attendance!D34="P", 5, IF(Attendance!D34="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E30">
         <f>IF(Attendance!E34="P", 5, IF(Attendance!E34="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F30">
         <f>IF(Attendance!F34="P", 5, IF(Attendance!F34="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G30">
         <f>IF(Attendance!G34="P", 5, IF(Attendance!G34="O", 3, 0))</f>
@@ -12001,7 +12402,7 @@
       </c>
       <c r="H30">
         <f>IF(Attendance!H34="P", 5, IF(Attendance!H34="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I30">
         <f>IF(Attendance!I34="P", 5, IF(Attendance!I34="O", 3, 0))</f>
@@ -12009,35 +12410,35 @@
       </c>
       <c r="J30">
         <f>IF(Attendance!J34="P", 5, IF(Attendance!J34="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K30">
         <f>IF(Attendance!K34="P", 5, IF(Attendance!K34="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L30">
         <f>IF(Attendance!L34="P", 5, IF(Attendance!L34="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M30">
         <f>IF(Attendance!M34="P", 5, IF(Attendance!M34="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N30">
         <f>IF(Attendance!N34="P", 5, IF(Attendance!N34="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O30">
         <f>IF(Attendance!O34="P", 5, IF(Attendance!O34="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P30">
         <f>IF(Attendance!P34="P", 5, IF(Attendance!P34="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q30">
         <f>IF(Attendance!Q34="P", 5, IF(Attendance!Q34="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R30">
         <f>IF(Attendance!R34="P", 5, IF(Attendance!R34="O", 3, 0))</f>
@@ -12045,15 +12446,15 @@
       </c>
       <c r="S30">
         <f>IF(Attendance!S34="P", 5, IF(Attendance!S34="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T30">
         <f>IF(Attendance!T34="P", 5, IF(Attendance!T34="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U30">
         <f>IF(Attendance!U34="P", 5, IF(Attendance!U34="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V30">
         <f>IF(Attendance!V34="P", 5, IF(Attendance!V34="O", 3, 0))</f>
@@ -12073,19 +12474,19 @@
       </c>
       <c r="Z30">
         <f>IF(Attendance!Z34="P", 5, IF(Attendance!Z34="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AA30">
         <f>IF(Attendance!AA34="P", 5, IF(Attendance!AA34="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB30">
         <f>IF(Attendance!AB34="P", 5, IF(Attendance!AB34="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AC30">
         <f>IF(Attendance!AC34="P", 5, IF(Attendance!AC34="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD30">
         <f>IF(Attendance!AD34="P", 5, IF(Attendance!AD34="O", 3, 0))</f>
@@ -12097,11 +12498,11 @@
       </c>
       <c r="AF30">
         <f>IF(Attendance!AF34="P", 5, IF(Attendance!AF34="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG30">
         <f>IF(Attendance!AG34="P", 5, IF(Attendance!AG34="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH30">
         <f>IF(Attendance!AH34="P", 5, IF(Attendance!AH34="O", 3, 0))</f>
@@ -12109,7 +12510,7 @@
       </c>
       <c r="AI30">
         <f t="shared" si="0"/>
-        <v>143</v>
+        <v>100</v>
       </c>
       <c r="AJ30">
         <f t="shared" si="1"/>
@@ -12117,7 +12518,7 @@
       </c>
       <c r="AK30">
         <f t="shared" si="2"/>
-        <v>4.47</v>
+        <v>3.13</v>
       </c>
       <c r="AM30">
         <v>0</v>
@@ -12132,7 +12533,7 @@
       </c>
       <c r="C31">
         <f>IF(Attendance!C35="P", 5, IF(Attendance!C35="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <f>IF(Attendance!D35="P", 5, IF(Attendance!D35="O", 3, 0))</f>
@@ -12140,11 +12541,11 @@
       </c>
       <c r="E31">
         <f>IF(Attendance!E35="P", 5, IF(Attendance!E35="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F31">
         <f>IF(Attendance!F35="P", 5, IF(Attendance!F35="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G31">
         <f>IF(Attendance!G35="P", 5, IF(Attendance!G35="O", 3, 0))</f>
@@ -12152,7 +12553,7 @@
       </c>
       <c r="H31">
         <f>IF(Attendance!H35="P", 5, IF(Attendance!H35="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I31">
         <f>IF(Attendance!I35="P", 5, IF(Attendance!I35="O", 3, 0))</f>
@@ -12160,11 +12561,11 @@
       </c>
       <c r="J31">
         <f>IF(Attendance!J35="P", 5, IF(Attendance!J35="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K31">
         <f>IF(Attendance!K35="P", 5, IF(Attendance!K35="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L31">
         <f>IF(Attendance!L35="P", 5, IF(Attendance!L35="O", 3, 0))</f>
@@ -12172,15 +12573,15 @@
       </c>
       <c r="M31">
         <f>IF(Attendance!M35="P", 5, IF(Attendance!M35="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <f>IF(Attendance!N35="P", 5, IF(Attendance!N35="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O31">
         <f>IF(Attendance!O35="P", 5, IF(Attendance!O35="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P31">
         <f>IF(Attendance!P35="P", 5, IF(Attendance!P35="O", 3, 0))</f>
@@ -12188,7 +12589,7 @@
       </c>
       <c r="Q31">
         <f>IF(Attendance!Q35="P", 5, IF(Attendance!Q35="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R31">
         <f>IF(Attendance!R35="P", 5, IF(Attendance!R35="O", 3, 0))</f>
@@ -12196,7 +12597,7 @@
       </c>
       <c r="S31">
         <f>IF(Attendance!S35="P", 5, IF(Attendance!S35="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T31">
         <f>IF(Attendance!T35="P", 5, IF(Attendance!T35="O", 3, 0))</f>
@@ -12220,7 +12621,7 @@
       </c>
       <c r="Y31">
         <f>IF(Attendance!Y35="P", 5, IF(Attendance!Y35="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z31">
         <f>IF(Attendance!Z35="P", 5, IF(Attendance!Z35="O", 3, 0))</f>
@@ -12228,23 +12629,23 @@
       </c>
       <c r="AA31">
         <f>IF(Attendance!AA35="P", 5, IF(Attendance!AA35="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB31">
         <f>IF(Attendance!AB35="P", 5, IF(Attendance!AB35="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC31">
         <f>IF(Attendance!AC35="P", 5, IF(Attendance!AC35="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD31">
         <f>IF(Attendance!AD35="P", 5, IF(Attendance!AD35="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE31">
         <f>IF(Attendance!AE35="P", 5, IF(Attendance!AE35="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF31">
         <f>IF(Attendance!AF35="P", 5, IF(Attendance!AF35="O", 3, 0))</f>
@@ -12260,7 +12661,7 @@
       </c>
       <c r="AI31">
         <f t="shared" si="0"/>
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="AJ31">
         <f t="shared" si="1"/>
@@ -12268,7 +12669,7 @@
       </c>
       <c r="AK31">
         <f t="shared" si="2"/>
-        <v>3.69</v>
+        <v>4.47</v>
       </c>
       <c r="AL31">
         <v>16</v>
@@ -12287,23 +12688,23 @@
       </c>
       <c r="C32">
         <f>IF(Attendance!C37="P", 5, IF(Attendance!C37="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D32">
         <f>IF(Attendance!D37="P", 5, IF(Attendance!D37="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E32">
         <f>IF(Attendance!E37="P", 5, IF(Attendance!E37="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F32">
         <f>IF(Attendance!F37="P", 5, IF(Attendance!F37="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G32">
         <f>IF(Attendance!G37="P", 5, IF(Attendance!G37="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H32">
         <f>IF(Attendance!H37="P", 5, IF(Attendance!H37="O", 3, 0))</f>
@@ -12311,19 +12712,19 @@
       </c>
       <c r="I32">
         <f>IF(Attendance!I37="P", 5, IF(Attendance!I37="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J32">
         <f>IF(Attendance!J37="P", 5, IF(Attendance!J37="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K32">
         <f>IF(Attendance!K37="P", 5, IF(Attendance!K37="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L32">
         <f>IF(Attendance!L37="P", 5, IF(Attendance!L37="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M32">
         <f>IF(Attendance!M37="P", 5, IF(Attendance!M37="O", 3, 0))</f>
@@ -12331,7 +12732,7 @@
       </c>
       <c r="N32">
         <f>IF(Attendance!N37="P", 5, IF(Attendance!N37="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O32">
         <f>IF(Attendance!O37="P", 5, IF(Attendance!O37="O", 3, 0))</f>
@@ -12355,15 +12756,15 @@
       </c>
       <c r="T32">
         <f>IF(Attendance!T37="P", 5, IF(Attendance!T37="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U32">
         <f>IF(Attendance!U37="P", 5, IF(Attendance!U37="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V32">
         <f>IF(Attendance!V37="P", 5, IF(Attendance!V37="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W32">
         <f>IF(Attendance!W37="P", 5, IF(Attendance!W37="O", 3, 0))</f>
@@ -12371,7 +12772,7 @@
       </c>
       <c r="X32">
         <f>IF(Attendance!X37="P", 5, IF(Attendance!X37="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y32">
         <f>IF(Attendance!Y37="P", 5, IF(Attendance!Y37="O", 3, 0))</f>
@@ -12387,7 +12788,7 @@
       </c>
       <c r="AB32">
         <f>IF(Attendance!AB37="P", 5, IF(Attendance!AB37="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC32">
         <f>IF(Attendance!AC37="P", 5, IF(Attendance!AC37="O", 3, 0))</f>
@@ -12403,7 +12804,7 @@
       </c>
       <c r="AF32">
         <f>IF(Attendance!AF37="P", 5, IF(Attendance!AF37="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG32">
         <f>IF(Attendance!AG37="P", 5, IF(Attendance!AG37="O", 3, 0))</f>
@@ -12411,11 +12812,11 @@
       </c>
       <c r="AH32">
         <f>IF(Attendance!AH37="P", 5, IF(Attendance!AH37="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI32">
         <f t="shared" si="0"/>
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AJ32">
         <f t="shared" si="1"/>
@@ -12423,7 +12824,7 @@
       </c>
       <c r="AK32">
         <f t="shared" si="2"/>
-        <v>2.44</v>
+        <v>2.72</v>
       </c>
       <c r="AL32">
         <v>10</v>
@@ -12442,39 +12843,39 @@
       </c>
       <c r="C33">
         <f>IF(Attendance!C38="P", 5, IF(Attendance!C38="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D33">
         <f>IF(Attendance!D38="P", 5, IF(Attendance!D38="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <f>IF(Attendance!E38="P", 5, IF(Attendance!E38="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F33">
         <f>IF(Attendance!F38="P", 5, IF(Attendance!F38="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G33">
         <f>IF(Attendance!G38="P", 5, IF(Attendance!G38="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H33">
         <f>IF(Attendance!H38="P", 5, IF(Attendance!H38="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I33">
         <f>IF(Attendance!I38="P", 5, IF(Attendance!I38="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J33">
         <f>IF(Attendance!J38="P", 5, IF(Attendance!J38="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K33">
         <f>IF(Attendance!K38="P", 5, IF(Attendance!K38="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L33">
         <f>IF(Attendance!L38="P", 5, IF(Attendance!L38="O", 3, 0))</f>
@@ -12486,7 +12887,7 @@
       </c>
       <c r="N33">
         <f>IF(Attendance!N38="P", 5, IF(Attendance!N38="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O33">
         <f>IF(Attendance!O38="P", 5, IF(Attendance!O38="O", 3, 0))</f>
@@ -12494,7 +12895,7 @@
       </c>
       <c r="P33">
         <f>IF(Attendance!P38="P", 5, IF(Attendance!P38="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q33">
         <f>IF(Attendance!Q38="P", 5, IF(Attendance!Q38="O", 3, 0))</f>
@@ -12502,7 +12903,7 @@
       </c>
       <c r="R33">
         <f>IF(Attendance!R38="P", 5, IF(Attendance!R38="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S33">
         <f>IF(Attendance!S38="P", 5, IF(Attendance!S38="O", 3, 0))</f>
@@ -12526,7 +12927,7 @@
       </c>
       <c r="X33">
         <f>IF(Attendance!X38="P", 5, IF(Attendance!X38="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y33">
         <f>IF(Attendance!Y38="P", 5, IF(Attendance!Y38="O", 3, 0))</f>
@@ -12534,7 +12935,7 @@
       </c>
       <c r="Z33">
         <f>IF(Attendance!Z38="P", 5, IF(Attendance!Z38="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AA33">
         <f>IF(Attendance!AA38="P", 5, IF(Attendance!AA38="O", 3, 0))</f>
@@ -12550,7 +12951,7 @@
       </c>
       <c r="AD33">
         <f>IF(Attendance!AD38="P", 5, IF(Attendance!AD38="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE33">
         <f>IF(Attendance!AE38="P", 5, IF(Attendance!AE38="O", 3, 0))</f>
@@ -12558,7 +12959,7 @@
       </c>
       <c r="AF33">
         <f>IF(Attendance!AF38="P", 5, IF(Attendance!AF38="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG33">
         <f>IF(Attendance!AG38="P", 5, IF(Attendance!AG38="O", 3, 0))</f>
@@ -12570,7 +12971,7 @@
       </c>
       <c r="AI33">
         <f t="shared" si="0"/>
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AJ33">
         <f t="shared" si="1"/>
@@ -12578,7 +12979,7 @@
       </c>
       <c r="AK33">
         <f t="shared" si="2"/>
-        <v>3.63</v>
+        <v>2.44</v>
       </c>
       <c r="AL33">
         <v>10</v>
@@ -12613,7 +13014,7 @@
       </c>
       <c r="G34">
         <f>IF(Attendance!G39="P", 5, IF(Attendance!G39="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H34">
         <f>IF(Attendance!H39="P", 5, IF(Attendance!H39="O", 3, 0))</f>
@@ -12621,7 +13022,7 @@
       </c>
       <c r="I34">
         <f>IF(Attendance!I39="P", 5, IF(Attendance!I39="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J34">
         <f>IF(Attendance!J39="P", 5, IF(Attendance!J39="O", 3, 0))</f>
@@ -12633,7 +13034,7 @@
       </c>
       <c r="L34">
         <f>IF(Attendance!L39="P", 5, IF(Attendance!L39="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M34">
         <f>IF(Attendance!M39="P", 5, IF(Attendance!M39="O", 3, 0))</f>
@@ -12649,7 +13050,7 @@
       </c>
       <c r="P34">
         <f>IF(Attendance!P39="P", 5, IF(Attendance!P39="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q34">
         <f>IF(Attendance!Q39="P", 5, IF(Attendance!Q39="O", 3, 0))</f>
@@ -12657,7 +13058,7 @@
       </c>
       <c r="R34">
         <f>IF(Attendance!R39="P", 5, IF(Attendance!R39="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S34">
         <f>IF(Attendance!S39="P", 5, IF(Attendance!S39="O", 3, 0))</f>
@@ -12665,7 +13066,7 @@
       </c>
       <c r="T34">
         <f>IF(Attendance!T39="P", 5, IF(Attendance!T39="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U34">
         <f>IF(Attendance!U39="P", 5, IF(Attendance!U39="O", 3, 0))</f>
@@ -12673,7 +13074,7 @@
       </c>
       <c r="V34">
         <f>IF(Attendance!V39="P", 5, IF(Attendance!V39="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W34">
         <f>IF(Attendance!W39="P", 5, IF(Attendance!W39="O", 3, 0))</f>
@@ -12685,11 +13086,11 @@
       </c>
       <c r="Y34">
         <f>IF(Attendance!Y39="P", 5, IF(Attendance!Y39="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z34">
         <f>IF(Attendance!Z39="P", 5, IF(Attendance!Z39="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA34">
         <f>IF(Attendance!AA39="P", 5, IF(Attendance!AA39="O", 3, 0))</f>
@@ -12701,15 +13102,15 @@
       </c>
       <c r="AC34">
         <f>IF(Attendance!AC39="P", 5, IF(Attendance!AC39="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD34">
         <f>IF(Attendance!AD39="P", 5, IF(Attendance!AD39="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE34">
         <f>IF(Attendance!AE39="P", 5, IF(Attendance!AE39="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF34">
         <f>IF(Attendance!AF39="P", 5, IF(Attendance!AF39="O", 3, 0))</f>
@@ -12717,15 +13118,15 @@
       </c>
       <c r="AG34">
         <f>IF(Attendance!AG39="P", 5, IF(Attendance!AG39="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH34">
         <f>IF(Attendance!AH39="P", 5, IF(Attendance!AH39="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI34">
         <f t="shared" si="0"/>
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AJ34">
         <f t="shared" si="1"/>
@@ -12733,7 +13134,7 @@
       </c>
       <c r="AK34">
         <f t="shared" si="2"/>
-        <v>2.5299999999999998</v>
+        <v>3.63</v>
       </c>
       <c r="AM34">
         <v>0</v>
@@ -12748,75 +13149,75 @@
       </c>
       <c r="C35">
         <f>IF(Attendance!C40="P", 5, IF(Attendance!C40="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D35">
         <f>IF(Attendance!D40="P", 5, IF(Attendance!D40="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E35">
         <f>IF(Attendance!E40="P", 5, IF(Attendance!E40="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F35">
         <f>IF(Attendance!F40="P", 5, IF(Attendance!F40="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G35">
         <f>IF(Attendance!G40="P", 5, IF(Attendance!G40="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H35">
         <f>IF(Attendance!H40="P", 5, IF(Attendance!H40="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I35">
         <f>IF(Attendance!I40="P", 5, IF(Attendance!I40="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J35">
         <f>IF(Attendance!J40="P", 5, IF(Attendance!J40="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K35">
         <f>IF(Attendance!K40="P", 5, IF(Attendance!K40="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L35">
         <f>IF(Attendance!L40="P", 5, IF(Attendance!L40="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M35">
         <f>IF(Attendance!M40="P", 5, IF(Attendance!M40="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N35">
         <f>IF(Attendance!N40="P", 5, IF(Attendance!N40="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O35">
         <f>IF(Attendance!O40="P", 5, IF(Attendance!O40="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P35">
         <f>IF(Attendance!P40="P", 5, IF(Attendance!P40="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q35">
         <f>IF(Attendance!Q40="P", 5, IF(Attendance!Q40="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R35">
         <f>IF(Attendance!R40="P", 5, IF(Attendance!R40="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S35">
         <f>IF(Attendance!S40="P", 5, IF(Attendance!S40="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35">
         <f>IF(Attendance!T40="P", 5, IF(Attendance!T40="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U35">
         <f>IF(Attendance!U40="P", 5, IF(Attendance!U40="O", 3, 0))</f>
@@ -12824,39 +13225,39 @@
       </c>
       <c r="V35">
         <f>IF(Attendance!V40="P", 5, IF(Attendance!V40="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W35">
         <f>IF(Attendance!W40="P", 5, IF(Attendance!W40="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X35">
         <f>IF(Attendance!X40="P", 5, IF(Attendance!X40="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y35">
         <f>IF(Attendance!Y40="P", 5, IF(Attendance!Y40="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z35">
         <f>IF(Attendance!Z40="P", 5, IF(Attendance!Z40="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AA35">
         <f>IF(Attendance!AA40="P", 5, IF(Attendance!AA40="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB35">
         <f>IF(Attendance!AB40="P", 5, IF(Attendance!AB40="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC35">
         <f>IF(Attendance!AC40="P", 5, IF(Attendance!AC40="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD35">
         <f>IF(Attendance!AD40="P", 5, IF(Attendance!AD40="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE35">
         <f>IF(Attendance!AE40="P", 5, IF(Attendance!AE40="O", 3, 0))</f>
@@ -12864,19 +13265,19 @@
       </c>
       <c r="AF35">
         <f>IF(Attendance!AF40="P", 5, IF(Attendance!AF40="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG35">
         <f>IF(Attendance!AG40="P", 5, IF(Attendance!AG40="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AH35">
         <f>IF(Attendance!AH40="P", 5, IF(Attendance!AH40="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI35">
         <f t="shared" si="0"/>
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AJ35">
         <f t="shared" si="1"/>
@@ -12884,7 +13285,7 @@
       </c>
       <c r="AK35">
         <f t="shared" si="2"/>
-        <v>4.16</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="AM35">
         <v>0</v>
@@ -12899,11 +13300,11 @@
       </c>
       <c r="C36">
         <f>IF(Attendance!C41="P", 5, IF(Attendance!C41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D36">
         <f>IF(Attendance!D41="P", 5, IF(Attendance!D41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E36">
         <f>IF(Attendance!E41="P", 5, IF(Attendance!E41="O", 3, 0))</f>
@@ -12911,75 +13312,75 @@
       </c>
       <c r="F36">
         <f>IF(Attendance!F41="P", 5, IF(Attendance!F41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G36">
         <f>IF(Attendance!G41="P", 5, IF(Attendance!G41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H36">
         <f>IF(Attendance!H41="P", 5, IF(Attendance!H41="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I36">
         <f>IF(Attendance!I41="P", 5, IF(Attendance!I41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J36">
         <f>IF(Attendance!J41="P", 5, IF(Attendance!J41="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K36">
         <f>IF(Attendance!K41="P", 5, IF(Attendance!K41="O", 3, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L36">
         <f>IF(Attendance!L41="P", 5, IF(Attendance!L41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M36">
         <f>IF(Attendance!M41="P", 5, IF(Attendance!M41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N36">
         <f>IF(Attendance!N41="P", 5, IF(Attendance!N41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O36">
         <f>IF(Attendance!O41="P", 5, IF(Attendance!O41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P36">
         <f>IF(Attendance!P41="P", 5, IF(Attendance!P41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q36">
         <f>IF(Attendance!Q41="P", 5, IF(Attendance!Q41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R36">
         <f>IF(Attendance!R41="P", 5, IF(Attendance!R41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S36">
         <f>IF(Attendance!S41="P", 5, IF(Attendance!S41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T36">
         <f>IF(Attendance!T41="P", 5, IF(Attendance!T41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U36">
         <f>IF(Attendance!U41="P", 5, IF(Attendance!U41="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V36">
         <f>IF(Attendance!V41="P", 5, IF(Attendance!V41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W36">
         <f>IF(Attendance!W41="P", 5, IF(Attendance!W41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X36">
         <f>IF(Attendance!X41="P", 5, IF(Attendance!X41="O", 3, 0))</f>
@@ -12987,15 +13388,15 @@
       </c>
       <c r="Y36">
         <f>IF(Attendance!Y41="P", 5, IF(Attendance!Y41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z36">
         <f>IF(Attendance!Z41="P", 5, IF(Attendance!Z41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA36">
         <f>IF(Attendance!AA41="P", 5, IF(Attendance!AA41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB36">
         <f>IF(Attendance!AB41="P", 5, IF(Attendance!AB41="O", 3, 0))</f>
@@ -13003,11 +13404,11 @@
       </c>
       <c r="AC36">
         <f>IF(Attendance!AC41="P", 5, IF(Attendance!AC41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD36">
         <f>IF(Attendance!AD41="P", 5, IF(Attendance!AD41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE36">
         <f>IF(Attendance!AE41="P", 5, IF(Attendance!AE41="O", 3, 0))</f>
@@ -13019,15 +13420,15 @@
       </c>
       <c r="AG36">
         <f>IF(Attendance!AG41="P", 5, IF(Attendance!AG41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH36">
         <f>IF(Attendance!AH41="P", 5, IF(Attendance!AH41="O", 3, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI36">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>133</v>
       </c>
       <c r="AJ36">
         <f t="shared" si="1"/>
@@ -13035,7 +13436,7 @@
       </c>
       <c r="AK36">
         <f t="shared" si="2"/>
-        <v>0.28000000000000003</v>
+        <v>4.16</v>
       </c>
       <c r="AM36">
         <v>0</v>
@@ -13058,23 +13459,23 @@
       </c>
       <c r="E37">
         <f>IF(Attendance!E42="P", 5, IF(Attendance!E42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <f>IF(Attendance!F42="P", 5, IF(Attendance!F42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G37">
         <f>IF(Attendance!G42="P", 5, IF(Attendance!G42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H37">
         <f>IF(Attendance!H42="P", 5, IF(Attendance!H42="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I37">
         <f>IF(Attendance!I42="P", 5, IF(Attendance!I42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J37">
         <f>IF(Attendance!J42="P", 5, IF(Attendance!J42="O", 3, 0))</f>
@@ -13082,11 +13483,11 @@
       </c>
       <c r="K37">
         <f>IF(Attendance!K42="P", 5, IF(Attendance!K42="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L37">
         <f>IF(Attendance!L42="P", 5, IF(Attendance!L42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M37">
         <f>IF(Attendance!M42="P", 5, IF(Attendance!M42="O", 3, 0))</f>
@@ -13094,31 +13495,31 @@
       </c>
       <c r="N37">
         <f>IF(Attendance!N42="P", 5, IF(Attendance!N42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O37">
         <f>IF(Attendance!O42="P", 5, IF(Attendance!O42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P37">
         <f>IF(Attendance!P42="P", 5, IF(Attendance!P42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q37">
         <f>IF(Attendance!Q42="P", 5, IF(Attendance!Q42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R37">
         <f>IF(Attendance!R42="P", 5, IF(Attendance!R42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <f>IF(Attendance!S42="P", 5, IF(Attendance!S42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T37">
         <f>IF(Attendance!T42="P", 5, IF(Attendance!T42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U37">
         <f>IF(Attendance!U42="P", 5, IF(Attendance!U42="O", 3, 0))</f>
@@ -13126,59 +13527,59 @@
       </c>
       <c r="V37">
         <f>IF(Attendance!V42="P", 5, IF(Attendance!V42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W37">
         <f>IF(Attendance!W42="P", 5, IF(Attendance!W42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X37">
         <f>IF(Attendance!X42="P", 5, IF(Attendance!X42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y37">
         <f>IF(Attendance!Y42="P", 5, IF(Attendance!Y42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z37">
         <f>IF(Attendance!Z42="P", 5, IF(Attendance!Z42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA37">
         <f>IF(Attendance!AA42="P", 5, IF(Attendance!AA42="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB37">
         <f>IF(Attendance!AB42="P", 5, IF(Attendance!AB42="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC37">
         <f>IF(Attendance!AC42="P", 5, IF(Attendance!AC42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD37">
         <f>IF(Attendance!AD42="P", 5, IF(Attendance!AD42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE37">
         <f>IF(Attendance!AE42="P", 5, IF(Attendance!AE42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF37">
         <f>IF(Attendance!AF42="P", 5, IF(Attendance!AF42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG37">
         <f>IF(Attendance!AG42="P", 5, IF(Attendance!AG42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH37">
         <f>IF(Attendance!AH42="P", 5, IF(Attendance!AH42="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI37">
         <f t="shared" si="0"/>
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="AJ37">
         <f t="shared" si="1"/>
@@ -13186,7 +13587,7 @@
       </c>
       <c r="AK37">
         <f t="shared" si="2"/>
-        <v>2.72</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AL37">
         <v>14</v>
@@ -13205,135 +13606,135 @@
       </c>
       <c r="C38">
         <f>IF(Attendance!C44="P", 5, IF(Attendance!C44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D38">
         <f>IF(Attendance!D44="P", 5, IF(Attendance!D44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <f>IF(Attendance!E44="P", 5, IF(Attendance!E44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <f>IF(Attendance!F44="P", 5, IF(Attendance!F44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G38">
         <f>IF(Attendance!G44="P", 5, IF(Attendance!G44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H38">
         <f>IF(Attendance!H44="P", 5, IF(Attendance!H44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I38">
         <f>IF(Attendance!I44="P", 5, IF(Attendance!I44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J38">
         <f>IF(Attendance!J44="P", 5, IF(Attendance!J44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K38">
         <f>IF(Attendance!K44="P", 5, IF(Attendance!K44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L38">
         <f>IF(Attendance!L44="P", 5, IF(Attendance!L44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M38">
         <f>IF(Attendance!M44="P", 5, IF(Attendance!M44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N38">
         <f>IF(Attendance!N44="P", 5, IF(Attendance!N44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O38">
         <f>IF(Attendance!O44="P", 5, IF(Attendance!O44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P38">
         <f>IF(Attendance!P44="P", 5, IF(Attendance!P44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q38">
         <f>IF(Attendance!Q44="P", 5, IF(Attendance!Q44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R38">
         <f>IF(Attendance!R44="P", 5, IF(Attendance!R44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <f>IF(Attendance!S44="P", 5, IF(Attendance!S44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T38">
         <f>IF(Attendance!T44="P", 5, IF(Attendance!T44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U38">
         <f>IF(Attendance!U44="P", 5, IF(Attendance!U44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V38">
         <f>IF(Attendance!V44="P", 5, IF(Attendance!V44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W38">
         <f>IF(Attendance!W44="P", 5, IF(Attendance!W44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X38">
         <f>IF(Attendance!X44="P", 5, IF(Attendance!X44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y38">
         <f>IF(Attendance!Y44="P", 5, IF(Attendance!Y44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z38">
         <f>IF(Attendance!Z44="P", 5, IF(Attendance!Z44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA38">
         <f>IF(Attendance!AA44="P", 5, IF(Attendance!AA44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB38">
         <f>IF(Attendance!AB44="P", 5, IF(Attendance!AB44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC38">
         <f>IF(Attendance!AC44="P", 5, IF(Attendance!AC44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD38">
         <f>IF(Attendance!AD44="P", 5, IF(Attendance!AD44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE38">
         <f>IF(Attendance!AE44="P", 5, IF(Attendance!AE44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF38">
         <f>IF(Attendance!AF44="P", 5, IF(Attendance!AF44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG38">
         <f>IF(Attendance!AG44="P", 5, IF(Attendance!AG44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH38">
         <f>IF(Attendance!AH44="P", 5, IF(Attendance!AH44="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI38">
         <f t="shared" si="0"/>
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="AJ38">
         <f t="shared" si="1"/>
@@ -13341,7 +13742,7 @@
       </c>
       <c r="AK38">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL38">
         <v>20</v>
@@ -13360,47 +13761,47 @@
       </c>
       <c r="C39">
         <f>IF(Attendance!C45="P", 5, IF(Attendance!C45="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D39">
         <f>IF(Attendance!D45="P", 5, IF(Attendance!D45="O", 3, 0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <f>IF(Attendance!E45="P", 5, IF(Attendance!E45="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <f>IF(Attendance!F45="P", 5, IF(Attendance!F45="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G39">
         <f>IF(Attendance!G45="P", 5, IF(Attendance!G45="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H39">
         <f>IF(Attendance!H45="P", 5, IF(Attendance!H45="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I39">
         <f>IF(Attendance!I45="P", 5, IF(Attendance!I45="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J39">
         <f>IF(Attendance!J45="P", 5, IF(Attendance!J45="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K39">
         <f>IF(Attendance!K45="P", 5, IF(Attendance!K45="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L39">
         <f>IF(Attendance!L45="P", 5, IF(Attendance!L45="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M39">
         <f>IF(Attendance!M45="P", 5, IF(Attendance!M45="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N39">
         <f>IF(Attendance!N45="P", 5, IF(Attendance!N45="O", 3, 0))</f>
@@ -13448,7 +13849,7 @@
       </c>
       <c r="Y39">
         <f>IF(Attendance!Y45="P", 5, IF(Attendance!Y45="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z39">
         <f>IF(Attendance!Z45="P", 5, IF(Attendance!Z45="O", 3, 0))</f>
@@ -13460,11 +13861,11 @@
       </c>
       <c r="AB39">
         <f>IF(Attendance!AB45="P", 5, IF(Attendance!AB45="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC39">
         <f>IF(Attendance!AC45="P", 5, IF(Attendance!AC45="O", 3, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD39">
         <f>IF(Attendance!AD45="P", 5, IF(Attendance!AD45="O", 3, 0))</f>
@@ -13488,7 +13889,7 @@
       </c>
       <c r="AI39">
         <f t="shared" si="0"/>
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="AJ39">
         <f t="shared" si="1"/>
@@ -13496,7 +13897,7 @@
       </c>
       <c r="AK39">
         <f t="shared" si="2"/>
-        <v>3.06</v>
+        <v>1.69</v>
       </c>
       <c r="AL39">
         <v>20</v>
@@ -13515,63 +13916,63 @@
       </c>
       <c r="C40">
         <f>IF(Attendance!C46="P", 5, IF(Attendance!C46="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D40">
         <f>IF(Attendance!D46="P", 5, IF(Attendance!D46="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E40">
         <f>IF(Attendance!E46="P", 5, IF(Attendance!E46="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F40">
         <f>IF(Attendance!F46="P", 5, IF(Attendance!F46="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G40">
         <f>IF(Attendance!G46="P", 5, IF(Attendance!G46="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H40">
         <f>IF(Attendance!H46="P", 5, IF(Attendance!H46="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I40">
         <f>IF(Attendance!I46="P", 5, IF(Attendance!I46="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J40">
         <f>IF(Attendance!J46="P", 5, IF(Attendance!J46="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K40">
         <f>IF(Attendance!K46="P", 5, IF(Attendance!K46="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L40">
         <f>IF(Attendance!L46="P", 5, IF(Attendance!L46="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M40">
         <f>IF(Attendance!M46="P", 5, IF(Attendance!M46="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N40">
         <f>IF(Attendance!N46="P", 5, IF(Attendance!N46="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O40">
         <f>IF(Attendance!O46="P", 5, IF(Attendance!O46="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P40">
         <f>IF(Attendance!P46="P", 5, IF(Attendance!P46="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q40">
         <f>IF(Attendance!Q46="P", 5, IF(Attendance!Q46="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R40">
         <f>IF(Attendance!R46="P", 5, IF(Attendance!R46="O", 3, 0))</f>
@@ -13583,15 +13984,15 @@
       </c>
       <c r="T40">
         <f>IF(Attendance!T46="P", 5, IF(Attendance!T46="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U40">
         <f>IF(Attendance!U46="P", 5, IF(Attendance!U46="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V40">
         <f>IF(Attendance!V46="P", 5, IF(Attendance!V46="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W40">
         <f>IF(Attendance!W46="P", 5, IF(Attendance!W46="O", 3, 0))</f>
@@ -13607,11 +14008,11 @@
       </c>
       <c r="Z40">
         <f>IF(Attendance!Z46="P", 5, IF(Attendance!Z46="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA40">
         <f>IF(Attendance!AA46="P", 5, IF(Attendance!AA46="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB40">
         <f>IF(Attendance!AB46="P", 5, IF(Attendance!AB46="O", 3, 0))</f>
@@ -13619,31 +14020,31 @@
       </c>
       <c r="AC40">
         <f>IF(Attendance!AC46="P", 5, IF(Attendance!AC46="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD40">
         <f>IF(Attendance!AD46="P", 5, IF(Attendance!AD46="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE40">
         <f>IF(Attendance!AE46="P", 5, IF(Attendance!AE46="O", 3, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF40">
         <f>IF(Attendance!AF46="P", 5, IF(Attendance!AF46="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG40">
         <f>IF(Attendance!AG46="P", 5, IF(Attendance!AG46="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AH40">
         <f>IF(Attendance!AH46="P", 5, IF(Attendance!AH46="O", 3, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI40">
         <f t="shared" si="0"/>
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="AJ40">
         <f t="shared" si="1"/>
@@ -13651,7 +14052,7 @@
       </c>
       <c r="AK40">
         <f t="shared" si="2"/>
-        <v>1.81</v>
+        <v>3</v>
       </c>
       <c r="AL40">
         <v>18</v>

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0504FC8-5495-4D1E-93B1-01D7798DC66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12179B14-D0C6-4906-9B55-276A88C52643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2350" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2381" uniqueCount="79">
   <si>
     <t>Name</t>
   </si>
@@ -717,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:AT50"/>
+  <dimension ref="A1:AU50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -737,7 +737,7 @@
     <col min="39" max="43" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -876,8 +876,11 @@
       <c r="AT1" s="1">
         <v>45636</v>
       </c>
+      <c r="AU1" s="1">
+        <v>45639</v>
+      </c>
     </row>
-    <row r="2" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1016,8 +1019,11 @@
       <c r="AT2" t="s">
         <v>2</v>
       </c>
+      <c r="AU2" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1156,8 +1162,11 @@
       <c r="AT3" t="s">
         <v>1</v>
       </c>
+      <c r="AU3" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1287,8 +1296,11 @@
       <c r="AR4" t="s">
         <v>2</v>
       </c>
+      <c r="AU4" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -1424,8 +1436,11 @@
       <c r="AS5" t="s">
         <v>2</v>
       </c>
+      <c r="AU5" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1564,8 +1579,11 @@
       <c r="AT6" t="s">
         <v>1</v>
       </c>
+      <c r="AU6" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1687,7 +1705,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1821,7 +1839,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1952,7 +1970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -2071,7 +2089,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -2193,7 +2211,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2326,8 +2344,11 @@
       <c r="AT12" t="s">
         <v>1</v>
       </c>
+      <c r="AU12" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="13" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2460,8 +2481,11 @@
       <c r="AT13" t="s">
         <v>2</v>
       </c>
+      <c r="AU13" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -2583,7 +2607,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -2719,8 +2743,11 @@
       <c r="AT15" t="s">
         <v>2</v>
       </c>
+      <c r="AU15" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -2859,8 +2886,11 @@
       <c r="AT16" t="s">
         <v>2</v>
       </c>
+      <c r="AU16" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -2999,8 +3029,11 @@
       <c r="AT17" t="s">
         <v>2</v>
       </c>
+      <c r="AU17" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="18" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -3139,8 +3172,11 @@
       <c r="AT18" t="s">
         <v>2</v>
       </c>
+      <c r="AU18" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -3262,7 +3298,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -3398,8 +3434,11 @@
       <c r="AT20" t="s">
         <v>1</v>
       </c>
+      <c r="AU20" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="21" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3538,8 +3577,11 @@
       <c r="AT21" t="s">
         <v>1</v>
       </c>
+      <c r="AU21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -3634,7 +3676,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -3768,7 +3810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -3890,7 +3932,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -4015,7 +4057,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -4151,8 +4193,11 @@
       <c r="AT26" t="s">
         <v>1</v>
       </c>
+      <c r="AU26" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="27" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -4289,7 +4334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -4428,8 +4473,11 @@
       <c r="AT28" t="s">
         <v>2</v>
       </c>
+      <c r="AU28" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="29" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -4559,8 +4607,17 @@
       <c r="AR29" t="s">
         <v>2</v>
       </c>
+      <c r="AS29" t="s">
+        <v>25</v>
+      </c>
+      <c r="AT29" t="s">
+        <v>25</v>
+      </c>
+      <c r="AU29" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="30" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -4696,8 +4753,11 @@
       <c r="AS30" t="s">
         <v>2</v>
       </c>
+      <c r="AU30" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="31" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -4801,7 +4861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>78</v>
       </c>
@@ -4934,8 +4994,11 @@
       <c r="AR32" t="s">
         <v>2</v>
       </c>
+      <c r="AU32" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="33" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>45</v>
       </c>
@@ -5066,7 +5129,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -5191,7 +5254,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>24</v>
       </c>
@@ -5327,8 +5390,11 @@
       <c r="AS35" t="s">
         <v>2</v>
       </c>
+      <c r="AU35" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="36" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -5464,8 +5530,11 @@
       <c r="AT36" t="s">
         <v>2</v>
       </c>
+      <c r="AU36" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="37" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -5601,8 +5670,11 @@
       <c r="AT37" t="s">
         <v>2</v>
       </c>
+      <c r="AU37" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="38" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -5738,8 +5810,11 @@
       <c r="AT38" t="s">
         <v>2</v>
       </c>
+      <c r="AU38" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -5875,8 +5950,11 @@
       <c r="AT39" t="s">
         <v>1</v>
       </c>
+      <c r="AU39" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="40" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -6001,7 +6079,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>23</v>
       </c>
@@ -6125,8 +6203,11 @@
       <c r="AR41" t="s">
         <v>25</v>
       </c>
+      <c r="AU41" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="42" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>39</v>
       </c>
@@ -6248,7 +6329,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>29</v>
       </c>
@@ -6387,8 +6468,11 @@
       <c r="AT43" t="s">
         <v>2</v>
       </c>
+      <c r="AU43" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="44" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>77</v>
       </c>
@@ -6528,7 +6612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -6637,8 +6721,11 @@
       <c r="AT45" t="s">
         <v>2</v>
       </c>
+      <c r="AU45" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="46" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>16</v>
       </c>
@@ -6777,8 +6864,11 @@
       <c r="AT46" t="s">
         <v>2</v>
       </c>
+      <c r="AU46" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="47" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>17</v>
       </c>
@@ -6917,8 +7007,11 @@
       <c r="AT47" t="s">
         <v>2</v>
       </c>
+      <c r="AU47" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -7056,6 +7149,9 @@
       </c>
       <c r="AT48" t="s">
         <v>2</v>
+      </c>
+      <c r="AU48" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:46" x14ac:dyDescent="0.3">

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12179B14-D0C6-4906-9B55-276A88C52643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C9D277-667F-49F9-BBCC-B6DFBEE87739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2381" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2415" uniqueCount="79">
   <si>
     <t>Name</t>
   </si>
@@ -717,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:AU50"/>
+  <dimension ref="A1:AV50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -737,7 +737,7 @@
     <col min="39" max="43" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -879,8 +879,11 @@
       <c r="AU1" s="1">
         <v>45639</v>
       </c>
+      <c r="AV1" s="1">
+        <v>45643</v>
+      </c>
     </row>
-    <row r="2" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1022,8 +1025,11 @@
       <c r="AU2" t="s">
         <v>1</v>
       </c>
+      <c r="AV2" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1165,8 +1171,11 @@
       <c r="AU3" t="s">
         <v>2</v>
       </c>
+      <c r="AV3" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1299,8 +1308,11 @@
       <c r="AU4" t="s">
         <v>2</v>
       </c>
+      <c r="AV4" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -1439,8 +1451,11 @@
       <c r="AU5" t="s">
         <v>2</v>
       </c>
+      <c r="AV5" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1582,8 +1597,11 @@
       <c r="AU6" t="s">
         <v>1</v>
       </c>
+      <c r="AV6" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1705,7 +1723,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1839,7 +1857,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1969,8 +1987,11 @@
       <c r="AT9" t="s">
         <v>2</v>
       </c>
+      <c r="AV9" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="10" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -2089,7 +2110,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -2211,7 +2232,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2347,8 +2368,11 @@
       <c r="AU12" t="s">
         <v>2</v>
       </c>
+      <c r="AV12" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="13" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2484,8 +2508,11 @@
       <c r="AU13" t="s">
         <v>2</v>
       </c>
+      <c r="AV13" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="14" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -2607,7 +2634,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -2746,8 +2773,11 @@
       <c r="AU15" t="s">
         <v>2</v>
       </c>
+      <c r="AV15" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="16" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -2889,8 +2919,11 @@
       <c r="AU16" t="s">
         <v>1</v>
       </c>
+      <c r="AV16" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -3032,8 +3065,11 @@
       <c r="AU17" t="s">
         <v>2</v>
       </c>
+      <c r="AV17" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="18" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -3175,8 +3211,11 @@
       <c r="AU18" t="s">
         <v>2</v>
       </c>
+      <c r="AV18" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -3298,7 +3337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -3437,8 +3476,11 @@
       <c r="AU20" t="s">
         <v>2</v>
       </c>
+      <c r="AV20" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="21" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3580,8 +3622,11 @@
       <c r="AU21" t="s">
         <v>1</v>
       </c>
+      <c r="AV21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -3676,7 +3721,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -3809,8 +3854,11 @@
       <c r="AT23" t="s">
         <v>2</v>
       </c>
+      <c r="AV23" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="24" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -3932,7 +3980,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -4056,8 +4104,11 @@
       <c r="AR25" t="s">
         <v>25</v>
       </c>
+      <c r="AV25" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="26" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -4196,8 +4247,11 @@
       <c r="AU26" t="s">
         <v>2</v>
       </c>
+      <c r="AV26" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="27" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -4333,8 +4387,11 @@
       <c r="AT27" t="s">
         <v>2</v>
       </c>
+      <c r="AV27" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="28" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -4476,8 +4533,11 @@
       <c r="AU28" t="s">
         <v>2</v>
       </c>
+      <c r="AV28" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="29" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -4616,8 +4676,11 @@
       <c r="AU29" t="s">
         <v>1</v>
       </c>
+      <c r="AV29" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="30" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -4756,8 +4819,11 @@
       <c r="AU30" t="s">
         <v>2</v>
       </c>
+      <c r="AV30" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="31" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -4860,8 +4926,11 @@
       <c r="AS31" t="s">
         <v>2</v>
       </c>
+      <c r="AV31" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="32" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>78</v>
       </c>
@@ -4997,8 +5066,11 @@
       <c r="AU32" t="s">
         <v>2</v>
       </c>
+      <c r="AV32" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="33" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>45</v>
       </c>
@@ -5128,8 +5200,11 @@
       <c r="AR33" t="s">
         <v>25</v>
       </c>
+      <c r="AV33" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="34" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -5254,7 +5329,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>24</v>
       </c>
@@ -5393,8 +5468,11 @@
       <c r="AU35" t="s">
         <v>2</v>
       </c>
+      <c r="AV35" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="36" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -5533,8 +5611,11 @@
       <c r="AU36" t="s">
         <v>2</v>
       </c>
+      <c r="AV36" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="37" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -5673,8 +5754,11 @@
       <c r="AU37" t="s">
         <v>2</v>
       </c>
+      <c r="AV37" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="38" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -5814,7 +5898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -5953,8 +6037,11 @@
       <c r="AU39" t="s">
         <v>1</v>
       </c>
+      <c r="AV39" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="40" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -6079,7 +6166,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>23</v>
       </c>
@@ -6207,7 +6294,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>39</v>
       </c>
@@ -6329,7 +6416,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>29</v>
       </c>
@@ -6471,8 +6558,11 @@
       <c r="AU43" t="s">
         <v>2</v>
       </c>
+      <c r="AV43" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="44" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>77</v>
       </c>
@@ -6611,8 +6701,11 @@
       <c r="AT44" t="s">
         <v>1</v>
       </c>
+      <c r="AV44" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="45" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -6724,8 +6817,11 @@
       <c r="AU45" t="s">
         <v>2</v>
       </c>
+      <c r="AV45" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="46" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>16</v>
       </c>
@@ -6867,8 +6963,11 @@
       <c r="AU46" t="s">
         <v>2</v>
       </c>
+      <c r="AV46" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="47" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>17</v>
       </c>
@@ -7010,8 +7109,11 @@
       <c r="AU47" t="s">
         <v>2</v>
       </c>
+      <c r="AV47" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -7151,6 +7253,9 @@
         <v>2</v>
       </c>
       <c r="AU48" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV48" t="s">
         <v>1</v>
       </c>
     </row>

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C9D277-667F-49F9-BBCC-B6DFBEE87739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F792516B-2318-4A2C-8958-273924015011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2415" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2515" uniqueCount="79">
   <si>
     <t>Name</t>
   </si>
@@ -717,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:AV50"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -737,7 +737,7 @@
     <col min="39" max="43" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -882,8 +882,17 @@
       <c r="AV1" s="1">
         <v>45643</v>
       </c>
+      <c r="AW1" s="1">
+        <v>45646</v>
+      </c>
+      <c r="AX1" s="1">
+        <v>45650</v>
+      </c>
+      <c r="AY1" s="1">
+        <v>45653</v>
+      </c>
     </row>
-    <row r="2" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1028,8 +1037,17 @@
       <c r="AV2" t="s">
         <v>1</v>
       </c>
+      <c r="AW2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1174,8 +1192,17 @@
       <c r="AV3" t="s">
         <v>2</v>
       </c>
+      <c r="AW3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1311,8 +1338,14 @@
       <c r="AV4" t="s">
         <v>2</v>
       </c>
+      <c r="AX4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="5" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -1454,8 +1487,14 @@
       <c r="AV5" t="s">
         <v>2</v>
       </c>
+      <c r="AW5" t="s">
+        <v>2</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1600,8 +1639,17 @@
       <c r="AV6" t="s">
         <v>1</v>
       </c>
+      <c r="AW6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="7" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1722,8 +1770,11 @@
       <c r="AR7" t="s">
         <v>25</v>
       </c>
+      <c r="AY7" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="8" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1856,8 +1907,11 @@
       <c r="AR8" t="s">
         <v>25</v>
       </c>
+      <c r="AY8" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="9" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1990,8 +2044,14 @@
       <c r="AV9" t="s">
         <v>2</v>
       </c>
+      <c r="AX9" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="10" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -2109,8 +2169,11 @@
       <c r="AR10" t="s">
         <v>25</v>
       </c>
+      <c r="AY10" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="11" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -2231,8 +2294,11 @@
       <c r="AR11" t="s">
         <v>25</v>
       </c>
+      <c r="AY11" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="12" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2371,8 +2437,17 @@
       <c r="AV12" t="s">
         <v>2</v>
       </c>
+      <c r="AW12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY12" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="13" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2511,8 +2586,17 @@
       <c r="AV13" t="s">
         <v>2</v>
       </c>
+      <c r="AW13" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>2</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="14" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -2634,7 +2718,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -2776,8 +2860,14 @@
       <c r="AV15" t="s">
         <v>2</v>
       </c>
+      <c r="AW15" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX15" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="16" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -2922,8 +3012,17 @@
       <c r="AV16" t="s">
         <v>1</v>
       </c>
+      <c r="AW16" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX16" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY16" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -3068,8 +3167,17 @@
       <c r="AV17" t="s">
         <v>2</v>
       </c>
+      <c r="AW17" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX17" t="s">
+        <v>2</v>
+      </c>
+      <c r="AY17" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="18" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -3214,8 +3322,17 @@
       <c r="AV18" t="s">
         <v>2</v>
       </c>
+      <c r="AW18" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX18" t="s">
+        <v>2</v>
+      </c>
+      <c r="AY18" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -3337,7 +3454,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -3479,8 +3596,17 @@
       <c r="AV20" t="s">
         <v>1</v>
       </c>
+      <c r="AW20" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX20" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY20" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="21" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3625,8 +3751,17 @@
       <c r="AV21" t="s">
         <v>1</v>
       </c>
+      <c r="AW21" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX21" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -3721,7 +3856,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -3857,8 +3992,11 @@
       <c r="AV23" t="s">
         <v>2</v>
       </c>
+      <c r="AW23" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="24" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -3980,7 +4118,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -4108,7 +4246,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -4250,8 +4388,14 @@
       <c r="AV26" t="s">
         <v>1</v>
       </c>
+      <c r="AW26" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX26" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="27" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -4390,8 +4534,11 @@
       <c r="AV27" t="s">
         <v>2</v>
       </c>
+      <c r="AX27" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -4536,8 +4683,17 @@
       <c r="AV28" t="s">
         <v>2</v>
       </c>
+      <c r="AW28" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX28" t="s">
+        <v>2</v>
+      </c>
+      <c r="AY28" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="29" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -4679,8 +4835,11 @@
       <c r="AV29" t="s">
         <v>1</v>
       </c>
+      <c r="AW29" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -4823,7 +4982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -4929,8 +5088,17 @@
       <c r="AV31" t="s">
         <v>1</v>
       </c>
+      <c r="AW31" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX31" t="s">
+        <v>2</v>
+      </c>
+      <c r="AY31" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="32" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>78</v>
       </c>
@@ -5069,8 +5237,14 @@
       <c r="AV32" t="s">
         <v>2</v>
       </c>
+      <c r="AW32" t="s">
+        <v>2</v>
+      </c>
+      <c r="AY32" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="33" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>45</v>
       </c>
@@ -5200,11 +5374,23 @@
       <c r="AR33" t="s">
         <v>25</v>
       </c>
+      <c r="AS33" t="s">
+        <v>25</v>
+      </c>
+      <c r="AT33" t="s">
+        <v>25</v>
+      </c>
+      <c r="AU33" t="s">
+        <v>25</v>
+      </c>
       <c r="AV33" t="s">
         <v>2</v>
       </c>
+      <c r="AW33" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -5328,8 +5514,29 @@
       <c r="AR34" t="s">
         <v>25</v>
       </c>
+      <c r="AS34" t="s">
+        <v>25</v>
+      </c>
+      <c r="AT34" t="s">
+        <v>25</v>
+      </c>
+      <c r="AU34" t="s">
+        <v>25</v>
+      </c>
+      <c r="AV34" t="s">
+        <v>25</v>
+      </c>
+      <c r="AW34" t="s">
+        <v>25</v>
+      </c>
+      <c r="AX34" t="s">
+        <v>25</v>
+      </c>
+      <c r="AY34" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="35" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>24</v>
       </c>
@@ -5471,8 +5678,17 @@
       <c r="AV35" t="s">
         <v>1</v>
       </c>
+      <c r="AW35" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY35" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="36" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -5614,8 +5830,17 @@
       <c r="AV36" t="s">
         <v>2</v>
       </c>
+      <c r="AW36" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX36" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY36" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="37" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -5757,8 +5982,17 @@
       <c r="AV37" t="s">
         <v>2</v>
       </c>
+      <c r="AW37" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX37" t="s">
+        <v>2</v>
+      </c>
+      <c r="AY37" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="38" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -5897,8 +6131,20 @@
       <c r="AU38" t="s">
         <v>2</v>
       </c>
+      <c r="AV38" t="s">
+        <v>2</v>
+      </c>
+      <c r="AW38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY38" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -6040,8 +6286,17 @@
       <c r="AV39" t="s">
         <v>1</v>
       </c>
+      <c r="AW39" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX39" t="s">
+        <v>2</v>
+      </c>
+      <c r="AY39" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="40" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -6165,8 +6420,26 @@
       <c r="AR40" t="s">
         <v>25</v>
       </c>
+      <c r="AS40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AT40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AU40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AV40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AW40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AX40" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="41" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>23</v>
       </c>
@@ -6293,8 +6566,11 @@
       <c r="AU41" t="s">
         <v>2</v>
       </c>
+      <c r="AX41" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="42" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>39</v>
       </c>
@@ -6416,7 +6692,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>29</v>
       </c>
@@ -6561,8 +6837,17 @@
       <c r="AV43" t="s">
         <v>2</v>
       </c>
+      <c r="AW43" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX43" t="s">
+        <v>2</v>
+      </c>
+      <c r="AY43" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="44" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>77</v>
       </c>
@@ -6701,11 +6986,17 @@
       <c r="AT44" t="s">
         <v>1</v>
       </c>
+      <c r="AU44" t="s">
+        <v>25</v>
+      </c>
       <c r="AV44" t="s">
         <v>1</v>
       </c>
+      <c r="AW44" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="45" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -6820,8 +7111,11 @@
       <c r="AV45" t="s">
         <v>2</v>
       </c>
+      <c r="AW45" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="46" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>16</v>
       </c>
@@ -6966,8 +7260,14 @@
       <c r="AV46" t="s">
         <v>2</v>
       </c>
+      <c r="AX46" t="s">
+        <v>2</v>
+      </c>
+      <c r="AY46" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="47" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>17</v>
       </c>
@@ -7112,8 +7412,14 @@
       <c r="AV47" t="s">
         <v>2</v>
       </c>
+      <c r="AX47" t="s">
+        <v>2</v>
+      </c>
+      <c r="AY47" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -7256,6 +7562,9 @@
         <v>1</v>
       </c>
       <c r="AV48" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW48" t="s">
         <v>1</v>
       </c>
     </row>

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F792516B-2318-4A2C-8958-273924015011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686EB603-D9B0-4969-88B5-24BAFCAF3551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2515" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2573" uniqueCount="79">
   <si>
     <t>Name</t>
   </si>
@@ -717,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:BA50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -737,7 +737,7 @@
     <col min="39" max="43" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -891,8 +891,14 @@
       <c r="AY1" s="1">
         <v>45653</v>
       </c>
+      <c r="AZ1" s="1">
+        <v>45660</v>
+      </c>
+      <c r="BA1" s="1">
+        <v>45664</v>
+      </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1046,8 +1052,14 @@
       <c r="AY2" t="s">
         <v>1</v>
       </c>
+      <c r="AZ2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1201,8 +1213,14 @@
       <c r="AY3" t="s">
         <v>2</v>
       </c>
+      <c r="AZ3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1344,8 +1362,14 @@
       <c r="AY4" t="s">
         <v>25</v>
       </c>
+      <c r="AZ4" t="s">
+        <v>2</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -1493,8 +1517,11 @@
       <c r="AY5" t="s">
         <v>2</v>
       </c>
+      <c r="AZ5" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1648,8 +1675,14 @@
       <c r="AY6" t="s">
         <v>2</v>
       </c>
+      <c r="AZ6" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1774,7 +1807,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1911,7 +1944,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -2017,6 +2050,12 @@
       <c r="AI9" t="s">
         <v>2</v>
       </c>
+      <c r="AJ9" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>25</v>
+      </c>
       <c r="AL9" t="s">
         <v>2</v>
       </c>
@@ -2038,20 +2077,35 @@
       <c r="AR9" t="s">
         <v>2</v>
       </c>
+      <c r="AS9" t="s">
+        <v>25</v>
+      </c>
       <c r="AT9" t="s">
         <v>2</v>
       </c>
+      <c r="AU9" t="s">
+        <v>25</v>
+      </c>
       <c r="AV9" t="s">
         <v>2</v>
       </c>
+      <c r="AW9" t="s">
+        <v>25</v>
+      </c>
       <c r="AX9" t="s">
         <v>1</v>
       </c>
       <c r="AY9" t="s">
         <v>25</v>
       </c>
+      <c r="AZ9" t="s">
+        <v>25</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -2173,7 +2227,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -2298,7 +2352,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2446,8 +2500,14 @@
       <c r="AY12" t="s">
         <v>2</v>
       </c>
+      <c r="AZ12" t="s">
+        <v>2</v>
+      </c>
+      <c r="BA12" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="13" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2595,8 +2655,11 @@
       <c r="AY13" t="s">
         <v>2</v>
       </c>
+      <c r="AZ13" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="14" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -2718,7 +2781,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -2866,8 +2929,14 @@
       <c r="AX15" t="s">
         <v>2</v>
       </c>
+      <c r="AZ15" t="s">
+        <v>2</v>
+      </c>
+      <c r="BA15" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="16" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -3021,8 +3090,14 @@
       <c r="AY16" t="s">
         <v>1</v>
       </c>
+      <c r="AZ16" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA16" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -3176,8 +3251,11 @@
       <c r="AY17" t="s">
         <v>2</v>
       </c>
+      <c r="AZ17" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -3331,8 +3409,11 @@
       <c r="AY18" t="s">
         <v>2</v>
       </c>
+      <c r="AZ18" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -3454,7 +3535,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -3605,8 +3686,11 @@
       <c r="AY20" t="s">
         <v>2</v>
       </c>
+      <c r="AZ20" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3760,8 +3844,14 @@
       <c r="AY21" t="s">
         <v>1</v>
       </c>
+      <c r="AZ21" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -3856,7 +3946,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -3995,8 +4085,11 @@
       <c r="AW23" t="s">
         <v>2</v>
       </c>
+      <c r="AZ23" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -4118,7 +4211,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -4246,7 +4339,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -4394,8 +4487,11 @@
       <c r="AX26" t="s">
         <v>1</v>
       </c>
+      <c r="AZ26" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="27" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -4537,8 +4633,11 @@
       <c r="AX27" t="s">
         <v>1</v>
       </c>
+      <c r="BA27" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -4692,8 +4791,14 @@
       <c r="AY28" t="s">
         <v>2</v>
       </c>
+      <c r="AZ28" t="s">
+        <v>2</v>
+      </c>
+      <c r="BA28" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="29" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -4838,8 +4943,11 @@
       <c r="AW29" t="s">
         <v>2</v>
       </c>
+      <c r="BA29" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -4982,7 +5090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -5097,8 +5205,14 @@
       <c r="AY31" t="s">
         <v>2</v>
       </c>
+      <c r="AZ31" t="s">
+        <v>2</v>
+      </c>
+      <c r="BA31" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="32" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>78</v>
       </c>
@@ -5243,8 +5357,14 @@
       <c r="AY32" t="s">
         <v>2</v>
       </c>
+      <c r="AZ32" t="s">
+        <v>2</v>
+      </c>
+      <c r="BA32" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="33" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>45</v>
       </c>
@@ -5390,7 +5510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -5535,8 +5655,14 @@
       <c r="AY34" t="s">
         <v>2</v>
       </c>
+      <c r="AZ34" t="s">
+        <v>2</v>
+      </c>
+      <c r="BA34" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="35" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>24</v>
       </c>
@@ -5687,8 +5813,14 @@
       <c r="AY35" t="s">
         <v>2</v>
       </c>
+      <c r="AZ35" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA35" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="36" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -5839,8 +5971,11 @@
       <c r="AY36" t="s">
         <v>2</v>
       </c>
+      <c r="BA36" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="37" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -5991,8 +6126,14 @@
       <c r="AY37" t="s">
         <v>2</v>
       </c>
+      <c r="AZ37" t="s">
+        <v>2</v>
+      </c>
+      <c r="BA37" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="38" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -6143,8 +6284,14 @@
       <c r="AY38" t="s">
         <v>2</v>
       </c>
+      <c r="AZ38" t="s">
+        <v>2</v>
+      </c>
+      <c r="BA38" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -6295,8 +6442,11 @@
       <c r="AY39" t="s">
         <v>2</v>
       </c>
+      <c r="AZ39" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="40" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -6438,8 +6588,11 @@
       <c r="AX40" t="s">
         <v>2</v>
       </c>
+      <c r="AZ40" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="41" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>23</v>
       </c>
@@ -6570,7 +6723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>39</v>
       </c>
@@ -6692,7 +6845,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>29</v>
       </c>
@@ -6846,8 +6999,14 @@
       <c r="AY43" t="s">
         <v>2</v>
       </c>
+      <c r="AZ43" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA43" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="44" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>77</v>
       </c>
@@ -6995,8 +7154,11 @@
       <c r="AW44" t="s">
         <v>1</v>
       </c>
+      <c r="BA44" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="45" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -7115,7 +7277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>16</v>
       </c>
@@ -7266,8 +7428,14 @@
       <c r="AY46" t="s">
         <v>2</v>
       </c>
+      <c r="AZ46" t="s">
+        <v>2</v>
+      </c>
+      <c r="BA46" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="47" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>17</v>
       </c>
@@ -7418,8 +7586,14 @@
       <c r="AY47" t="s">
         <v>2</v>
       </c>
+      <c r="AZ47" t="s">
+        <v>2</v>
+      </c>
+      <c r="BA47" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -7565,6 +7739,12 @@
         <v>1</v>
       </c>
       <c r="AW48" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ48" t="s">
+        <v>2</v>
+      </c>
+      <c r="BA48" t="s">
         <v>1</v>
       </c>
     </row>

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686EB603-D9B0-4969-88B5-24BAFCAF3551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377BC8A3-0880-4714-A544-A901F3AB6D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2573" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2618" uniqueCount="79">
   <si>
     <t>Name</t>
   </si>
@@ -387,7 +387,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -403,6 +403,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -717,188 +723,187 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:BA50"/>
+  <dimension ref="A1:BB50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="16" width="5.77734375" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="36" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="6" bestFit="1" customWidth="1"/>
-    <col min="39" max="43" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="8" bestFit="1" customWidth="1"/>
+    <col min="17" max="25" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="26" max="36" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="37" max="43" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="9" bestFit="1" customWidth="1"/>
+    <col min="45" max="51" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="52" max="54" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:54" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="1">
+      <c r="C1" s="8">
         <v>45442</v>
       </c>
-      <c r="D1" s="1">
+      <c r="D1" s="8">
         <v>45449</v>
       </c>
-      <c r="E1" s="1">
+      <c r="E1" s="8">
         <v>45454</v>
       </c>
-      <c r="F1" s="1">
+      <c r="F1" s="8">
         <v>45457</v>
       </c>
-      <c r="G1" s="1">
+      <c r="G1" s="8">
         <v>45461</v>
       </c>
-      <c r="H1" s="1">
+      <c r="H1" s="8">
         <v>45464</v>
       </c>
-      <c r="I1" s="1">
+      <c r="I1" s="8">
         <v>45468</v>
       </c>
-      <c r="J1" s="1">
+      <c r="J1" s="8">
         <v>45471</v>
       </c>
-      <c r="K1" s="1">
+      <c r="K1" s="8">
         <v>45475</v>
       </c>
-      <c r="L1" s="1">
+      <c r="L1" s="8">
         <v>45489</v>
       </c>
-      <c r="M1" s="1">
+      <c r="M1" s="8">
         <v>45492</v>
       </c>
-      <c r="N1" s="1">
+      <c r="N1" s="8">
         <v>45496</v>
       </c>
-      <c r="O1" s="1">
+      <c r="O1" s="8">
         <v>45499</v>
       </c>
-      <c r="P1" s="1">
+      <c r="P1" s="8">
         <v>45503</v>
       </c>
-      <c r="Q1" s="1">
+      <c r="Q1" s="8">
         <v>45506</v>
       </c>
-      <c r="R1" s="1">
+      <c r="R1" s="8">
         <v>45510</v>
       </c>
-      <c r="S1" s="1">
+      <c r="S1" s="8">
         <v>45513</v>
       </c>
-      <c r="T1" s="1">
+      <c r="T1" s="8">
         <v>45517</v>
       </c>
-      <c r="U1" s="1">
+      <c r="U1" s="8">
         <v>45520</v>
       </c>
-      <c r="V1" s="1">
+      <c r="V1" s="8">
         <v>45524</v>
       </c>
-      <c r="W1" s="1">
+      <c r="W1" s="8">
         <v>45527</v>
       </c>
-      <c r="X1" s="1">
+      <c r="X1" s="8">
         <v>45531</v>
       </c>
-      <c r="Y1" s="1">
+      <c r="Y1" s="8">
         <v>45534</v>
       </c>
-      <c r="Z1" s="1">
+      <c r="Z1" s="8">
         <v>45538</v>
       </c>
-      <c r="AA1" s="1">
+      <c r="AA1" s="8">
         <v>45541</v>
       </c>
-      <c r="AB1" s="1">
+      <c r="AB1" s="8">
         <v>45548</v>
       </c>
-      <c r="AC1" s="1">
+      <c r="AC1" s="8">
         <v>45555</v>
       </c>
-      <c r="AD1" s="1">
+      <c r="AD1" s="8">
         <v>45566</v>
       </c>
-      <c r="AE1" s="1">
+      <c r="AE1" s="8">
         <v>45576</v>
       </c>
-      <c r="AF1" s="1">
+      <c r="AF1" s="8">
         <v>45580</v>
       </c>
-      <c r="AG1" s="1">
+      <c r="AG1" s="8">
         <v>45583</v>
       </c>
-      <c r="AH1" s="1">
+      <c r="AH1" s="8">
         <v>45587</v>
       </c>
-      <c r="AI1" s="1">
+      <c r="AI1" s="8">
         <v>45590</v>
       </c>
-      <c r="AJ1" s="1">
+      <c r="AJ1" s="8">
         <v>45594</v>
       </c>
-      <c r="AK1" s="1">
+      <c r="AK1" s="8">
         <v>45601</v>
       </c>
-      <c r="AL1" s="1">
+      <c r="AL1" s="8">
         <v>45604</v>
       </c>
-      <c r="AM1" s="1">
+      <c r="AM1" s="8">
         <v>45608</v>
       </c>
-      <c r="AN1" s="1">
+      <c r="AN1" s="8">
         <v>45611</v>
       </c>
-      <c r="AO1" s="1">
+      <c r="AO1" s="8">
         <v>45615</v>
       </c>
-      <c r="AP1" s="1">
+      <c r="AP1" s="8">
         <v>45622</v>
       </c>
-      <c r="AQ1" s="1">
+      <c r="AQ1" s="8">
         <v>45625</v>
       </c>
-      <c r="AR1" s="1">
+      <c r="AR1" s="8">
         <v>45629</v>
       </c>
-      <c r="AS1" s="1">
+      <c r="AS1" s="8">
         <v>45632</v>
       </c>
-      <c r="AT1" s="1">
+      <c r="AT1" s="8">
         <v>45636</v>
       </c>
-      <c r="AU1" s="1">
+      <c r="AU1" s="8">
         <v>45639</v>
       </c>
-      <c r="AV1" s="1">
+      <c r="AV1" s="8">
         <v>45643</v>
       </c>
-      <c r="AW1" s="1">
+      <c r="AW1" s="8">
         <v>45646</v>
       </c>
-      <c r="AX1" s="1">
+      <c r="AX1" s="8">
         <v>45650</v>
       </c>
-      <c r="AY1" s="1">
+      <c r="AY1" s="8">
         <v>45653</v>
       </c>
-      <c r="AZ1" s="1">
+      <c r="AZ1" s="8">
         <v>45660</v>
       </c>
-      <c r="BA1" s="1">
+      <c r="BA1" s="8">
         <v>45664</v>
       </c>
+      <c r="BB1" s="8">
+        <v>45667</v>
+      </c>
     </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1058,8 +1063,11 @@
       <c r="BA2" t="s">
         <v>1</v>
       </c>
+      <c r="BB2" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1220,7 +1228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1368,8 +1376,11 @@
       <c r="BA4" t="s">
         <v>2</v>
       </c>
+      <c r="BB4" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -1521,7 +1532,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1681,8 +1692,11 @@
       <c r="BA6" t="s">
         <v>1</v>
       </c>
+      <c r="BB6" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1807,7 +1821,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1944,7 +1958,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -2105,7 +2119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -2227,7 +2241,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -2352,7 +2366,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2506,8 +2520,11 @@
       <c r="BA12" t="s">
         <v>2</v>
       </c>
+      <c r="BB12" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2658,8 +2675,11 @@
       <c r="AZ13" t="s">
         <v>2</v>
       </c>
+      <c r="BB13" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -2781,7 +2801,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -2935,8 +2955,11 @@
       <c r="BA15" t="s">
         <v>2</v>
       </c>
+      <c r="BB15" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -3096,8 +3119,11 @@
       <c r="BA16" t="s">
         <v>2</v>
       </c>
+      <c r="BB16" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -3254,8 +3280,11 @@
       <c r="AZ17" t="s">
         <v>2</v>
       </c>
+      <c r="BB17" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="18" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -3412,8 +3441,11 @@
       <c r="AZ18" t="s">
         <v>2</v>
       </c>
+      <c r="BB18" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -3535,7 +3567,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -3690,7 +3722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3850,8 +3882,11 @@
       <c r="BA21" t="s">
         <v>1</v>
       </c>
+      <c r="BB21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -3946,7 +3981,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -4089,7 +4124,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -4211,7 +4246,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -4339,7 +4374,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -4491,7 +4526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -4637,7 +4672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -4798,7 +4833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -4946,8 +4981,11 @@
       <c r="BA29" t="s">
         <v>2</v>
       </c>
+      <c r="BB29" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="30" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -5089,8 +5127,11 @@
       <c r="AV30" t="s">
         <v>2</v>
       </c>
+      <c r="BB30" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="31" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -5211,8 +5252,11 @@
       <c r="BA31" t="s">
         <v>1</v>
       </c>
+      <c r="BB31" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="32" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>78</v>
       </c>
@@ -5364,7 +5408,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>45</v>
       </c>
@@ -5509,8 +5553,23 @@
       <c r="AW33" t="s">
         <v>1</v>
       </c>
+      <c r="AX33" t="s">
+        <v>25</v>
+      </c>
+      <c r="AY33" t="s">
+        <v>25</v>
+      </c>
+      <c r="AZ33" t="s">
+        <v>25</v>
+      </c>
+      <c r="BA33" t="s">
+        <v>25</v>
+      </c>
+      <c r="BB33" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -5661,8 +5720,11 @@
       <c r="BA34" t="s">
         <v>2</v>
       </c>
+      <c r="BB34" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="35" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>24</v>
       </c>
@@ -5819,8 +5881,11 @@
       <c r="BA35" t="s">
         <v>1</v>
       </c>
+      <c r="BB35" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="36" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -5974,8 +6039,11 @@
       <c r="BA36" t="s">
         <v>1</v>
       </c>
+      <c r="BB36" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="37" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -6132,8 +6200,11 @@
       <c r="BA37" t="s">
         <v>1</v>
       </c>
+      <c r="BB37" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="38" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -6290,8 +6361,11 @@
       <c r="BA38" t="s">
         <v>2</v>
       </c>
+      <c r="BB38" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="39" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -6445,8 +6519,11 @@
       <c r="AZ39" t="s">
         <v>2</v>
       </c>
+      <c r="BB39" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="40" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -6592,7 +6669,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>23</v>
       </c>
@@ -6698,6 +6775,15 @@
       <c r="AI41" t="s">
         <v>1</v>
       </c>
+      <c r="AJ41" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK41" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL41" t="s">
+        <v>25</v>
+      </c>
       <c r="AM41" t="s">
         <v>1</v>
       </c>
@@ -6716,14 +6802,38 @@
       <c r="AR41" t="s">
         <v>25</v>
       </c>
+      <c r="AS41" t="s">
+        <v>25</v>
+      </c>
+      <c r="AT41" t="s">
+        <v>25</v>
+      </c>
       <c r="AU41" t="s">
         <v>2</v>
       </c>
+      <c r="AV41" t="s">
+        <v>25</v>
+      </c>
+      <c r="AW41" t="s">
+        <v>25</v>
+      </c>
       <c r="AX41" t="s">
         <v>1</v>
       </c>
+      <c r="AY41" t="s">
+        <v>25</v>
+      </c>
+      <c r="AZ41" t="s">
+        <v>25</v>
+      </c>
+      <c r="BA41" t="s">
+        <v>25</v>
+      </c>
+      <c r="BB41" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="42" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>39</v>
       </c>
@@ -6845,7 +6955,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>29</v>
       </c>
@@ -7005,8 +7115,11 @@
       <c r="BA43" t="s">
         <v>2</v>
       </c>
+      <c r="BB43" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="44" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>77</v>
       </c>
@@ -7157,8 +7270,11 @@
       <c r="BA44" t="s">
         <v>1</v>
       </c>
+      <c r="BB44" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="45" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -7276,8 +7392,23 @@
       <c r="AW45" t="s">
         <v>2</v>
       </c>
+      <c r="AX45" t="s">
+        <v>25</v>
+      </c>
+      <c r="AY45" t="s">
+        <v>25</v>
+      </c>
+      <c r="AZ45" t="s">
+        <v>25</v>
+      </c>
+      <c r="BA45" t="s">
+        <v>25</v>
+      </c>
+      <c r="BB45" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="46" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>16</v>
       </c>
@@ -7434,8 +7565,11 @@
       <c r="BA46" t="s">
         <v>2</v>
       </c>
+      <c r="BB46" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="47" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>17</v>
       </c>
@@ -7592,8 +7726,11 @@
       <c r="BA47" t="s">
         <v>2</v>
       </c>
+      <c r="BB47" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -7745,6 +7882,9 @@
         <v>2</v>
       </c>
       <c r="BA48" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB48" t="s">
         <v>1</v>
       </c>
     </row>

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377BC8A3-0880-4714-A544-A901F3AB6D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19683E99-C292-426D-B6CA-31C622FB3454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2618" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2715" uniqueCount="79">
   <si>
     <t>Name</t>
   </si>
@@ -723,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:BB50"/>
+  <dimension ref="A1:BE50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -739,7 +739,7 @@
     <col min="52" max="54" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:57" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -902,8 +902,17 @@
       <c r="BB1" s="8">
         <v>45667</v>
       </c>
+      <c r="BC1" s="8">
+        <v>45674</v>
+      </c>
+      <c r="BD1" s="8">
+        <v>45678</v>
+      </c>
+      <c r="BE1" s="8">
+        <v>45681</v>
+      </c>
     </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1066,8 +1075,17 @@
       <c r="BB2" t="s">
         <v>1</v>
       </c>
+      <c r="BC2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="3" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1227,8 +1245,11 @@
       <c r="BA3" t="s">
         <v>1</v>
       </c>
+      <c r="BC3" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1379,8 +1400,17 @@
       <c r="BB4" t="s">
         <v>2</v>
       </c>
+      <c r="BC4" t="s">
+        <v>25</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -1531,8 +1561,17 @@
       <c r="AZ5" t="s">
         <v>2</v>
       </c>
+      <c r="BA5" t="s">
+        <v>25</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>25</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1695,8 +1734,17 @@
       <c r="BB6" t="s">
         <v>1</v>
       </c>
+      <c r="BC6" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>1</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1821,7 +1869,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1958,7 +2006,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -2118,8 +2166,17 @@
       <c r="BA9" t="s">
         <v>1</v>
       </c>
+      <c r="BB9" t="s">
+        <v>25</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>25</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -2241,7 +2298,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -2366,7 +2423,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2523,8 +2580,14 @@
       <c r="BB12" t="s">
         <v>2</v>
       </c>
+      <c r="BC12" t="s">
+        <v>2</v>
+      </c>
+      <c r="BD12" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2678,8 +2741,17 @@
       <c r="BB13" t="s">
         <v>2</v>
       </c>
+      <c r="BC13" t="s">
+        <v>2</v>
+      </c>
+      <c r="BD13" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE13" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -2801,7 +2873,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -2958,8 +3030,17 @@
       <c r="BB15" t="s">
         <v>1</v>
       </c>
+      <c r="BC15" t="s">
+        <v>2</v>
+      </c>
+      <c r="BD15" t="s">
+        <v>1</v>
+      </c>
+      <c r="BE15" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="16" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -3122,8 +3203,17 @@
       <c r="BB16" t="s">
         <v>1</v>
       </c>
+      <c r="BC16" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD16" t="s">
+        <v>1</v>
+      </c>
+      <c r="BE16" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -3283,8 +3373,11 @@
       <c r="BB17" t="s">
         <v>2</v>
       </c>
+      <c r="BC17" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="18" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -3444,8 +3537,17 @@
       <c r="BB18" t="s">
         <v>2</v>
       </c>
+      <c r="BC18" t="s">
+        <v>2</v>
+      </c>
+      <c r="BD18" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE18" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -3567,7 +3669,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -3722,7 +3824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3885,8 +3987,14 @@
       <c r="BB21" t="s">
         <v>1</v>
       </c>
+      <c r="BD21" t="s">
+        <v>1</v>
+      </c>
+      <c r="BE21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -3981,7 +4089,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -4114,17 +4222,41 @@
       <c r="AT23" t="s">
         <v>2</v>
       </c>
+      <c r="AU23" t="s">
+        <v>25</v>
+      </c>
       <c r="AV23" t="s">
         <v>2</v>
       </c>
       <c r="AW23" t="s">
         <v>2</v>
       </c>
+      <c r="AX23" t="s">
+        <v>25</v>
+      </c>
+      <c r="AY23" t="s">
+        <v>25</v>
+      </c>
       <c r="AZ23" t="s">
         <v>2</v>
       </c>
+      <c r="BA23" t="s">
+        <v>25</v>
+      </c>
+      <c r="BB23" t="s">
+        <v>25</v>
+      </c>
+      <c r="BC23" t="s">
+        <v>2</v>
+      </c>
+      <c r="BD23" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE23" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="24" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -4246,7 +4378,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -4374,7 +4506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -4522,11 +4654,23 @@
       <c r="AX26" t="s">
         <v>1</v>
       </c>
+      <c r="AY26" t="s">
+        <v>25</v>
+      </c>
       <c r="AZ26" t="s">
         <v>2</v>
       </c>
+      <c r="BA26" t="s">
+        <v>25</v>
+      </c>
+      <c r="BB26" t="s">
+        <v>2</v>
+      </c>
+      <c r="BC26" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="27" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -4671,8 +4815,11 @@
       <c r="BA27" t="s">
         <v>1</v>
       </c>
+      <c r="BD27" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -4832,8 +4979,17 @@
       <c r="BA28" t="s">
         <v>2</v>
       </c>
+      <c r="BC28" t="s">
+        <v>2</v>
+      </c>
+      <c r="BD28" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE28" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="29" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -4984,8 +5140,11 @@
       <c r="BB29" t="s">
         <v>1</v>
       </c>
+      <c r="BC29" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="30" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -5130,8 +5289,14 @@
       <c r="BB30" t="s">
         <v>2</v>
       </c>
+      <c r="BC30" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE30" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="31" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -5255,8 +5420,14 @@
       <c r="BB31" t="s">
         <v>2</v>
       </c>
+      <c r="BC31" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE31" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="32" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>78</v>
       </c>
@@ -5407,8 +5578,17 @@
       <c r="BA32" t="s">
         <v>2</v>
       </c>
+      <c r="BB32" t="s">
+        <v>25</v>
+      </c>
+      <c r="BC32" t="s">
+        <v>25</v>
+      </c>
+      <c r="BD32" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="33" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>45</v>
       </c>
@@ -5568,8 +5748,17 @@
       <c r="BB33" t="s">
         <v>1</v>
       </c>
+      <c r="BC33" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD33" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE33" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -5723,8 +5912,14 @@
       <c r="BB34" t="s">
         <v>2</v>
       </c>
+      <c r="BC34" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE34" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="35" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>24</v>
       </c>
@@ -5884,8 +6079,17 @@
       <c r="BB35" t="s">
         <v>1</v>
       </c>
+      <c r="BC35" t="s">
+        <v>2</v>
+      </c>
+      <c r="BD35" t="s">
+        <v>1</v>
+      </c>
+      <c r="BE35" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="36" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -6042,8 +6246,14 @@
       <c r="BB36" t="s">
         <v>2</v>
       </c>
+      <c r="BC36" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE36" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="37" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -6203,8 +6413,17 @@
       <c r="BB37" t="s">
         <v>1</v>
       </c>
+      <c r="BC37" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD37" t="s">
+        <v>1</v>
+      </c>
+      <c r="BE37" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="38" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -6364,8 +6583,17 @@
       <c r="BB38" t="s">
         <v>1</v>
       </c>
+      <c r="BC38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD38" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE38" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -6519,11 +6747,23 @@
       <c r="AZ39" t="s">
         <v>2</v>
       </c>
+      <c r="BA39" t="s">
+        <v>25</v>
+      </c>
       <c r="BB39" t="s">
         <v>2</v>
       </c>
+      <c r="BC39" t="s">
+        <v>25</v>
+      </c>
+      <c r="BD39" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE39" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="40" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -6669,7 +6909,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>23</v>
       </c>
@@ -6832,8 +7072,14 @@
       <c r="BB41" t="s">
         <v>1</v>
       </c>
+      <c r="BC41" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD41" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="42" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>39</v>
       </c>
@@ -6955,7 +7201,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>29</v>
       </c>
@@ -7118,8 +7364,17 @@
       <c r="BB43" t="s">
         <v>2</v>
       </c>
+      <c r="BC43" t="s">
+        <v>2</v>
+      </c>
+      <c r="BD43" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE43" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="44" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>77</v>
       </c>
@@ -7273,8 +7528,17 @@
       <c r="BB44" t="s">
         <v>1</v>
       </c>
+      <c r="BC44" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD44" t="s">
+        <v>1</v>
+      </c>
+      <c r="BE44" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="45" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -7407,8 +7671,17 @@
       <c r="BB45" t="s">
         <v>2</v>
       </c>
+      <c r="BC45" t="s">
+        <v>2</v>
+      </c>
+      <c r="BD45" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE45" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="46" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>16</v>
       </c>
@@ -7568,8 +7841,17 @@
       <c r="BB46" t="s">
         <v>2</v>
       </c>
+      <c r="BC46" t="s">
+        <v>2</v>
+      </c>
+      <c r="BD46" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE46" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="47" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>17</v>
       </c>
@@ -7729,8 +8011,17 @@
       <c r="BB47" t="s">
         <v>2</v>
       </c>
+      <c r="BC47" t="s">
+        <v>2</v>
+      </c>
+      <c r="BD47" t="s">
+        <v>25</v>
+      </c>
+      <c r="BE47" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -7885,6 +8176,15 @@
         <v>1</v>
       </c>
       <c r="BB48" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC48" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD48" t="s">
+        <v>1</v>
+      </c>
+      <c r="BE48" t="s">
         <v>1</v>
       </c>
     </row>

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19683E99-C292-426D-B6CA-31C622FB3454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE402FA-DC15-4CBB-AF30-92EDF4E28619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
+    <workbookView xWindow="5844" yWindow="0" windowWidth="16716" windowHeight="12360" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendance" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2715" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2747" uniqueCount="79">
   <si>
     <t>Name</t>
   </si>
@@ -723,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:BE50"/>
+  <dimension ref="A1:BF50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -739,7 +739,7 @@
     <col min="52" max="54" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:58" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -911,8 +911,11 @@
       <c r="BE1" s="8">
         <v>45681</v>
       </c>
+      <c r="BF1" s="8">
+        <v>45685</v>
+      </c>
     </row>
-    <row r="2" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1084,8 +1087,11 @@
       <c r="BE2" t="s">
         <v>2</v>
       </c>
+      <c r="BF2" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1248,8 +1254,11 @@
       <c r="BC3" t="s">
         <v>2</v>
       </c>
+      <c r="BF3" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1409,8 +1418,11 @@
       <c r="BE4" t="s">
         <v>2</v>
       </c>
+      <c r="BF4" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -1570,8 +1582,11 @@
       <c r="BC5" t="s">
         <v>2</v>
       </c>
+      <c r="BF5" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1743,8 +1758,11 @@
       <c r="BE6" t="s">
         <v>1</v>
       </c>
+      <c r="BF6" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1869,7 +1887,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -2006,7 +2024,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -2175,8 +2193,11 @@
       <c r="BD9" t="s">
         <v>1</v>
       </c>
+      <c r="BF9" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -2298,7 +2319,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -2423,7 +2444,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2586,8 +2607,11 @@
       <c r="BD12" t="s">
         <v>2</v>
       </c>
+      <c r="BF12" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="13" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2750,8 +2774,11 @@
       <c r="BE13" t="s">
         <v>2</v>
       </c>
+      <c r="BF13" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="14" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -2873,7 +2900,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -3039,8 +3066,11 @@
       <c r="BE15" t="s">
         <v>2</v>
       </c>
+      <c r="BF15" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="16" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -3212,8 +3242,11 @@
       <c r="BE16" t="s">
         <v>1</v>
       </c>
+      <c r="BF16" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -3377,7 +3410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -3546,8 +3579,11 @@
       <c r="BE18" t="s">
         <v>2</v>
       </c>
+      <c r="BF18" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -3669,7 +3705,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -3824,7 +3860,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3993,8 +4029,11 @@
       <c r="BE21" t="s">
         <v>1</v>
       </c>
+      <c r="BF21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -4089,7 +4128,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -4255,8 +4294,11 @@
       <c r="BE23" t="s">
         <v>2</v>
       </c>
+      <c r="BF23" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="24" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -4378,7 +4420,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -4506,7 +4548,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -4670,7 +4712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -4818,8 +4860,11 @@
       <c r="BD27" t="s">
         <v>1</v>
       </c>
+      <c r="BF27" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="28" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -4988,8 +5033,11 @@
       <c r="BE28" t="s">
         <v>2</v>
       </c>
+      <c r="BF28" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="29" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -5144,7 +5192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -5296,7 +5344,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -5426,8 +5474,11 @@
       <c r="BE31" t="s">
         <v>2</v>
       </c>
+      <c r="BF31" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="32" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>78</v>
       </c>
@@ -5587,8 +5638,14 @@
       <c r="BD32" t="s">
         <v>2</v>
       </c>
+      <c r="BE32" t="s">
+        <v>25</v>
+      </c>
+      <c r="BF32" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="33" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>45</v>
       </c>
@@ -5757,8 +5814,11 @@
       <c r="BE33" t="s">
         <v>1</v>
       </c>
+      <c r="BF33" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="34" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -5918,8 +5978,11 @@
       <c r="BE34" t="s">
         <v>2</v>
       </c>
+      <c r="BF34" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="35" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>24</v>
       </c>
@@ -6088,8 +6151,11 @@
       <c r="BE35" t="s">
         <v>2</v>
       </c>
+      <c r="BF35" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="36" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -6252,8 +6318,11 @@
       <c r="BE36" t="s">
         <v>2</v>
       </c>
+      <c r="BF36" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="37" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -6422,8 +6491,11 @@
       <c r="BE37" t="s">
         <v>1</v>
       </c>
+      <c r="BF37" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="38" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -6592,8 +6664,11 @@
       <c r="BE38" t="s">
         <v>2</v>
       </c>
+      <c r="BF38" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="39" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -6762,8 +6837,11 @@
       <c r="BE39" t="s">
         <v>2</v>
       </c>
+      <c r="BF39" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="40" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -6909,7 +6987,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>23</v>
       </c>
@@ -7078,8 +7156,11 @@
       <c r="BD41" t="s">
         <v>1</v>
       </c>
+      <c r="BF41" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="42" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>39</v>
       </c>
@@ -7201,7 +7282,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>29</v>
       </c>
@@ -7373,8 +7454,11 @@
       <c r="BE43" t="s">
         <v>2</v>
       </c>
+      <c r="BF43" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="44" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>77</v>
       </c>
@@ -7537,8 +7621,11 @@
       <c r="BE44" t="s">
         <v>1</v>
       </c>
+      <c r="BF44" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="45" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -7680,8 +7767,11 @@
       <c r="BE45" t="s">
         <v>2</v>
       </c>
+      <c r="BF45" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="46" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>16</v>
       </c>
@@ -7850,8 +7940,11 @@
       <c r="BE46" t="s">
         <v>2</v>
       </c>
+      <c r="BF46" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="47" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>17</v>
       </c>
@@ -8020,8 +8113,11 @@
       <c r="BE47" t="s">
         <v>2</v>
       </c>
+      <c r="BF47" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -8185,6 +8281,9 @@
         <v>1</v>
       </c>
       <c r="BE48" t="s">
+        <v>1</v>
+      </c>
+      <c r="BF48" t="s">
         <v>1</v>
       </c>
     </row>

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE402FA-DC15-4CBB-AF30-92EDF4E28619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757C573E-2ABA-4403-AB39-934F9DA9BADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5844" yWindow="0" windowWidth="16716" windowHeight="12360" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendance" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2747" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2792" uniqueCount="88">
   <si>
     <t>Name</t>
   </si>
@@ -269,6 +269,33 @@
   </si>
   <si>
     <t>Prit Patel</t>
+  </si>
+  <si>
+    <t>Arin Prajapati</t>
+  </si>
+  <si>
+    <t>Bansi Kadia</t>
+  </si>
+  <si>
+    <t>Marmik Patel</t>
+  </si>
+  <si>
+    <t>Dhyey Patel</t>
+  </si>
+  <si>
+    <t>Yash Chauhan</t>
+  </si>
+  <si>
+    <t>Riya Patel</t>
+  </si>
+  <si>
+    <t>Harsh Vyas</t>
+  </si>
+  <si>
+    <t>Krupanshi Patel</t>
+  </si>
+  <si>
+    <t>Zeel Prajapati</t>
   </si>
 </sst>
 </file>
@@ -723,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:BF50"/>
+  <dimension ref="A1:BG59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -739,7 +766,7 @@
     <col min="52" max="54" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:59" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -914,8 +941,11 @@
       <c r="BF1" s="8">
         <v>45685</v>
       </c>
+      <c r="BG1" s="8">
+        <v>45692</v>
+      </c>
     </row>
-    <row r="2" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1090,8 +1120,11 @@
       <c r="BF2" t="s">
         <v>1</v>
       </c>
+      <c r="BG2" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1257,8 +1290,11 @@
       <c r="BF3" t="s">
         <v>1</v>
       </c>
+      <c r="BG3" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1421,8 +1457,11 @@
       <c r="BF4" t="s">
         <v>2</v>
       </c>
+      <c r="BG4" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -1586,7 +1625,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1761,8 +1800,11 @@
       <c r="BF6" t="s">
         <v>1</v>
       </c>
+      <c r="BG6" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1887,7 +1929,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -2024,7 +2066,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -2196,8 +2238,11 @@
       <c r="BF9" t="s">
         <v>2</v>
       </c>
+      <c r="BG9" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -2319,7 +2364,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -2444,7 +2489,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2610,8 +2655,11 @@
       <c r="BF12" t="s">
         <v>2</v>
       </c>
+      <c r="BG12" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="13" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2778,7 +2826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -2900,7 +2948,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -3069,8 +3117,11 @@
       <c r="BF15" t="s">
         <v>2</v>
       </c>
+      <c r="BG15" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="16" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -3245,8 +3296,11 @@
       <c r="BF16" t="s">
         <v>1</v>
       </c>
+      <c r="BG16" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="17" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -3410,7 +3464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -3582,8 +3636,11 @@
       <c r="BF18" t="s">
         <v>2</v>
       </c>
+      <c r="BG18" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -3705,7 +3762,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -3860,7 +3917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -4032,8 +4089,11 @@
       <c r="BF21" t="s">
         <v>1</v>
       </c>
+      <c r="BG21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -4128,7 +4188,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -4297,8 +4357,11 @@
       <c r="BF23" t="s">
         <v>2</v>
       </c>
+      <c r="BG23" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="24" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -4420,7 +4483,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -4548,7 +4611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -4712,7 +4775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -4863,8 +4926,11 @@
       <c r="BF27" t="s">
         <v>2</v>
       </c>
+      <c r="BG27" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -5036,8 +5102,11 @@
       <c r="BF28" t="s">
         <v>2</v>
       </c>
+      <c r="BG28" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="29" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -5191,8 +5260,11 @@
       <c r="BC29" t="s">
         <v>1</v>
       </c>
+      <c r="BG29" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="30" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -5343,8 +5415,11 @@
       <c r="BE30" t="s">
         <v>2</v>
       </c>
+      <c r="BG30" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="31" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -5478,7 +5553,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>78</v>
       </c>
@@ -5644,8 +5719,11 @@
       <c r="BF32" t="s">
         <v>2</v>
       </c>
+      <c r="BG32" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="33" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>45</v>
       </c>
@@ -5817,8 +5895,11 @@
       <c r="BF33" t="s">
         <v>2</v>
       </c>
+      <c r="BG33" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="34" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -5981,8 +6062,11 @@
       <c r="BF34" t="s">
         <v>2</v>
       </c>
+      <c r="BG34" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="35" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>24</v>
       </c>
@@ -6155,7 +6239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -6321,8 +6405,11 @@
       <c r="BF36" t="s">
         <v>1</v>
       </c>
+      <c r="BG36" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="37" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -6494,8 +6581,11 @@
       <c r="BF37" t="s">
         <v>1</v>
       </c>
+      <c r="BG37" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="38" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -6667,8 +6757,11 @@
       <c r="BF38" t="s">
         <v>1</v>
       </c>
+      <c r="BG38" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="39" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -6840,8 +6933,11 @@
       <c r="BF39" t="s">
         <v>1</v>
       </c>
+      <c r="BG39" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="40" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -6987,7 +7083,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>23</v>
       </c>
@@ -7159,8 +7255,11 @@
       <c r="BF41" t="s">
         <v>1</v>
       </c>
+      <c r="BG41" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="42" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>39</v>
       </c>
@@ -7282,7 +7381,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>29</v>
       </c>
@@ -7458,7 +7557,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>77</v>
       </c>
@@ -7625,7 +7724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -7770,8 +7869,11 @@
       <c r="BF45" t="s">
         <v>2</v>
       </c>
+      <c r="BG45" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="46" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>16</v>
       </c>
@@ -7943,8 +8045,11 @@
       <c r="BF46" t="s">
         <v>2</v>
       </c>
+      <c r="BG46" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="47" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>17</v>
       </c>
@@ -8116,8 +8221,11 @@
       <c r="BF47" t="s">
         <v>2</v>
       </c>
+      <c r="BG47" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -8286,184 +8394,259 @@
       <c r="BF48" t="s">
         <v>1</v>
       </c>
+      <c r="BG48" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="50" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:59" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>79</v>
+      </c>
+      <c r="BG49" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>80</v>
+      </c>
+      <c r="BG50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:59" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>81</v>
+      </c>
+      <c r="BG51" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:59" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>82</v>
+      </c>
+      <c r="BG52" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:59" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>83</v>
+      </c>
+      <c r="BG53" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:59" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>84</v>
+      </c>
+      <c r="BG54" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:59" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>85</v>
+      </c>
+      <c r="BG55" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:59" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>86</v>
+      </c>
+      <c r="BG56" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:59" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>87</v>
+      </c>
+      <c r="BG57" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:59" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>38</v>
       </c>
-      <c r="C50">
+      <c r="C59">
         <f>COUNTIF(C1:C41, "P") +COUNTIF(C1:C41, "O")</f>
         <v>19</v>
       </c>
-      <c r="D50">
+      <c r="D59">
         <f>COUNTIF(D1:D41, "P") +COUNTIF(D1:D41, "O")</f>
         <v>21</v>
       </c>
-      <c r="E50">
+      <c r="E59">
         <f>COUNTIF(E1:E41, "P") +COUNTIF(E1:E41, "O")</f>
         <v>22</v>
       </c>
-      <c r="F50">
+      <c r="F59">
         <f>COUNTIF(F1:F41, "P") +COUNTIF(F1:F41, "O")</f>
         <v>24</v>
       </c>
-      <c r="G50">
-        <f t="shared" ref="G50:AT50" si="0">COUNTIF(G1:G41, "P") +COUNTIF(G1:G41, "O")</f>
+      <c r="G59">
+        <f t="shared" ref="G59:AT59" si="0">COUNTIF(G1:G41, "P") +COUNTIF(G1:G41, "O")</f>
         <v>24</v>
       </c>
-      <c r="H50">
+      <c r="H59">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="I50">
+      <c r="I59">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="J50">
+      <c r="J59">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="K50">
+      <c r="K59">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="L50">
+      <c r="L59">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="M50">
+      <c r="M59">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="N50">
+      <c r="N59">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="O50">
+      <c r="O59">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="P50">
+      <c r="P59">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="Q50">
+      <c r="Q59">
         <f>COUNTIF(Q1:Q41, "P") +COUNTIF(Q1:Q41, "O")</f>
         <v>28</v>
       </c>
-      <c r="R50">
+      <c r="R59">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="S50">
+      <c r="S59">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="T50">
+      <c r="T59">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="U50">
+      <c r="U59">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="V50">
+      <c r="V59">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="W50">
+      <c r="W59">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="X50">
+      <c r="X59">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="Y50">
+      <c r="Y59">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="Z50">
+      <c r="Z59">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="AA50">
+      <c r="AA59">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="AB50">
+      <c r="AB59">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="AC50">
+      <c r="AC59">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="AD50">
+      <c r="AD59">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="AE50">
+      <c r="AE59">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="AF50">
+      <c r="AF59">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="AG50">
+      <c r="AG59">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="AH50">
+      <c r="AH59">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="AI50">
+      <c r="AI59">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="AJ50">
+      <c r="AJ59">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="AK50">
+      <c r="AK59">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="AL50">
+      <c r="AL59">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="AM50">
+      <c r="AM59">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="AN50">
+      <c r="AN59">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="AO50">
+      <c r="AO59">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="AP50">
+      <c r="AP59">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="AQ50">
+      <c r="AQ59">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="AR50">
+      <c r="AR59">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="AS50">
+      <c r="AS59">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="AT50">
+      <c r="AT59">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13FAFE47-E2B9-449A-9B8F-ED2F2530D45E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA275EE-1F4E-402F-8B1B-DEC2619EE321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2840" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2880" uniqueCount="92">
   <si>
     <t>Name</t>
   </si>
@@ -302,6 +302,12 @@
   </si>
   <si>
     <t>Anagh Patel</t>
+  </si>
+  <si>
+    <t>Mithil Parmar</t>
+  </si>
+  <si>
+    <t>Dhairya Patel</t>
   </si>
 </sst>
 </file>
@@ -756,7 +762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:BH61"/>
+  <dimension ref="A1:BI63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -772,7 +778,7 @@
     <col min="52" max="54" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:61" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -953,8 +959,11 @@
       <c r="BH1" s="8">
         <v>45695</v>
       </c>
+      <c r="BI1" s="8">
+        <v>45699</v>
+      </c>
     </row>
-    <row r="2" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1135,8 +1144,11 @@
       <c r="BH2" t="s">
         <v>1</v>
       </c>
+      <c r="BI2" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1305,8 +1317,11 @@
       <c r="BG3" t="s">
         <v>2</v>
       </c>
+      <c r="BI3" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1475,8 +1490,11 @@
       <c r="BH4" t="s">
         <v>2</v>
       </c>
+      <c r="BI4" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>79</v>
       </c>
@@ -1487,7 +1505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -1653,8 +1671,11 @@
       <c r="BH6" t="s">
         <v>2</v>
       </c>
+      <c r="BI6" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="7" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -1835,8 +1856,11 @@
       <c r="BH7" t="s">
         <v>1</v>
       </c>
+      <c r="BI7" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>80</v>
       </c>
@@ -1846,8 +1870,11 @@
       <c r="BH8" t="s">
         <v>1</v>
       </c>
+      <c r="BI8" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1972,7 +1999,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -2109,7 +2136,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -2287,8 +2314,11 @@
       <c r="BH11" t="s">
         <v>2</v>
       </c>
+      <c r="BI11" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="12" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -2410,7 +2440,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -2535,7 +2565,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>82</v>
       </c>
@@ -2545,8 +2575,11 @@
       <c r="BH14" t="s">
         <v>1</v>
       </c>
+      <c r="BI14" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="15" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -2718,8 +2751,11 @@
       <c r="BH15" t="s">
         <v>2</v>
       </c>
+      <c r="BI15" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -2888,8 +2924,11 @@
       <c r="BH16" t="s">
         <v>2</v>
       </c>
+      <c r="BI16" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="17" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -3011,7 +3050,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -3186,8 +3225,11 @@
       <c r="BH18" t="s">
         <v>2</v>
       </c>
+      <c r="BI18" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -3368,8 +3410,11 @@
       <c r="BH19" t="s">
         <v>1</v>
       </c>
+      <c r="BI19" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="20" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -3533,7 +3578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>85</v>
       </c>
@@ -3543,8 +3588,11 @@
       <c r="BH21" t="s">
         <v>1</v>
       </c>
+      <c r="BI21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -3722,8 +3770,11 @@
       <c r="BH22" t="s">
         <v>2</v>
       </c>
+      <c r="BI22" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="23" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -3845,7 +3896,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -4000,7 +4051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -4178,8 +4229,11 @@
       <c r="BH25" t="s">
         <v>1</v>
       </c>
+      <c r="BI25" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="26" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>47</v>
       </c>
@@ -4274,7 +4328,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -4447,7 +4501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>86</v>
       </c>
@@ -4457,8 +4511,11 @@
       <c r="BH28" t="s">
         <v>1</v>
       </c>
+      <c r="BI28" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="29" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>52</v>
       </c>
@@ -4580,7 +4637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>81</v>
       </c>
@@ -4588,7 +4645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>56</v>
       </c>
@@ -4716,7 +4773,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>22</v>
       </c>
@@ -4880,7 +4937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>88</v>
       </c>
@@ -4890,8 +4947,11 @@
       <c r="BH33" t="s">
         <v>1</v>
       </c>
+      <c r="BI33" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>21</v>
       </c>
@@ -5048,8 +5108,11 @@
       <c r="BH34" t="s">
         <v>2</v>
       </c>
+      <c r="BI34" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="35" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>8</v>
       </c>
@@ -5227,8 +5290,11 @@
       <c r="BH35" t="s">
         <v>2</v>
       </c>
+      <c r="BI35" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="36" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>54</v>
       </c>
@@ -5389,7 +5455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>57</v>
       </c>
@@ -5544,7 +5610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -5680,8 +5746,11 @@
       <c r="BH38" t="s">
         <v>2</v>
       </c>
+      <c r="BI38" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>78</v>
       </c>
@@ -5853,8 +5922,11 @@
       <c r="BH39" t="s">
         <v>2</v>
       </c>
+      <c r="BI39" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="40" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -6033,7 +6105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>10</v>
       </c>
@@ -6199,8 +6271,11 @@
       <c r="BG41" t="s">
         <v>1</v>
       </c>
+      <c r="BI41" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="42" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>24</v>
       </c>
@@ -6372,8 +6447,11 @@
       <c r="BF42" t="s">
         <v>1</v>
       </c>
+      <c r="BI42" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="43" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>84</v>
       </c>
@@ -6383,8 +6461,11 @@
       <c r="BH43" t="s">
         <v>1</v>
       </c>
+      <c r="BI43" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="44" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>11</v>
       </c>
@@ -6556,8 +6637,11 @@
       <c r="BH44" t="s">
         <v>2</v>
       </c>
+      <c r="BI44" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="45" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>12</v>
       </c>
@@ -6735,8 +6819,11 @@
       <c r="BH45" t="s">
         <v>1</v>
       </c>
+      <c r="BI45" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="46" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>42</v>
       </c>
@@ -6914,8 +7001,11 @@
       <c r="BH46" t="s">
         <v>1</v>
       </c>
+      <c r="BI46" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="47" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>14</v>
       </c>
@@ -7093,8 +7183,11 @@
       <c r="BH47" t="s">
         <v>2</v>
       </c>
+      <c r="BI47" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="48" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>15</v>
       </c>
@@ -7266,8 +7359,11 @@
       <c r="BH48" t="s">
         <v>2</v>
       </c>
+      <c r="BI48" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="49" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>23</v>
       </c>
@@ -7445,8 +7541,11 @@
       <c r="BH49" t="s">
         <v>2</v>
       </c>
+      <c r="BI49" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="50" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>39</v>
       </c>
@@ -7568,7 +7667,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>29</v>
       </c>
@@ -7746,8 +7845,11 @@
       <c r="BH51" t="s">
         <v>2</v>
       </c>
+      <c r="BI51" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="52" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -7913,8 +8015,11 @@
       <c r="BF52" t="s">
         <v>1</v>
       </c>
+      <c r="BI52" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="53" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>49</v>
       </c>
@@ -8065,8 +8170,11 @@
       <c r="BH53" t="s">
         <v>2</v>
       </c>
+      <c r="BI53" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="54" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -8074,7 +8182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>16</v>
       </c>
@@ -8252,8 +8360,11 @@
       <c r="BH55" t="s">
         <v>2</v>
       </c>
+      <c r="BI55" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="56" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -8431,8 +8542,11 @@
       <c r="BH56" t="s">
         <v>2</v>
       </c>
+      <c r="BI56" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="57" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -8604,8 +8718,11 @@
       <c r="BG57" t="s">
         <v>1</v>
       </c>
+      <c r="BI57" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="58" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>87</v>
       </c>
@@ -8616,7 +8733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>89</v>
       </c>
@@ -8627,183 +8744,199 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:61" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>90</v>
+      </c>
+      <c r="BI60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>91</v>
+      </c>
+      <c r="BI61" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:61" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>38</v>
       </c>
-      <c r="C61">
+      <c r="C63">
         <f>COUNTIF(C1:C41, "P") +COUNTIF(C1:C41, "O")</f>
         <v>14</v>
       </c>
-      <c r="D61">
+      <c r="D63">
         <f>COUNTIF(D1:D41, "P") +COUNTIF(D1:D41, "O")</f>
         <v>15</v>
       </c>
-      <c r="E61">
+      <c r="E63">
         <f>COUNTIF(E1:E41, "P") +COUNTIF(E1:E41, "O")</f>
         <v>17</v>
       </c>
-      <c r="F61">
+      <c r="F63">
         <f>COUNTIF(F1:F41, "P") +COUNTIF(F1:F41, "O")</f>
         <v>18</v>
       </c>
-      <c r="G61">
-        <f t="shared" ref="G61:AT61" si="0">COUNTIF(G1:G41, "P") +COUNTIF(G1:G41, "O")</f>
+      <c r="G63">
+        <f t="shared" ref="G63:AT63" si="0">COUNTIF(G1:G41, "P") +COUNTIF(G1:G41, "O")</f>
         <v>18</v>
       </c>
-      <c r="H61">
+      <c r="H63">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="I61">
+      <c r="I63">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="J61">
+      <c r="J63">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="K61">
+      <c r="K63">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="L61">
+      <c r="L63">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="M61">
+      <c r="M63">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="N61">
+      <c r="N63">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="O61">
+      <c r="O63">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="P61">
+      <c r="P63">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="Q61">
+      <c r="Q63">
         <f>COUNTIF(Q1:Q41, "P") +COUNTIF(Q1:Q41, "O")</f>
         <v>21</v>
       </c>
-      <c r="R61">
+      <c r="R63">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="S61">
+      <c r="S63">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="T61">
+      <c r="T63">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="U61">
+      <c r="U63">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="V61">
+      <c r="V63">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="W61">
+      <c r="W63">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="X61">
+      <c r="X63">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="Y61">
+      <c r="Y63">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="Z61">
+      <c r="Z63">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="AA61">
+      <c r="AA63">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="AB61">
+      <c r="AB63">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="AC61">
+      <c r="AC63">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="AD61">
+      <c r="AD63">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="AE61">
+      <c r="AE63">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="AF61">
+      <c r="AF63">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="AG61">
+      <c r="AG63">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="AH61">
+      <c r="AH63">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="AI61">
+      <c r="AI63">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="AJ61">
+      <c r="AJ63">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="AK61">
+      <c r="AK63">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="AL61">
+      <c r="AL63">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="AM61">
+      <c r="AM63">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="AN61">
+      <c r="AN63">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="AO61">
+      <c r="AO63">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="AP61">
+      <c r="AP63">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="AQ61">
+      <c r="AQ63">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="AR61">
+      <c r="AR63">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="AS61">
+      <c r="AS63">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="AT61">
+      <c r="AT63">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA275EE-1F4E-402F-8B1B-DEC2619EE321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B678A950-BC11-4D53-AA08-A66153B74354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2880" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2993" uniqueCount="92">
   <si>
     <t>Name</t>
   </si>
@@ -762,7 +762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:BI63"/>
+  <dimension ref="A1:BL63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -778,7 +778,7 @@
     <col min="52" max="54" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:64" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -962,8 +962,17 @@
       <c r="BI1" s="8">
         <v>45699</v>
       </c>
+      <c r="BJ1" s="8">
+        <v>45702</v>
+      </c>
+      <c r="BK1" s="8">
+        <v>45706</v>
+      </c>
+      <c r="BL1" s="8">
+        <v>45713</v>
+      </c>
     </row>
-    <row r="2" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1147,8 +1156,17 @@
       <c r="BI2" t="s">
         <v>1</v>
       </c>
+      <c r="BJ2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="3" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1320,8 +1338,17 @@
       <c r="BI3" t="s">
         <v>1</v>
       </c>
+      <c r="BJ3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="4" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1493,8 +1520,14 @@
       <c r="BI4" t="s">
         <v>2</v>
       </c>
+      <c r="BJ4" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>79</v>
       </c>
@@ -1504,8 +1537,11 @@
       <c r="BH5" t="s">
         <v>1</v>
       </c>
+      <c r="BJ5" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -1674,8 +1710,14 @@
       <c r="BI6" t="s">
         <v>2</v>
       </c>
+      <c r="BJ6" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="7" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -1859,8 +1901,17 @@
       <c r="BI7" t="s">
         <v>1</v>
       </c>
+      <c r="BJ7" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>80</v>
       </c>
@@ -1873,8 +1924,14 @@
       <c r="BI8" t="s">
         <v>1</v>
       </c>
+      <c r="BJ8" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK8" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1999,7 +2056,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -2136,7 +2193,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -2317,8 +2374,17 @@
       <c r="BI11" t="s">
         <v>1</v>
       </c>
+      <c r="BJ11" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK11" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL11" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="12" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -2440,7 +2506,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -2565,7 +2631,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>82</v>
       </c>
@@ -2578,8 +2644,14 @@
       <c r="BI14" t="s">
         <v>1</v>
       </c>
+      <c r="BJ14" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK14" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="15" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -2754,8 +2826,17 @@
       <c r="BI15" t="s">
         <v>1</v>
       </c>
+      <c r="BJ15" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK15" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL15" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -2927,8 +3008,17 @@
       <c r="BI16" t="s">
         <v>2</v>
       </c>
+      <c r="BJ16" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK16" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL16" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="17" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -3050,7 +3140,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -3228,8 +3318,17 @@
       <c r="BI18" t="s">
         <v>2</v>
       </c>
+      <c r="BJ18" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK18" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL18" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="19" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -3413,8 +3512,14 @@
       <c r="BI19" t="s">
         <v>1</v>
       </c>
+      <c r="BJ19" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK19" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="20" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -3578,7 +3683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>85</v>
       </c>
@@ -3591,8 +3696,14 @@
       <c r="BI21" t="s">
         <v>1</v>
       </c>
+      <c r="BJ21" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -3773,8 +3884,17 @@
       <c r="BI22" t="s">
         <v>2</v>
       </c>
+      <c r="BJ22" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK22" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL22" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="23" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -3896,7 +4016,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -4051,7 +4171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -4232,8 +4352,17 @@
       <c r="BI25" t="s">
         <v>1</v>
       </c>
+      <c r="BJ25" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK25" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL25" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="26" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>47</v>
       </c>
@@ -4328,7 +4457,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -4500,8 +4629,17 @@
       <c r="BG27" t="s">
         <v>2</v>
       </c>
+      <c r="BJ27" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK27" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL27" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="28" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>86</v>
       </c>
@@ -4514,8 +4652,17 @@
       <c r="BI28" t="s">
         <v>1</v>
       </c>
+      <c r="BJ28" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK28" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL28" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="29" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>52</v>
       </c>
@@ -4637,15 +4784,24 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>81</v>
       </c>
       <c r="BG30" t="s">
         <v>1</v>
       </c>
+      <c r="BJ30" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK30" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL30" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="31" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>56</v>
       </c>
@@ -4773,7 +4929,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>22</v>
       </c>
@@ -4937,7 +5093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>88</v>
       </c>
@@ -4950,8 +5106,14 @@
       <c r="BI33" t="s">
         <v>1</v>
       </c>
+      <c r="BJ33" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK33" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>21</v>
       </c>
@@ -5111,8 +5273,17 @@
       <c r="BI34" t="s">
         <v>1</v>
       </c>
+      <c r="BJ34" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK34" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL34" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="35" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>8</v>
       </c>
@@ -5293,8 +5464,14 @@
       <c r="BI35" t="s">
         <v>2</v>
       </c>
+      <c r="BJ35" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK35" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="36" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>54</v>
       </c>
@@ -5454,8 +5631,11 @@
       <c r="BH36" t="s">
         <v>1</v>
       </c>
+      <c r="BJ36" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="37" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>57</v>
       </c>
@@ -5609,8 +5789,14 @@
       <c r="BG37" t="s">
         <v>2</v>
       </c>
+      <c r="BK37" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL37" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="38" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -5749,8 +5935,17 @@
       <c r="BI38" t="s">
         <v>2</v>
       </c>
+      <c r="BJ38" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK38" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL38" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>78</v>
       </c>
@@ -5925,8 +6120,14 @@
       <c r="BI39" t="s">
         <v>2</v>
       </c>
+      <c r="BK39" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL39" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="40" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -6105,7 +6306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>10</v>
       </c>
@@ -6274,8 +6475,17 @@
       <c r="BI41" t="s">
         <v>1</v>
       </c>
+      <c r="BJ41" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK41" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL41" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="42" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>24</v>
       </c>
@@ -6450,8 +6660,17 @@
       <c r="BI42" t="s">
         <v>1</v>
       </c>
+      <c r="BJ42" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK42" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL42" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="43" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>84</v>
       </c>
@@ -6464,8 +6683,17 @@
       <c r="BI43" t="s">
         <v>1</v>
       </c>
+      <c r="BJ43" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK43" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL43" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="44" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>11</v>
       </c>
@@ -6640,8 +6868,17 @@
       <c r="BI44" t="s">
         <v>1</v>
       </c>
+      <c r="BJ44" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK44" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL44" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="45" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>12</v>
       </c>
@@ -6822,8 +7059,17 @@
       <c r="BI45" t="s">
         <v>1</v>
       </c>
+      <c r="BJ45" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK45" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL45" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="46" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>42</v>
       </c>
@@ -7004,8 +7250,17 @@
       <c r="BI46" t="s">
         <v>1</v>
       </c>
+      <c r="BJ46" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK46" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL46" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="47" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>14</v>
       </c>
@@ -7186,8 +7441,17 @@
       <c r="BI47" t="s">
         <v>1</v>
       </c>
+      <c r="BJ47" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK47" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL47" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="48" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>15</v>
       </c>
@@ -7362,8 +7626,11 @@
       <c r="BI48" t="s">
         <v>2</v>
       </c>
+      <c r="BJ48" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="49" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>23</v>
       </c>
@@ -7544,8 +7811,17 @@
       <c r="BI49" t="s">
         <v>1</v>
       </c>
+      <c r="BJ49" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK49" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL49" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="50" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>39</v>
       </c>
@@ -7667,7 +7943,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>29</v>
       </c>
@@ -7848,8 +8124,17 @@
       <c r="BI51" t="s">
         <v>2</v>
       </c>
+      <c r="BJ51" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK51" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL51" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="52" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -8018,8 +8303,14 @@
       <c r="BI52" t="s">
         <v>1</v>
       </c>
+      <c r="BK52" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL52" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="53" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>49</v>
       </c>
@@ -8173,16 +8464,34 @@
       <c r="BI53" t="s">
         <v>2</v>
       </c>
+      <c r="BJ53" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK53" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL53" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="54" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>83</v>
       </c>
       <c r="BG54" t="s">
         <v>1</v>
       </c>
+      <c r="BJ54" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK54" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL54" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="55" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>16</v>
       </c>
@@ -8363,8 +8672,17 @@
       <c r="BI55" t="s">
         <v>2</v>
       </c>
+      <c r="BJ55" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK55" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL55" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="56" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -8545,8 +8863,17 @@
       <c r="BI56" t="s">
         <v>1</v>
       </c>
+      <c r="BJ56" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK56" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL56" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="57" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -8721,8 +9048,14 @@
       <c r="BI57" t="s">
         <v>1</v>
       </c>
+      <c r="BJ57" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK57" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="58" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>87</v>
       </c>
@@ -8733,7 +9066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>89</v>
       </c>
@@ -8744,23 +9077,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>90</v>
       </c>
       <c r="BI60" t="s">
         <v>1</v>
       </c>
+      <c r="BJ60" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK60" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL60" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="61" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>91</v>
       </c>
       <c r="BI61" t="s">
         <v>1</v>
       </c>
+      <c r="BJ61" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK61" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="63" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>38</v>
       </c>

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66BCC3BD-53E8-4A0A-AD05-77F131BE92A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E14E83-C0D0-4229-9E45-A800DB1D2F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3024" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3048" uniqueCount="92">
   <si>
     <t>Name</t>
   </si>
@@ -762,7 +762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:BM63"/>
+  <dimension ref="A1:BN63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -773,12 +773,13 @@
     <col min="17" max="25" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="26" max="36" width="8.77734375" bestFit="1" customWidth="1"/>
     <col min="37" max="43" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="9" bestFit="1" customWidth="1"/>
-    <col min="45" max="51" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="52" max="54" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="44" max="51" width="9" bestFit="1" customWidth="1"/>
+    <col min="52" max="58" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="59" max="64" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:65" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:66" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -974,8 +975,11 @@
       <c r="BM1" s="8">
         <v>45716</v>
       </c>
+      <c r="BN1" s="8">
+        <v>45720</v>
+      </c>
     </row>
-    <row r="2" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1168,8 +1172,11 @@
       <c r="BL2" t="s">
         <v>25</v>
       </c>
+      <c r="BN2" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1353,8 +1360,11 @@
       <c r="BM3" t="s">
         <v>2</v>
       </c>
+      <c r="BN3" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>89</v>
       </c>
@@ -1365,7 +1375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -1546,8 +1556,11 @@
       <c r="BM5" t="s">
         <v>2</v>
       </c>
+      <c r="BN5" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>79</v>
       </c>
@@ -1561,7 +1574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -1739,8 +1752,11 @@
       <c r="BM7" t="s">
         <v>2</v>
       </c>
+      <c r="BN7" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="8" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -1936,8 +1952,11 @@
       <c r="BM8" t="s">
         <v>1</v>
       </c>
+      <c r="BN8" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>80</v>
       </c>
@@ -1956,8 +1975,11 @@
       <c r="BK9" t="s">
         <v>1</v>
       </c>
+      <c r="BN9" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2082,7 +2104,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -2219,7 +2241,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>91</v>
       </c>
@@ -2235,8 +2257,11 @@
       <c r="BM12" t="s">
         <v>1</v>
       </c>
+      <c r="BN12" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -2429,8 +2454,11 @@
       <c r="BM13" t="s">
         <v>2</v>
       </c>
+      <c r="BN13" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="14" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -2552,7 +2580,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2677,7 +2705,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -2700,7 +2728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -2887,8 +2915,11 @@
       <c r="BM17" t="s">
         <v>1</v>
       </c>
+      <c r="BN17" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="18" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -3072,8 +3103,11 @@
       <c r="BM18" t="s">
         <v>2</v>
       </c>
+      <c r="BN18" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -3195,7 +3229,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -3382,8 +3416,11 @@
       <c r="BL20" t="s">
         <v>1</v>
       </c>
+      <c r="BN20" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="21" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -3573,8 +3610,11 @@
       <c r="BK21" t="s">
         <v>1</v>
       </c>
+      <c r="BN21" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="22" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -3738,7 +3778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>85</v>
       </c>
@@ -3758,7 +3798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -3952,7 +3992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -4074,7 +4114,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -4229,7 +4269,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -4422,8 +4462,11 @@
       <c r="BM27" t="s">
         <v>1</v>
       </c>
+      <c r="BN27" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -4518,7 +4561,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -4558,12 +4601,6 @@
       <c r="M29" t="s">
         <v>2</v>
       </c>
-      <c r="N29" t="s">
-        <v>25</v>
-      </c>
-      <c r="O29" t="s">
-        <v>25</v>
-      </c>
       <c r="P29" t="s">
         <v>2</v>
       </c>
@@ -4609,9 +4646,6 @@
       <c r="AD29" t="s">
         <v>2</v>
       </c>
-      <c r="AE29" t="s">
-        <v>25</v>
-      </c>
       <c r="AF29" t="s">
         <v>2</v>
       </c>
@@ -4630,18 +4664,9 @@
       <c r="AM29" t="s">
         <v>2</v>
       </c>
-      <c r="AN29" t="s">
-        <v>25</v>
-      </c>
       <c r="AO29" t="s">
         <v>2</v>
       </c>
-      <c r="AP29" t="s">
-        <v>25</v>
-      </c>
-      <c r="AQ29" t="s">
-        <v>25</v>
-      </c>
       <c r="AR29" t="s">
         <v>2</v>
       </c>
@@ -4651,30 +4676,15 @@
       <c r="AT29" t="s">
         <v>2</v>
       </c>
-      <c r="AU29" t="s">
-        <v>25</v>
-      </c>
       <c r="AV29" t="s">
         <v>2</v>
       </c>
       <c r="AW29" t="s">
         <v>2</v>
       </c>
-      <c r="AX29" t="s">
-        <v>25</v>
-      </c>
-      <c r="AY29" t="s">
-        <v>25</v>
-      </c>
       <c r="AZ29" t="s">
         <v>2</v>
       </c>
-      <c r="BA29" t="s">
-        <v>25</v>
-      </c>
-      <c r="BB29" t="s">
-        <v>25</v>
-      </c>
       <c r="BC29" t="s">
         <v>2</v>
       </c>
@@ -4702,8 +4712,11 @@
       <c r="BM29" t="s">
         <v>2</v>
       </c>
+      <c r="BN29" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -4728,8 +4741,11 @@
       <c r="BM30" t="s">
         <v>1</v>
       </c>
+      <c r="BN30" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="31" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -4851,7 +4867,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>81</v>
       </c>
@@ -4870,8 +4886,11 @@
       <c r="BM32" t="s">
         <v>1</v>
       </c>
+      <c r="BN32" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>90</v>
       </c>
@@ -4891,7 +4910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>56</v>
       </c>
@@ -5019,7 +5038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>22</v>
       </c>
@@ -5183,7 +5202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>88</v>
       </c>
@@ -5202,8 +5221,11 @@
       <c r="BK36" t="s">
         <v>1</v>
       </c>
+      <c r="BN36" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="37" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>21</v>
       </c>
@@ -5375,8 +5397,11 @@
       <c r="BM37" t="s">
         <v>2</v>
       </c>
+      <c r="BN37" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="38" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -5566,8 +5591,11 @@
       <c r="BM38" t="s">
         <v>2</v>
       </c>
+      <c r="BN38" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>54</v>
       </c>
@@ -5731,7 +5759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>57</v>
       </c>
@@ -5894,8 +5922,11 @@
       <c r="BM40" t="s">
         <v>2</v>
       </c>
+      <c r="BN40" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="41" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -6043,8 +6074,11 @@
       <c r="BL41" t="s">
         <v>2</v>
       </c>
+      <c r="BN41" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="42" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>78</v>
       </c>
@@ -6229,7 +6263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -6408,7 +6442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>10</v>
       </c>
@@ -6587,7 +6621,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>24</v>
       </c>
@@ -6774,8 +6808,11 @@
       <c r="BM45" t="s">
         <v>2</v>
       </c>
+      <c r="BN45" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="46" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>84</v>
       </c>
@@ -6797,8 +6834,11 @@
       <c r="BL46" t="s">
         <v>1</v>
       </c>
+      <c r="BN46" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="47" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -6985,8 +7025,11 @@
       <c r="BM47" t="s">
         <v>2</v>
       </c>
+      <c r="BN47" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -7176,8 +7219,11 @@
       <c r="BL48" t="s">
         <v>1</v>
       </c>
+      <c r="BN48" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="49" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>42</v>
       </c>
@@ -7370,8 +7416,11 @@
       <c r="BM49" t="s">
         <v>2</v>
       </c>
+      <c r="BN49" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="50" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>14</v>
       </c>
@@ -7564,8 +7613,11 @@
       <c r="BM50" t="s">
         <v>1</v>
       </c>
+      <c r="BN50" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="51" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -7744,7 +7796,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>23</v>
       </c>
@@ -7937,8 +7989,11 @@
       <c r="BM52" t="s">
         <v>1</v>
       </c>
+      <c r="BN52" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="53" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>39</v>
       </c>
@@ -8060,7 +8115,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>29</v>
       </c>
@@ -8253,8 +8308,11 @@
       <c r="BM54" t="s">
         <v>2</v>
       </c>
+      <c r="BN54" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="55" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>77</v>
       </c>
@@ -8432,8 +8490,11 @@
       <c r="BM55" t="s">
         <v>1</v>
       </c>
+      <c r="BN55" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="56" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>49</v>
       </c>
@@ -8599,8 +8660,11 @@
       <c r="BM56" t="s">
         <v>2</v>
       </c>
+      <c r="BN56" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="57" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>83</v>
       </c>
@@ -8619,8 +8683,11 @@
       <c r="BM57" t="s">
         <v>1</v>
       </c>
+      <c r="BN57" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="58" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>16</v>
       </c>
@@ -8813,8 +8880,11 @@
       <c r="BM58" t="s">
         <v>2</v>
       </c>
+      <c r="BN58" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="59" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -9007,8 +9077,11 @@
       <c r="BM59" t="s">
         <v>1</v>
       </c>
+      <c r="BN59" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="60" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>55</v>
       </c>
@@ -9192,8 +9265,11 @@
       <c r="BM60" t="s">
         <v>1</v>
       </c>
+      <c r="BN60" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="61" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>87</v>
       </c>
@@ -9204,7 +9280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>38</v>
       </c>

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E14E83-C0D0-4229-9E45-A800DB1D2F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE60CB1-8E50-4378-A510-1178B104D4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3048" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3128" uniqueCount="92">
   <si>
     <t>Name</t>
   </si>
@@ -762,7 +762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:BN63"/>
+  <dimension ref="A1:BP63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -779,7 +779,7 @@
     <col min="65" max="65" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:66" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:68" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -978,8 +978,14 @@
       <c r="BN1" s="8">
         <v>45720</v>
       </c>
+      <c r="BO1" s="8">
+        <v>45723</v>
+      </c>
+      <c r="BP1" s="8">
+        <v>45727</v>
+      </c>
     </row>
-    <row r="2" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1175,8 +1181,14 @@
       <c r="BN2" t="s">
         <v>1</v>
       </c>
+      <c r="BO2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1363,8 +1375,14 @@
       <c r="BN3" t="s">
         <v>1</v>
       </c>
+      <c r="BO3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>89</v>
       </c>
@@ -1375,7 +1393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -1559,8 +1577,11 @@
       <c r="BN5" t="s">
         <v>2</v>
       </c>
+      <c r="BP5" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>79</v>
       </c>
@@ -1574,7 +1595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -1755,8 +1776,14 @@
       <c r="BN7" t="s">
         <v>2</v>
       </c>
+      <c r="BO7" t="s">
+        <v>2</v>
+      </c>
+      <c r="BP7" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="8" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -1955,8 +1982,14 @@
       <c r="BN8" t="s">
         <v>1</v>
       </c>
+      <c r="BO8" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP8" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>80</v>
       </c>
@@ -1978,8 +2011,14 @@
       <c r="BN9" t="s">
         <v>1</v>
       </c>
+      <c r="BO9" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP9" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2104,7 +2143,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -2241,7 +2280,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>91</v>
       </c>
@@ -2260,8 +2299,11 @@
       <c r="BN12" t="s">
         <v>1</v>
       </c>
+      <c r="BP12" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -2457,8 +2499,14 @@
       <c r="BN13" t="s">
         <v>2</v>
       </c>
+      <c r="BO13" t="s">
+        <v>2</v>
+      </c>
+      <c r="BP13" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -2580,7 +2628,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2705,7 +2753,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -2727,8 +2775,11 @@
       <c r="BM16" t="s">
         <v>1</v>
       </c>
+      <c r="BP16" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -2918,8 +2969,11 @@
       <c r="BN17" t="s">
         <v>1</v>
       </c>
+      <c r="BO17" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="18" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -3106,8 +3160,14 @@
       <c r="BN18" t="s">
         <v>2</v>
       </c>
+      <c r="BO18" t="s">
+        <v>2</v>
+      </c>
+      <c r="BP18" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -3229,7 +3289,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -3419,8 +3479,14 @@
       <c r="BN20" t="s">
         <v>2</v>
       </c>
+      <c r="BO20" t="s">
+        <v>2</v>
+      </c>
+      <c r="BP20" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="21" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -3613,8 +3679,14 @@
       <c r="BN21" t="s">
         <v>2</v>
       </c>
+      <c r="BO21" t="s">
+        <v>2</v>
+      </c>
+      <c r="BP21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -3778,7 +3850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>85</v>
       </c>
@@ -3797,8 +3869,14 @@
       <c r="BK23" t="s">
         <v>1</v>
       </c>
+      <c r="BO23" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP23" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -3991,8 +4069,14 @@
       <c r="BM24" t="s">
         <v>2</v>
       </c>
+      <c r="BO24" t="s">
+        <v>2</v>
+      </c>
+      <c r="BP24" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="25" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -4114,7 +4198,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -4269,7 +4353,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -4465,8 +4549,14 @@
       <c r="BN27" t="s">
         <v>1</v>
       </c>
+      <c r="BO27" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP27" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -4561,7 +4651,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -4715,8 +4805,14 @@
       <c r="BN29" t="s">
         <v>2</v>
       </c>
+      <c r="BO29" t="s">
+        <v>2</v>
+      </c>
+      <c r="BP29" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -4744,8 +4840,14 @@
       <c r="BN30" t="s">
         <v>1</v>
       </c>
+      <c r="BO30" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP30" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="31" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -4867,7 +4969,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>81</v>
       </c>
@@ -4889,8 +4991,14 @@
       <c r="BN32" t="s">
         <v>1</v>
       </c>
+      <c r="BO32" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP32" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>90</v>
       </c>
@@ -4909,8 +5017,11 @@
       <c r="BM33" t="s">
         <v>1</v>
       </c>
+      <c r="BP33" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>56</v>
       </c>
@@ -5038,7 +5149,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>22</v>
       </c>
@@ -5202,7 +5313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>88</v>
       </c>
@@ -5224,8 +5335,14 @@
       <c r="BN36" t="s">
         <v>1</v>
       </c>
+      <c r="BO36" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP36" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="37" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>21</v>
       </c>
@@ -5400,8 +5517,14 @@
       <c r="BN37" t="s">
         <v>2</v>
       </c>
+      <c r="BO37" t="s">
+        <v>2</v>
+      </c>
+      <c r="BP37" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="38" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -5594,8 +5717,14 @@
       <c r="BN38" t="s">
         <v>2</v>
       </c>
+      <c r="BO38" t="s">
+        <v>2</v>
+      </c>
+      <c r="BP38" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>54</v>
       </c>
@@ -5758,8 +5887,14 @@
       <c r="BJ39" t="s">
         <v>1</v>
       </c>
+      <c r="BO39" t="s">
+        <v>2</v>
+      </c>
+      <c r="BP39" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="40" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>57</v>
       </c>
@@ -5925,8 +6060,14 @@
       <c r="BN40" t="s">
         <v>2</v>
       </c>
+      <c r="BO40" t="s">
+        <v>2</v>
+      </c>
+      <c r="BP40" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="41" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -6077,8 +6218,11 @@
       <c r="BN41" t="s">
         <v>2</v>
       </c>
+      <c r="BP41" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="42" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>78</v>
       </c>
@@ -6262,8 +6406,11 @@
       <c r="BM42" t="s">
         <v>2</v>
       </c>
+      <c r="BP42" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="43" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -6442,7 +6589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>10</v>
       </c>
@@ -6620,8 +6767,11 @@
       <c r="BL44" t="s">
         <v>2</v>
       </c>
+      <c r="BP44" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="45" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>24</v>
       </c>
@@ -6811,8 +6961,14 @@
       <c r="BN45" t="s">
         <v>2</v>
       </c>
+      <c r="BO45" t="s">
+        <v>2</v>
+      </c>
+      <c r="BP45" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="46" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>84</v>
       </c>
@@ -6837,8 +6993,11 @@
       <c r="BN46" t="s">
         <v>1</v>
       </c>
+      <c r="BP46" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="47" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -7028,8 +7187,14 @@
       <c r="BN47" t="s">
         <v>2</v>
       </c>
+      <c r="BO47" t="s">
+        <v>2</v>
+      </c>
+      <c r="BP47" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -7222,8 +7387,11 @@
       <c r="BN48" t="s">
         <v>1</v>
       </c>
+      <c r="BP48" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="49" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>42</v>
       </c>
@@ -7419,8 +7587,14 @@
       <c r="BN49" t="s">
         <v>1</v>
       </c>
+      <c r="BO49" t="s">
+        <v>2</v>
+      </c>
+      <c r="BP49" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="50" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>14</v>
       </c>
@@ -7616,8 +7790,14 @@
       <c r="BN50" t="s">
         <v>1</v>
       </c>
+      <c r="BO50" t="s">
+        <v>2</v>
+      </c>
+      <c r="BP50" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="51" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -7795,8 +7975,26 @@
       <c r="BJ51" t="s">
         <v>2</v>
       </c>
+      <c r="BK51" t="s">
+        <v>25</v>
+      </c>
+      <c r="BL51" t="s">
+        <v>25</v>
+      </c>
+      <c r="BM51" t="s">
+        <v>25</v>
+      </c>
+      <c r="BN51" t="s">
+        <v>25</v>
+      </c>
+      <c r="BO51" t="s">
+        <v>25</v>
+      </c>
+      <c r="BP51" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="52" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>23</v>
       </c>
@@ -7992,8 +8190,11 @@
       <c r="BN52" t="s">
         <v>1</v>
       </c>
+      <c r="BP52" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="53" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>39</v>
       </c>
@@ -8115,7 +8316,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>29</v>
       </c>
@@ -8311,8 +8512,14 @@
       <c r="BN54" t="s">
         <v>2</v>
       </c>
+      <c r="BO54" t="s">
+        <v>2</v>
+      </c>
+      <c r="BP54" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="55" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>77</v>
       </c>
@@ -8493,8 +8700,14 @@
       <c r="BN55" t="s">
         <v>1</v>
       </c>
+      <c r="BO55" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP55" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="56" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>49</v>
       </c>
@@ -8663,8 +8876,14 @@
       <c r="BN56" t="s">
         <v>2</v>
       </c>
+      <c r="BO56" t="s">
+        <v>2</v>
+      </c>
+      <c r="BP56" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="57" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>83</v>
       </c>
@@ -8686,8 +8905,14 @@
       <c r="BN57" t="s">
         <v>1</v>
       </c>
+      <c r="BO57" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP57" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="58" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>16</v>
       </c>
@@ -8883,8 +9108,14 @@
       <c r="BN58" t="s">
         <v>2</v>
       </c>
+      <c r="BO58" t="s">
+        <v>2</v>
+      </c>
+      <c r="BP58" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="59" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -9080,8 +9311,14 @@
       <c r="BN59" t="s">
         <v>1</v>
       </c>
+      <c r="BO59" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP59" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="60" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>55</v>
       </c>
@@ -9268,8 +9505,14 @@
       <c r="BN60" t="s">
         <v>2</v>
       </c>
+      <c r="BO60" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP60" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="61" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>87</v>
       </c>
@@ -9279,8 +9522,11 @@
       <c r="BH61" t="s">
         <v>1</v>
       </c>
+      <c r="BP61" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="63" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>38</v>
       </c>

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE60CB1-8E50-4378-A510-1178B104D4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA50606-041B-4E4F-9E8C-815340C2AD20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3128" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3202" uniqueCount="92">
   <si>
     <t>Name</t>
   </si>
@@ -762,7 +762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:BP63"/>
+  <dimension ref="A1:BR63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -779,7 +779,7 @@
     <col min="65" max="65" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:70" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -984,8 +984,14 @@
       <c r="BP1" s="8">
         <v>45727</v>
       </c>
+      <c r="BQ1" s="8">
+        <v>45734</v>
+      </c>
+      <c r="BR1" s="8">
+        <v>45737</v>
+      </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1187,8 +1193,14 @@
       <c r="BP2" t="s">
         <v>1</v>
       </c>
+      <c r="BQ2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1381,8 +1393,14 @@
       <c r="BP3" t="s">
         <v>1</v>
       </c>
+      <c r="BQ3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>89</v>
       </c>
@@ -1393,7 +1411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -1580,8 +1598,14 @@
       <c r="BP5" t="s">
         <v>2</v>
       </c>
+      <c r="BQ5" t="s">
+        <v>2</v>
+      </c>
+      <c r="BR5" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>79</v>
       </c>
@@ -1594,8 +1618,11 @@
       <c r="BJ6" t="s">
         <v>1</v>
       </c>
+      <c r="BR6" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -1782,8 +1809,11 @@
       <c r="BP7" t="s">
         <v>2</v>
       </c>
+      <c r="BQ7" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -1988,8 +2018,14 @@
       <c r="BP8" t="s">
         <v>1</v>
       </c>
+      <c r="BQ8" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR8" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>80</v>
       </c>
@@ -2017,8 +2053,14 @@
       <c r="BP9" t="s">
         <v>1</v>
       </c>
+      <c r="BQ9" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR9" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2143,7 +2185,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -2280,7 +2322,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>91</v>
       </c>
@@ -2303,7 +2345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -2505,8 +2547,14 @@
       <c r="BP13" t="s">
         <v>1</v>
       </c>
+      <c r="BQ13" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR13" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="14" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -2628,7 +2676,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2753,7 +2801,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -2778,8 +2826,14 @@
       <c r="BP16" t="s">
         <v>1</v>
       </c>
+      <c r="BQ16" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR16" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -2972,8 +3026,14 @@
       <c r="BO17" t="s">
         <v>1</v>
       </c>
+      <c r="BQ17" t="s">
+        <v>2</v>
+      </c>
+      <c r="BR17" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="18" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -3166,8 +3226,14 @@
       <c r="BP18" t="s">
         <v>2</v>
       </c>
+      <c r="BQ18" t="s">
+        <v>2</v>
+      </c>
+      <c r="BR18" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -3289,7 +3355,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -3485,8 +3551,14 @@
       <c r="BP20" t="s">
         <v>2</v>
       </c>
+      <c r="BQ20" t="s">
+        <v>2</v>
+      </c>
+      <c r="BR20" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="21" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -3685,8 +3757,14 @@
       <c r="BP21" t="s">
         <v>1</v>
       </c>
+      <c r="BQ21" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -3849,8 +3927,11 @@
       <c r="BC22" t="s">
         <v>2</v>
       </c>
+      <c r="BQ22" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="23" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>85</v>
       </c>
@@ -3875,8 +3956,14 @@
       <c r="BP23" t="s">
         <v>1</v>
       </c>
+      <c r="BQ23" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR23" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -4076,7 +4163,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -4198,7 +4285,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -4353,7 +4440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -4555,8 +4642,14 @@
       <c r="BP27" t="s">
         <v>1</v>
       </c>
+      <c r="BQ27" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR27" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -4651,7 +4744,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -4811,8 +4904,11 @@
       <c r="BP29" t="s">
         <v>2</v>
       </c>
+      <c r="BR29" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -4846,8 +4942,11 @@
       <c r="BP30" t="s">
         <v>1</v>
       </c>
+      <c r="BQ30" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="31" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -4969,7 +5068,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>81</v>
       </c>
@@ -4997,8 +5096,14 @@
       <c r="BP32" t="s">
         <v>1</v>
       </c>
+      <c r="BQ32" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR32" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>90</v>
       </c>
@@ -5020,8 +5125,14 @@
       <c r="BP33" t="s">
         <v>1</v>
       </c>
+      <c r="BQ33" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR33" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>56</v>
       </c>
@@ -5149,7 +5260,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>22</v>
       </c>
@@ -5313,7 +5424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>88</v>
       </c>
@@ -5341,8 +5452,14 @@
       <c r="BP36" t="s">
         <v>1</v>
       </c>
+      <c r="BQ36" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR36" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="37" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>21</v>
       </c>
@@ -5523,8 +5640,14 @@
       <c r="BP37" t="s">
         <v>1</v>
       </c>
+      <c r="BQ37" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR37" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="38" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -5723,8 +5846,14 @@
       <c r="BP38" t="s">
         <v>2</v>
       </c>
+      <c r="BQ38" t="s">
+        <v>2</v>
+      </c>
+      <c r="BR38" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>54</v>
       </c>
@@ -5893,8 +6022,11 @@
       <c r="BP39" t="s">
         <v>1</v>
       </c>
+      <c r="BQ39" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="40" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>57</v>
       </c>
@@ -6066,8 +6198,14 @@
       <c r="BP40" t="s">
         <v>2</v>
       </c>
+      <c r="BQ40" t="s">
+        <v>2</v>
+      </c>
+      <c r="BR40" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="41" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -6221,8 +6359,11 @@
       <c r="BP41" t="s">
         <v>2</v>
       </c>
+      <c r="BR41" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="42" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>78</v>
       </c>
@@ -6409,8 +6550,11 @@
       <c r="BP42" t="s">
         <v>2</v>
       </c>
+      <c r="BQ42" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="43" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -6589,7 +6733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>10</v>
       </c>
@@ -6770,8 +6914,14 @@
       <c r="BP44" t="s">
         <v>2</v>
       </c>
+      <c r="BQ44" t="s">
+        <v>2</v>
+      </c>
+      <c r="BR44" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="45" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>24</v>
       </c>
@@ -6967,8 +7117,14 @@
       <c r="BP45" t="s">
         <v>2</v>
       </c>
+      <c r="BQ45" t="s">
+        <v>2</v>
+      </c>
+      <c r="BR45" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="46" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>84</v>
       </c>
@@ -6996,8 +7152,14 @@
       <c r="BP46" t="s">
         <v>1</v>
       </c>
+      <c r="BQ46" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR46" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="47" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -7193,8 +7355,14 @@
       <c r="BP47" t="s">
         <v>2</v>
       </c>
+      <c r="BQ47" t="s">
+        <v>2</v>
+      </c>
+      <c r="BR47" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -7390,8 +7558,14 @@
       <c r="BP48" t="s">
         <v>1</v>
       </c>
+      <c r="BQ48" t="s">
+        <v>2</v>
+      </c>
+      <c r="BR48" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="49" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>42</v>
       </c>
@@ -7593,8 +7767,14 @@
       <c r="BP49" t="s">
         <v>1</v>
       </c>
+      <c r="BQ49" t="s">
+        <v>2</v>
+      </c>
+      <c r="BR49" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="50" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>14</v>
       </c>
@@ -7796,8 +7976,14 @@
       <c r="BP50" t="s">
         <v>1</v>
       </c>
+      <c r="BQ50" t="s">
+        <v>2</v>
+      </c>
+      <c r="BR50" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="51" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -7993,8 +8179,11 @@
       <c r="BP51" t="s">
         <v>2</v>
       </c>
+      <c r="BQ51" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="52" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>23</v>
       </c>
@@ -8193,8 +8382,14 @@
       <c r="BP52" t="s">
         <v>1</v>
       </c>
+      <c r="BQ52" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR52" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="53" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>39</v>
       </c>
@@ -8316,7 +8511,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>29</v>
       </c>
@@ -8518,8 +8713,11 @@
       <c r="BP54" t="s">
         <v>2</v>
       </c>
+      <c r="BR54" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="55" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>77</v>
       </c>
@@ -8706,8 +8904,11 @@
       <c r="BP55" t="s">
         <v>1</v>
       </c>
+      <c r="BQ55" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="56" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>49</v>
       </c>
@@ -8882,8 +9083,14 @@
       <c r="BP56" t="s">
         <v>2</v>
       </c>
+      <c r="BQ56" t="s">
+        <v>2</v>
+      </c>
+      <c r="BR56" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="57" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>83</v>
       </c>
@@ -8911,8 +9118,14 @@
       <c r="BP57" t="s">
         <v>1</v>
       </c>
+      <c r="BQ57" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR57" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="58" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>16</v>
       </c>
@@ -9114,8 +9327,14 @@
       <c r="BP58" t="s">
         <v>2</v>
       </c>
+      <c r="BQ58" t="s">
+        <v>2</v>
+      </c>
+      <c r="BR58" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="59" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -9317,8 +9536,14 @@
       <c r="BP59" t="s">
         <v>1</v>
       </c>
+      <c r="BQ59" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR59" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="60" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>55</v>
       </c>
@@ -9511,8 +9736,14 @@
       <c r="BP60" t="s">
         <v>1</v>
       </c>
+      <c r="BQ60" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR60" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="61" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>87</v>
       </c>
@@ -9522,11 +9753,8 @@
       <c r="BH61" t="s">
         <v>1</v>
       </c>
-      <c r="BP61" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="63" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>38</v>
       </c>

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA50606-041B-4E4F-9E8C-815340C2AD20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A96E02-9534-4CA7-A8E4-894B28109E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3202" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3242" uniqueCount="93">
   <si>
     <t>Name</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t>Dhairya Patel</t>
+  </si>
+  <si>
+    <t>Jay Parmar</t>
   </si>
 </sst>
 </file>
@@ -762,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:BR63"/>
+  <dimension ref="A1:BS63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -779,7 +782,7 @@
     <col min="65" max="65" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:71" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -990,8 +993,11 @@
       <c r="BR1" s="8">
         <v>45737</v>
       </c>
+      <c r="BS1" s="8">
+        <v>45741</v>
+      </c>
     </row>
-    <row r="2" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1199,8 +1205,11 @@
       <c r="BR2" t="s">
         <v>1</v>
       </c>
+      <c r="BS2" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1399,8 +1408,11 @@
       <c r="BR3" t="s">
         <v>2</v>
       </c>
+      <c r="BS3" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>89</v>
       </c>
@@ -1411,7 +1423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -1604,8 +1616,11 @@
       <c r="BR5" t="s">
         <v>2</v>
       </c>
+      <c r="BS5" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>79</v>
       </c>
@@ -1622,7 +1637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -1813,7 +1828,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -2024,8 +2039,11 @@
       <c r="BR8" t="s">
         <v>1</v>
       </c>
+      <c r="BS8" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>80</v>
       </c>
@@ -2060,7 +2078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2185,7 +2203,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -2322,7 +2340,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>91</v>
       </c>
@@ -2344,8 +2362,11 @@
       <c r="BP12" t="s">
         <v>1</v>
       </c>
+      <c r="BS12" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -2553,8 +2574,11 @@
       <c r="BR13" t="s">
         <v>2</v>
       </c>
+      <c r="BS13" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -2676,7 +2700,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2801,7 +2825,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -2833,7 +2857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -3032,8 +3056,11 @@
       <c r="BR17" t="s">
         <v>1</v>
       </c>
+      <c r="BS17" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="18" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -3232,8 +3259,11 @@
       <c r="BR18" t="s">
         <v>2</v>
       </c>
+      <c r="BS18" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -3355,7 +3385,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -3557,8 +3587,11 @@
       <c r="BR20" t="s">
         <v>2</v>
       </c>
+      <c r="BS20" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="21" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -3763,8 +3796,11 @@
       <c r="BR21" t="s">
         <v>1</v>
       </c>
+      <c r="BS21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -3931,7 +3967,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>85</v>
       </c>
@@ -3962,8 +3998,11 @@
       <c r="BR23" t="s">
         <v>1</v>
       </c>
+      <c r="BS23" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -4163,7 +4202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -4285,7 +4324,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -4440,7 +4479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -4648,8 +4687,11 @@
       <c r="BR27" t="s">
         <v>1</v>
       </c>
+      <c r="BS27" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -4744,7 +4786,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -4907,8 +4949,11 @@
       <c r="BR29" t="s">
         <v>2</v>
       </c>
+      <c r="BS29" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -4945,8 +4990,11 @@
       <c r="BQ30" t="s">
         <v>1</v>
       </c>
+      <c r="BS30" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="31" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -5068,7 +5116,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>81</v>
       </c>
@@ -5102,8 +5150,11 @@
       <c r="BR32" t="s">
         <v>1</v>
       </c>
+      <c r="BS32" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>90</v>
       </c>
@@ -5131,8 +5182,11 @@
       <c r="BR33" t="s">
         <v>1</v>
       </c>
+      <c r="BS33" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>56</v>
       </c>
@@ -5260,7 +5314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>22</v>
       </c>
@@ -5424,7 +5478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>88</v>
       </c>
@@ -5458,8 +5512,11 @@
       <c r="BR36" t="s">
         <v>1</v>
       </c>
+      <c r="BS36" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="37" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>21</v>
       </c>
@@ -5646,8 +5703,11 @@
       <c r="BR37" t="s">
         <v>2</v>
       </c>
+      <c r="BS37" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="38" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -5852,8 +5912,11 @@
       <c r="BR38" t="s">
         <v>2</v>
       </c>
+      <c r="BS38" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>54</v>
       </c>
@@ -6026,7 +6089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>57</v>
       </c>
@@ -6204,8 +6267,11 @@
       <c r="BR40" t="s">
         <v>2</v>
       </c>
+      <c r="BS40" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="41" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -6362,8 +6428,11 @@
       <c r="BR41" t="s">
         <v>2</v>
       </c>
+      <c r="BS41" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="42" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>78</v>
       </c>
@@ -6553,8 +6622,11 @@
       <c r="BQ42" t="s">
         <v>2</v>
       </c>
+      <c r="BS42" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="43" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -6733,7 +6805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>10</v>
       </c>
@@ -6920,8 +6992,11 @@
       <c r="BR44" t="s">
         <v>2</v>
       </c>
+      <c r="BS44" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="45" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>24</v>
       </c>
@@ -7123,8 +7198,11 @@
       <c r="BR45" t="s">
         <v>2</v>
       </c>
+      <c r="BS45" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="46" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>84</v>
       </c>
@@ -7158,8 +7236,11 @@
       <c r="BR46" t="s">
         <v>1</v>
       </c>
+      <c r="BS46" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="47" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -7361,8 +7442,11 @@
       <c r="BR47" t="s">
         <v>2</v>
       </c>
+      <c r="BS47" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -7564,8 +7648,11 @@
       <c r="BR48" t="s">
         <v>1</v>
       </c>
+      <c r="BS48" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="49" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>42</v>
       </c>
@@ -7773,8 +7860,11 @@
       <c r="BR49" t="s">
         <v>2</v>
       </c>
+      <c r="BS49" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="50" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>14</v>
       </c>
@@ -7982,8 +8072,11 @@
       <c r="BR50" t="s">
         <v>2</v>
       </c>
+      <c r="BS50" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="51" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -8182,8 +8275,11 @@
       <c r="BQ51" t="s">
         <v>2</v>
       </c>
+      <c r="BS51" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="52" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>23</v>
       </c>
@@ -8388,8 +8484,11 @@
       <c r="BR52" t="s">
         <v>2</v>
       </c>
+      <c r="BS52" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="53" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>39</v>
       </c>
@@ -8511,7 +8610,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>29</v>
       </c>
@@ -8716,8 +8815,11 @@
       <c r="BR54" t="s">
         <v>2</v>
       </c>
+      <c r="BS54" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="55" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>77</v>
       </c>
@@ -8907,8 +9009,11 @@
       <c r="BQ55" t="s">
         <v>1</v>
       </c>
+      <c r="BS55" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="56" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>49</v>
       </c>
@@ -9089,8 +9194,11 @@
       <c r="BR56" t="s">
         <v>2</v>
       </c>
+      <c r="BS56" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="57" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>83</v>
       </c>
@@ -9124,8 +9232,11 @@
       <c r="BR57" t="s">
         <v>1</v>
       </c>
+      <c r="BS57" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="58" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>16</v>
       </c>
@@ -9333,8 +9444,11 @@
       <c r="BR58" t="s">
         <v>2</v>
       </c>
+      <c r="BS58" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="59" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -9542,8 +9656,11 @@
       <c r="BR59" t="s">
         <v>2</v>
       </c>
+      <c r="BS59" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="60" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>55</v>
       </c>
@@ -9742,8 +9859,11 @@
       <c r="BR60" t="s">
         <v>2</v>
       </c>
+      <c r="BS60" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="61" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>87</v>
       </c>
@@ -9754,7 +9874,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:71" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>92</v>
+      </c>
+      <c r="BS62" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>38</v>
       </c>

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A96E02-9534-4CA7-A8E4-894B28109E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2533BB7-E05F-4E26-AA1B-4291A18246A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3242" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3313" uniqueCount="93">
   <si>
     <t>Name</t>
   </si>
@@ -765,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:BS63"/>
+  <dimension ref="A1:BU63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -782,7 +782,7 @@
     <col min="65" max="65" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:73" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -996,8 +996,14 @@
       <c r="BS1" s="8">
         <v>45741</v>
       </c>
+      <c r="BT1" s="8">
+        <v>45744</v>
+      </c>
+      <c r="BU1" s="8">
+        <v>45748</v>
+      </c>
     </row>
-    <row r="2" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1208,8 +1214,14 @@
       <c r="BS2" t="s">
         <v>1</v>
       </c>
+      <c r="BT2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1411,8 +1423,14 @@
       <c r="BS3" t="s">
         <v>1</v>
       </c>
+      <c r="BT3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>89</v>
       </c>
@@ -1423,7 +1441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -1619,8 +1637,14 @@
       <c r="BS5" t="s">
         <v>2</v>
       </c>
+      <c r="BT5" t="s">
+        <v>2</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>79</v>
       </c>
@@ -1636,8 +1660,14 @@
       <c r="BR6" t="s">
         <v>1</v>
       </c>
+      <c r="BT6" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -1827,8 +1857,11 @@
       <c r="BQ7" t="s">
         <v>2</v>
       </c>
+      <c r="BT7" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="8" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -2042,8 +2075,14 @@
       <c r="BS8" t="s">
         <v>1</v>
       </c>
+      <c r="BT8" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>80</v>
       </c>
@@ -2077,8 +2116,14 @@
       <c r="BR9" t="s">
         <v>1</v>
       </c>
+      <c r="BT9" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2203,7 +2248,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -2340,7 +2385,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>91</v>
       </c>
@@ -2365,8 +2410,14 @@
       <c r="BS12" t="s">
         <v>1</v>
       </c>
+      <c r="BT12" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU12" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -2577,8 +2628,14 @@
       <c r="BS13" t="s">
         <v>1</v>
       </c>
+      <c r="BT13" t="s">
+        <v>2</v>
+      </c>
+      <c r="BU13" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -2700,7 +2757,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2825,7 +2882,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -2856,8 +2913,14 @@
       <c r="BR16" t="s">
         <v>1</v>
       </c>
+      <c r="BT16" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU16" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -3059,8 +3122,14 @@
       <c r="BS17" t="s">
         <v>2</v>
       </c>
+      <c r="BT17" t="s">
+        <v>2</v>
+      </c>
+      <c r="BU17" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="18" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -3262,8 +3331,11 @@
       <c r="BS18" t="s">
         <v>2</v>
       </c>
+      <c r="BT18" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -3385,7 +3457,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -3590,8 +3662,11 @@
       <c r="BS20" t="s">
         <v>2</v>
       </c>
+      <c r="BT20" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="21" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -3799,8 +3874,14 @@
       <c r="BS21" t="s">
         <v>1</v>
       </c>
+      <c r="BT21" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -3966,8 +4047,11 @@
       <c r="BQ22" t="s">
         <v>2</v>
       </c>
+      <c r="BU22" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="23" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>85</v>
       </c>
@@ -4001,8 +4085,11 @@
       <c r="BS23" t="s">
         <v>1</v>
       </c>
+      <c r="BU23" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -4202,7 +4289,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -4324,7 +4411,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -4479,7 +4566,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -4690,8 +4777,14 @@
       <c r="BS27" t="s">
         <v>1</v>
       </c>
+      <c r="BT27" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU27" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -4786,7 +4879,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -4952,8 +5045,14 @@
       <c r="BS29" t="s">
         <v>2</v>
       </c>
+      <c r="BT29" t="s">
+        <v>2</v>
+      </c>
+      <c r="BU29" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -4993,8 +5092,11 @@
       <c r="BS30" t="s">
         <v>1</v>
       </c>
+      <c r="BT30" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="31" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -5116,7 +5218,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>81</v>
       </c>
@@ -5153,8 +5255,14 @@
       <c r="BS32" t="s">
         <v>1</v>
       </c>
+      <c r="BT32" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU32" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>90</v>
       </c>
@@ -5186,7 +5294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>56</v>
       </c>
@@ -5314,7 +5422,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>22</v>
       </c>
@@ -5478,7 +5586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>88</v>
       </c>
@@ -5515,8 +5623,11 @@
       <c r="BS36" t="s">
         <v>1</v>
       </c>
+      <c r="BT36" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="37" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>21</v>
       </c>
@@ -5706,8 +5817,14 @@
       <c r="BS37" t="s">
         <v>1</v>
       </c>
+      <c r="BT37" t="s">
+        <v>2</v>
+      </c>
+      <c r="BU37" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="38" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -5915,8 +6032,14 @@
       <c r="BS38" t="s">
         <v>2</v>
       </c>
+      <c r="BT38" t="s">
+        <v>2</v>
+      </c>
+      <c r="BU38" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>54</v>
       </c>
@@ -6088,8 +6211,11 @@
       <c r="BQ39" t="s">
         <v>1</v>
       </c>
+      <c r="BT39" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="40" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>57</v>
       </c>
@@ -6270,8 +6396,11 @@
       <c r="BS40" t="s">
         <v>2</v>
       </c>
+      <c r="BT40" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="41" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -6432,7 +6561,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>78</v>
       </c>
@@ -6625,8 +6754,11 @@
       <c r="BS42" t="s">
         <v>2</v>
       </c>
+      <c r="BT42" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="43" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -6805,7 +6937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>10</v>
       </c>
@@ -6995,8 +7127,11 @@
       <c r="BS44" t="s">
         <v>2</v>
       </c>
+      <c r="BU44" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="45" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>24</v>
       </c>
@@ -7201,8 +7336,14 @@
       <c r="BS45" t="s">
         <v>1</v>
       </c>
+      <c r="BT45" t="s">
+        <v>2</v>
+      </c>
+      <c r="BU45" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="46" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>84</v>
       </c>
@@ -7239,8 +7380,11 @@
       <c r="BS46" t="s">
         <v>1</v>
       </c>
+      <c r="BU46" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="47" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -7445,8 +7589,14 @@
       <c r="BS47" t="s">
         <v>2</v>
       </c>
+      <c r="BT47" t="s">
+        <v>2</v>
+      </c>
+      <c r="BU47" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -7651,8 +7801,11 @@
       <c r="BS48" t="s">
         <v>2</v>
       </c>
+      <c r="BT48" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="49" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>42</v>
       </c>
@@ -7863,8 +8016,14 @@
       <c r="BS49" t="s">
         <v>2</v>
       </c>
+      <c r="BT49" t="s">
+        <v>2</v>
+      </c>
+      <c r="BU49" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="50" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>14</v>
       </c>
@@ -8075,8 +8234,14 @@
       <c r="BS50" t="s">
         <v>2</v>
       </c>
+      <c r="BT50" t="s">
+        <v>2</v>
+      </c>
+      <c r="BU50" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="51" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -8278,8 +8443,11 @@
       <c r="BS51" t="s">
         <v>2</v>
       </c>
+      <c r="BT51" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="52" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>23</v>
       </c>
@@ -8487,8 +8655,14 @@
       <c r="BS52" t="s">
         <v>1</v>
       </c>
+      <c r="BT52" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU52" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="53" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>39</v>
       </c>
@@ -8610,7 +8784,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>29</v>
       </c>
@@ -8818,8 +8992,14 @@
       <c r="BS54" t="s">
         <v>2</v>
       </c>
+      <c r="BT54" t="s">
+        <v>2</v>
+      </c>
+      <c r="BU54" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="55" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>77</v>
       </c>
@@ -9012,8 +9192,14 @@
       <c r="BS55" t="s">
         <v>1</v>
       </c>
+      <c r="BT55" t="s">
+        <v>2</v>
+      </c>
+      <c r="BU55" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="56" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>49</v>
       </c>
@@ -9197,8 +9383,14 @@
       <c r="BS56" t="s">
         <v>2</v>
       </c>
+      <c r="BT56" t="s">
+        <v>2</v>
+      </c>
+      <c r="BU56" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="57" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>83</v>
       </c>
@@ -9235,8 +9427,14 @@
       <c r="BS57" t="s">
         <v>1</v>
       </c>
+      <c r="BT57" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU57" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="58" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>16</v>
       </c>
@@ -9447,8 +9645,14 @@
       <c r="BS58" t="s">
         <v>2</v>
       </c>
+      <c r="BT58" t="s">
+        <v>2</v>
+      </c>
+      <c r="BU58" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="59" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -9659,8 +9863,14 @@
       <c r="BS59" t="s">
         <v>2</v>
       </c>
+      <c r="BT59" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU59" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="60" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>55</v>
       </c>
@@ -9862,8 +10072,14 @@
       <c r="BS60" t="s">
         <v>1</v>
       </c>
+      <c r="BT60" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU60" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="61" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>87</v>
       </c>
@@ -9874,15 +10090,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>92</v>
       </c>
       <c r="BS62" t="s">
         <v>1</v>
       </c>
+      <c r="BT62" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="63" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>38</v>
       </c>

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2533BB7-E05F-4E26-AA1B-4291A18246A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E7622E1-EDBE-4387-82D2-AA0BE44738C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3313" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3345" uniqueCount="93">
   <si>
     <t>Name</t>
   </si>
@@ -765,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:BU63"/>
+  <dimension ref="A1:BV63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -782,7 +782,7 @@
     <col min="65" max="65" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:74" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1002,8 +1002,11 @@
       <c r="BU1" s="8">
         <v>45748</v>
       </c>
+      <c r="BV1" s="8">
+        <v>45751</v>
+      </c>
     </row>
-    <row r="2" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1220,8 +1223,11 @@
       <c r="BU2" t="s">
         <v>1</v>
       </c>
+      <c r="BV2" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1429,8 +1435,11 @@
       <c r="BU3" t="s">
         <v>1</v>
       </c>
+      <c r="BV3" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>89</v>
       </c>
@@ -1441,7 +1450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -1643,8 +1652,11 @@
       <c r="BU5" t="s">
         <v>2</v>
       </c>
+      <c r="BV5" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>79</v>
       </c>
@@ -1667,7 +1679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -1860,8 +1872,11 @@
       <c r="BT7" t="s">
         <v>2</v>
       </c>
+      <c r="BV7" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="8" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -2081,8 +2096,11 @@
       <c r="BU8" t="s">
         <v>1</v>
       </c>
+      <c r="BV8" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>80</v>
       </c>
@@ -2122,8 +2140,11 @@
       <c r="BU9" t="s">
         <v>1</v>
       </c>
+      <c r="BV9" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2248,7 +2269,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -2385,7 +2406,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>91</v>
       </c>
@@ -2416,8 +2437,11 @@
       <c r="BU12" t="s">
         <v>1</v>
       </c>
+      <c r="BV12" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -2634,8 +2658,11 @@
       <c r="BU13" t="s">
         <v>1</v>
       </c>
+      <c r="BV13" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="14" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -2757,7 +2784,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2882,7 +2909,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -2919,8 +2946,11 @@
       <c r="BU16" t="s">
         <v>1</v>
       </c>
+      <c r="BV16" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -3128,8 +3158,11 @@
       <c r="BU17" t="s">
         <v>2</v>
       </c>
+      <c r="BV17" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="18" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -3335,7 +3368,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -3457,7 +3490,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -3665,8 +3698,11 @@
       <c r="BT20" t="s">
         <v>2</v>
       </c>
+      <c r="BV20" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="21" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -3880,8 +3916,11 @@
       <c r="BU21" t="s">
         <v>1</v>
       </c>
+      <c r="BV21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -4051,7 +4090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>85</v>
       </c>
@@ -4088,8 +4127,11 @@
       <c r="BU23" t="s">
         <v>1</v>
       </c>
+      <c r="BV23" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -4289,7 +4331,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -4411,7 +4453,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -4566,7 +4608,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -4783,8 +4825,11 @@
       <c r="BU27" t="s">
         <v>1</v>
       </c>
+      <c r="BV27" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -4879,7 +4924,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -5051,8 +5096,11 @@
       <c r="BU29" t="s">
         <v>2</v>
       </c>
+      <c r="BV29" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -5096,7 +5144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -5218,7 +5266,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>81</v>
       </c>
@@ -5262,7 +5310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>90</v>
       </c>
@@ -5293,8 +5341,11 @@
       <c r="BS33" t="s">
         <v>1</v>
       </c>
+      <c r="BV33" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>56</v>
       </c>
@@ -5422,7 +5473,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>22</v>
       </c>
@@ -5586,7 +5637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>88</v>
       </c>
@@ -5626,8 +5677,11 @@
       <c r="BT36" t="s">
         <v>1</v>
       </c>
+      <c r="BV36" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="37" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>21</v>
       </c>
@@ -5823,8 +5877,11 @@
       <c r="BU37" t="s">
         <v>1</v>
       </c>
+      <c r="BV37" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="38" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -6038,8 +6095,11 @@
       <c r="BU38" t="s">
         <v>2</v>
       </c>
+      <c r="BV38" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>54</v>
       </c>
@@ -6215,7 +6275,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>57</v>
       </c>
@@ -6400,7 +6460,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -6561,7 +6621,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>78</v>
       </c>
@@ -6758,7 +6818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -6937,7 +6997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>10</v>
       </c>
@@ -7130,8 +7190,11 @@
       <c r="BU44" t="s">
         <v>1</v>
       </c>
+      <c r="BV44" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="45" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>24</v>
       </c>
@@ -7342,8 +7405,11 @@
       <c r="BU45" t="s">
         <v>1</v>
       </c>
+      <c r="BV45" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="46" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>84</v>
       </c>
@@ -7384,7 +7450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -7595,8 +7661,11 @@
       <c r="BU47" t="s">
         <v>2</v>
       </c>
+      <c r="BV47" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -7805,7 +7874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>42</v>
       </c>
@@ -8022,8 +8091,11 @@
       <c r="BU49" t="s">
         <v>1</v>
       </c>
+      <c r="BV49" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="50" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>14</v>
       </c>
@@ -8240,8 +8312,11 @@
       <c r="BU50" t="s">
         <v>1</v>
       </c>
+      <c r="BV50" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="51" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -8447,7 +8522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>23</v>
       </c>
@@ -8662,7 +8737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>39</v>
       </c>
@@ -8784,7 +8859,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>29</v>
       </c>
@@ -8998,8 +9073,11 @@
       <c r="BU54" t="s">
         <v>2</v>
       </c>
+      <c r="BV54" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="55" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>77</v>
       </c>
@@ -9198,8 +9276,11 @@
       <c r="BU55" t="s">
         <v>1</v>
       </c>
+      <c r="BV55" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="56" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>49</v>
       </c>
@@ -9389,8 +9470,11 @@
       <c r="BU56" t="s">
         <v>2</v>
       </c>
+      <c r="BV56" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="57" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>83</v>
       </c>
@@ -9433,8 +9517,11 @@
       <c r="BU57" t="s">
         <v>1</v>
       </c>
+      <c r="BV57" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="58" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>16</v>
       </c>
@@ -9651,8 +9738,11 @@
       <c r="BU58" t="s">
         <v>2</v>
       </c>
+      <c r="BV58" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="59" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -9869,8 +9959,11 @@
       <c r="BU59" t="s">
         <v>1</v>
       </c>
+      <c r="BV59" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="60" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>55</v>
       </c>
@@ -10078,8 +10171,11 @@
       <c r="BU60" t="s">
         <v>1</v>
       </c>
+      <c r="BV60" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="61" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>87</v>
       </c>
@@ -10090,7 +10186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>92</v>
       </c>
@@ -10100,8 +10196,11 @@
       <c r="BT62" t="s">
         <v>1</v>
       </c>
+      <c r="BV62" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="63" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>38</v>
       </c>

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E7622E1-EDBE-4387-82D2-AA0BE44738C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F13E2B0-9C60-4C8F-8974-5993E5D6E9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3345" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3381" uniqueCount="94">
   <si>
     <t>Name</t>
   </si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>Jay Parmar</t>
+  </si>
+  <si>
+    <t>Discontinued</t>
   </si>
 </sst>
 </file>
@@ -765,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:BV63"/>
+  <dimension ref="A1:BW63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -780,9 +783,10 @@
     <col min="52" max="58" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="59" max="64" width="8.77734375" bestFit="1" customWidth="1"/>
     <col min="65" max="65" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:74" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:75" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1005,8 +1009,11 @@
       <c r="BV1" s="8">
         <v>45751</v>
       </c>
+      <c r="BW1" s="8">
+        <v>45755</v>
+      </c>
     </row>
-    <row r="2" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1226,8 +1233,11 @@
       <c r="BV2" t="s">
         <v>1</v>
       </c>
+      <c r="BW2" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1438,8 +1448,11 @@
       <c r="BV3" t="s">
         <v>1</v>
       </c>
+      <c r="BW3" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>89</v>
       </c>
@@ -1450,7 +1463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -1655,8 +1668,11 @@
       <c r="BV5" t="s">
         <v>2</v>
       </c>
+      <c r="BW5" t="s">
+        <v>93</v>
+      </c>
     </row>
-    <row r="6" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>79</v>
       </c>
@@ -1679,7 +1695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -1876,7 +1892,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -2099,8 +2115,11 @@
       <c r="BV8" t="s">
         <v>1</v>
       </c>
+      <c r="BW8" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>80</v>
       </c>
@@ -2144,7 +2163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2269,7 +2288,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -2406,7 +2425,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>91</v>
       </c>
@@ -2441,7 +2460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -2661,8 +2680,11 @@
       <c r="BV13" t="s">
         <v>2</v>
       </c>
+      <c r="BW13" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -2784,7 +2806,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2909,7 +2931,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -2949,8 +2971,11 @@
       <c r="BV16" t="s">
         <v>1</v>
       </c>
+      <c r="BW16" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -3161,8 +3186,11 @@
       <c r="BV17" t="s">
         <v>2</v>
       </c>
+      <c r="BW17" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="18" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -3367,8 +3395,11 @@
       <c r="BT18" t="s">
         <v>2</v>
       </c>
+      <c r="BW18" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -3490,7 +3521,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -3701,8 +3732,11 @@
       <c r="BV20" t="s">
         <v>2</v>
       </c>
+      <c r="BW20" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="21" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -3919,8 +3953,11 @@
       <c r="BV21" t="s">
         <v>1</v>
       </c>
+      <c r="BW21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -4089,8 +4126,11 @@
       <c r="BU22" t="s">
         <v>2</v>
       </c>
+      <c r="BW22" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="23" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>85</v>
       </c>
@@ -4130,8 +4170,11 @@
       <c r="BV23" t="s">
         <v>1</v>
       </c>
+      <c r="BW23" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -4331,7 +4374,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -4453,7 +4496,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -4608,7 +4651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -4828,8 +4871,11 @@
       <c r="BV27" t="s">
         <v>1</v>
       </c>
+      <c r="BW27" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -4924,7 +4970,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -5099,8 +5145,11 @@
       <c r="BV29" t="s">
         <v>2</v>
       </c>
+      <c r="BW29" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -5143,8 +5192,11 @@
       <c r="BT30" t="s">
         <v>1</v>
       </c>
+      <c r="BW30" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="31" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -5266,7 +5318,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>81</v>
       </c>
@@ -5309,8 +5361,11 @@
       <c r="BU32" t="s">
         <v>1</v>
       </c>
+      <c r="BW32" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>90</v>
       </c>
@@ -5344,8 +5399,11 @@
       <c r="BV33" t="s">
         <v>1</v>
       </c>
+      <c r="BW33" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>56</v>
       </c>
@@ -5473,7 +5531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>22</v>
       </c>
@@ -5637,7 +5695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>88</v>
       </c>
@@ -5681,7 +5739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>21</v>
       </c>
@@ -5880,8 +5938,11 @@
       <c r="BV37" t="s">
         <v>2</v>
       </c>
+      <c r="BW37" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="38" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -6098,8 +6159,11 @@
       <c r="BV38" t="s">
         <v>2</v>
       </c>
+      <c r="BW38" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>54</v>
       </c>
@@ -6275,7 +6339,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>57</v>
       </c>
@@ -6459,8 +6523,11 @@
       <c r="BT40" t="s">
         <v>2</v>
       </c>
+      <c r="BW40" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="41" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -6621,7 +6688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>78</v>
       </c>
@@ -6817,8 +6884,11 @@
       <c r="BT42" t="s">
         <v>2</v>
       </c>
+      <c r="BW42" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="43" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -6997,7 +7067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>10</v>
       </c>
@@ -7194,7 +7264,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>24</v>
       </c>
@@ -7408,8 +7478,11 @@
       <c r="BV45" t="s">
         <v>2</v>
       </c>
+      <c r="BW45" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="46" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>84</v>
       </c>
@@ -7449,8 +7522,11 @@
       <c r="BU46" t="s">
         <v>1</v>
       </c>
+      <c r="BW46" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="47" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -7664,8 +7740,11 @@
       <c r="BV47" t="s">
         <v>2</v>
       </c>
+      <c r="BW47" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="48" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -7873,8 +7952,11 @@
       <c r="BT48" t="s">
         <v>2</v>
       </c>
+      <c r="BW48" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="49" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>42</v>
       </c>
@@ -8094,8 +8176,11 @@
       <c r="BV49" t="s">
         <v>2</v>
       </c>
+      <c r="BW49" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="50" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>14</v>
       </c>
@@ -8315,8 +8400,11 @@
       <c r="BV50" t="s">
         <v>2</v>
       </c>
+      <c r="BW50" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="51" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -8521,8 +8609,11 @@
       <c r="BT51" t="s">
         <v>2</v>
       </c>
+      <c r="BW51" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="52" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>23</v>
       </c>
@@ -8736,8 +8827,14 @@
       <c r="BU52" t="s">
         <v>1</v>
       </c>
+      <c r="BV52" t="s">
+        <v>25</v>
+      </c>
+      <c r="BW52" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="53" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>39</v>
       </c>
@@ -8859,7 +8956,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>29</v>
       </c>
@@ -9076,8 +9173,11 @@
       <c r="BV54" t="s">
         <v>2</v>
       </c>
+      <c r="BW54" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="55" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>77</v>
       </c>
@@ -9279,8 +9379,11 @@
       <c r="BV55" t="s">
         <v>1</v>
       </c>
+      <c r="BW55" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="56" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>49</v>
       </c>
@@ -9473,8 +9576,11 @@
       <c r="BV56" t="s">
         <v>2</v>
       </c>
+      <c r="BW56" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="57" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>83</v>
       </c>
@@ -9521,7 +9627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>16</v>
       </c>
@@ -9741,8 +9847,11 @@
       <c r="BV58" t="s">
         <v>2</v>
       </c>
+      <c r="BW58" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="59" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -9962,8 +10071,11 @@
       <c r="BV59" t="s">
         <v>2</v>
       </c>
+      <c r="BW59" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="60" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>55</v>
       </c>
@@ -10174,8 +10286,11 @@
       <c r="BV60" t="s">
         <v>1</v>
       </c>
+      <c r="BW60" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="61" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>87</v>
       </c>
@@ -10186,7 +10301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>92</v>
       </c>
@@ -10200,7 +10315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>38</v>
       </c>

--- a/24_DS_Gen_Ahm_1/Attendance.xlsx
+++ b/24_DS_Gen_Ahm_1/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F13E2B0-9C60-4C8F-8974-5993E5D6E9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2301BDD-BA5D-4611-9B58-2EE47EF53281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3381" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3444" uniqueCount="94">
   <si>
     <t>Name</t>
   </si>
@@ -768,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:BW63"/>
+  <dimension ref="A1:BY63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -786,7 +786,7 @@
     <col min="75" max="75" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:75" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:77" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1012,8 +1012,14 @@
       <c r="BW1" s="8">
         <v>45755</v>
       </c>
+      <c r="BX1" s="8">
+        <v>45758</v>
+      </c>
+      <c r="BY1" s="8">
+        <v>45762</v>
+      </c>
     </row>
-    <row r="2" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1236,8 +1242,14 @@
       <c r="BW2" t="s">
         <v>1</v>
       </c>
+      <c r="BX2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1451,8 +1463,14 @@
       <c r="BW3" t="s">
         <v>1</v>
       </c>
+      <c r="BX3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY3" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>89</v>
       </c>
@@ -1463,7 +1481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -1672,7 +1690,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>79</v>
       </c>
@@ -1695,7 +1713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -1891,8 +1909,11 @@
       <c r="BV7" t="s">
         <v>2</v>
       </c>
+      <c r="BY7" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="8" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -2118,8 +2139,14 @@
       <c r="BW8" t="s">
         <v>1</v>
       </c>
+      <c r="BX8" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY8" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>80</v>
       </c>
@@ -2163,7 +2190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2288,7 +2315,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -2425,7 +2452,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>91</v>
       </c>
@@ -2459,8 +2486,14 @@
       <c r="BV12" t="s">
         <v>1</v>
       </c>
+      <c r="BX12" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY12" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -2683,8 +2716,14 @@
       <c r="BW13" t="s">
         <v>1</v>
       </c>
+      <c r="BX13" t="s">
+        <v>2</v>
+      </c>
+      <c r="BY13" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -2806,7 +2845,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2931,7 +2970,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -2974,8 +3013,14 @@
       <c r="BW16" t="s">
         <v>1</v>
       </c>
+      <c r="BX16" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY16" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -3189,8 +3234,14 @@
       <c r="BW17" t="s">
         <v>1</v>
       </c>
+      <c r="BX17" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY17" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="18" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -3398,8 +3449,14 @@
       <c r="BW18" t="s">
         <v>2</v>
       </c>
+      <c r="BX18" t="s">
+        <v>2</v>
+      </c>
+      <c r="BY18" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -3521,7 +3578,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -3735,8 +3792,11 @@
       <c r="BW20" t="s">
         <v>2</v>
       </c>
+      <c r="BX20" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="21" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -3956,8 +4016,14 @@
       <c r="BW21" t="s">
         <v>1</v>
       </c>
+      <c r="BX21" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY21" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -4129,8 +4195,14 @@
       <c r="BW22" t="s">
         <v>2</v>
       </c>
+      <c r="BX22" t="s">
+        <v>2</v>
+      </c>
+      <c r="BY22" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="23" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>85</v>
       </c>
@@ -4173,8 +4245,11 @@
       <c r="BW23" t="s">
         <v>1</v>
       </c>
+      <c r="BY23" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -4374,7 +4449,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -4496,7 +4571,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -4651,7 +4726,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -4874,8 +4949,14 @@
       <c r="BW27" t="s">
         <v>1</v>
       </c>
+      <c r="BX27" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY27" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -4970,7 +5051,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -5148,8 +5229,11 @@
       <c r="BW29" t="s">
         <v>2</v>
       </c>
+      <c r="BY29" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -5195,8 +5279,11 @@
       <c r="BW30" t="s">
         <v>1</v>
       </c>
+      <c r="BY30" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="31" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -5318,7 +5405,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>81</v>
       </c>
@@ -5364,8 +5451,14 @@
       <c r="BW32" t="s">
         <v>1</v>
       </c>
+      <c r="BX32" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY32" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>90</v>
       </c>
@@ -5402,8 +5495,11 @@
       <c r="BW33" t="s">
         <v>1</v>
       </c>
+      <c r="BY33" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>56</v>
       </c>
@@ -5531,7 +5627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>22</v>
       </c>
@@ -5695,7 +5791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>88</v>
       </c>
@@ -5738,8 +5834,14 @@
       <c r="BV36" t="s">
         <v>1</v>
       </c>
+      <c r="BX36" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY36" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="37" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>21</v>
       </c>
@@ -5941,8 +6043,14 @@
       <c r="BW37" t="s">
         <v>1</v>
       </c>
+      <c r="BX37" t="s">
+        <v>2</v>
+      </c>
+      <c r="BY37" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="38" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -6162,8 +6270,14 @@
       <c r="BW38" t="s">
         <v>2</v>
       </c>
+      <c r="BX38" t="s">
+        <v>2</v>
+      </c>
+      <c r="BY38" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>54</v>
       </c>
@@ -6339,7 +6453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>57</v>
       </c>
@@ -6526,8 +6640,11 @@
       <c r="BW40" t="s">
         <v>2</v>
       </c>
+      <c r="BX40" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="41" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -6688,7 +6805,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>78</v>
       </c>
@@ -6887,8 +7004,11 @@
       <c r="BW42" t="s">
         <v>2</v>
       </c>
+      <c r="BX42" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="43" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -7067,7 +7187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>10</v>
       </c>
@@ -7263,8 +7383,11 @@
       <c r="BV44" t="s">
         <v>2</v>
       </c>
+      <c r="BX44" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="45" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>24</v>
       </c>
@@ -7481,8 +7604,11 @@
       <c r="BW45" t="s">
         <v>1</v>
       </c>
+      <c r="BY45" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="46" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>84</v>
       </c>
@@ -7526,7 +7652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -7743,8 +7869,14 @@
       <c r="BW47" t="s">
         <v>1</v>
       </c>
+      <c r="BX47" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY47" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="48" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -7955,8 +8087,14 @@
       <c r="BW48" t="s">
         <v>2</v>
       </c>
+      <c r="BX48" t="s">
+        <v>2</v>
+      </c>
+      <c r="BY48" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="49" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>42</v>
       </c>
@@ -8179,8 +8317,11 @@
       <c r="BW49" t="s">
         <v>2</v>
       </c>
+      <c r="BY49" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="50" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>14</v>
       </c>
@@ -8403,8 +8544,14 @@
       <c r="BW50" t="s">
         <v>1</v>
       </c>
+      <c r="BX50" t="s">
+        <v>2</v>
+      </c>
+      <c r="BY50" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="51" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -8612,8 +8759,14 @@
       <c r="BW51" t="s">
         <v>2</v>
       </c>
+      <c r="BX51" t="s">
+        <v>2</v>
+      </c>
+      <c r="BY51" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="52" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>23</v>
       </c>
@@ -8833,8 +8986,14 @@
       <c r="BW52" t="s">
         <v>1</v>
       </c>
+      <c r="BX52" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY52" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="53" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>39</v>
       </c>
@@ -8956,7 +9115,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>29</v>
       </c>
@@ -9176,8 +9335,14 @@
       <c r="BW54" t="s">
         <v>2</v>
       </c>
+      <c r="BX54" t="s">
+        <v>2</v>
+      </c>
+      <c r="BY54" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="55" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>77</v>
       </c>
@@ -9382,8 +9547,14 @@
       <c r="BW55" t="s">
         <v>1</v>
       </c>
+      <c r="BX55" t="s">
+        <v>2</v>
+      </c>
+      <c r="BY55" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="56" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>49</v>
       </c>
@@ -9579,8 +9750,14 @@
       <c r="BW56" t="s">
         <v>2</v>
       </c>
+      <c r="BX56" t="s">
+        <v>2</v>
+      </c>
+      <c r="BY56" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="57" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>83</v>
       </c>
@@ -9627,7 +9804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>16</v>
       </c>
@@ -9850,8 +10027,14 @@
       <c r="BW58" t="s">
         <v>2</v>
       </c>
+      <c r="BX58" t="s">
+        <v>2</v>
+      </c>
+      <c r="BY58" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="59" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -10074,8 +10257,14 @@
       <c r="BW59" t="s">
         <v>1</v>
       </c>
+      <c r="BX59" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY59" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="60" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>55</v>
       </c>
@@ -10289,8 +10478,14 @@
       <c r="BW60" t="s">
         <v>1</v>
       </c>
+      <c r="BX60" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY60" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="61" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>87</v>
       </c>
@@ -10301,7 +10496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>92</v>
       </c>
@@ -10315,7 +10510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>38</v>
       </c>
